--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -11,11 +11,12 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="PandL" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Jobs'!$A$4:$L$165</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Jobs'!$A$4:$L$165</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -123,7 +124,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="26">
+  <cellXfs count="29">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -156,6 +157,13 @@
     </xf>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="165" fontId="10" fillId="3" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -651,7 +659,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>West End café air-con</t>
+          <t>West End cafe air-con</t>
         </is>
       </c>
       <c r="B12" s="8" t="n">
@@ -1829,6 +1837,1008 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C104"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="52" customWidth="1" min="1" max="1"/>
+    <col width="26" customWidth="1" min="2" max="2"/>
+    <col width="26" customWidth="1" min="3" max="3"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>How each number is worked out</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Sample Electrical &amp; Air Pty Ltd · SAMPLE DATA (invented) · The Fourth Sheet · generated 2026-10-06</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="4" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="20" t="inlineStr"/>
+      <c r="B6" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C6" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="21" t="inlineStr">
+        <is>
+          <t>Revenue (every job invoiced in the month)</t>
+        </is>
+      </c>
+      <c r="B7" s="22" t="inlineStr">
+        <is>
+          <t>$202,337</t>
+        </is>
+      </c>
+      <c r="C7" s="22" t="inlineStr">
+        <is>
+          <t>$179,007</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B8" s="22" t="inlineStr">
+        <is>
+          <t>$-64,860</t>
+        </is>
+      </c>
+      <c r="C8" s="22" t="inlineStr">
+        <is>
+          <t>$-51,530</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B9" s="22" t="inlineStr">
+        <is>
+          <t>$-13,200</t>
+        </is>
+      </c>
+      <c r="C9" s="22" t="inlineStr">
+        <is>
+          <t>$-9,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="21" t="inlineStr">
+        <is>
+          <t>Technician wages</t>
+        </is>
+      </c>
+      <c r="B10" s="22" t="inlineStr">
+        <is>
+          <t>$-54,600</t>
+        </is>
+      </c>
+      <c r="C10" s="22" t="inlineStr">
+        <is>
+          <t>$-54,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B11" s="22" t="inlineStr">
+        <is>
+          <t>$69,677</t>
+        </is>
+      </c>
+      <c r="C11" s="22" t="inlineStr">
+        <is>
+          <t>$63,577</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="21" t="inlineStr">
+        <is>
+          <t>Gross margin</t>
+        </is>
+      </c>
+      <c r="B12" s="22" t="inlineStr">
+        <is>
+          <t>34.4%</t>
+        </is>
+      </c>
+      <c r="C12" s="22" t="inlineStr">
+        <is>
+          <t>35.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>Technicians are on salary, so a quiet month for jobs lowers the margin even if every job is priced well.</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="4" t="inlineStr">
+        <is>
+          <t>Cost to win a customer</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>Marketing spend ÷ new customers</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="20" t="inlineStr"/>
+      <c r="B18" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C18" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="21" t="inlineStr">
+        <is>
+          <t>Marketing spend</t>
+        </is>
+      </c>
+      <c r="B19" s="22" t="inlineStr">
+        <is>
+          <t>$7,600</t>
+        </is>
+      </c>
+      <c r="C19" s="22" t="inlineStr">
+        <is>
+          <t>$8,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="21" t="inlineStr">
+        <is>
+          <t>New customers (first job ever)</t>
+        </is>
+      </c>
+      <c r="B20" s="22" t="inlineStr">
+        <is>
+          <t>47</t>
+        </is>
+      </c>
+      <c r="C20" s="22" t="inlineStr">
+        <is>
+          <t>41</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="21" t="inlineStr">
+        <is>
+          <t>Cost per new customer</t>
+        </is>
+      </c>
+      <c r="B21" s="22" t="inlineStr">
+        <is>
+          <t>$162</t>
+        </is>
+      </c>
+      <c r="C21" s="22" t="inlineStr">
+        <is>
+          <t>$205</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="4" t="inlineStr">
+        <is>
+          <t>Technician time on jobs</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="9" t="inlineStr">
+        <is>
+          <t>Hours charged to jobs ÷ hours available</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="20" t="inlineStr"/>
+      <c r="B26" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+      <c r="C26" s="20" t="inlineStr">
+        <is>
+          <t>Aug 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="21" t="inlineStr">
+        <is>
+          <t>Hours charged to jobs (timesheets)</t>
+        </is>
+      </c>
+      <c r="B27" s="22" t="inlineStr">
+        <is>
+          <t>752.5 h</t>
+        </is>
+      </c>
+      <c r="C27" s="22" t="inlineStr">
+        <is>
+          <t>655 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="21" t="inlineStr">
+        <is>
+          <t>Technicians</t>
+        </is>
+      </c>
+      <c r="B28" s="22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C28" s="22" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="21" t="inlineStr">
+        <is>
+          <t>Working days</t>
+        </is>
+      </c>
+      <c r="B29" s="22" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="C29" s="22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="21" t="inlineStr">
+        <is>
+          <t>Hours available (technicians × days × 7.6)</t>
+        </is>
+      </c>
+      <c r="B30" s="22" t="inlineStr">
+        <is>
+          <t>1,170.4 h</t>
+        </is>
+      </c>
+      <c r="C30" s="22" t="inlineStr">
+        <is>
+          <t>1,064 h</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="21" t="inlineStr">
+        <is>
+          <t>Time on jobs</t>
+        </is>
+      </c>
+      <c r="B31" s="22" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="C31" s="22" t="inlineStr">
+        <is>
+          <t>62%</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>August had one fewer working day for the Ekka show holiday. The rest is travel, training, quoting and waiting time.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="4" t="inlineStr">
+        <is>
+          <t>Wacol warehouse switchboard</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="20" t="inlineStr"/>
+      <c r="B37" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B38" s="22" t="inlineStr">
+        <is>
+          <t>4 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B39" s="22" t="inlineStr">
+        <is>
+          <t>$46,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B40" s="22" t="inlineStr">
+        <is>
+          <t>$-22,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B41" s="22" t="inlineStr">
+        <is>
+          <t>$-7,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B42" s="22" t="inlineStr">
+        <is>
+          <t>150 h × $68 = $-10,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B43" s="22" t="inlineStr">
+        <is>
+          <t>$6,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B44" s="22" t="inlineStr">
+        <is>
+          <t>13.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="4" t="inlineStr">
+        <is>
+          <t>Milton office LED lighting</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="20" t="inlineStr"/>
+      <c r="B49" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B50" s="22" t="inlineStr">
+        <is>
+          <t>9 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B51" s="22" t="inlineStr">
+        <is>
+          <t>$18,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B52" s="22" t="inlineStr">
+        <is>
+          <t>$-6,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B53" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B54" s="22" t="inlineStr">
+        <is>
+          <t>64 h × $68 = $-4,352</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B55" s="22" t="inlineStr">
+        <is>
+          <t>$7,348</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B56" s="22" t="inlineStr">
+        <is>
+          <t>39.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="4" t="inlineStr">
+        <is>
+          <t>Carindale solar and battery</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="20" t="inlineStr"/>
+      <c r="B61" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B62" s="22" t="inlineStr">
+        <is>
+          <t>15 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B63" s="22" t="inlineStr">
+        <is>
+          <t>$27,400</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B64" s="22" t="inlineStr">
+        <is>
+          <t>$-13,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B65" s="22" t="inlineStr">
+        <is>
+          <t>$-3,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B66" s="22" t="inlineStr">
+        <is>
+          <t>46 h × $68 = $-3,128</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B67" s="22" t="inlineStr">
+        <is>
+          <t>$7,372</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B68" s="22" t="inlineStr">
+        <is>
+          <t>26.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="4" t="inlineStr">
+        <is>
+          <t>West End cafe air-con</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="20" t="inlineStr"/>
+      <c r="B73" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B74" s="22" t="inlineStr">
+        <is>
+          <t>18 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B75" s="22" t="inlineStr">
+        <is>
+          <t>$12,900</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B76" s="22" t="inlineStr">
+        <is>
+          <t>$-5,100</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B77" s="22" t="inlineStr">
+        <is>
+          <t>$-900</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B78" s="22" t="inlineStr">
+        <is>
+          <t>38 h × $68 = $-2,584</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B79" s="22" t="inlineStr">
+        <is>
+          <t>$4,316</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B80" s="22" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="4" t="inlineStr">
+        <is>
+          <t>Bulimba EV chargers</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" s="20" t="inlineStr"/>
+      <c r="B85" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B86" s="22" t="inlineStr">
+        <is>
+          <t>23 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B87" s="22" t="inlineStr">
+        <is>
+          <t>$9,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B88" s="22" t="inlineStr">
+        <is>
+          <t>$-3,600</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B89" s="22" t="inlineStr">
+        <is>
+          <t>$0</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B90" s="22" t="inlineStr">
+        <is>
+          <t>26 h × $68 = $-1,768</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B91" s="22" t="inlineStr">
+        <is>
+          <t>$4,432</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B92" s="22" t="inlineStr">
+        <is>
+          <t>45.2%</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" s="4" t="inlineStr">
+        <is>
+          <t>Chermside clinic cabling</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" s="9" t="inlineStr">
+        <is>
+          <t>Gross profit ÷ revenue for this job</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" s="20" t="inlineStr"/>
+      <c r="B97" s="20" t="inlineStr">
+        <is>
+          <t>Sep 2026</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" s="21" t="inlineStr">
+        <is>
+          <t>Invoiced</t>
+        </is>
+      </c>
+      <c r="B98" s="22" t="inlineStr">
+        <is>
+          <t>29 Sep</t>
+        </is>
+      </c>
+    </row>
+    <row r="99">
+      <c r="A99" s="21" t="inlineStr">
+        <is>
+          <t>Revenue</t>
+        </is>
+      </c>
+      <c r="B99" s="22" t="inlineStr">
+        <is>
+          <t>$15,200</t>
+        </is>
+      </c>
+    </row>
+    <row r="100">
+      <c r="A100" s="21" t="inlineStr">
+        <is>
+          <t>Materials</t>
+        </is>
+      </c>
+      <c r="B100" s="22" t="inlineStr">
+        <is>
+          <t>$-4,300</t>
+        </is>
+      </c>
+    </row>
+    <row r="101">
+      <c r="A101" s="21" t="inlineStr">
+        <is>
+          <t>Subcontractors</t>
+        </is>
+      </c>
+      <c r="B101" s="22" t="inlineStr">
+        <is>
+          <t>$-1,800</t>
+        </is>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" s="21" t="inlineStr">
+        <is>
+          <t>Technician time</t>
+        </is>
+      </c>
+      <c r="B102" s="22" t="inlineStr">
+        <is>
+          <t>52 h × $68 = $-3,536</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="21" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B103" s="22" t="inlineStr">
+        <is>
+          <t>$5,564</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="21" t="inlineStr">
+        <is>
+          <t>Margin</t>
+        </is>
+      </c>
+      <c r="B104" s="22" t="inlineStr">
+        <is>
+          <t>36.6%</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1866,62 +2876,62 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="20" t="inlineStr">
+      <c r="A4" s="23" t="inlineStr">
         <is>
           <t>Month</t>
         </is>
       </c>
-      <c r="B4" s="20" t="inlineStr">
+      <c r="B4" s="23" t="inlineStr">
         <is>
           <t>Job</t>
         </is>
       </c>
-      <c r="C4" s="20" t="inlineStr">
+      <c r="C4" s="23" t="inlineStr">
         <is>
           <t>Type</t>
         </is>
       </c>
-      <c r="D4" s="20" t="inlineStr">
+      <c r="D4" s="23" t="inlineStr">
         <is>
           <t>Invoiced</t>
         </is>
       </c>
-      <c r="E4" s="20" t="inlineStr">
+      <c r="E4" s="23" t="inlineStr">
         <is>
           <t>Paid</t>
         </is>
       </c>
-      <c r="F4" s="21" t="inlineStr">
+      <c r="F4" s="24" t="inlineStr">
         <is>
           <t>Revenue</t>
         </is>
       </c>
-      <c r="G4" s="21" t="inlineStr">
+      <c r="G4" s="24" t="inlineStr">
         <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="H4" s="21" t="inlineStr">
+      <c r="H4" s="24" t="inlineStr">
         <is>
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="I4" s="21" t="inlineStr">
+      <c r="I4" s="24" t="inlineStr">
         <is>
           <t>Tech hours</t>
         </is>
       </c>
-      <c r="J4" s="21" t="inlineStr">
+      <c r="J4" s="24" t="inlineStr">
         <is>
           <t>Labour cost</t>
         </is>
       </c>
-      <c r="K4" s="21" t="inlineStr">
+      <c r="K4" s="24" t="inlineStr">
         <is>
           <t>Gross profit</t>
         </is>
       </c>
-      <c r="L4" s="21" t="inlineStr">
+      <c r="L4" s="24" t="inlineStr">
         <is>
           <t>Margin %</t>
         </is>
@@ -1953,22 +2963,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F5" s="22" t="n">
+      <c r="F5" s="25" t="n">
         <v>589</v>
       </c>
-      <c r="G5" s="22" t="n">
+      <c r="G5" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H5" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I5" s="22" t="n">
+      <c r="H5" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I5" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J5" s="22" t="n">
+      <c r="J5" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K5" s="22" t="n">
+      <c r="K5" s="25" t="n">
         <v>223</v>
       </c>
       <c r="L5" s="8" t="n">
@@ -2001,22 +3011,22 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="F6" s="22" t="n">
+      <c r="F6" s="25" t="n">
         <v>539</v>
       </c>
-      <c r="G6" s="22" t="n">
+      <c r="G6" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H6" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I6" s="22" t="n">
+      <c r="H6" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I6" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J6" s="22" t="n">
+      <c r="J6" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K6" s="22" t="n">
+      <c r="K6" s="25" t="n">
         <v>255</v>
       </c>
       <c r="L6" s="8" t="n">
@@ -2049,22 +3059,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F7" s="22" t="n">
+      <c r="F7" s="25" t="n">
         <v>526</v>
       </c>
-      <c r="G7" s="22" t="n">
+      <c r="G7" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H7" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="22" t="n">
+      <c r="H7" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I7" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J7" s="22" t="n">
+      <c r="J7" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K7" s="22" t="n">
+      <c r="K7" s="25" t="n">
         <v>252</v>
       </c>
       <c r="L7" s="8" t="n">
@@ -2097,22 +3107,22 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F8" s="22" t="n">
+      <c r="F8" s="25" t="n">
         <v>413</v>
       </c>
-      <c r="G8" s="22" t="n">
+      <c r="G8" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H8" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="23" t="n">
+      <c r="H8" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I8" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J8" s="22" t="n">
+      <c r="J8" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K8" s="22" t="n">
+      <c r="K8" s="25" t="n">
         <v>161</v>
       </c>
       <c r="L8" s="8" t="n">
@@ -2145,22 +3155,22 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F9" s="22" t="n">
+      <c r="F9" s="25" t="n">
         <v>775</v>
       </c>
-      <c r="G9" s="22" t="n">
+      <c r="G9" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H9" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="22" t="n">
+      <c r="H9" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I9" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J9" s="22" t="n">
+      <c r="J9" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K9" s="22" t="n">
+      <c r="K9" s="25" t="n">
         <v>353</v>
       </c>
       <c r="L9" s="8" t="n">
@@ -2193,22 +3203,22 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="25" t="n">
         <v>348</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H10" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="23" t="n">
+      <c r="H10" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I10" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J10" s="22" t="n">
+      <c r="J10" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K10" s="22" t="n">
+      <c r="K10" s="25" t="n">
         <v>146</v>
       </c>
       <c r="L10" s="8" t="n">
@@ -2241,22 +3251,22 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F11" s="22" t="n">
+      <c r="F11" s="25" t="n">
         <v>775</v>
       </c>
-      <c r="G11" s="22" t="n">
+      <c r="G11" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H11" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="22" t="n">
+      <c r="H11" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I11" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="22" t="n">
+      <c r="J11" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K11" s="22" t="n">
+      <c r="K11" s="25" t="n">
         <v>353</v>
       </c>
       <c r="L11" s="8" t="n">
@@ -2289,22 +3299,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F12" s="22" t="n">
+      <c r="F12" s="25" t="n">
         <v>368</v>
       </c>
-      <c r="G12" s="22" t="n">
+      <c r="G12" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="22" t="n">
+      <c r="H12" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I12" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J12" s="22" t="n">
+      <c r="J12" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K12" s="22" t="n">
+      <c r="K12" s="25" t="n">
         <v>172</v>
       </c>
       <c r="L12" s="8" t="n">
@@ -2337,22 +3347,22 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F13" s="22" t="n">
+      <c r="F13" s="25" t="n">
         <v>526</v>
       </c>
-      <c r="G13" s="22" t="n">
+      <c r="G13" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H13" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="22" t="n">
+      <c r="H13" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I13" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J13" s="22" t="n">
+      <c r="J13" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K13" s="22" t="n">
+      <c r="K13" s="25" t="n">
         <v>252</v>
       </c>
       <c r="L13" s="8" t="n">
@@ -2385,22 +3395,22 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="25" t="n">
         <v>467</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H14" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="23" t="n">
+      <c r="H14" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I14" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J14" s="22" t="n">
+      <c r="J14" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K14" s="22" t="n">
+      <c r="K14" s="25" t="n">
         <v>217</v>
       </c>
       <c r="L14" s="8" t="n">
@@ -2433,22 +3443,22 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="F15" s="22" t="n">
+      <c r="F15" s="25" t="n">
         <v>589</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H15" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="22" t="n">
+      <c r="H15" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I15" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J15" s="22" t="n">
+      <c r="J15" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K15" s="22" t="n">
+      <c r="K15" s="25" t="n">
         <v>223</v>
       </c>
       <c r="L15" s="8" t="n">
@@ -2481,22 +3491,22 @@
           <t>2026-09-15</t>
         </is>
       </c>
-      <c r="F16" s="22" t="n">
+      <c r="F16" s="25" t="n">
         <v>604</v>
       </c>
-      <c r="G16" s="22" t="n">
+      <c r="G16" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H16" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="22" t="n">
+      <c r="H16" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I16" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J16" s="22" t="n">
+      <c r="J16" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K16" s="22" t="n">
+      <c r="K16" s="25" t="n">
         <v>270</v>
       </c>
       <c r="L16" s="8" t="n">
@@ -2529,22 +3539,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F17" s="22" t="n">
+      <c r="F17" s="25" t="n">
         <v>342</v>
       </c>
-      <c r="G17" s="22" t="n">
+      <c r="G17" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H17" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="22" t="n">
+      <c r="H17" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="22" t="n">
+      <c r="J17" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K17" s="22" t="n">
+      <c r="K17" s="25" t="n">
         <v>166</v>
       </c>
       <c r="L17" s="8" t="n">
@@ -2577,22 +3587,22 @@
           <t>2026-10-02</t>
         </is>
       </c>
-      <c r="F18" s="22" t="n">
+      <c r="F18" s="25" t="n">
         <v>461</v>
       </c>
-      <c r="G18" s="22" t="n">
+      <c r="G18" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H18" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="22" t="n">
+      <c r="H18" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I18" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="22" t="n">
+      <c r="J18" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K18" s="22" t="n">
+      <c r="K18" s="25" t="n">
         <v>237</v>
       </c>
       <c r="L18" s="8" t="n">
@@ -2625,22 +3635,22 @@
           <t>2026-10-17</t>
         </is>
       </c>
-      <c r="F19" s="22" t="n">
+      <c r="F19" s="25" t="n">
         <v>441</v>
       </c>
-      <c r="G19" s="22" t="n">
+      <c r="G19" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H19" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="23" t="n">
+      <c r="H19" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I19" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J19" s="22" t="n">
+      <c r="J19" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K19" s="22" t="n">
+      <c r="K19" s="25" t="n">
         <v>211</v>
       </c>
       <c r="L19" s="8" t="n">
@@ -2673,22 +3683,22 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="F20" s="22" t="n">
+      <c r="F20" s="25" t="n">
         <v>749</v>
       </c>
-      <c r="G20" s="22" t="n">
+      <c r="G20" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H20" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="22" t="n">
+      <c r="H20" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I20" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J20" s="22" t="n">
+      <c r="J20" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K20" s="22" t="n">
+      <c r="K20" s="25" t="n">
         <v>347</v>
       </c>
       <c r="L20" s="8" t="n">
@@ -2721,22 +3731,22 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F21" s="22" t="n">
+      <c r="F21" s="25" t="n">
         <v>801</v>
       </c>
-      <c r="G21" s="22" t="n">
+      <c r="G21" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="H21" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="22" t="n">
+      <c r="H21" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I21" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J21" s="22" t="n">
+      <c r="J21" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K21" s="22" t="n">
+      <c r="K21" s="25" t="n">
         <v>359</v>
       </c>
       <c r="L21" s="8" t="n">
@@ -2769,22 +3779,22 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="F22" s="22" t="n">
+      <c r="F22" s="25" t="n">
         <v>322</v>
       </c>
-      <c r="G22" s="22" t="n">
+      <c r="G22" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H22" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="23" t="n">
+      <c r="H22" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I22" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J22" s="22" t="n">
+      <c r="J22" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K22" s="22" t="n">
+      <c r="K22" s="25" t="n">
         <v>140</v>
       </c>
       <c r="L22" s="8" t="n">
@@ -2817,22 +3827,22 @@
           <t>2026-10-10</t>
         </is>
       </c>
-      <c r="F23" s="22" t="n">
+      <c r="F23" s="25" t="n">
         <v>374</v>
       </c>
-      <c r="G23" s="22" t="n">
+      <c r="G23" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H23" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="23" t="n">
+      <c r="H23" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I23" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J23" s="22" t="n">
+      <c r="J23" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K23" s="22" t="n">
+      <c r="K23" s="25" t="n">
         <v>152</v>
       </c>
       <c r="L23" s="8" t="n">
@@ -2865,22 +3875,22 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="F24" s="22" t="n">
+      <c r="F24" s="25" t="n">
         <v>550</v>
       </c>
-      <c r="G24" s="22" t="n">
+      <c r="G24" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H24" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="22" t="n">
+      <c r="H24" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I24" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J24" s="22" t="n">
+      <c r="J24" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K24" s="22" t="n">
+      <c r="K24" s="25" t="n">
         <v>214</v>
       </c>
       <c r="L24" s="8" t="n">
@@ -2913,22 +3923,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F25" s="22" t="n">
+      <c r="F25" s="25" t="n">
         <v>563</v>
       </c>
-      <c r="G25" s="22" t="n">
+      <c r="G25" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="H25" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="22" t="n">
+      <c r="H25" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I25" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J25" s="22" t="n">
+      <c r="J25" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K25" s="22" t="n">
+      <c r="K25" s="25" t="n">
         <v>217</v>
       </c>
       <c r="L25" s="8" t="n">
@@ -2961,22 +3971,22 @@
           <t>2026-10-05</t>
         </is>
       </c>
-      <c r="F26" s="22" t="n">
+      <c r="F26" s="25" t="n">
         <v>606</v>
       </c>
-      <c r="G26" s="22" t="n">
+      <c r="G26" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H26" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="22" t="n">
+      <c r="H26" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I26" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J26" s="22" t="n">
+      <c r="J26" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K26" s="22" t="n">
+      <c r="K26" s="25" t="n">
         <v>314</v>
       </c>
       <c r="L26" s="8" t="n">
@@ -3009,22 +4019,22 @@
           <t>2026-09-11</t>
         </is>
       </c>
-      <c r="F27" s="22" t="n">
+      <c r="F27" s="25" t="n">
         <v>565</v>
       </c>
-      <c r="G27" s="22" t="n">
+      <c r="G27" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H27" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="22" t="n">
+      <c r="H27" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I27" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J27" s="22" t="n">
+      <c r="J27" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K27" s="22" t="n">
+      <c r="K27" s="25" t="n">
         <v>261</v>
       </c>
       <c r="L27" s="8" t="n">
@@ -3057,22 +4067,22 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="F28" s="22" t="n">
+      <c r="F28" s="25" t="n">
         <v>643</v>
       </c>
-      <c r="G28" s="22" t="n">
+      <c r="G28" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="H28" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="22" t="n">
+      <c r="H28" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I28" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J28" s="22" t="n">
+      <c r="J28" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K28" s="22" t="n">
+      <c r="K28" s="25" t="n">
         <v>279</v>
       </c>
       <c r="L28" s="8" t="n">
@@ -3105,22 +4115,22 @@
           <t>2026-10-13</t>
         </is>
       </c>
-      <c r="F29" s="22" t="n">
+      <c r="F29" s="25" t="n">
         <v>342</v>
       </c>
-      <c r="G29" s="22" t="n">
+      <c r="G29" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H29" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="22" t="n">
+      <c r="H29" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I29" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J29" s="22" t="n">
+      <c r="J29" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K29" s="22" t="n">
+      <c r="K29" s="25" t="n">
         <v>166</v>
       </c>
       <c r="L29" s="8" t="n">
@@ -3153,22 +4163,22 @@
           <t>2026-10-21</t>
         </is>
       </c>
-      <c r="F30" s="22" t="n">
+      <c r="F30" s="25" t="n">
         <v>597</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H30" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="23" t="n">
+      <c r="H30" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I30" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J30" s="22" t="n">
+      <c r="J30" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K30" s="22" t="n">
+      <c r="K30" s="25" t="n">
         <v>247</v>
       </c>
       <c r="L30" s="8" t="n">
@@ -3201,22 +4211,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F31" s="22" t="n">
+      <c r="F31" s="25" t="n">
         <v>452</v>
       </c>
-      <c r="G31" s="22" t="n">
+      <c r="G31" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H31" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="23" t="n">
+      <c r="H31" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I31" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J31" s="22" t="n">
+      <c r="J31" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K31" s="22" t="n">
+      <c r="K31" s="25" t="n">
         <v>170</v>
       </c>
       <c r="L31" s="8" t="n">
@@ -3249,22 +4259,22 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F32" s="22" t="n">
+      <c r="F32" s="25" t="n">
         <v>441</v>
       </c>
-      <c r="G32" s="22" t="n">
+      <c r="G32" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H32" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="23" t="n">
+      <c r="H32" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I32" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" s="22" t="n">
+      <c r="J32" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K32" s="22" t="n">
+      <c r="K32" s="25" t="n">
         <v>211</v>
       </c>
       <c r="L32" s="8" t="n">
@@ -3297,22 +4307,22 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F33" s="22" t="n">
+      <c r="F33" s="25" t="n">
         <v>316</v>
       </c>
-      <c r="G33" s="22" t="n">
+      <c r="G33" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H33" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="22" t="n">
+      <c r="H33" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I33" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J33" s="22" t="n">
+      <c r="J33" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K33" s="22" t="n">
+      <c r="K33" s="25" t="n">
         <v>160</v>
       </c>
       <c r="L33" s="8" t="n">
@@ -3345,22 +4355,22 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="F34" s="22" t="n">
+      <c r="F34" s="25" t="n">
         <v>335</v>
       </c>
-      <c r="G34" s="22" t="n">
+      <c r="G34" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H34" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="23" t="n">
+      <c r="H34" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I34" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J34" s="22" t="n">
+      <c r="J34" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K34" s="22" t="n">
+      <c r="K34" s="25" t="n">
         <v>143</v>
       </c>
       <c r="L34" s="8" t="n">
@@ -3393,22 +4403,22 @@
           <t>2026-09-20</t>
         </is>
       </c>
-      <c r="F35" s="22" t="n">
+      <c r="F35" s="25" t="n">
         <v>322</v>
       </c>
-      <c r="G35" s="22" t="n">
+      <c r="G35" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H35" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="23" t="n">
+      <c r="H35" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I35" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J35" s="22" t="n">
+      <c r="J35" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K35" s="22" t="n">
+      <c r="K35" s="25" t="n">
         <v>140</v>
       </c>
       <c r="L35" s="8" t="n">
@@ -3441,22 +4451,22 @@
           <t>2026-10-07</t>
         </is>
       </c>
-      <c r="F36" s="22" t="n">
+      <c r="F36" s="25" t="n">
         <v>381</v>
       </c>
-      <c r="G36" s="22" t="n">
+      <c r="G36" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H36" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="22" t="n">
+      <c r="H36" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I36" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J36" s="22" t="n">
+      <c r="J36" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K36" s="22" t="n">
+      <c r="K36" s="25" t="n">
         <v>175</v>
       </c>
       <c r="L36" s="8" t="n">
@@ -3489,22 +4499,22 @@
           <t>2026-09-23</t>
         </is>
       </c>
-      <c r="F37" s="22" t="n">
+      <c r="F37" s="25" t="n">
         <v>262</v>
       </c>
-      <c r="G37" s="22" t="n">
+      <c r="G37" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H37" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="22" t="n">
+      <c r="H37" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I37" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J37" s="22" t="n">
+      <c r="J37" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K37" s="22" t="n">
+      <c r="K37" s="25" t="n">
         <v>104</v>
       </c>
       <c r="L37" s="8" t="n">
@@ -3537,22 +4547,22 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F38" s="22" t="n">
+      <c r="F38" s="25" t="n">
         <v>472</v>
       </c>
-      <c r="G38" s="22" t="n">
+      <c r="G38" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H38" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="22" t="n">
+      <c r="H38" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I38" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="22" t="n">
+      <c r="J38" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K38" s="22" t="n">
+      <c r="K38" s="25" t="n">
         <v>196</v>
       </c>
       <c r="L38" s="8" t="n">
@@ -3585,22 +4595,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F39" s="22" t="n">
+      <c r="F39" s="25" t="n">
         <v>623</v>
       </c>
-      <c r="G39" s="22" t="n">
+      <c r="G39" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H39" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="23" t="n">
+      <c r="H39" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I39" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J39" s="22" t="n">
+      <c r="J39" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K39" s="22" t="n">
+      <c r="K39" s="25" t="n">
         <v>253</v>
       </c>
       <c r="L39" s="8" t="n">
@@ -3633,22 +4643,22 @@
           <t>2026-09-25</t>
         </is>
       </c>
-      <c r="F40" s="22" t="n">
+      <c r="F40" s="25" t="n">
         <v>288</v>
       </c>
-      <c r="G40" s="22" t="n">
+      <c r="G40" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="H40" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="22" t="n">
+      <c r="H40" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I40" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J40" s="22" t="n">
+      <c r="J40" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K40" s="22" t="n">
+      <c r="K40" s="25" t="n">
         <v>110</v>
       </c>
       <c r="L40" s="8" t="n">
@@ -3681,22 +4691,22 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F41" s="22" t="n">
+      <c r="F41" s="25" t="n">
         <v>552</v>
       </c>
-      <c r="G41" s="22" t="n">
+      <c r="G41" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H41" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="22" t="n">
+      <c r="H41" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I41" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J41" s="22" t="n">
+      <c r="J41" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K41" s="22" t="n">
+      <c r="K41" s="25" t="n">
         <v>258</v>
       </c>
       <c r="L41" s="8" t="n">
@@ -3729,22 +4739,22 @@
           <t>2026-10-16</t>
         </is>
       </c>
-      <c r="F42" s="22" t="n">
+      <c r="F42" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="G42" s="22" t="n">
+      <c r="G42" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H42" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="23" t="n">
+      <c r="H42" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I42" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J42" s="22" t="n">
+      <c r="J42" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K42" s="22" t="n">
+      <c r="K42" s="25" t="n">
         <v>128</v>
       </c>
       <c r="L42" s="8" t="n">
@@ -3777,22 +4787,22 @@
           <t>2026-09-28</t>
         </is>
       </c>
-      <c r="F43" s="22" t="n">
+      <c r="F43" s="25" t="n">
         <v>684</v>
       </c>
-      <c r="G43" s="22" t="n">
+      <c r="G43" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H43" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="22" t="n">
+      <c r="H43" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I43" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J43" s="22" t="n">
+      <c r="J43" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K43" s="22" t="n">
+      <c r="K43" s="25" t="n">
         <v>332</v>
       </c>
       <c r="L43" s="8" t="n">
@@ -3825,22 +4835,22 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="F44" s="22" t="n">
+      <c r="F44" s="25" t="n">
         <v>645</v>
       </c>
-      <c r="G44" s="22" t="n">
+      <c r="G44" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H44" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="22" t="n">
+      <c r="H44" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I44" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J44" s="22" t="n">
+      <c r="J44" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K44" s="22" t="n">
+      <c r="K44" s="25" t="n">
         <v>323</v>
       </c>
       <c r="L44" s="8" t="n">
@@ -3873,22 +4883,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F45" s="22" t="n">
+      <c r="F45" s="25" t="n">
         <v>565</v>
       </c>
-      <c r="G45" s="22" t="n">
+      <c r="G45" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H45" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="22" t="n">
+      <c r="H45" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I45" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J45" s="22" t="n">
+      <c r="J45" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K45" s="22" t="n">
+      <c r="K45" s="25" t="n">
         <v>261</v>
       </c>
       <c r="L45" s="8" t="n">
@@ -3921,22 +4931,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F46" s="22" t="n">
+      <c r="F46" s="25" t="n">
         <v>441</v>
       </c>
-      <c r="G46" s="22" t="n">
+      <c r="G46" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H46" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="23" t="n">
+      <c r="H46" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I46" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J46" s="22" t="n">
+      <c r="J46" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K46" s="22" t="n">
+      <c r="K46" s="25" t="n">
         <v>211</v>
       </c>
       <c r="L46" s="8" t="n">
@@ -3969,22 +4979,22 @@
           <t>2026-09-18</t>
         </is>
       </c>
-      <c r="F47" s="22" t="n">
+      <c r="F47" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="G47" s="22" t="n">
+      <c r="G47" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H47" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="22" t="n">
+      <c r="H47" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I47" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J47" s="22" t="n">
+      <c r="J47" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K47" s="22" t="n">
+      <c r="K47" s="25" t="n">
         <v>119</v>
       </c>
       <c r="L47" s="8" t="n">
@@ -4017,22 +5027,22 @@
           <t>2026-10-11</t>
         </is>
       </c>
-      <c r="F48" s="22" t="n">
+      <c r="F48" s="25" t="n">
         <v>550</v>
       </c>
-      <c r="G48" s="22" t="n">
+      <c r="G48" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H48" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="22" t="n">
+      <c r="H48" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I48" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J48" s="22" t="n">
+      <c r="J48" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K48" s="22" t="n">
+      <c r="K48" s="25" t="n">
         <v>214</v>
       </c>
       <c r="L48" s="8" t="n">
@@ -4065,22 +5075,22 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="F49" s="22" t="n">
+      <c r="F49" s="25" t="n">
         <v>472</v>
       </c>
-      <c r="G49" s="22" t="n">
+      <c r="G49" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H49" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="22" t="n">
+      <c r="H49" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I49" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J49" s="22" t="n">
+      <c r="J49" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K49" s="22" t="n">
+      <c r="K49" s="25" t="n">
         <v>196</v>
       </c>
       <c r="L49" s="8" t="n">
@@ -4113,22 +5123,22 @@
           <t>2026-10-28</t>
         </is>
       </c>
-      <c r="F50" s="22" t="n">
+      <c r="F50" s="25" t="n">
         <v>517</v>
       </c>
-      <c r="G50" s="22" t="n">
+      <c r="G50" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H50" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="23" t="n">
+      <c r="H50" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I50" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J50" s="22" t="n">
+      <c r="J50" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K50" s="22" t="n">
+      <c r="K50" s="25" t="n">
         <v>185</v>
       </c>
       <c r="L50" s="8" t="n">
@@ -4161,22 +5171,22 @@
           <t>2026-09-22</t>
         </is>
       </c>
-      <c r="F51" s="22" t="n">
+      <c r="F51" s="25" t="n">
         <v>643</v>
       </c>
-      <c r="G51" s="22" t="n">
+      <c r="G51" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="H51" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="22" t="n">
+      <c r="H51" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I51" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J51" s="22" t="n">
+      <c r="J51" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K51" s="22" t="n">
+      <c r="K51" s="25" t="n">
         <v>279</v>
       </c>
       <c r="L51" s="8" t="n">
@@ -4209,22 +5219,22 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="F52" s="22" t="n">
+      <c r="F52" s="25" t="n">
         <v>420</v>
       </c>
-      <c r="G52" s="22" t="n">
+      <c r="G52" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H52" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="22" t="n">
+      <c r="H52" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I52" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J52" s="22" t="n">
+      <c r="J52" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K52" s="22" t="n">
+      <c r="K52" s="25" t="n">
         <v>184</v>
       </c>
       <c r="L52" s="8" t="n">
@@ -4257,22 +5267,22 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F53" s="22" t="n">
+      <c r="F53" s="25" t="n">
         <v>309</v>
       </c>
-      <c r="G53" s="22" t="n">
+      <c r="G53" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H53" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="23" t="n">
+      <c r="H53" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I53" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J53" s="22" t="n">
+      <c r="J53" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K53" s="22" t="n">
+      <c r="K53" s="25" t="n">
         <v>137</v>
       </c>
       <c r="L53" s="8" t="n">
@@ -4305,22 +5315,22 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="F54" s="22" t="n">
+      <c r="F54" s="25" t="n">
         <v>446</v>
       </c>
-      <c r="G54" s="22" t="n">
+      <c r="G54" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H54" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="22" t="n">
+      <c r="H54" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I54" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="22" t="n">
+      <c r="J54" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K54" s="22" t="n">
+      <c r="K54" s="25" t="n">
         <v>190</v>
       </c>
       <c r="L54" s="8" t="n">
@@ -4353,22 +5363,22 @@
           <t>2026-09-14</t>
         </is>
       </c>
-      <c r="F55" s="22" t="n">
+      <c r="F55" s="25" t="n">
         <v>171</v>
       </c>
-      <c r="G55" s="22" t="n">
+      <c r="G55" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H55" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="22" t="n">
+      <c r="H55" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I55" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J55" s="22" t="n">
+      <c r="J55" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K55" s="22" t="n">
+      <c r="K55" s="25" t="n">
         <v>83</v>
       </c>
       <c r="L55" s="8" t="n">
@@ -4401,22 +5411,22 @@
           <t>2026-09-10</t>
         </is>
       </c>
-      <c r="F56" s="22" t="n">
+      <c r="F56" s="25" t="n">
         <v>736</v>
       </c>
-      <c r="G56" s="22" t="n">
+      <c r="G56" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H56" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="22" t="n">
+      <c r="H56" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I56" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J56" s="22" t="n">
+      <c r="J56" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K56" s="22" t="n">
+      <c r="K56" s="25" t="n">
         <v>344</v>
       </c>
       <c r="L56" s="8" t="n">
@@ -4449,22 +5459,22 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F57" s="22" t="n">
+      <c r="F57" s="25" t="n">
         <v>550</v>
       </c>
-      <c r="G57" s="22" t="n">
+      <c r="G57" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H57" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="22" t="n">
+      <c r="H57" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I57" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J57" s="22" t="n">
+      <c r="J57" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K57" s="22" t="n">
+      <c r="K57" s="25" t="n">
         <v>214</v>
       </c>
       <c r="L57" s="8" t="n">
@@ -4497,22 +5507,22 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F58" s="22" t="n">
+      <c r="F58" s="25" t="n">
         <v>322</v>
       </c>
-      <c r="G58" s="22" t="n">
+      <c r="G58" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H58" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="23" t="n">
+      <c r="H58" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I58" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J58" s="22" t="n">
+      <c r="J58" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K58" s="22" t="n">
+      <c r="K58" s="25" t="n">
         <v>140</v>
       </c>
       <c r="L58" s="8" t="n">
@@ -4545,22 +5555,22 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="F59" s="22" t="n">
+      <c r="F59" s="25" t="n">
         <v>348</v>
       </c>
-      <c r="G59" s="22" t="n">
+      <c r="G59" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H59" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="23" t="n">
+      <c r="H59" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I59" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J59" s="22" t="n">
+      <c r="J59" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K59" s="22" t="n">
+      <c r="K59" s="25" t="n">
         <v>146</v>
       </c>
       <c r="L59" s="8" t="n">
@@ -4593,22 +5603,22 @@
           <t>2026-09-17</t>
         </is>
       </c>
-      <c r="F60" s="22" t="n">
+      <c r="F60" s="25" t="n">
         <v>454</v>
       </c>
-      <c r="G60" s="22" t="n">
+      <c r="G60" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H60" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="23" t="n">
+      <c r="H60" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I60" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J60" s="22" t="n">
+      <c r="J60" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K60" s="22" t="n">
+      <c r="K60" s="25" t="n">
         <v>214</v>
       </c>
       <c r="L60" s="8" t="n">
@@ -4641,22 +5651,22 @@
           <t>2026-09-19</t>
         </is>
       </c>
-      <c r="F61" s="22" t="n">
+      <c r="F61" s="25" t="n">
         <v>381</v>
       </c>
-      <c r="G61" s="22" t="n">
+      <c r="G61" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H61" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="22" t="n">
+      <c r="H61" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I61" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J61" s="22" t="n">
+      <c r="J61" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K61" s="22" t="n">
+      <c r="K61" s="25" t="n">
         <v>175</v>
       </c>
       <c r="L61" s="8" t="n">
@@ -4689,22 +5699,22 @@
           <t>2026-10-03</t>
         </is>
       </c>
-      <c r="F62" s="22" t="n">
+      <c r="F62" s="25" t="n">
         <v>301</v>
       </c>
-      <c r="G62" s="22" t="n">
+      <c r="G62" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H62" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="22" t="n">
+      <c r="H62" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I62" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J62" s="22" t="n">
+      <c r="J62" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K62" s="22" t="n">
+      <c r="K62" s="25" t="n">
         <v>113</v>
       </c>
       <c r="L62" s="8" t="n">
@@ -4737,22 +5747,22 @@
           <t>2026-09-16</t>
         </is>
       </c>
-      <c r="F63" s="22" t="n">
+      <c r="F63" s="25" t="n">
         <v>335</v>
       </c>
-      <c r="G63" s="22" t="n">
+      <c r="G63" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H63" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="23" t="n">
+      <c r="H63" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I63" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J63" s="22" t="n">
+      <c r="J63" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K63" s="22" t="n">
+      <c r="K63" s="25" t="n">
         <v>143</v>
       </c>
       <c r="L63" s="8" t="n">
@@ -4785,22 +5795,22 @@
           <t>2026-10-15</t>
         </is>
       </c>
-      <c r="F64" s="22" t="n">
+      <c r="F64" s="25" t="n">
         <v>532</v>
       </c>
-      <c r="G64" s="22" t="n">
+      <c r="G64" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H64" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="23" t="n">
+      <c r="H64" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I64" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J64" s="22" t="n">
+      <c r="J64" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K64" s="22" t="n">
+      <c r="K64" s="25" t="n">
         <v>232</v>
       </c>
       <c r="L64" s="8" t="n">
@@ -4833,22 +5843,22 @@
           <t>2026-09-12</t>
         </is>
       </c>
-      <c r="F65" s="22" t="n">
+      <c r="F65" s="25" t="n">
         <v>459</v>
       </c>
-      <c r="G65" s="22" t="n">
+      <c r="G65" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H65" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="22" t="n">
+      <c r="H65" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I65" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J65" s="22" t="n">
+      <c r="J65" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K65" s="22" t="n">
+      <c r="K65" s="25" t="n">
         <v>193</v>
       </c>
       <c r="L65" s="8" t="n">
@@ -4881,22 +5891,22 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="F66" s="22" t="n">
+      <c r="F66" s="25" t="n">
         <v>734</v>
       </c>
-      <c r="G66" s="22" t="n">
+      <c r="G66" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H66" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="22" t="n">
+      <c r="H66" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I66" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J66" s="22" t="n">
+      <c r="J66" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K66" s="22" t="n">
+      <c r="K66" s="25" t="n">
         <v>300</v>
       </c>
       <c r="L66" s="8" t="n">
@@ -4929,22 +5939,22 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F67" s="22" t="n">
+      <c r="F67" s="25" t="n">
         <v>444</v>
       </c>
-      <c r="G67" s="22" t="n">
+      <c r="G67" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H67" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="22" t="n">
+      <c r="H67" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I67" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J67" s="22" t="n">
+      <c r="J67" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K67" s="22" t="n">
+      <c r="K67" s="25" t="n">
         <v>146</v>
       </c>
       <c r="L67" s="8" t="n">
@@ -4977,22 +5987,22 @@
           <t>2026-10-22</t>
         </is>
       </c>
-      <c r="F68" s="22" t="n">
+      <c r="F68" s="25" t="n">
         <v>762</v>
       </c>
-      <c r="G68" s="22" t="n">
+      <c r="G68" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H68" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="22" t="n">
+      <c r="H68" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I68" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J68" s="22" t="n">
+      <c r="J68" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K68" s="22" t="n">
+      <c r="K68" s="25" t="n">
         <v>350</v>
       </c>
       <c r="L68" s="8" t="n">
@@ -5025,22 +6035,22 @@
           <t>2026-10-23</t>
         </is>
       </c>
-      <c r="F69" s="22" t="n">
+      <c r="F69" s="25" t="n">
         <v>9800</v>
       </c>
-      <c r="G69" s="22" t="n">
+      <c r="G69" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="H69" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="22" t="n">
+      <c r="H69" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I69" s="25" t="n">
         <v>26</v>
       </c>
-      <c r="J69" s="22" t="n">
+      <c r="J69" s="25" t="n">
         <v>1768</v>
       </c>
-      <c r="K69" s="22" t="n">
+      <c r="K69" s="25" t="n">
         <v>4432</v>
       </c>
       <c r="L69" s="8" t="n">
@@ -5073,22 +6083,22 @@
           <t>2026-09-29</t>
         </is>
       </c>
-      <c r="F70" s="22" t="n">
+      <c r="F70" s="25" t="n">
         <v>27400</v>
       </c>
-      <c r="G70" s="22" t="n">
+      <c r="G70" s="25" t="n">
         <v>13800</v>
       </c>
-      <c r="H70" s="22" t="n">
+      <c r="H70" s="25" t="n">
         <v>3100</v>
       </c>
-      <c r="I70" s="22" t="n">
+      <c r="I70" s="25" t="n">
         <v>46</v>
       </c>
-      <c r="J70" s="22" t="n">
+      <c r="J70" s="25" t="n">
         <v>3128</v>
       </c>
-      <c r="K70" s="22" t="n">
+      <c r="K70" s="25" t="n">
         <v>7372</v>
       </c>
       <c r="L70" s="8" t="n">
@@ -5121,22 +6131,22 @@
           <t>2026-10-29</t>
         </is>
       </c>
-      <c r="F71" s="22" t="n">
+      <c r="F71" s="25" t="n">
         <v>15200</v>
       </c>
-      <c r="G71" s="22" t="n">
+      <c r="G71" s="25" t="n">
         <v>4300</v>
       </c>
-      <c r="H71" s="22" t="n">
+      <c r="H71" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="I71" s="22" t="n">
+      <c r="I71" s="25" t="n">
         <v>52</v>
       </c>
-      <c r="J71" s="22" t="n">
+      <c r="J71" s="25" t="n">
         <v>3536</v>
       </c>
-      <c r="K71" s="22" t="n">
+      <c r="K71" s="25" t="n">
         <v>5564</v>
       </c>
       <c r="L71" s="8" t="n">
@@ -5169,22 +6179,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F72" s="22" t="n">
+      <c r="F72" s="25" t="n">
         <v>18600</v>
       </c>
-      <c r="G72" s="22" t="n">
+      <c r="G72" s="25" t="n">
         <v>6900</v>
       </c>
-      <c r="H72" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I72" s="22" t="n">
+      <c r="H72" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I72" s="25" t="n">
         <v>64</v>
       </c>
-      <c r="J72" s="22" t="n">
+      <c r="J72" s="25" t="n">
         <v>4352</v>
       </c>
-      <c r="K72" s="22" t="n">
+      <c r="K72" s="25" t="n">
         <v>7348</v>
       </c>
       <c r="L72" s="8" t="n">
@@ -5217,22 +6227,22 @@
           <t>2026-10-19</t>
         </is>
       </c>
-      <c r="F73" s="22" t="n">
+      <c r="F73" s="25" t="n">
         <v>46800</v>
       </c>
-      <c r="G73" s="22" t="n">
+      <c r="G73" s="25" t="n">
         <v>22900</v>
       </c>
-      <c r="H73" s="22" t="n">
+      <c r="H73" s="25" t="n">
         <v>7400</v>
       </c>
-      <c r="I73" s="22" t="n">
+      <c r="I73" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="J73" s="22" t="n">
+      <c r="J73" s="25" t="n">
         <v>10200</v>
       </c>
-      <c r="K73" s="22" t="n">
+      <c r="K73" s="25" t="n">
         <v>6300</v>
       </c>
       <c r="L73" s="8" t="n">
@@ -5247,7 +6257,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>West End café air-con</t>
+          <t>West End cafe air-con</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -5265,22 +6275,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F74" s="22" t="n">
+      <c r="F74" s="25" t="n">
         <v>12900</v>
       </c>
-      <c r="G74" s="22" t="n">
+      <c r="G74" s="25" t="n">
         <v>5100</v>
       </c>
-      <c r="H74" s="22" t="n">
+      <c r="H74" s="25" t="n">
         <v>900</v>
       </c>
-      <c r="I74" s="22" t="n">
+      <c r="I74" s="25" t="n">
         <v>38</v>
       </c>
-      <c r="J74" s="22" t="n">
+      <c r="J74" s="25" t="n">
         <v>2584</v>
       </c>
-      <c r="K74" s="22" t="n">
+      <c r="K74" s="25" t="n">
         <v>4316</v>
       </c>
       <c r="L74" s="8" t="n">
@@ -5313,22 +6323,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F75" s="22" t="n">
+      <c r="F75" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="G75" s="22" t="n">
+      <c r="G75" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H75" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I75" s="22" t="n">
+      <c r="H75" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I75" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="J75" s="22" t="n">
+      <c r="J75" s="25" t="n">
         <v>1360</v>
       </c>
-      <c r="K75" s="22" t="n">
+      <c r="K75" s="25" t="n">
         <v>2160</v>
       </c>
       <c r="L75" s="8" t="n">
@@ -5361,22 +6371,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F76" s="22" t="n">
+      <c r="F76" s="25" t="n">
         <v>2800</v>
       </c>
-      <c r="G76" s="22" t="n">
+      <c r="G76" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H76" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I76" s="22" t="n">
+      <c r="H76" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I76" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="J76" s="22" t="n">
+      <c r="J76" s="25" t="n">
         <v>1088</v>
       </c>
-      <c r="K76" s="22" t="n">
+      <c r="K76" s="25" t="n">
         <v>1652</v>
       </c>
       <c r="L76" s="8" t="n">
@@ -5409,22 +6419,22 @@
           <t>2026-09-26</t>
         </is>
       </c>
-      <c r="F77" s="22" t="n">
+      <c r="F77" s="25" t="n">
         <v>1700</v>
       </c>
-      <c r="G77" s="22" t="n">
+      <c r="G77" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H77" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="22" t="n">
+      <c r="H77" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I77" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="J77" s="22" t="n">
+      <c r="J77" s="25" t="n">
         <v>612</v>
       </c>
-      <c r="K77" s="22" t="n">
+      <c r="K77" s="25" t="n">
         <v>1058</v>
       </c>
       <c r="L77" s="8" t="n">
@@ -5457,22 +6467,22 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F78" s="22" t="n">
+      <c r="F78" s="25" t="n">
         <v>4100</v>
       </c>
-      <c r="G78" s="22" t="n">
+      <c r="G78" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H78" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="22" t="n">
+      <c r="H78" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I78" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="J78" s="22" t="n">
+      <c r="J78" s="25" t="n">
         <v>1564</v>
       </c>
-      <c r="K78" s="22" t="n">
+      <c r="K78" s="25" t="n">
         <v>2436</v>
       </c>
       <c r="L78" s="8" t="n">
@@ -5505,22 +6515,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F79" s="22" t="n">
+      <c r="F79" s="25" t="n">
         <v>3400</v>
       </c>
-      <c r="G79" s="22" t="n">
+      <c r="G79" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H79" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="22" t="n">
+      <c r="H79" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I79" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="J79" s="22" t="n">
+      <c r="J79" s="25" t="n">
         <v>1292</v>
       </c>
-      <c r="K79" s="22" t="n">
+      <c r="K79" s="25" t="n">
         <v>2038</v>
       </c>
       <c r="L79" s="8" t="n">
@@ -5553,22 +6563,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F80" s="22" t="n">
+      <c r="F80" s="25" t="n">
         <v>2400</v>
       </c>
-      <c r="G80" s="22" t="n">
+      <c r="G80" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H80" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="22" t="n">
+      <c r="H80" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I80" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="J80" s="22" t="n">
+      <c r="J80" s="25" t="n">
         <v>952</v>
       </c>
-      <c r="K80" s="22" t="n">
+      <c r="K80" s="25" t="n">
         <v>1398</v>
       </c>
       <c r="L80" s="8" t="n">
@@ -5601,22 +6611,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F81" s="22" t="n">
+      <c r="F81" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="G81" s="22" t="n">
+      <c r="G81" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H81" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="22" t="n">
+      <c r="H81" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I81" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="J81" s="22" t="n">
+      <c r="J81" s="25" t="n">
         <v>1632</v>
       </c>
-      <c r="K81" s="22" t="n">
+      <c r="K81" s="25" t="n">
         <v>2478</v>
       </c>
       <c r="L81" s="8" t="n">
@@ -5649,22 +6659,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F82" s="22" t="n">
+      <c r="F82" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="G82" s="22" t="n">
+      <c r="G82" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H82" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="22" t="n">
+      <c r="H82" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I82" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="J82" s="22" t="n">
+      <c r="J82" s="25" t="n">
         <v>612</v>
       </c>
-      <c r="K82" s="22" t="n">
+      <c r="K82" s="25" t="n">
         <v>958</v>
       </c>
       <c r="L82" s="8" t="n">
@@ -5697,22 +6707,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F83" s="22" t="n">
+      <c r="F83" s="25" t="n">
         <v>3200</v>
       </c>
-      <c r="G83" s="22" t="n">
+      <c r="G83" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H83" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="22" t="n">
+      <c r="H83" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I83" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="J83" s="22" t="n">
+      <c r="J83" s="25" t="n">
         <v>1224</v>
       </c>
-      <c r="K83" s="22" t="n">
+      <c r="K83" s="25" t="n">
         <v>1916</v>
       </c>
       <c r="L83" s="8" t="n">
@@ -5745,22 +6755,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F84" s="22" t="n">
+      <c r="F84" s="25" t="n">
         <v>3900</v>
       </c>
-      <c r="G84" s="22" t="n">
+      <c r="G84" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="H84" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="22" t="n">
+      <c r="H84" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I84" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="J84" s="22" t="n">
+      <c r="J84" s="25" t="n">
         <v>1496</v>
       </c>
-      <c r="K84" s="22" t="n">
+      <c r="K84" s="25" t="n">
         <v>2294</v>
       </c>
       <c r="L84" s="8" t="n">
@@ -5775,7 +6785,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Southbank café group</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -5793,22 +6803,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F85" s="22" t="n">
+      <c r="F85" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="G85" s="22" t="n">
+      <c r="G85" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H85" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="22" t="n">
+      <c r="H85" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I85" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="J85" s="22" t="n">
+      <c r="J85" s="25" t="n">
         <v>680</v>
       </c>
-      <c r="K85" s="22" t="n">
+      <c r="K85" s="25" t="n">
         <v>1080</v>
       </c>
       <c r="L85" s="8" t="n">
@@ -5841,22 +6851,22 @@
           <t>2026-10-01</t>
         </is>
       </c>
-      <c r="F86" s="22" t="n">
+      <c r="F86" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="G86" s="22" t="n">
+      <c r="G86" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H86" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="22" t="n">
+      <c r="H86" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I86" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="J86" s="22" t="n">
+      <c r="J86" s="25" t="n">
         <v>1156</v>
       </c>
-      <c r="K86" s="22" t="n">
+      <c r="K86" s="25" t="n">
         <v>1774</v>
       </c>
       <c r="L86" s="8" t="n">
@@ -5889,22 +6899,22 @@
           <t>2026-10-09</t>
         </is>
       </c>
-      <c r="F87" s="22" t="n">
+      <c r="F87" s="25" t="n">
         <v>2600</v>
       </c>
-      <c r="G87" s="22" t="n">
+      <c r="G87" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H87" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="22" t="n">
+      <c r="H87" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I87" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="J87" s="22" t="n">
+      <c r="J87" s="25" t="n">
         <v>1020</v>
       </c>
-      <c r="K87" s="22" t="n">
+      <c r="K87" s="25" t="n">
         <v>1530</v>
       </c>
       <c r="L87" s="8" t="n">
@@ -5937,22 +6947,22 @@
           <t>2026-10-04</t>
         </is>
       </c>
-      <c r="F88" s="22" t="n">
+      <c r="F88" s="25" t="n">
         <v>2200</v>
       </c>
-      <c r="G88" s="22" t="n">
+      <c r="G88" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H88" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="22" t="n">
+      <c r="H88" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I88" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="J88" s="22" t="n">
+      <c r="J88" s="25" t="n">
         <v>816</v>
       </c>
-      <c r="K88" s="22" t="n">
+      <c r="K88" s="25" t="n">
         <v>1344</v>
       </c>
       <c r="L88" s="8" t="n">
@@ -5985,22 +6995,22 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F89" s="22" t="n">
+      <c r="F89" s="25" t="n">
         <v>853</v>
       </c>
-      <c r="G89" s="22" t="n">
+      <c r="G89" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="H89" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="22" t="n">
+      <c r="H89" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I89" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J89" s="22" t="n">
+      <c r="J89" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K89" s="22" t="n">
+      <c r="K89" s="25" t="n">
         <v>371</v>
       </c>
       <c r="L89" s="8" t="n">
@@ -6033,22 +7043,22 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F90" s="22" t="n">
+      <c r="F90" s="25" t="n">
         <v>342</v>
       </c>
-      <c r="G90" s="22" t="n">
+      <c r="G90" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H90" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="22" t="n">
+      <c r="H90" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I90" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J90" s="22" t="n">
+      <c r="J90" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K90" s="22" t="n">
+      <c r="K90" s="25" t="n">
         <v>166</v>
       </c>
       <c r="L90" s="8" t="n">
@@ -6081,22 +7091,22 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F91" s="22" t="n">
+      <c r="F91" s="25" t="n">
         <v>474</v>
       </c>
-      <c r="G91" s="22" t="n">
+      <c r="G91" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H91" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="22" t="n">
+      <c r="H91" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I91" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J91" s="22" t="n">
+      <c r="J91" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K91" s="22" t="n">
+      <c r="K91" s="25" t="n">
         <v>240</v>
       </c>
       <c r="L91" s="8" t="n">
@@ -6129,22 +7139,22 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="F92" s="22" t="n">
+      <c r="F92" s="25" t="n">
         <v>708</v>
       </c>
-      <c r="G92" s="22" t="n">
+      <c r="G92" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="H92" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="22" t="n">
+      <c r="H92" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I92" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J92" s="22" t="n">
+      <c r="J92" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K92" s="22" t="n">
+      <c r="K92" s="25" t="n">
         <v>294</v>
       </c>
       <c r="L92" s="8" t="n">
@@ -6177,22 +7187,22 @@
           <t>2026-08-12</t>
         </is>
       </c>
-      <c r="F93" s="22" t="n">
+      <c r="F93" s="25" t="n">
         <v>381</v>
       </c>
-      <c r="G93" s="22" t="n">
+      <c r="G93" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H93" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="22" t="n">
+      <c r="H93" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I93" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J93" s="22" t="n">
+      <c r="J93" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K93" s="22" t="n">
+      <c r="K93" s="25" t="n">
         <v>175</v>
       </c>
       <c r="L93" s="8" t="n">
@@ -6225,22 +7235,22 @@
           <t>2026-09-04</t>
         </is>
       </c>
-      <c r="F94" s="22" t="n">
+      <c r="F94" s="25" t="n">
         <v>695</v>
       </c>
-      <c r="G94" s="22" t="n">
+      <c r="G94" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H94" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="22" t="n">
+      <c r="H94" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I94" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J94" s="22" t="n">
+      <c r="J94" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K94" s="22" t="n">
+      <c r="K94" s="25" t="n">
         <v>291</v>
       </c>
       <c r="L94" s="8" t="n">
@@ -6273,22 +7283,22 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="F95" s="22" t="n">
+      <c r="F95" s="25" t="n">
         <v>539</v>
       </c>
-      <c r="G95" s="22" t="n">
+      <c r="G95" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H95" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="22" t="n">
+      <c r="H95" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I95" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J95" s="22" t="n">
+      <c r="J95" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K95" s="22" t="n">
+      <c r="K95" s="25" t="n">
         <v>255</v>
       </c>
       <c r="L95" s="8" t="n">
@@ -6321,22 +7331,22 @@
           <t>2026-09-21</t>
         </is>
       </c>
-      <c r="F96" s="22" t="n">
+      <c r="F96" s="25" t="n">
         <v>840</v>
       </c>
-      <c r="G96" s="22" t="n">
+      <c r="G96" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H96" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="22" t="n">
+      <c r="H96" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I96" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J96" s="22" t="n">
+      <c r="J96" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K96" s="22" t="n">
+      <c r="K96" s="25" t="n">
         <v>368</v>
       </c>
       <c r="L96" s="8" t="n">
@@ -6369,22 +7379,22 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="F97" s="22" t="n">
+      <c r="F97" s="25" t="n">
         <v>866</v>
       </c>
-      <c r="G97" s="22" t="n">
+      <c r="G97" s="25" t="n">
         <v>220</v>
       </c>
-      <c r="H97" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="22" t="n">
+      <c r="H97" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I97" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J97" s="22" t="n">
+      <c r="J97" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K97" s="22" t="n">
+      <c r="K97" s="25" t="n">
         <v>374</v>
       </c>
       <c r="L97" s="8" t="n">
@@ -6417,22 +7427,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F98" s="22" t="n">
+      <c r="F98" s="25" t="n">
         <v>604</v>
       </c>
-      <c r="G98" s="22" t="n">
+      <c r="G98" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H98" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="22" t="n">
+      <c r="H98" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I98" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J98" s="22" t="n">
+      <c r="J98" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K98" s="22" t="n">
+      <c r="K98" s="25" t="n">
         <v>270</v>
       </c>
       <c r="L98" s="8" t="n">
@@ -6465,22 +7475,22 @@
           <t>2026-08-25</t>
         </is>
       </c>
-      <c r="F99" s="22" t="n">
+      <c r="F99" s="25" t="n">
         <v>524</v>
       </c>
-      <c r="G99" s="22" t="n">
+      <c r="G99" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H99" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="22" t="n">
+      <c r="H99" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I99" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J99" s="22" t="n">
+      <c r="J99" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K99" s="22" t="n">
+      <c r="K99" s="25" t="n">
         <v>208</v>
       </c>
       <c r="L99" s="8" t="n">
@@ -6513,22 +7523,22 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F100" s="22" t="n">
+      <c r="F100" s="25" t="n">
         <v>368</v>
       </c>
-      <c r="G100" s="22" t="n">
+      <c r="G100" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H100" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="22" t="n">
+      <c r="H100" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I100" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J100" s="22" t="n">
+      <c r="J100" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K100" s="22" t="n">
+      <c r="K100" s="25" t="n">
         <v>172</v>
       </c>
       <c r="L100" s="8" t="n">
@@ -6561,22 +7571,22 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F101" s="22" t="n">
+      <c r="F101" s="25" t="n">
         <v>658</v>
       </c>
-      <c r="G101" s="22" t="n">
+      <c r="G101" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H101" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="22" t="n">
+      <c r="H101" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I101" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J101" s="22" t="n">
+      <c r="J101" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K101" s="22" t="n">
+      <c r="K101" s="25" t="n">
         <v>326</v>
       </c>
       <c r="L101" s="8" t="n">
@@ -6609,22 +7619,22 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F102" s="22" t="n">
+      <c r="F102" s="25" t="n">
         <v>511</v>
       </c>
-      <c r="G102" s="22" t="n">
+      <c r="G102" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="H102" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="22" t="n">
+      <c r="H102" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I102" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="22" t="n">
+      <c r="J102" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K102" s="22" t="n">
+      <c r="K102" s="25" t="n">
         <v>205</v>
       </c>
       <c r="L102" s="8" t="n">
@@ -6657,22 +7667,22 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F103" s="22" t="n">
+      <c r="F103" s="25" t="n">
         <v>433</v>
       </c>
-      <c r="G103" s="22" t="n">
+      <c r="G103" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="H103" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="22" t="n">
+      <c r="H103" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I103" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J103" s="22" t="n">
+      <c r="J103" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K103" s="22" t="n">
+      <c r="K103" s="25" t="n">
         <v>187</v>
       </c>
       <c r="L103" s="8" t="n">
@@ -6705,22 +7715,22 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F104" s="22" t="n">
+      <c r="F104" s="25" t="n">
         <v>439</v>
       </c>
-      <c r="G104" s="22" t="n">
+      <c r="G104" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="H104" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="23" t="n">
+      <c r="H104" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I104" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J104" s="22" t="n">
+      <c r="J104" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K104" s="22" t="n">
+      <c r="K104" s="25" t="n">
         <v>167</v>
       </c>
       <c r="L104" s="8" t="n">
@@ -6753,22 +7763,22 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="F105" s="22" t="n">
+      <c r="F105" s="25" t="n">
         <v>617</v>
       </c>
-      <c r="G105" s="22" t="n">
+      <c r="G105" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H105" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="22" t="n">
+      <c r="H105" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I105" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J105" s="22" t="n">
+      <c r="J105" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K105" s="22" t="n">
+      <c r="K105" s="25" t="n">
         <v>273</v>
       </c>
       <c r="L105" s="8" t="n">
@@ -6801,22 +7811,22 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="F106" s="22" t="n">
+      <c r="F106" s="25" t="n">
         <v>478</v>
       </c>
-      <c r="G106" s="22" t="n">
+      <c r="G106" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H106" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="23" t="n">
+      <c r="H106" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I106" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J106" s="22" t="n">
+      <c r="J106" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K106" s="22" t="n">
+      <c r="K106" s="25" t="n">
         <v>176</v>
       </c>
       <c r="L106" s="8" t="n">
@@ -6849,22 +7859,22 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F107" s="22" t="n">
+      <c r="F107" s="25" t="n">
         <v>682</v>
       </c>
-      <c r="G107" s="22" t="n">
+      <c r="G107" s="25" t="n">
         <v>190</v>
       </c>
-      <c r="H107" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="22" t="n">
+      <c r="H107" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I107" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J107" s="22" t="n">
+      <c r="J107" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K107" s="22" t="n">
+      <c r="K107" s="25" t="n">
         <v>288</v>
       </c>
       <c r="L107" s="8" t="n">
@@ -6897,22 +7907,22 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F108" s="22" t="n">
+      <c r="F108" s="25" t="n">
         <v>571</v>
       </c>
-      <c r="G108" s="22" t="n">
+      <c r="G108" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="H108" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="23" t="n">
+      <c r="H108" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I108" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J108" s="22" t="n">
+      <c r="J108" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K108" s="22" t="n">
+      <c r="K108" s="25" t="n">
         <v>241</v>
       </c>
       <c r="L108" s="8" t="n">
@@ -6945,22 +7955,22 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="F109" s="22" t="n">
+      <c r="F109" s="25" t="n">
         <v>493</v>
       </c>
-      <c r="G109" s="22" t="n">
+      <c r="G109" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H109" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="23" t="n">
+      <c r="H109" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I109" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J109" s="22" t="n">
+      <c r="J109" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K109" s="22" t="n">
+      <c r="K109" s="25" t="n">
         <v>223</v>
       </c>
       <c r="L109" s="8" t="n">
@@ -6993,22 +8003,22 @@
           <t>2026-08-27</t>
         </is>
       </c>
-      <c r="F110" s="22" t="n">
+      <c r="F110" s="25" t="n">
         <v>669</v>
       </c>
-      <c r="G110" s="22" t="n">
+      <c r="G110" s="25" t="n">
         <v>180</v>
       </c>
-      <c r="H110" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="22" t="n">
+      <c r="H110" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I110" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J110" s="22" t="n">
+      <c r="J110" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K110" s="22" t="n">
+      <c r="K110" s="25" t="n">
         <v>285</v>
       </c>
       <c r="L110" s="8" t="n">
@@ -7041,22 +8051,22 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F111" s="22" t="n">
+      <c r="F111" s="25" t="n">
         <v>322</v>
       </c>
-      <c r="G111" s="22" t="n">
+      <c r="G111" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H111" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="23" t="n">
+      <c r="H111" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I111" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J111" s="22" t="n">
+      <c r="J111" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K111" s="22" t="n">
+      <c r="K111" s="25" t="n">
         <v>140</v>
       </c>
       <c r="L111" s="8" t="n">
@@ -7089,22 +8099,22 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F112" s="22" t="n">
+      <c r="F112" s="25" t="n">
         <v>467</v>
       </c>
-      <c r="G112" s="22" t="n">
+      <c r="G112" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H112" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="23" t="n">
+      <c r="H112" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I112" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J112" s="22" t="n">
+      <c r="J112" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K112" s="22" t="n">
+      <c r="K112" s="25" t="n">
         <v>217</v>
       </c>
       <c r="L112" s="8" t="n">
@@ -7137,22 +8147,22 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F113" s="22" t="n">
+      <c r="F113" s="25" t="n">
         <v>537</v>
       </c>
-      <c r="G113" s="22" t="n">
+      <c r="G113" s="25" t="n">
         <v>190</v>
       </c>
-      <c r="H113" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="22" t="n">
+      <c r="H113" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I113" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J113" s="22" t="n">
+      <c r="J113" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K113" s="22" t="n">
+      <c r="K113" s="25" t="n">
         <v>211</v>
       </c>
       <c r="L113" s="8" t="n">
@@ -7185,22 +8195,22 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F114" s="22" t="n">
+      <c r="F114" s="25" t="n">
         <v>623</v>
       </c>
-      <c r="G114" s="22" t="n">
+      <c r="G114" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H114" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="23" t="n">
+      <c r="H114" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I114" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J114" s="22" t="n">
+      <c r="J114" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K114" s="22" t="n">
+      <c r="K114" s="25" t="n">
         <v>253</v>
       </c>
       <c r="L114" s="8" t="n">
@@ -7233,22 +8243,22 @@
           <t>2026-08-03</t>
         </is>
       </c>
-      <c r="F115" s="22" t="n">
+      <c r="F115" s="25" t="n">
         <v>472</v>
       </c>
-      <c r="G115" s="22" t="n">
+      <c r="G115" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H115" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="22" t="n">
+      <c r="H115" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I115" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J115" s="22" t="n">
+      <c r="J115" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K115" s="22" t="n">
+      <c r="K115" s="25" t="n">
         <v>196</v>
       </c>
       <c r="L115" s="8" t="n">
@@ -7281,22 +8291,22 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="F116" s="22" t="n">
+      <c r="F116" s="25" t="n">
         <v>517</v>
       </c>
-      <c r="G116" s="22" t="n">
+      <c r="G116" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H116" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="23" t="n">
+      <c r="H116" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I116" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J116" s="22" t="n">
+      <c r="J116" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K116" s="22" t="n">
+      <c r="K116" s="25" t="n">
         <v>185</v>
       </c>
       <c r="L116" s="8" t="n">
@@ -7329,22 +8339,22 @@
           <t>2026-08-05</t>
         </is>
       </c>
-      <c r="F117" s="22" t="n">
+      <c r="F117" s="25" t="n">
         <v>526</v>
       </c>
-      <c r="G117" s="22" t="n">
+      <c r="G117" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H117" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="22" t="n">
+      <c r="H117" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I117" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J117" s="22" t="n">
+      <c r="J117" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K117" s="22" t="n">
+      <c r="K117" s="25" t="n">
         <v>252</v>
       </c>
       <c r="L117" s="8" t="n">
@@ -7377,22 +8387,22 @@
           <t>2026-08-19</t>
         </is>
       </c>
-      <c r="F118" s="22" t="n">
+      <c r="F118" s="25" t="n">
         <v>658</v>
       </c>
-      <c r="G118" s="22" t="n">
+      <c r="G118" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H118" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="22" t="n">
+      <c r="H118" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I118" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J118" s="22" t="n">
+      <c r="J118" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K118" s="22" t="n">
+      <c r="K118" s="25" t="n">
         <v>326</v>
       </c>
       <c r="L118" s="8" t="n">
@@ -7425,22 +8435,22 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F119" s="22" t="n">
+      <c r="F119" s="25" t="n">
         <v>420</v>
       </c>
-      <c r="G119" s="22" t="n">
+      <c r="G119" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H119" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="22" t="n">
+      <c r="H119" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J119" s="22" t="n">
+      <c r="J119" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K119" s="22" t="n">
+      <c r="K119" s="25" t="n">
         <v>184</v>
       </c>
       <c r="L119" s="8" t="n">
@@ -7473,22 +8483,22 @@
           <t>2026-09-24</t>
         </is>
       </c>
-      <c r="F120" s="22" t="n">
+      <c r="F120" s="25" t="n">
         <v>656</v>
       </c>
-      <c r="G120" s="22" t="n">
+      <c r="G120" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="H120" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="22" t="n">
+      <c r="H120" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I120" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J120" s="22" t="n">
+      <c r="J120" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K120" s="22" t="n">
+      <c r="K120" s="25" t="n">
         <v>282</v>
       </c>
       <c r="L120" s="8" t="n">
@@ -7521,22 +8531,22 @@
           <t>2026-09-01</t>
         </is>
       </c>
-      <c r="F121" s="22" t="n">
+      <c r="F121" s="25" t="n">
         <v>446</v>
       </c>
-      <c r="G121" s="22" t="n">
+      <c r="G121" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H121" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="22" t="n">
+      <c r="H121" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I121" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J121" s="22" t="n">
+      <c r="J121" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K121" s="22" t="n">
+      <c r="K121" s="25" t="n">
         <v>190</v>
       </c>
       <c r="L121" s="8" t="n">
@@ -7569,22 +8579,22 @@
           <t>2026-08-06</t>
         </is>
       </c>
-      <c r="F122" s="22" t="n">
+      <c r="F122" s="25" t="n">
         <v>327</v>
       </c>
-      <c r="G122" s="22" t="n">
+      <c r="G122" s="25" t="n">
         <v>140</v>
       </c>
-      <c r="H122" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="22" t="n">
+      <c r="H122" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I122" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J122" s="22" t="n">
+      <c r="J122" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K122" s="22" t="n">
+      <c r="K122" s="25" t="n">
         <v>119</v>
       </c>
       <c r="L122" s="8" t="n">
@@ -7617,22 +8627,22 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F123" s="22" t="n">
+      <c r="F123" s="25" t="n">
         <v>441</v>
       </c>
-      <c r="G123" s="22" t="n">
+      <c r="G123" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H123" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="23" t="n">
+      <c r="H123" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I123" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J123" s="22" t="n">
+      <c r="J123" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K123" s="22" t="n">
+      <c r="K123" s="25" t="n">
         <v>211</v>
       </c>
       <c r="L123" s="8" t="n">
@@ -7665,22 +8675,22 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="F124" s="22" t="n">
+      <c r="F124" s="25" t="n">
         <v>402</v>
       </c>
-      <c r="G124" s="22" t="n">
+      <c r="G124" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H124" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="23" t="n">
+      <c r="H124" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I124" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J124" s="22" t="n">
+      <c r="J124" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K124" s="22" t="n">
+      <c r="K124" s="25" t="n">
         <v>202</v>
       </c>
       <c r="L124" s="8" t="n">
@@ -7713,22 +8723,22 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="F125" s="22" t="n">
+      <c r="F125" s="25" t="n">
         <v>710</v>
       </c>
-      <c r="G125" s="22" t="n">
+      <c r="G125" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H125" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="22" t="n">
+      <c r="H125" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I125" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J125" s="22" t="n">
+      <c r="J125" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K125" s="22" t="n">
+      <c r="K125" s="25" t="n">
         <v>338</v>
       </c>
       <c r="L125" s="8" t="n">
@@ -7761,22 +8771,22 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F126" s="22" t="n">
+      <c r="F126" s="25" t="n">
         <v>355</v>
       </c>
-      <c r="G126" s="22" t="n">
+      <c r="G126" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H126" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="22" t="n">
+      <c r="H126" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I126" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J126" s="22" t="n">
+      <c r="J126" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K126" s="22" t="n">
+      <c r="K126" s="25" t="n">
         <v>169</v>
       </c>
       <c r="L126" s="8" t="n">
@@ -7809,22 +8819,22 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F127" s="22" t="n">
+      <c r="F127" s="25" t="n">
         <v>335</v>
       </c>
-      <c r="G127" s="22" t="n">
+      <c r="G127" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H127" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="23" t="n">
+      <c r="H127" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I127" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J127" s="22" t="n">
+      <c r="J127" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K127" s="22" t="n">
+      <c r="K127" s="25" t="n">
         <v>143</v>
       </c>
       <c r="L127" s="8" t="n">
@@ -7857,22 +8867,22 @@
           <t>2026-08-14</t>
         </is>
       </c>
-      <c r="F128" s="22" t="n">
+      <c r="F128" s="25" t="n">
         <v>301</v>
       </c>
-      <c r="G128" s="22" t="n">
+      <c r="G128" s="25" t="n">
         <v>120</v>
       </c>
-      <c r="H128" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="22" t="n">
+      <c r="H128" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I128" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J128" s="22" t="n">
+      <c r="J128" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K128" s="22" t="n">
+      <c r="K128" s="25" t="n">
         <v>113</v>
       </c>
       <c r="L128" s="8" t="n">
@@ -7905,22 +8915,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F129" s="22" t="n">
+      <c r="F129" s="25" t="n">
         <v>734</v>
       </c>
-      <c r="G129" s="22" t="n">
+      <c r="G129" s="25" t="n">
         <v>230</v>
       </c>
-      <c r="H129" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="22" t="n">
+      <c r="H129" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I129" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J129" s="22" t="n">
+      <c r="J129" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K129" s="22" t="n">
+      <c r="K129" s="25" t="n">
         <v>300</v>
       </c>
       <c r="L129" s="8" t="n">
@@ -7953,22 +8963,22 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F130" s="22" t="n">
+      <c r="F130" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="G130" s="22" t="n">
+      <c r="G130" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H130" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="23" t="n">
+      <c r="H130" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I130" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J130" s="22" t="n">
+      <c r="J130" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K130" s="22" t="n">
+      <c r="K130" s="25" t="n">
         <v>128</v>
       </c>
       <c r="L130" s="8" t="n">
@@ -8001,22 +9011,22 @@
           <t>2026-08-18</t>
         </is>
       </c>
-      <c r="F131" s="22" t="n">
+      <c r="F131" s="25" t="n">
         <v>394</v>
       </c>
-      <c r="G131" s="22" t="n">
+      <c r="G131" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H131" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="22" t="n">
+      <c r="H131" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I131" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J131" s="22" t="n">
+      <c r="J131" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K131" s="22" t="n">
+      <c r="K131" s="25" t="n">
         <v>178</v>
       </c>
       <c r="L131" s="8" t="n">
@@ -8049,22 +9059,22 @@
           <t>2026-08-28</t>
         </is>
       </c>
-      <c r="F132" s="22" t="n">
+      <c r="F132" s="25" t="n">
         <v>288</v>
       </c>
-      <c r="G132" s="22" t="n">
+      <c r="G132" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="H132" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="22" t="n">
+      <c r="H132" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I132" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J132" s="22" t="n">
+      <c r="J132" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K132" s="22" t="n">
+      <c r="K132" s="25" t="n">
         <v>110</v>
       </c>
       <c r="L132" s="8" t="n">
@@ -8097,22 +9107,22 @@
           <t>2026-09-02</t>
         </is>
       </c>
-      <c r="F133" s="22" t="n">
+      <c r="F133" s="25" t="n">
         <v>493</v>
       </c>
-      <c r="G133" s="22" t="n">
+      <c r="G133" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H133" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="23" t="n">
+      <c r="H133" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I133" s="26" t="n">
         <v>2.5</v>
       </c>
-      <c r="J133" s="22" t="n">
+      <c r="J133" s="25" t="n">
         <v>170</v>
       </c>
-      <c r="K133" s="22" t="n">
+      <c r="K133" s="25" t="n">
         <v>223</v>
       </c>
       <c r="L133" s="8" t="n">
@@ -8145,22 +9155,22 @@
           <t>2026-08-15</t>
         </is>
       </c>
-      <c r="F134" s="22" t="n">
+      <c r="F134" s="25" t="n">
         <v>314</v>
       </c>
-      <c r="G134" s="22" t="n">
+      <c r="G134" s="25" t="n">
         <v>130</v>
       </c>
-      <c r="H134" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="22" t="n">
+      <c r="H134" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I134" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="22" t="n">
+      <c r="J134" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K134" s="22" t="n">
+      <c r="K134" s="25" t="n">
         <v>116</v>
       </c>
       <c r="L134" s="8" t="n">
@@ -8193,22 +9203,22 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F135" s="22" t="n">
+      <c r="F135" s="25" t="n">
         <v>340</v>
       </c>
-      <c r="G135" s="22" t="n">
+      <c r="G135" s="25" t="n">
         <v>150</v>
       </c>
-      <c r="H135" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="22" t="n">
+      <c r="H135" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I135" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J135" s="22" t="n">
+      <c r="J135" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K135" s="22" t="n">
+      <c r="K135" s="25" t="n">
         <v>122</v>
       </c>
       <c r="L135" s="8" t="n">
@@ -8241,22 +9251,22 @@
           <t>2026-08-10</t>
         </is>
       </c>
-      <c r="F136" s="22" t="n">
+      <c r="F136" s="25" t="n">
         <v>262</v>
       </c>
-      <c r="G136" s="22" t="n">
+      <c r="G136" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H136" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="22" t="n">
+      <c r="H136" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I136" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="22" t="n">
+      <c r="J136" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K136" s="22" t="n">
+      <c r="K136" s="25" t="n">
         <v>104</v>
       </c>
       <c r="L136" s="8" t="n">
@@ -8289,22 +9299,22 @@
           <t>2026-08-24</t>
         </is>
       </c>
-      <c r="F137" s="22" t="n">
+      <c r="F137" s="25" t="n">
         <v>643</v>
       </c>
-      <c r="G137" s="22" t="n">
+      <c r="G137" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="H137" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="22" t="n">
+      <c r="H137" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I137" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J137" s="22" t="n">
+      <c r="J137" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K137" s="22" t="n">
+      <c r="K137" s="25" t="n">
         <v>279</v>
       </c>
       <c r="L137" s="8" t="n">
@@ -8337,22 +9347,22 @@
           <t>2026-08-04</t>
         </is>
       </c>
-      <c r="F138" s="22" t="n">
+      <c r="F138" s="25" t="n">
         <v>210</v>
       </c>
-      <c r="G138" s="22" t="n">
+      <c r="G138" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H138" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="22" t="n">
+      <c r="H138" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I138" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="22" t="n">
+      <c r="J138" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K138" s="22" t="n">
+      <c r="K138" s="25" t="n">
         <v>92</v>
       </c>
       <c r="L138" s="8" t="n">
@@ -8385,22 +9395,22 @@
           <t>2026-08-08</t>
         </is>
       </c>
-      <c r="F139" s="22" t="n">
+      <c r="F139" s="25" t="n">
         <v>526</v>
       </c>
-      <c r="G139" s="22" t="n">
+      <c r="G139" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H139" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="22" t="n">
+      <c r="H139" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I139" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J139" s="22" t="n">
+      <c r="J139" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K139" s="22" t="n">
+      <c r="K139" s="25" t="n">
         <v>252</v>
       </c>
       <c r="L139" s="8" t="n">
@@ -8433,22 +9443,22 @@
           <t>2026-08-22</t>
         </is>
       </c>
-      <c r="F140" s="22" t="n">
+      <c r="F140" s="25" t="n">
         <v>270</v>
       </c>
-      <c r="G140" s="22" t="n">
+      <c r="G140" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H140" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="23" t="n">
+      <c r="H140" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I140" s="26" t="n">
         <v>1.5</v>
       </c>
-      <c r="J140" s="22" t="n">
+      <c r="J140" s="25" t="n">
         <v>102</v>
       </c>
-      <c r="K140" s="22" t="n">
+      <c r="K140" s="25" t="n">
         <v>128</v>
       </c>
       <c r="L140" s="8" t="n">
@@ -8481,22 +9491,22 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="F141" s="22" t="n">
+      <c r="F141" s="25" t="n">
         <v>342</v>
       </c>
-      <c r="G141" s="22" t="n">
+      <c r="G141" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H141" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="22" t="n">
+      <c r="H141" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I141" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J141" s="22" t="n">
+      <c r="J141" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K141" s="22" t="n">
+      <c r="K141" s="25" t="n">
         <v>166</v>
       </c>
       <c r="L141" s="8" t="n">
@@ -8529,22 +9539,22 @@
           <t>2026-08-29</t>
         </is>
       </c>
-      <c r="F142" s="22" t="n">
+      <c r="F142" s="25" t="n">
         <v>355</v>
       </c>
-      <c r="G142" s="22" t="n">
+      <c r="G142" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H142" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="22" t="n">
+      <c r="H142" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I142" s="25" t="n">
         <v>2</v>
       </c>
-      <c r="J142" s="22" t="n">
+      <c r="J142" s="25" t="n">
         <v>136</v>
       </c>
-      <c r="K142" s="22" t="n">
+      <c r="K142" s="25" t="n">
         <v>169</v>
       </c>
       <c r="L142" s="8" t="n">
@@ -8577,22 +9587,22 @@
           <t>2026-08-11</t>
         </is>
       </c>
-      <c r="F143" s="22" t="n">
+      <c r="F143" s="25" t="n">
         <v>552</v>
       </c>
-      <c r="G143" s="22" t="n">
+      <c r="G143" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H143" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="22" t="n">
+      <c r="H143" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I143" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J143" s="22" t="n">
+      <c r="J143" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K143" s="22" t="n">
+      <c r="K143" s="25" t="n">
         <v>258</v>
       </c>
       <c r="L143" s="8" t="n">
@@ -8625,22 +9635,22 @@
           <t>2026-08-20</t>
         </is>
       </c>
-      <c r="F144" s="22" t="n">
+      <c r="F144" s="25" t="n">
         <v>171</v>
       </c>
-      <c r="G144" s="22" t="n">
+      <c r="G144" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="H144" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="22" t="n">
+      <c r="H144" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I144" s="25" t="n">
         <v>1</v>
       </c>
-      <c r="J144" s="22" t="n">
+      <c r="J144" s="25" t="n">
         <v>68</v>
       </c>
-      <c r="K144" s="22" t="n">
+      <c r="K144" s="25" t="n">
         <v>83</v>
       </c>
       <c r="L144" s="8" t="n">
@@ -8673,22 +9683,22 @@
           <t>2026-08-17</t>
         </is>
       </c>
-      <c r="F145" s="22" t="n">
+      <c r="F145" s="25" t="n">
         <v>695</v>
       </c>
-      <c r="G145" s="22" t="n">
+      <c r="G145" s="25" t="n">
         <v>200</v>
       </c>
-      <c r="H145" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="22" t="n">
+      <c r="H145" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I145" s="25" t="n">
         <v>3</v>
       </c>
-      <c r="J145" s="22" t="n">
+      <c r="J145" s="25" t="n">
         <v>204</v>
       </c>
-      <c r="K145" s="22" t="n">
+      <c r="K145" s="25" t="n">
         <v>291</v>
       </c>
       <c r="L145" s="8" t="n">
@@ -8721,22 +9731,22 @@
           <t>2026-08-23</t>
         </is>
       </c>
-      <c r="F146" s="22" t="n">
+      <c r="F146" s="25" t="n">
         <v>788</v>
       </c>
-      <c r="G146" s="22" t="n">
+      <c r="G146" s="25" t="n">
         <v>160</v>
       </c>
-      <c r="H146" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="22" t="n">
+      <c r="H146" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I146" s="25" t="n">
         <v>4</v>
       </c>
-      <c r="J146" s="22" t="n">
+      <c r="J146" s="25" t="n">
         <v>272</v>
       </c>
-      <c r="K146" s="22" t="n">
+      <c r="K146" s="25" t="n">
         <v>356</v>
       </c>
       <c r="L146" s="8" t="n">
@@ -8769,22 +9779,22 @@
           <t>2026-09-13</t>
         </is>
       </c>
-      <c r="F147" s="22" t="n">
+      <c r="F147" s="25" t="n">
         <v>21300</v>
       </c>
-      <c r="G147" s="22" t="n">
+      <c r="G147" s="25" t="n">
         <v>8100</v>
       </c>
-      <c r="H147" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="22" t="n">
+      <c r="H147" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I147" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="J147" s="22" t="n">
+      <c r="J147" s="25" t="n">
         <v>4760</v>
       </c>
-      <c r="K147" s="22" t="n">
+      <c r="K147" s="25" t="n">
         <v>8440</v>
       </c>
       <c r="L147" s="8" t="n">
@@ -8817,22 +9827,22 @@
           <t>2026-09-09</t>
         </is>
       </c>
-      <c r="F148" s="22" t="n">
+      <c r="F148" s="25" t="n">
         <v>16800</v>
       </c>
-      <c r="G148" s="22" t="n">
+      <c r="G148" s="25" t="n">
         <v>6700</v>
       </c>
-      <c r="H148" s="22" t="n">
+      <c r="H148" s="25" t="n">
         <v>1200</v>
       </c>
-      <c r="I148" s="22" t="n">
+      <c r="I148" s="25" t="n">
         <v>44</v>
       </c>
-      <c r="J148" s="22" t="n">
+      <c r="J148" s="25" t="n">
         <v>2992</v>
       </c>
-      <c r="K148" s="22" t="n">
+      <c r="K148" s="25" t="n">
         <v>5908</v>
       </c>
       <c r="L148" s="8" t="n">
@@ -8865,22 +9875,22 @@
           <t>2026-09-06</t>
         </is>
       </c>
-      <c r="F149" s="22" t="n">
+      <c r="F149" s="25" t="n">
         <v>38500</v>
       </c>
-      <c r="G149" s="22" t="n">
+      <c r="G149" s="25" t="n">
         <v>15600</v>
       </c>
-      <c r="H149" s="22" t="n">
+      <c r="H149" s="25" t="n">
         <v>4800</v>
       </c>
-      <c r="I149" s="22" t="n">
+      <c r="I149" s="25" t="n">
         <v>92</v>
       </c>
-      <c r="J149" s="22" t="n">
+      <c r="J149" s="25" t="n">
         <v>6256</v>
       </c>
-      <c r="K149" s="22" t="n">
+      <c r="K149" s="25" t="n">
         <v>11844</v>
       </c>
       <c r="L149" s="8" t="n">
@@ -8913,22 +9923,22 @@
           <t>2026-09-27</t>
         </is>
       </c>
-      <c r="F150" s="22" t="n">
+      <c r="F150" s="25" t="n">
         <v>13400</v>
       </c>
-      <c r="G150" s="22" t="n">
+      <c r="G150" s="25" t="n">
         <v>3900</v>
       </c>
-      <c r="H150" s="22" t="n">
+      <c r="H150" s="25" t="n">
         <v>1100</v>
       </c>
-      <c r="I150" s="22" t="n">
+      <c r="I150" s="25" t="n">
         <v>48</v>
       </c>
-      <c r="J150" s="22" t="n">
+      <c r="J150" s="25" t="n">
         <v>3264</v>
       </c>
-      <c r="K150" s="22" t="n">
+      <c r="K150" s="25" t="n">
         <v>5136</v>
       </c>
       <c r="L150" s="8" t="n">
@@ -8961,22 +9971,22 @@
           <t>2026-09-07</t>
         </is>
       </c>
-      <c r="F151" s="22" t="n">
+      <c r="F151" s="25" t="n">
         <v>19600</v>
       </c>
-      <c r="G151" s="22" t="n">
+      <c r="G151" s="25" t="n">
         <v>9400</v>
       </c>
-      <c r="H151" s="22" t="n">
+      <c r="H151" s="25" t="n">
         <v>2200</v>
       </c>
-      <c r="I151" s="22" t="n">
+      <c r="I151" s="25" t="n">
         <v>36</v>
       </c>
-      <c r="J151" s="22" t="n">
+      <c r="J151" s="25" t="n">
         <v>2448</v>
       </c>
-      <c r="K151" s="22" t="n">
+      <c r="K151" s="25" t="n">
         <v>5552</v>
       </c>
       <c r="L151" s="8" t="n">
@@ -9009,22 +10019,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F152" s="22" t="n">
+      <c r="F152" s="25" t="n">
         <v>3600</v>
       </c>
-      <c r="G152" s="22" t="n">
+      <c r="G152" s="25" t="n">
         <v>80</v>
       </c>
-      <c r="H152" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I152" s="22" t="n">
+      <c r="H152" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I152" s="25" t="n">
         <v>20</v>
       </c>
-      <c r="J152" s="22" t="n">
+      <c r="J152" s="25" t="n">
         <v>1360</v>
       </c>
-      <c r="K152" s="22" t="n">
+      <c r="K152" s="25" t="n">
         <v>2160</v>
       </c>
       <c r="L152" s="8" t="n">
@@ -9057,22 +10067,22 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F153" s="22" t="n">
+      <c r="F153" s="25" t="n">
         <v>2800</v>
       </c>
-      <c r="G153" s="22" t="n">
+      <c r="G153" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H153" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I153" s="22" t="n">
+      <c r="H153" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I153" s="25" t="n">
         <v>16</v>
       </c>
-      <c r="J153" s="22" t="n">
+      <c r="J153" s="25" t="n">
         <v>1088</v>
       </c>
-      <c r="K153" s="22" t="n">
+      <c r="K153" s="25" t="n">
         <v>1652</v>
       </c>
       <c r="L153" s="8" t="n">
@@ -9105,22 +10115,22 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F154" s="22" t="n">
+      <c r="F154" s="25" t="n">
         <v>1700</v>
       </c>
-      <c r="G154" s="22" t="n">
+      <c r="G154" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H154" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="22" t="n">
+      <c r="H154" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I154" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="J154" s="22" t="n">
+      <c r="J154" s="25" t="n">
         <v>612</v>
       </c>
-      <c r="K154" s="22" t="n">
+      <c r="K154" s="25" t="n">
         <v>1058</v>
       </c>
       <c r="L154" s="8" t="n">
@@ -9153,22 +10163,22 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F155" s="22" t="n">
+      <c r="F155" s="25" t="n">
         <v>4100</v>
       </c>
-      <c r="G155" s="22" t="n">
+      <c r="G155" s="25" t="n">
         <v>100</v>
       </c>
-      <c r="H155" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" s="22" t="n">
+      <c r="H155" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I155" s="25" t="n">
         <v>23</v>
       </c>
-      <c r="J155" s="22" t="n">
+      <c r="J155" s="25" t="n">
         <v>1564</v>
       </c>
-      <c r="K155" s="22" t="n">
+      <c r="K155" s="25" t="n">
         <v>2436</v>
       </c>
       <c r="L155" s="8" t="n">
@@ -9201,22 +10211,22 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F156" s="22" t="n">
+      <c r="F156" s="25" t="n">
         <v>3400</v>
       </c>
-      <c r="G156" s="22" t="n">
+      <c r="G156" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H156" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" s="22" t="n">
+      <c r="H156" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I156" s="25" t="n">
         <v>19</v>
       </c>
-      <c r="J156" s="22" t="n">
+      <c r="J156" s="25" t="n">
         <v>1292</v>
       </c>
-      <c r="K156" s="22" t="n">
+      <c r="K156" s="25" t="n">
         <v>2038</v>
       </c>
       <c r="L156" s="8" t="n">
@@ -9249,22 +10259,22 @@
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="F157" s="22" t="n">
+      <c r="F157" s="25" t="n">
         <v>2400</v>
       </c>
-      <c r="G157" s="22" t="n">
+      <c r="G157" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H157" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="22" t="n">
+      <c r="H157" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I157" s="25" t="n">
         <v>14</v>
       </c>
-      <c r="J157" s="22" t="n">
+      <c r="J157" s="25" t="n">
         <v>952</v>
       </c>
-      <c r="K157" s="22" t="n">
+      <c r="K157" s="25" t="n">
         <v>1398</v>
       </c>
       <c r="L157" s="8" t="n">
@@ -9297,22 +10307,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F158" s="22" t="n">
+      <c r="F158" s="25" t="n">
         <v>4200</v>
       </c>
-      <c r="G158" s="22" t="n">
+      <c r="G158" s="25" t="n">
         <v>90</v>
       </c>
-      <c r="H158" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" s="22" t="n">
+      <c r="H158" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I158" s="25" t="n">
         <v>24</v>
       </c>
-      <c r="J158" s="22" t="n">
+      <c r="J158" s="25" t="n">
         <v>1632</v>
       </c>
-      <c r="K158" s="22" t="n">
+      <c r="K158" s="25" t="n">
         <v>2478</v>
       </c>
       <c r="L158" s="8" t="n">
@@ -9345,22 +10355,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F159" s="22" t="n">
+      <c r="F159" s="25" t="n">
         <v>1600</v>
       </c>
-      <c r="G159" s="22" t="n">
+      <c r="G159" s="25" t="n">
         <v>30</v>
       </c>
-      <c r="H159" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="22" t="n">
+      <c r="H159" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I159" s="25" t="n">
         <v>9</v>
       </c>
-      <c r="J159" s="22" t="n">
+      <c r="J159" s="25" t="n">
         <v>612</v>
       </c>
-      <c r="K159" s="22" t="n">
+      <c r="K159" s="25" t="n">
         <v>958</v>
       </c>
       <c r="L159" s="8" t="n">
@@ -9393,22 +10403,22 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F160" s="22" t="n">
+      <c r="F160" s="25" t="n">
         <v>3200</v>
       </c>
-      <c r="G160" s="22" t="n">
+      <c r="G160" s="25" t="n">
         <v>60</v>
       </c>
-      <c r="H160" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="22" t="n">
+      <c r="H160" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I160" s="25" t="n">
         <v>18</v>
       </c>
-      <c r="J160" s="22" t="n">
+      <c r="J160" s="25" t="n">
         <v>1224</v>
       </c>
-      <c r="K160" s="22" t="n">
+      <c r="K160" s="25" t="n">
         <v>1916</v>
       </c>
       <c r="L160" s="8" t="n">
@@ -9441,22 +10451,22 @@
           <t>2026-09-08</t>
         </is>
       </c>
-      <c r="F161" s="22" t="n">
+      <c r="F161" s="25" t="n">
         <v>3900</v>
       </c>
-      <c r="G161" s="22" t="n">
+      <c r="G161" s="25" t="n">
         <v>110</v>
       </c>
-      <c r="H161" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="22" t="n">
+      <c r="H161" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I161" s="25" t="n">
         <v>22</v>
       </c>
-      <c r="J161" s="22" t="n">
+      <c r="J161" s="25" t="n">
         <v>1496</v>
       </c>
-      <c r="K161" s="22" t="n">
+      <c r="K161" s="25" t="n">
         <v>2294</v>
       </c>
       <c r="L161" s="8" t="n">
@@ -9471,7 +10481,7 @@
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Southbank café group</t>
+          <t>Southbank cafe group</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
@@ -9489,22 +10499,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F162" s="22" t="n">
+      <c r="F162" s="25" t="n">
         <v>1800</v>
       </c>
-      <c r="G162" s="22" t="n">
+      <c r="G162" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H162" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="22" t="n">
+      <c r="H162" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I162" s="25" t="n">
         <v>10</v>
       </c>
-      <c r="J162" s="22" t="n">
+      <c r="J162" s="25" t="n">
         <v>680</v>
       </c>
-      <c r="K162" s="22" t="n">
+      <c r="K162" s="25" t="n">
         <v>1080</v>
       </c>
       <c r="L162" s="8" t="n">
@@ -9537,22 +10547,22 @@
           <t>2026-09-03</t>
         </is>
       </c>
-      <c r="F163" s="22" t="n">
+      <c r="F163" s="25" t="n">
         <v>3000</v>
       </c>
-      <c r="G163" s="22" t="n">
+      <c r="G163" s="25" t="n">
         <v>70</v>
       </c>
-      <c r="H163" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="22" t="n">
+      <c r="H163" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I163" s="25" t="n">
         <v>17</v>
       </c>
-      <c r="J163" s="22" t="n">
+      <c r="J163" s="25" t="n">
         <v>1156</v>
       </c>
-      <c r="K163" s="22" t="n">
+      <c r="K163" s="25" t="n">
         <v>1774</v>
       </c>
       <c r="L163" s="8" t="n">
@@ -9585,22 +10595,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F164" s="22" t="n">
+      <c r="F164" s="25" t="n">
         <v>2600</v>
       </c>
-      <c r="G164" s="22" t="n">
+      <c r="G164" s="25" t="n">
         <v>50</v>
       </c>
-      <c r="H164" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="22" t="n">
+      <c r="H164" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I164" s="25" t="n">
         <v>15</v>
       </c>
-      <c r="J164" s="22" t="n">
+      <c r="J164" s="25" t="n">
         <v>1020</v>
       </c>
-      <c r="K164" s="22" t="n">
+      <c r="K164" s="25" t="n">
         <v>1530</v>
       </c>
       <c r="L164" s="8" t="n">
@@ -9633,22 +10643,22 @@
           <t>2026-08-26</t>
         </is>
       </c>
-      <c r="F165" s="22" t="n">
+      <c r="F165" s="25" t="n">
         <v>2200</v>
       </c>
-      <c r="G165" s="22" t="n">
+      <c r="G165" s="25" t="n">
         <v>40</v>
       </c>
-      <c r="H165" s="22" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="22" t="n">
+      <c r="H165" s="25" t="n">
+        <v>0</v>
+      </c>
+      <c r="I165" s="25" t="n">
         <v>12</v>
       </c>
-      <c r="J165" s="22" t="n">
+      <c r="J165" s="25" t="n">
         <v>816</v>
       </c>
-      <c r="K165" s="22" t="n">
+      <c r="K165" s="25" t="n">
         <v>1344</v>
       </c>
       <c r="L165" s="8" t="n">
@@ -9661,7 +10671,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9696,36 +10706,36 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="24" t="inlineStr">
+      <c r="A5" s="27" t="inlineStr">
         <is>
           <t>What it is</t>
         </is>
       </c>
-      <c r="B5" s="25" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>An electrical and air-conditioning contractor in Brisbane: maintenance contracts, installations and call-outs. 7 technicians, 3 office staff.</t>
         </is>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="24" t="inlineStr">
+      <c r="A6" s="27" t="inlineStr">
         <is>
           <t>Reporting month</t>
         </is>
       </c>
-      <c r="B6" s="25" t="inlineStr">
+      <c r="B6" s="28" t="inlineStr">
         <is>
           <t>September 2026 (the last closed month), compared with August 2026</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="27" t="inlineStr">
         <is>
           <t>Financial year</t>
         </is>
       </c>
-      <c r="B7" s="25" t="inlineStr">
+      <c r="B7" s="28" t="inlineStr">
         <is>
           <t>FY2027: 1 July 2026 to 30 June 2027</t>
         </is>
@@ -9739,48 +10749,48 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="24" t="inlineStr">
+      <c r="A10" s="27" t="inlineStr">
         <is>
           <t>Maintenance contracts</t>
         </is>
       </c>
-      <c r="B10" s="25" t="inlineStr">
+      <c r="B10" s="28" t="inlineStr">
         <is>
           <t>14 customers, invoiced on the 1st, paid in about 30 days</t>
         </is>
       </c>
     </row>
     <row r="11">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="27" t="inlineStr">
         <is>
           <t>Installations</t>
         </is>
       </c>
-      <c r="B11" s="25" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>6 named jobs, each with its own quote, materials, subcontractors and hours</t>
         </is>
       </c>
     </row>
     <row r="12">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="27" t="inlineStr">
         <is>
           <t>Call-outs</t>
         </is>
       </c>
-      <c r="B12" s="25" t="inlineStr">
+      <c r="B12" s="28" t="inlineStr">
         <is>
           <t>64 jobs at $145/hour plus materials marked up 30%</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" s="24" t="inlineStr">
+      <c r="A13" s="27" t="inlineStr">
         <is>
           <t>Jobs in September</t>
         </is>
       </c>
-      <c r="B13" s="25" t="inlineStr">
+      <c r="B13" s="28" t="inlineStr">
         <is>
           <t>84 in total (every one is in the Excel download and CSV)</t>
         </is>
@@ -9794,60 +10804,60 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="27" t="inlineStr">
         <is>
           <t>Technicians</t>
         </is>
       </c>
-      <c r="B16" s="25" t="inlineStr">
+      <c r="B16" s="28" t="inlineStr">
         <is>
           <t>7 on salary: $54,600 a month incl. super</t>
         </is>
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="27" t="inlineStr">
         <is>
           <t>Job costing rate</t>
         </is>
       </c>
-      <c r="B17" s="25" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>$68/hour for technician time charged to a job</t>
         </is>
       </c>
     </row>
     <row r="18">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="27" t="inlineStr">
         <is>
           <t>Working days</t>
         </is>
       </c>
-      <c r="B18" s="25" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>20 in August (Ekka show holiday), 22 in September; 7.6 hours a day</t>
         </is>
       </c>
     </row>
     <row r="19">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="27" t="inlineStr">
         <is>
           <t>Overheads</t>
         </is>
       </c>
-      <c r="B19" s="25" t="inlineStr">
+      <c r="B19" s="28" t="inlineStr">
         <is>
           <t>set month by month, as shown in the P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="27" t="inlineStr">
         <is>
           <t>Income tax</t>
         </is>
       </c>
-      <c r="B20" s="25" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>25% of profit, provided monthly; next PAYG instalment due October</t>
         </is>
@@ -9861,60 +10871,60 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="27" t="inlineStr">
         <is>
           <t>Customer payments</t>
         </is>
       </c>
-      <c r="B23" s="25" t="inlineStr">
+      <c r="B23" s="28" t="inlineStr">
         <is>
           <t>each invoice is paid on its own date; unpaid invoices at month end = debtors</t>
         </is>
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="27" t="inlineStr">
         <is>
           <t>Supplier bills</t>
         </is>
       </c>
-      <c r="B24" s="25" t="inlineStr">
+      <c r="B24" s="28" t="inlineStr">
         <is>
           <t>materials and subcontractors are paid the following month</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="27" t="inlineStr">
         <is>
           <t>Equipment finance</t>
         </is>
       </c>
-      <c r="B25" s="25" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>$5,000 repaid each month</t>
         </is>
       </c>
     </row>
     <row r="26">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="27" t="inlineStr">
         <is>
           <t>New equipment</t>
         </is>
       </c>
-      <c r="B26" s="25" t="inlineStr">
+      <c r="B26" s="28" t="inlineStr">
         <is>
           <t>a $12,000 trailer bought in September</t>
         </is>
       </c>
     </row>
     <row r="27">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="27" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B27" s="25" t="inlineStr">
+      <c r="B27" s="28" t="inlineStr">
         <is>
           <t>excluded throughout, for simplicity</t>
         </is>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -16,7 +16,11 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'PandL'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'Jobs'!$A$4:$L$165</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Jobs'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -543,7 +547,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -568,6 +572,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -629,11 +640,11 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Wacol warehouse switchboard</t>
+          <t>Bulimba EV chargers</t>
         </is>
       </c>
       <c r="B9" s="8" t="n">
-        <v>13.5</v>
+        <v>45.2</v>
       </c>
     </row>
     <row r="10">
@@ -649,11 +660,11 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Carindale solar and battery</t>
+          <t>Chermside clinic cabling</t>
         </is>
       </c>
       <c r="B11" s="8" t="n">
-        <v>26.9</v>
+        <v>36.6</v>
       </c>
     </row>
     <row r="12">
@@ -669,21 +680,21 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Bulimba EV chargers</t>
+          <t>Carindale solar and battery</t>
         </is>
       </c>
       <c r="B13" s="8" t="n">
-        <v>45.2</v>
+        <v>26.9</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Chermside clinic cabling</t>
+          <t>Wacol warehouse switchboard</t>
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>36.6</v>
+        <v>13.5</v>
       </c>
     </row>
     <row r="15">
@@ -697,7 +708,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -730,6 +751,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1165,8 +1193,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1199,6 +1236,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1532,8 +1576,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1566,6 +1619,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="10" t="inlineStr">
         <is>
@@ -1831,8 +1891,17 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" fitToWidth="1"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -1840,7 +1909,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:C104"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -1864,6 +1933,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="4" t="inlineStr">
         <is>
@@ -1916,12 +1992,12 @@
       </c>
       <c r="B8" s="22" t="inlineStr">
         <is>
-          <t>$-64,860</t>
+          <t>($64,860)</t>
         </is>
       </c>
       <c r="C8" s="22" t="inlineStr">
         <is>
-          <t>$-51,530</t>
+          <t>($51,530)</t>
         </is>
       </c>
     </row>
@@ -1933,12 +2009,12 @@
       </c>
       <c r="B9" s="22" t="inlineStr">
         <is>
-          <t>$-13,200</t>
+          <t>($13,200)</t>
         </is>
       </c>
       <c r="C9" s="22" t="inlineStr">
         <is>
-          <t>$-9,300</t>
+          <t>($9,300)</t>
         </is>
       </c>
     </row>
@@ -1950,12 +2026,12 @@
       </c>
       <c r="B10" s="22" t="inlineStr">
         <is>
-          <t>$-54,600</t>
+          <t>($54,600)</t>
         </is>
       </c>
       <c r="C10" s="22" t="inlineStr">
         <is>
-          <t>$-54,600</t>
+          <t>($54,600)</t>
         </is>
       </c>
     </row>
@@ -2200,7 +2276,7 @@
     <row r="35">
       <c r="A35" s="4" t="inlineStr">
         <is>
-          <t>Wacol warehouse switchboard</t>
+          <t>Bulimba EV chargers</t>
         </is>
       </c>
     </row>
@@ -2227,7 +2303,7 @@
       </c>
       <c r="B38" s="22" t="inlineStr">
         <is>
-          <t>4 Sep</t>
+          <t>23 Sep</t>
         </is>
       </c>
     </row>
@@ -2239,7 +2315,7 @@
       </c>
       <c r="B39" s="22" t="inlineStr">
         <is>
-          <t>$46,800</t>
+          <t>$9,800</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2327,7 @@
       </c>
       <c r="B40" s="22" t="inlineStr">
         <is>
-          <t>$-22,900</t>
+          <t>($3,600)</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2339,7 @@
       </c>
       <c r="B41" s="22" t="inlineStr">
         <is>
-          <t>$-7,400</t>
+          <t>$0</t>
         </is>
       </c>
     </row>
@@ -2275,7 +2351,7 @@
       </c>
       <c r="B42" s="22" t="inlineStr">
         <is>
-          <t>150 h × $68 = $-10,200</t>
+          <t>26 h × $68 = ($1,768)</t>
         </is>
       </c>
     </row>
@@ -2287,7 +2363,7 @@
       </c>
       <c r="B43" s="22" t="inlineStr">
         <is>
-          <t>$6,300</t>
+          <t>$4,432</t>
         </is>
       </c>
     </row>
@@ -2299,7 +2375,7 @@
       </c>
       <c r="B44" s="22" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>45.2%</t>
         </is>
       </c>
     </row>
@@ -2357,7 +2433,7 @@
       </c>
       <c r="B52" s="22" t="inlineStr">
         <is>
-          <t>$-6,900</t>
+          <t>($6,900)</t>
         </is>
       </c>
     </row>
@@ -2381,7 +2457,7 @@
       </c>
       <c r="B54" s="22" t="inlineStr">
         <is>
-          <t>64 h × $68 = $-4,352</t>
+          <t>64 h × $68 = ($4,352)</t>
         </is>
       </c>
     </row>
@@ -2412,7 +2488,7 @@
     <row r="59">
       <c r="A59" s="4" t="inlineStr">
         <is>
-          <t>Carindale solar and battery</t>
+          <t>Chermside clinic cabling</t>
         </is>
       </c>
     </row>
@@ -2439,7 +2515,7 @@
       </c>
       <c r="B62" s="22" t="inlineStr">
         <is>
-          <t>15 Sep</t>
+          <t>29 Sep</t>
         </is>
       </c>
     </row>
@@ -2451,7 +2527,7 @@
       </c>
       <c r="B63" s="22" t="inlineStr">
         <is>
-          <t>$27,400</t>
+          <t>$15,200</t>
         </is>
       </c>
     </row>
@@ -2463,7 +2539,7 @@
       </c>
       <c r="B64" s="22" t="inlineStr">
         <is>
-          <t>$-13,800</t>
+          <t>($4,300)</t>
         </is>
       </c>
     </row>
@@ -2475,7 +2551,7 @@
       </c>
       <c r="B65" s="22" t="inlineStr">
         <is>
-          <t>$-3,100</t>
+          <t>($1,800)</t>
         </is>
       </c>
     </row>
@@ -2487,7 +2563,7 @@
       </c>
       <c r="B66" s="22" t="inlineStr">
         <is>
-          <t>46 h × $68 = $-3,128</t>
+          <t>52 h × $68 = ($3,536)</t>
         </is>
       </c>
     </row>
@@ -2499,7 +2575,7 @@
       </c>
       <c r="B67" s="22" t="inlineStr">
         <is>
-          <t>$7,372</t>
+          <t>$5,564</t>
         </is>
       </c>
     </row>
@@ -2511,7 +2587,7 @@
       </c>
       <c r="B68" s="22" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>36.6%</t>
         </is>
       </c>
     </row>
@@ -2569,7 +2645,7 @@
       </c>
       <c r="B76" s="22" t="inlineStr">
         <is>
-          <t>$-5,100</t>
+          <t>($5,100)</t>
         </is>
       </c>
     </row>
@@ -2581,7 +2657,7 @@
       </c>
       <c r="B77" s="22" t="inlineStr">
         <is>
-          <t>$-900</t>
+          <t>($900)</t>
         </is>
       </c>
     </row>
@@ -2593,7 +2669,7 @@
       </c>
       <c r="B78" s="22" t="inlineStr">
         <is>
-          <t>38 h × $68 = $-2,584</t>
+          <t>38 h × $68 = ($2,584)</t>
         </is>
       </c>
     </row>
@@ -2624,7 +2700,7 @@
     <row r="83">
       <c r="A83" s="4" t="inlineStr">
         <is>
-          <t>Bulimba EV chargers</t>
+          <t>Carindale solar and battery</t>
         </is>
       </c>
     </row>
@@ -2651,7 +2727,7 @@
       </c>
       <c r="B86" s="22" t="inlineStr">
         <is>
-          <t>23 Sep</t>
+          <t>15 Sep</t>
         </is>
       </c>
     </row>
@@ -2663,7 +2739,7 @@
       </c>
       <c r="B87" s="22" t="inlineStr">
         <is>
-          <t>$9,800</t>
+          <t>$27,400</t>
         </is>
       </c>
     </row>
@@ -2675,7 +2751,7 @@
       </c>
       <c r="B88" s="22" t="inlineStr">
         <is>
-          <t>$-3,600</t>
+          <t>($13,800)</t>
         </is>
       </c>
     </row>
@@ -2687,7 +2763,7 @@
       </c>
       <c r="B89" s="22" t="inlineStr">
         <is>
-          <t>$0</t>
+          <t>($3,100)</t>
         </is>
       </c>
     </row>
@@ -2699,7 +2775,7 @@
       </c>
       <c r="B90" s="22" t="inlineStr">
         <is>
-          <t>26 h × $68 = $-1,768</t>
+          <t>46 h × $68 = ($3,128)</t>
         </is>
       </c>
     </row>
@@ -2711,7 +2787,7 @@
       </c>
       <c r="B91" s="22" t="inlineStr">
         <is>
-          <t>$4,432</t>
+          <t>$7,372</t>
         </is>
       </c>
     </row>
@@ -2723,14 +2799,14 @@
       </c>
       <c r="B92" s="22" t="inlineStr">
         <is>
-          <t>45.2%</t>
+          <t>26.9%</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" s="4" t="inlineStr">
         <is>
-          <t>Chermside clinic cabling</t>
+          <t>Wacol warehouse switchboard</t>
         </is>
       </c>
     </row>
@@ -2757,7 +2833,7 @@
       </c>
       <c r="B98" s="22" t="inlineStr">
         <is>
-          <t>29 Sep</t>
+          <t>4 Sep</t>
         </is>
       </c>
     </row>
@@ -2769,7 +2845,7 @@
       </c>
       <c r="B99" s="22" t="inlineStr">
         <is>
-          <t>$15,200</t>
+          <t>$46,800</t>
         </is>
       </c>
     </row>
@@ -2781,7 +2857,7 @@
       </c>
       <c r="B100" s="22" t="inlineStr">
         <is>
-          <t>$-4,300</t>
+          <t>($22,900)</t>
         </is>
       </c>
     </row>
@@ -2793,7 +2869,7 @@
       </c>
       <c r="B101" s="22" t="inlineStr">
         <is>
-          <t>$-1,800</t>
+          <t>($7,400)</t>
         </is>
       </c>
     </row>
@@ -2805,7 +2881,7 @@
       </c>
       <c r="B102" s="22" t="inlineStr">
         <is>
-          <t>52 h × $68 = $-3,536</t>
+          <t>150 h × $68 = ($10,200)</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2893,7 @@
       </c>
       <c r="B103" s="22" t="inlineStr">
         <is>
-          <t>$5,564</t>
+          <t>$6,300</t>
         </is>
       </c>
     </row>
@@ -2829,12 +2905,22 @@
       </c>
       <c r="B104" s="22" t="inlineStr">
         <is>
-          <t>36.6%</t>
+          <t>13.5%</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -2842,7 +2928,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:L165"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -2875,6 +2961,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="23" t="inlineStr">
         <is>
@@ -10667,7 +10760,17 @@
     </row>
   </sheetData>
   <autoFilter ref="A4:L165"/>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
 
@@ -10675,7 +10778,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
+    <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:B35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
@@ -10698,6 +10801,13 @@
         </is>
       </c>
     </row>
+    <row r="3">
+      <c r="A3" s="2" t="inlineStr">
+        <is>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (as at 2pm, Tue 6 Oct 2026)</t>
+        </is>
+      </c>
+    </row>
     <row r="4">
       <c r="A4" s="12" t="inlineStr">
         <is>
@@ -10980,6 +11090,16 @@
       </c>
     </row>
   </sheetData>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.6" bottom="0.7" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <headerFooter>
+    <oddHeader>&amp;R&amp;8 Printed 6 Oct 2026</oddHeader>
+    <oddFooter>&amp;L&amp;8 The 4th Sheet · Sample data&amp;C&amp;8 Sep 2026 locked · Oct 2026 incomplete · as at 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <evenHeader/>
+    <evenFooter/>
+    <firstHeader/>
+    <firstFooter/>
+  </headerFooter>
 </worksheet>
 </file>
--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -611,7 +611,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Gross margin (P&amp;L)</t>
         </is>
       </c>
       <c r="B6" s="5">
@@ -670,14 +670,14 @@
     <row r="11">
       <c r="A11" s="7" t="inlineStr">
         <is>
-          <t>Margin on each installation job invoiced in September 2026</t>
+          <t>Job gross margin on each installation invoiced in September 2026</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Whole job, recognised when invoiced: revenue less materials, subcontractors and technician time at $68/hour. One 35.0% target for every job for now.</t>
+          <t>Whole job, recognised when invoiced: revenue less materials, subcontractors and technician time at $68/hour. Before overheads: not profit. One 35.0% target for every job for now.</t>
         </is>
       </c>
     </row>
@@ -685,12 +685,12 @@
       <c r="A13" s="3" t="inlineStr"/>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Gross margin %</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>Gross profit $</t>
+          <t>Gross margin $</t>
         </is>
       </c>
     </row>
@@ -988,7 +988,7 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Technician wages (incl. super)</t>
+          <t>Technician wages (incl. on-costs)</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
@@ -2075,7 +2075,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Technician cost rate ($ per hour)</t>
+          <t>Technician cost rate ($ per hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
@@ -2131,17 +2131,17 @@
       </c>
       <c r="J6" s="4" t="inlineStr">
         <is>
-          <t>Labour cost</t>
+          <t>Labour cost (incl. on-costs)</t>
         </is>
       </c>
       <c r="K6" s="4" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="L6" s="4" t="inlineStr">
         <is>
-          <t>Margin %</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
     </row>
@@ -9757,10 +9757,10 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="40" min="0" max="16383" man="1"/>
-    <brk id="80" min="0" max="16383" man="1"/>
+    <brk id="39" min="0" max="16383" man="1"/>
+    <brk id="78" min="0" max="16383" man="1"/>
     <brk id="90" min="0" max="16383" man="1"/>
-    <brk id="130" min="0" max="16383" man="1"/>
+    <brk id="129" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -9805,14 +9805,14 @@
     <row r="5">
       <c r="A5" s="26" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Gross margin (P&amp;L)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue</t>
+          <t>Gross profit ÷ revenue. All technician wages and on-costs included; overheads are not.</t>
         </is>
       </c>
     </row>
@@ -9899,7 +9899,7 @@
     <row r="13">
       <c r="A13" s="27" t="inlineStr">
         <is>
-          <t>Gross margin</t>
+          <t>Gross margin (P&amp;L)</t>
         </is>
       </c>
       <c r="B13" s="28">
@@ -9914,7 +9914,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Technicians are on salary, so a quiet month for jobs lowers the margin even if every job is priced well.</t>
+          <t>Gross margin is before overheads (office wages, marketing, vehicles, rent and so on): it is not profit. Wages include all on-costs (super, payroll tax, workers' compensation, leave). Technicians are on salary, so a quiet month for jobs lowers gross margin even if every job is priced well.</t>
         </is>
       </c>
     </row>
@@ -10118,7 +10118,7 @@
     <row r="38">
       <c r="A38" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10173,7 +10173,7 @@
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B44" s="20" t="n">
@@ -10194,7 +10194,7 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B46" s="20">
@@ -10205,7 +10205,7 @@
     <row r="47">
       <c r="A47" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B47" s="28">
@@ -10225,7 +10225,7 @@
     <row r="51">
       <c r="A51" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10280,7 +10280,7 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B57" s="20" t="n">
@@ -10301,7 +10301,7 @@
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B59" s="20">
@@ -10312,7 +10312,7 @@
     <row r="60">
       <c r="A60" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B60" s="28">
@@ -10332,7 +10332,7 @@
     <row r="64">
       <c r="A64" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10387,7 +10387,7 @@
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B70" s="20" t="n">
@@ -10408,7 +10408,7 @@
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B72" s="20">
@@ -10419,7 +10419,7 @@
     <row r="73">
       <c r="A73" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B73" s="28">
@@ -10439,7 +10439,7 @@
     <row r="77">
       <c r="A77" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10494,7 +10494,7 @@
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B83" s="20" t="n">
@@ -10515,7 +10515,7 @@
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B85" s="20">
@@ -10526,7 +10526,7 @@
     <row r="86">
       <c r="A86" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B86" s="28">
@@ -10546,7 +10546,7 @@
     <row r="90">
       <c r="A90" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10601,7 +10601,7 @@
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B96" s="20" t="n">
@@ -10622,7 +10622,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B98" s="20">
@@ -10633,7 +10633,7 @@
     <row r="99">
       <c r="A99" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B99" s="28">
@@ -10653,7 +10653,7 @@
     <row r="103">
       <c r="A103" s="8" t="inlineStr">
         <is>
-          <t>Gross profit ÷ revenue for this job</t>
+          <t>Job gross margin ÷ revenue for this job (before overheads)</t>
         </is>
       </c>
     </row>
@@ -10708,7 +10708,7 @@
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Technician cost rate ($/hour)</t>
+          <t>Technician cost rate ($/hour, wages and all on-costs)</t>
         </is>
       </c>
       <c r="B109" s="20" t="n">
@@ -10729,7 +10729,7 @@
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Job gross margin</t>
         </is>
       </c>
       <c r="B111" s="20">
@@ -10740,7 +10740,7 @@
     <row r="112">
       <c r="A112" s="27" t="inlineStr">
         <is>
-          <t>Margin</t>
+          <t>Job gross margin %</t>
         </is>
       </c>
       <c r="B112" s="28">
@@ -10922,7 +10922,7 @@
       </c>
       <c r="B17" s="31" t="inlineStr">
         <is>
-          <t>7 on salary: $54,600 a month incl. super</t>
+          <t>7 on salary: $54,600 a month incl. on-costs</t>
         </is>
       </c>
     </row>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -20,7 +20,7 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Profit and loss'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Jobs'!$A$6:$L$167</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Jobs'!$A$6:$N$167</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Jobs'!$6:$6</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -815,7 +815,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D30"/>
+  <dimension ref="A1:D31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -911,14 +911,14 @@
     <row r="8">
       <c r="A8" s="10" t="inlineStr">
         <is>
-          <t>Call-outs and repairs</t>
+          <t>Call-outs: technician time</t>
         </is>
       </c>
       <c r="B8" s="6" t="n">
-        <v>31137</v>
+        <v>21543</v>
       </c>
       <c r="C8" s="6" t="n">
-        <v>28907</v>
+        <v>19872</v>
       </c>
       <c r="D8" s="11">
         <f>B8-C8</f>
@@ -926,59 +926,59 @@
       </c>
     </row>
     <row r="9">
-      <c r="A9" s="12" t="inlineStr">
+      <c r="A9" s="10" t="inlineStr">
+        <is>
+          <t>Call-outs: materials charged</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>9594</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>9035</v>
+      </c>
+      <c r="D9" s="11">
+        <f>B9-C9</f>
+        <v/>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="12" t="inlineStr">
         <is>
           <t>Total revenue</t>
         </is>
       </c>
-      <c r="B9" s="13">
-        <f>SUM(B6:B8)</f>
-        <v/>
-      </c>
-      <c r="C9" s="13">
-        <f>SUM(C6:C8)</f>
-        <v/>
-      </c>
-      <c r="D9" s="14">
-        <f>B9-C9</f>
-        <v/>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" s="9" t="inlineStr">
+      <c r="B10" s="13">
+        <f>SUM(B6:B9)</f>
+        <v/>
+      </c>
+      <c r="C10" s="13">
+        <f>SUM(C6:C9)</f>
+        <v/>
+      </c>
+      <c r="D10" s="14">
+        <f>B10-C10</f>
+        <v/>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>Cost of sales</t>
         </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" s="10" t="inlineStr">
-        <is>
-          <t>Materials</t>
-        </is>
-      </c>
-      <c r="B11" s="6" t="n">
-        <v>-64860</v>
-      </c>
-      <c r="C11" s="6" t="n">
-        <v>-51530</v>
-      </c>
-      <c r="D11" s="11">
-        <f>B11-C11</f>
-        <v/>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="10" t="inlineStr">
         <is>
-          <t>Subcontractors</t>
+          <t>Materials</t>
         </is>
       </c>
       <c r="B12" s="6" t="n">
-        <v>-13200</v>
+        <v>-64860</v>
       </c>
       <c r="C12" s="6" t="n">
-        <v>-9300</v>
+        <v>-51530</v>
       </c>
       <c r="D12" s="11">
         <f>B12-C12</f>
@@ -988,14 +988,14 @@
     <row r="13">
       <c r="A13" s="10" t="inlineStr">
         <is>
-          <t>Technician wages (incl. on-costs)</t>
+          <t>Subcontractors</t>
         </is>
       </c>
       <c r="B13" s="6" t="n">
-        <v>-54600</v>
+        <v>-13200</v>
       </c>
       <c r="C13" s="6" t="n">
-        <v>-54600</v>
+        <v>-9300</v>
       </c>
       <c r="D13" s="11">
         <f>B13-C13</f>
@@ -1003,20 +1003,18 @@
       </c>
     </row>
     <row r="14">
-      <c r="A14" s="12" t="inlineStr">
-        <is>
-          <t>Total cost of sales</t>
-        </is>
-      </c>
-      <c r="B14" s="13">
-        <f>SUM(B11:B13)</f>
-        <v/>
-      </c>
-      <c r="C14" s="13">
-        <f>SUM(C11:C13)</f>
-        <v/>
-      </c>
-      <c r="D14" s="14">
+      <c r="A14" s="10" t="inlineStr">
+        <is>
+          <t>Technician wages (incl. on-costs)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>-54600</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>-54600</v>
+      </c>
+      <c r="D14" s="11">
         <f>B14-C14</f>
         <v/>
       </c>
@@ -1024,15 +1022,15 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Gross profit</t>
+          <t>Total cost of sales</t>
         </is>
       </c>
       <c r="B15" s="13">
-        <f>B9+B14</f>
+        <f>SUM(B12:B14)</f>
         <v/>
       </c>
       <c r="C15" s="13">
-        <f>C9+C14</f>
+        <f>SUM(C12:C14)</f>
         <v/>
       </c>
       <c r="D15" s="14">
@@ -1041,40 +1039,42 @@
       </c>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>Gross profit</t>
+        </is>
+      </c>
+      <c r="B16" s="13">
+        <f>B10+B15</f>
+        <v/>
+      </c>
+      <c r="C16" s="13">
+        <f>C10+C15</f>
+        <v/>
+      </c>
+      <c r="D16" s="14">
+        <f>B16-C16</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>Operating expenses</t>
         </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="10" t="inlineStr">
-        <is>
-          <t>Office and admin wages</t>
-        </is>
-      </c>
-      <c r="B17" s="6" t="n">
-        <v>-21900</v>
-      </c>
-      <c r="C17" s="6" t="n">
-        <v>-21900</v>
-      </c>
-      <c r="D17" s="11">
-        <f>B17-C17</f>
-        <v/>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>Marketing</t>
+          <t>Office and admin wages</t>
         </is>
       </c>
       <c r="B18" s="6" t="n">
-        <v>-7600</v>
+        <v>-21900</v>
       </c>
       <c r="C18" s="6" t="n">
-        <v>-8400</v>
+        <v>-21900</v>
       </c>
       <c r="D18" s="11">
         <f>B18-C18</f>
@@ -1084,14 +1084,14 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>Vehicles and fuel</t>
+          <t>Marketing</t>
         </is>
       </c>
       <c r="B19" s="6" t="n">
-        <v>-8300</v>
+        <v>-7600</v>
       </c>
       <c r="C19" s="6" t="n">
-        <v>-7900</v>
+        <v>-8400</v>
       </c>
       <c r="D19" s="11">
         <f>B19-C19</f>
@@ -1101,14 +1101,14 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>Rent and occupancy</t>
+          <t>Vehicles and fuel</t>
         </is>
       </c>
       <c r="B20" s="6" t="n">
-        <v>-7000</v>
+        <v>-8300</v>
       </c>
       <c r="C20" s="6" t="n">
-        <v>-7000</v>
+        <v>-7900</v>
       </c>
       <c r="D20" s="11">
         <f>B20-C20</f>
@@ -1118,14 +1118,14 @@
     <row r="21">
       <c r="A21" s="10" t="inlineStr">
         <is>
-          <t>Insurance</t>
+          <t>Rent and occupancy</t>
         </is>
       </c>
       <c r="B21" s="6" t="n">
-        <v>-3000</v>
+        <v>-7000</v>
       </c>
       <c r="C21" s="6" t="n">
-        <v>-3000</v>
+        <v>-7000</v>
       </c>
       <c r="D21" s="11">
         <f>B21-C21</f>
@@ -1135,14 +1135,14 @@
     <row r="22">
       <c r="A22" s="10" t="inlineStr">
         <is>
-          <t>IT and software</t>
+          <t>Insurance</t>
         </is>
       </c>
       <c r="B22" s="6" t="n">
-        <v>-2300</v>
+        <v>-3000</v>
       </c>
       <c r="C22" s="6" t="n">
-        <v>-2300</v>
+        <v>-3000</v>
       </c>
       <c r="D22" s="11">
         <f>B22-C22</f>
@@ -1152,14 +1152,14 @@
     <row r="23">
       <c r="A23" s="10" t="inlineStr">
         <is>
-          <t>Other overheads</t>
+          <t>IT and software</t>
         </is>
       </c>
       <c r="B23" s="6" t="n">
-        <v>-3900</v>
+        <v>-2300</v>
       </c>
       <c r="C23" s="6" t="n">
-        <v>-3600</v>
+        <v>-2300</v>
       </c>
       <c r="D23" s="11">
         <f>B23-C23</f>
@@ -1167,20 +1167,18 @@
       </c>
     </row>
     <row r="24">
-      <c r="A24" s="12" t="inlineStr">
-        <is>
-          <t>Total operating expenses</t>
-        </is>
-      </c>
-      <c r="B24" s="13">
-        <f>SUM(B17:B23)</f>
-        <v/>
-      </c>
-      <c r="C24" s="13">
-        <f>SUM(C17:C23)</f>
-        <v/>
-      </c>
-      <c r="D24" s="14">
+      <c r="A24" s="10" t="inlineStr">
+        <is>
+          <t>Other overheads</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n">
+        <v>-3900</v>
+      </c>
+      <c r="C24" s="6" t="n">
+        <v>-3600</v>
+      </c>
+      <c r="D24" s="11">
         <f>B24-C24</f>
         <v/>
       </c>
@@ -1188,15 +1186,15 @@
     <row r="25">
       <c r="A25" s="12" t="inlineStr">
         <is>
-          <t>EBITDA</t>
+          <t>Total operating expenses</t>
         </is>
       </c>
       <c r="B25" s="13">
-        <f>B15+B24</f>
+        <f>SUM(B18:B24)</f>
         <v/>
       </c>
       <c r="C25" s="13">
-        <f>C15+C24</f>
+        <f>SUM(C18:C24)</f>
         <v/>
       </c>
       <c r="D25" s="14">
@@ -1207,14 +1205,16 @@
     <row r="26">
       <c r="A26" s="12" t="inlineStr">
         <is>
-          <t>Depreciation</t>
-        </is>
-      </c>
-      <c r="B26" s="13" t="n">
-        <v>-4500</v>
-      </c>
-      <c r="C26" s="13" t="n">
-        <v>-4300</v>
+          <t>EBITDA</t>
+        </is>
+      </c>
+      <c r="B26" s="13">
+        <f>B16+B25</f>
+        <v/>
+      </c>
+      <c r="C26" s="13">
+        <f>C16+C25</f>
+        <v/>
       </c>
       <c r="D26" s="14">
         <f>B26-C26</f>
@@ -1224,14 +1224,14 @@
     <row r="27">
       <c r="A27" s="12" t="inlineStr">
         <is>
-          <t>Interest</t>
+          <t>Depreciation</t>
         </is>
       </c>
       <c r="B27" s="13" t="n">
-        <v>-1080</v>
+        <v>-4500</v>
       </c>
       <c r="C27" s="13" t="n">
-        <v>-1100</v>
+        <v>-4300</v>
       </c>
       <c r="D27" s="14">
         <f>B27-C27</f>
@@ -1241,16 +1241,14 @@
     <row r="28">
       <c r="A28" s="12" t="inlineStr">
         <is>
-          <t>Profit before tax</t>
-        </is>
-      </c>
-      <c r="B28" s="13">
-        <f>B25+B26+B27</f>
-        <v/>
-      </c>
-      <c r="C28" s="13">
-        <f>C25+C26+C27</f>
-        <v/>
+          <t>Interest</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="n">
+        <v>-1080</v>
+      </c>
+      <c r="C28" s="13" t="n">
+        <v>-1100</v>
       </c>
       <c r="D28" s="14">
         <f>B28-C28</f>
@@ -1260,14 +1258,16 @@
     <row r="29">
       <c r="A29" s="12" t="inlineStr">
         <is>
-          <t>Income tax provision (25%)</t>
-        </is>
-      </c>
-      <c r="B29" s="13" t="n">
-        <v>-2524</v>
-      </c>
-      <c r="C29" s="13" t="n">
-        <v>-1019</v>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B29" s="13">
+        <f>B26+B27+B28</f>
+        <v/>
+      </c>
+      <c r="C29" s="13">
+        <f>C26+C27+C28</f>
+        <v/>
       </c>
       <c r="D29" s="14">
         <f>B29-C29</f>
@@ -1275,21 +1275,38 @@
       </c>
     </row>
     <row r="30">
-      <c r="A30" s="15" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>Income tax provision (25%)</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="n">
+        <v>-2524</v>
+      </c>
+      <c r="C30" s="13" t="n">
+        <v>-1019</v>
+      </c>
+      <c r="D30" s="14">
+        <f>B30-C30</f>
+        <v/>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="15" t="inlineStr">
         <is>
           <t>Net profit after tax</t>
         </is>
       </c>
-      <c r="B30" s="16">
-        <f>B28+B29</f>
-        <v/>
-      </c>
-      <c r="C30" s="16">
-        <f>C28+C29</f>
-        <v/>
-      </c>
-      <c r="D30" s="17">
-        <f>B30-C30</f>
+      <c r="B31" s="16">
+        <f>B29+B30</f>
+        <v/>
+      </c>
+      <c r="C31" s="16">
+        <f>C29+C30</f>
+        <v/>
+      </c>
+      <c r="D31" s="17">
+        <f>B31-C31</f>
         <v/>
       </c>
     </row>
@@ -2034,7 +2051,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L168"/>
+  <dimension ref="A1:N168"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -2049,6 +2066,8 @@
     <col width="13" customWidth="1" min="10" max="10"/>
     <col width="13" customWidth="1" min="11" max="11"/>
     <col width="13" customWidth="1" min="12" max="12"/>
+    <col width="13" customWidth="1" min="13" max="13"/>
+    <col width="13" customWidth="1" min="14" max="14"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -2116,30 +2135,40 @@
       </c>
       <c r="G6" s="4" t="inlineStr">
         <is>
+          <t>Technician time charged (call-outs)</t>
+        </is>
+      </c>
+      <c r="H6" s="4" t="inlineStr">
+        <is>
+          <t>Materials charged (call-outs)</t>
+        </is>
+      </c>
+      <c r="I6" s="4" t="inlineStr">
+        <is>
           <t>Materials</t>
         </is>
       </c>
-      <c r="H6" s="4" t="inlineStr">
+      <c r="J6" s="4" t="inlineStr">
         <is>
           <t>Subcontractors</t>
         </is>
       </c>
-      <c r="I6" s="4" t="inlineStr">
+      <c r="K6" s="4" t="inlineStr">
         <is>
           <t>Tech hours</t>
         </is>
       </c>
-      <c r="J6" s="4" t="inlineStr">
+      <c r="L6" s="4" t="inlineStr">
         <is>
           <t>Labour cost (incl. on-costs)</t>
         </is>
       </c>
-      <c r="K6" s="4" t="inlineStr">
+      <c r="M6" s="4" t="inlineStr">
         <is>
           <t>Job gross margin</t>
         </is>
       </c>
-      <c r="L6" s="4" t="inlineStr">
+      <c r="N6" s="4" t="inlineStr">
         <is>
           <t>Job gross margin %</t>
         </is>
@@ -2171,24 +2200,30 @@
         <v>589</v>
       </c>
       <c r="G7" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H7" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I7" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H7" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I7" s="21" t="n">
+      <c r="J7" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K7" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J7" s="20">
-        <f>I7*$B$4</f>
-        <v/>
-      </c>
-      <c r="K7" s="20">
-        <f>F7-G7-H7-J7</f>
-        <v/>
-      </c>
-      <c r="L7" s="22">
-        <f>IF(F7=0,"",K7/F7)</f>
+      <c r="L7" s="20">
+        <f>K7*$B$4</f>
+        <v/>
+      </c>
+      <c r="M7" s="20">
+        <f>F7-I7-J7-L7</f>
+        <v/>
+      </c>
+      <c r="N7" s="22">
+        <f>IF(F7=0,"",M7/F7)</f>
         <v/>
       </c>
     </row>
@@ -2218,24 +2253,30 @@
         <v>539</v>
       </c>
       <c r="G8" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H8" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I8" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H8" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I8" s="21" t="n">
+      <c r="J8" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K8" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J8" s="20">
-        <f>I8*$B$4</f>
-        <v/>
-      </c>
-      <c r="K8" s="20">
-        <f>F8-G8-H8-J8</f>
-        <v/>
-      </c>
-      <c r="L8" s="22">
-        <f>IF(F8=0,"",K8/F8)</f>
+      <c r="L8" s="20">
+        <f>K8*$B$4</f>
+        <v/>
+      </c>
+      <c r="M8" s="20">
+        <f>F8-I8-J8-L8</f>
+        <v/>
+      </c>
+      <c r="N8" s="22">
+        <f>IF(F8=0,"",M8/F8)</f>
         <v/>
       </c>
     </row>
@@ -2265,24 +2306,30 @@
         <v>526</v>
       </c>
       <c r="G9" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H9" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I9" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H9" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I9" s="21" t="n">
+      <c r="J9" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K9" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J9" s="20">
-        <f>I9*$B$4</f>
-        <v/>
-      </c>
-      <c r="K9" s="20">
-        <f>F9-G9-H9-J9</f>
-        <v/>
-      </c>
-      <c r="L9" s="22">
-        <f>IF(F9=0,"",K9/F9)</f>
+      <c r="L9" s="20">
+        <f>K9*$B$4</f>
+        <v/>
+      </c>
+      <c r="M9" s="20">
+        <f>F9-I9-J9-L9</f>
+        <v/>
+      </c>
+      <c r="N9" s="22">
+        <f>IF(F9=0,"",M9/F9)</f>
         <v/>
       </c>
     </row>
@@ -2312,24 +2359,30 @@
         <v>413</v>
       </c>
       <c r="G10" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H10" s="20" t="n">
+        <v>195</v>
+      </c>
+      <c r="I10" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="H10" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I10" s="21" t="n">
+      <c r="J10" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J10" s="20">
-        <f>I10*$B$4</f>
-        <v/>
-      </c>
-      <c r="K10" s="20">
-        <f>F10-G10-H10-J10</f>
-        <v/>
-      </c>
-      <c r="L10" s="22">
-        <f>IF(F10=0,"",K10/F10)</f>
+      <c r="L10" s="20">
+        <f>K10*$B$4</f>
+        <v/>
+      </c>
+      <c r="M10" s="20">
+        <f>F10-I10-J10-L10</f>
+        <v/>
+      </c>
+      <c r="N10" s="22">
+        <f>IF(F10=0,"",M10/F10)</f>
         <v/>
       </c>
     </row>
@@ -2359,24 +2412,30 @@
         <v>775</v>
       </c>
       <c r="G11" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H11" s="20" t="n">
+        <v>195</v>
+      </c>
+      <c r="I11" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="H11" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I11" s="21" t="n">
+      <c r="J11" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K11" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J11" s="20">
-        <f>I11*$B$4</f>
-        <v/>
-      </c>
-      <c r="K11" s="20">
-        <f>F11-G11-H11-J11</f>
-        <v/>
-      </c>
-      <c r="L11" s="22">
-        <f>IF(F11=0,"",K11/F11)</f>
+      <c r="L11" s="20">
+        <f>K11*$B$4</f>
+        <v/>
+      </c>
+      <c r="M11" s="20">
+        <f>F11-I11-J11-L11</f>
+        <v/>
+      </c>
+      <c r="N11" s="22">
+        <f>IF(F11=0,"",M11/F11)</f>
         <v/>
       </c>
     </row>
@@ -2406,24 +2465,30 @@
         <v>348</v>
       </c>
       <c r="G12" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H12" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I12" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H12" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I12" s="21" t="n">
+      <c r="J12" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K12" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J12" s="20">
-        <f>I12*$B$4</f>
-        <v/>
-      </c>
-      <c r="K12" s="20">
-        <f>F12-G12-H12-J12</f>
-        <v/>
-      </c>
-      <c r="L12" s="22">
-        <f>IF(F12=0,"",K12/F12)</f>
+      <c r="L12" s="20">
+        <f>K12*$B$4</f>
+        <v/>
+      </c>
+      <c r="M12" s="20">
+        <f>F12-I12-J12-L12</f>
+        <v/>
+      </c>
+      <c r="N12" s="22">
+        <f>IF(F12=0,"",M12/F12)</f>
         <v/>
       </c>
     </row>
@@ -2453,24 +2518,30 @@
         <v>775</v>
       </c>
       <c r="G13" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H13" s="20" t="n">
+        <v>195</v>
+      </c>
+      <c r="I13" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="H13" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I13" s="21" t="n">
+      <c r="J13" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K13" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J13" s="20">
-        <f>I13*$B$4</f>
-        <v/>
-      </c>
-      <c r="K13" s="20">
-        <f>F13-G13-H13-J13</f>
-        <v/>
-      </c>
-      <c r="L13" s="22">
-        <f>IF(F13=0,"",K13/F13)</f>
+      <c r="L13" s="20">
+        <f>K13*$B$4</f>
+        <v/>
+      </c>
+      <c r="M13" s="20">
+        <f>F13-I13-J13-L13</f>
+        <v/>
+      </c>
+      <c r="N13" s="22">
+        <f>IF(F13=0,"",M13/F13)</f>
         <v/>
       </c>
     </row>
@@ -2500,24 +2571,30 @@
         <v>368</v>
       </c>
       <c r="G14" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H14" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I14" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H14" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I14" s="21" t="n">
+      <c r="J14" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K14" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J14" s="20">
-        <f>I14*$B$4</f>
-        <v/>
-      </c>
-      <c r="K14" s="20">
-        <f>F14-G14-H14-J14</f>
-        <v/>
-      </c>
-      <c r="L14" s="22">
-        <f>IF(F14=0,"",K14/F14)</f>
+      <c r="L14" s="20">
+        <f>K14*$B$4</f>
+        <v/>
+      </c>
+      <c r="M14" s="20">
+        <f>F14-I14-J14-L14</f>
+        <v/>
+      </c>
+      <c r="N14" s="22">
+        <f>IF(F14=0,"",M14/F14)</f>
         <v/>
       </c>
     </row>
@@ -2547,24 +2624,30 @@
         <v>526</v>
       </c>
       <c r="G15" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H15" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I15" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H15" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I15" s="21" t="n">
+      <c r="J15" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K15" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J15" s="20">
-        <f>I15*$B$4</f>
-        <v/>
-      </c>
-      <c r="K15" s="20">
-        <f>F15-G15-H15-J15</f>
-        <v/>
-      </c>
-      <c r="L15" s="22">
-        <f>IF(F15=0,"",K15/F15)</f>
+      <c r="L15" s="20">
+        <f>K15*$B$4</f>
+        <v/>
+      </c>
+      <c r="M15" s="20">
+        <f>F15-I15-J15-L15</f>
+        <v/>
+      </c>
+      <c r="N15" s="22">
+        <f>IF(F15=0,"",M15/F15)</f>
         <v/>
       </c>
     </row>
@@ -2594,24 +2677,30 @@
         <v>467</v>
       </c>
       <c r="G16" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H16" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I16" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H16" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I16" s="21" t="n">
+      <c r="J16" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K16" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J16" s="20">
-        <f>I16*$B$4</f>
-        <v/>
-      </c>
-      <c r="K16" s="20">
-        <f>F16-G16-H16-J16</f>
-        <v/>
-      </c>
-      <c r="L16" s="22">
-        <f>IF(F16=0,"",K16/F16)</f>
+      <c r="L16" s="20">
+        <f>K16*$B$4</f>
+        <v/>
+      </c>
+      <c r="M16" s="20">
+        <f>F16-I16-J16-L16</f>
+        <v/>
+      </c>
+      <c r="N16" s="22">
+        <f>IF(F16=0,"",M16/F16)</f>
         <v/>
       </c>
     </row>
@@ -2641,24 +2730,30 @@
         <v>589</v>
       </c>
       <c r="G17" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H17" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I17" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H17" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" s="21" t="n">
+      <c r="J17" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K17" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J17" s="20">
-        <f>I17*$B$4</f>
-        <v/>
-      </c>
-      <c r="K17" s="20">
-        <f>F17-G17-H17-J17</f>
-        <v/>
-      </c>
-      <c r="L17" s="22">
-        <f>IF(F17=0,"",K17/F17)</f>
+      <c r="L17" s="20">
+        <f>K17*$B$4</f>
+        <v/>
+      </c>
+      <c r="M17" s="20">
+        <f>F17-I17-J17-L17</f>
+        <v/>
+      </c>
+      <c r="N17" s="22">
+        <f>IF(F17=0,"",M17/F17)</f>
         <v/>
       </c>
     </row>
@@ -2688,24 +2783,30 @@
         <v>604</v>
       </c>
       <c r="G18" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H18" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I18" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H18" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I18" s="21" t="n">
+      <c r="J18" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K18" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J18" s="20">
-        <f>I18*$B$4</f>
-        <v/>
-      </c>
-      <c r="K18" s="20">
-        <f>F18-G18-H18-J18</f>
-        <v/>
-      </c>
-      <c r="L18" s="22">
-        <f>IF(F18=0,"",K18/F18)</f>
+      <c r="L18" s="20">
+        <f>K18*$B$4</f>
+        <v/>
+      </c>
+      <c r="M18" s="20">
+        <f>F18-I18-J18-L18</f>
+        <v/>
+      </c>
+      <c r="N18" s="22">
+        <f>IF(F18=0,"",M18/F18)</f>
         <v/>
       </c>
     </row>
@@ -2735,24 +2836,30 @@
         <v>342</v>
       </c>
       <c r="G19" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H19" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I19" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H19" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I19" s="21" t="n">
+      <c r="J19" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K19" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J19" s="20">
-        <f>I19*$B$4</f>
-        <v/>
-      </c>
-      <c r="K19" s="20">
-        <f>F19-G19-H19-J19</f>
-        <v/>
-      </c>
-      <c r="L19" s="22">
-        <f>IF(F19=0,"",K19/F19)</f>
+      <c r="L19" s="20">
+        <f>K19*$B$4</f>
+        <v/>
+      </c>
+      <c r="M19" s="20">
+        <f>F19-I19-J19-L19</f>
+        <v/>
+      </c>
+      <c r="N19" s="22">
+        <f>IF(F19=0,"",M19/F19)</f>
         <v/>
       </c>
     </row>
@@ -2782,24 +2889,30 @@
         <v>461</v>
       </c>
       <c r="G20" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H20" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I20" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="H20" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I20" s="21" t="n">
+      <c r="J20" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K20" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J20" s="20">
-        <f>I20*$B$4</f>
-        <v/>
-      </c>
-      <c r="K20" s="20">
-        <f>F20-G20-H20-J20</f>
-        <v/>
-      </c>
-      <c r="L20" s="22">
-        <f>IF(F20=0,"",K20/F20)</f>
+      <c r="L20" s="20">
+        <f>K20*$B$4</f>
+        <v/>
+      </c>
+      <c r="M20" s="20">
+        <f>F20-I20-J20-L20</f>
+        <v/>
+      </c>
+      <c r="N20" s="22">
+        <f>IF(F20=0,"",M20/F20)</f>
         <v/>
       </c>
     </row>
@@ -2829,24 +2942,30 @@
         <v>441</v>
       </c>
       <c r="G21" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H21" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I21" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H21" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I21" s="21" t="n">
+      <c r="J21" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K21" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J21" s="20">
-        <f>I21*$B$4</f>
-        <v/>
-      </c>
-      <c r="K21" s="20">
-        <f>F21-G21-H21-J21</f>
-        <v/>
-      </c>
-      <c r="L21" s="22">
-        <f>IF(F21=0,"",K21/F21)</f>
+      <c r="L21" s="20">
+        <f>K21*$B$4</f>
+        <v/>
+      </c>
+      <c r="M21" s="20">
+        <f>F21-I21-J21-L21</f>
+        <v/>
+      </c>
+      <c r="N21" s="22">
+        <f>IF(F21=0,"",M21/F21)</f>
         <v/>
       </c>
     </row>
@@ -2876,24 +2995,30 @@
         <v>749</v>
       </c>
       <c r="G22" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H22" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I22" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H22" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I22" s="21" t="n">
+      <c r="J22" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K22" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J22" s="20">
-        <f>I22*$B$4</f>
-        <v/>
-      </c>
-      <c r="K22" s="20">
-        <f>F22-G22-H22-J22</f>
-        <v/>
-      </c>
-      <c r="L22" s="22">
-        <f>IF(F22=0,"",K22/F22)</f>
+      <c r="L22" s="20">
+        <f>K22*$B$4</f>
+        <v/>
+      </c>
+      <c r="M22" s="20">
+        <f>F22-I22-J22-L22</f>
+        <v/>
+      </c>
+      <c r="N22" s="22">
+        <f>IF(F22=0,"",M22/F22)</f>
         <v/>
       </c>
     </row>
@@ -2923,24 +3048,30 @@
         <v>801</v>
       </c>
       <c r="G23" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H23" s="20" t="n">
+        <v>221</v>
+      </c>
+      <c r="I23" s="20" t="n">
         <v>170</v>
       </c>
-      <c r="H23" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I23" s="21" t="n">
+      <c r="J23" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K23" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J23" s="20">
-        <f>I23*$B$4</f>
-        <v/>
-      </c>
-      <c r="K23" s="20">
-        <f>F23-G23-H23-J23</f>
-        <v/>
-      </c>
-      <c r="L23" s="22">
-        <f>IF(F23=0,"",K23/F23)</f>
+      <c r="L23" s="20">
+        <f>K23*$B$4</f>
+        <v/>
+      </c>
+      <c r="M23" s="20">
+        <f>F23-I23-J23-L23</f>
+        <v/>
+      </c>
+      <c r="N23" s="22">
+        <f>IF(F23=0,"",M23/F23)</f>
         <v/>
       </c>
     </row>
@@ -2970,24 +3101,30 @@
         <v>322</v>
       </c>
       <c r="G24" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H24" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I24" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H24" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I24" s="21" t="n">
+      <c r="J24" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K24" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J24" s="20">
-        <f>I24*$B$4</f>
-        <v/>
-      </c>
-      <c r="K24" s="20">
-        <f>F24-G24-H24-J24</f>
-        <v/>
-      </c>
-      <c r="L24" s="22">
-        <f>IF(F24=0,"",K24/F24)</f>
+      <c r="L24" s="20">
+        <f>K24*$B$4</f>
+        <v/>
+      </c>
+      <c r="M24" s="20">
+        <f>F24-I24-J24-L24</f>
+        <v/>
+      </c>
+      <c r="N24" s="22">
+        <f>IF(F24=0,"",M24/F24)</f>
         <v/>
       </c>
     </row>
@@ -3017,24 +3154,30 @@
         <v>374</v>
       </c>
       <c r="G25" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H25" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I25" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H25" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I25" s="21" t="n">
+      <c r="J25" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K25" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J25" s="20">
-        <f>I25*$B$4</f>
-        <v/>
-      </c>
-      <c r="K25" s="20">
-        <f>F25-G25-H25-J25</f>
-        <v/>
-      </c>
-      <c r="L25" s="22">
-        <f>IF(F25=0,"",K25/F25)</f>
+      <c r="L25" s="20">
+        <f>K25*$B$4</f>
+        <v/>
+      </c>
+      <c r="M25" s="20">
+        <f>F25-I25-J25-L25</f>
+        <v/>
+      </c>
+      <c r="N25" s="22">
+        <f>IF(F25=0,"",M25/F25)</f>
         <v/>
       </c>
     </row>
@@ -3064,24 +3207,30 @@
         <v>550</v>
       </c>
       <c r="G26" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H26" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I26" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H26" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I26" s="21" t="n">
+      <c r="J26" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K26" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J26" s="20">
-        <f>I26*$B$4</f>
-        <v/>
-      </c>
-      <c r="K26" s="20">
-        <f>F26-G26-H26-J26</f>
-        <v/>
-      </c>
-      <c r="L26" s="22">
-        <f>IF(F26=0,"",K26/F26)</f>
+      <c r="L26" s="20">
+        <f>K26*$B$4</f>
+        <v/>
+      </c>
+      <c r="M26" s="20">
+        <f>F26-I26-J26-L26</f>
+        <v/>
+      </c>
+      <c r="N26" s="22">
+        <f>IF(F26=0,"",M26/F26)</f>
         <v/>
       </c>
     </row>
@@ -3111,24 +3260,30 @@
         <v>563</v>
       </c>
       <c r="G27" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H27" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="I27" s="20" t="n">
         <v>210</v>
       </c>
-      <c r="H27" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I27" s="21" t="n">
+      <c r="J27" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K27" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J27" s="20">
-        <f>I27*$B$4</f>
-        <v/>
-      </c>
-      <c r="K27" s="20">
-        <f>F27-G27-H27-J27</f>
-        <v/>
-      </c>
-      <c r="L27" s="22">
-        <f>IF(F27=0,"",K27/F27)</f>
+      <c r="L27" s="20">
+        <f>K27*$B$4</f>
+        <v/>
+      </c>
+      <c r="M27" s="20">
+        <f>F27-I27-J27-L27</f>
+        <v/>
+      </c>
+      <c r="N27" s="22">
+        <f>IF(F27=0,"",M27/F27)</f>
         <v/>
       </c>
     </row>
@@ -3158,24 +3313,30 @@
         <v>606</v>
       </c>
       <c r="G28" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H28" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I28" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="H28" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I28" s="21" t="n">
+      <c r="J28" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K28" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J28" s="20">
-        <f>I28*$B$4</f>
-        <v/>
-      </c>
-      <c r="K28" s="20">
-        <f>F28-G28-H28-J28</f>
-        <v/>
-      </c>
-      <c r="L28" s="22">
-        <f>IF(F28=0,"",K28/F28)</f>
+      <c r="L28" s="20">
+        <f>K28*$B$4</f>
+        <v/>
+      </c>
+      <c r="M28" s="20">
+        <f>F28-I28-J28-L28</f>
+        <v/>
+      </c>
+      <c r="N28" s="22">
+        <f>IF(F28=0,"",M28/F28)</f>
         <v/>
       </c>
     </row>
@@ -3205,24 +3366,30 @@
         <v>565</v>
       </c>
       <c r="G29" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H29" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I29" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H29" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I29" s="21" t="n">
+      <c r="J29" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K29" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J29" s="20">
-        <f>I29*$B$4</f>
-        <v/>
-      </c>
-      <c r="K29" s="20">
-        <f>F29-G29-H29-J29</f>
-        <v/>
-      </c>
-      <c r="L29" s="22">
-        <f>IF(F29=0,"",K29/F29)</f>
+      <c r="L29" s="20">
+        <f>K29*$B$4</f>
+        <v/>
+      </c>
+      <c r="M29" s="20">
+        <f>F29-I29-J29-L29</f>
+        <v/>
+      </c>
+      <c r="N29" s="22">
+        <f>IF(F29=0,"",M29/F29)</f>
         <v/>
       </c>
     </row>
@@ -3252,24 +3419,30 @@
         <v>643</v>
       </c>
       <c r="G30" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H30" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="I30" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H30" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I30" s="21" t="n">
+      <c r="J30" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K30" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J30" s="20">
-        <f>I30*$B$4</f>
-        <v/>
-      </c>
-      <c r="K30" s="20">
-        <f>F30-G30-H30-J30</f>
-        <v/>
-      </c>
-      <c r="L30" s="22">
-        <f>IF(F30=0,"",K30/F30)</f>
+      <c r="L30" s="20">
+        <f>K30*$B$4</f>
+        <v/>
+      </c>
+      <c r="M30" s="20">
+        <f>F30-I30-J30-L30</f>
+        <v/>
+      </c>
+      <c r="N30" s="22">
+        <f>IF(F30=0,"",M30/F30)</f>
         <v/>
       </c>
     </row>
@@ -3299,24 +3472,30 @@
         <v>342</v>
       </c>
       <c r="G31" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H31" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I31" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H31" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I31" s="21" t="n">
+      <c r="J31" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K31" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J31" s="20">
-        <f>I31*$B$4</f>
-        <v/>
-      </c>
-      <c r="K31" s="20">
-        <f>F31-G31-H31-J31</f>
-        <v/>
-      </c>
-      <c r="L31" s="22">
-        <f>IF(F31=0,"",K31/F31)</f>
+      <c r="L31" s="20">
+        <f>K31*$B$4</f>
+        <v/>
+      </c>
+      <c r="M31" s="20">
+        <f>F31-I31-J31-L31</f>
+        <v/>
+      </c>
+      <c r="N31" s="22">
+        <f>IF(F31=0,"",M31/F31)</f>
         <v/>
       </c>
     </row>
@@ -3346,24 +3525,30 @@
         <v>597</v>
       </c>
       <c r="G32" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H32" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="I32" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="H32" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I32" s="21" t="n">
+      <c r="J32" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K32" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J32" s="20">
-        <f>I32*$B$4</f>
-        <v/>
-      </c>
-      <c r="K32" s="20">
-        <f>F32-G32-H32-J32</f>
-        <v/>
-      </c>
-      <c r="L32" s="22">
-        <f>IF(F32=0,"",K32/F32)</f>
+      <c r="L32" s="20">
+        <f>K32*$B$4</f>
+        <v/>
+      </c>
+      <c r="M32" s="20">
+        <f>F32-I32-J32-L32</f>
+        <v/>
+      </c>
+      <c r="N32" s="22">
+        <f>IF(F32=0,"",M32/F32)</f>
         <v/>
       </c>
     </row>
@@ -3393,24 +3578,30 @@
         <v>452</v>
       </c>
       <c r="G33" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H33" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="I33" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="H33" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I33" s="21" t="n">
+      <c r="J33" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K33" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J33" s="20">
-        <f>I33*$B$4</f>
-        <v/>
-      </c>
-      <c r="K33" s="20">
-        <f>F33-G33-H33-J33</f>
-        <v/>
-      </c>
-      <c r="L33" s="22">
-        <f>IF(F33=0,"",K33/F33)</f>
+      <c r="L33" s="20">
+        <f>K33*$B$4</f>
+        <v/>
+      </c>
+      <c r="M33" s="20">
+        <f>F33-I33-J33-L33</f>
+        <v/>
+      </c>
+      <c r="N33" s="22">
+        <f>IF(F33=0,"",M33/F33)</f>
         <v/>
       </c>
     </row>
@@ -3440,24 +3631,30 @@
         <v>441</v>
       </c>
       <c r="G34" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H34" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I34" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H34" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I34" s="21" t="n">
+      <c r="J34" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K34" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J34" s="20">
-        <f>I34*$B$4</f>
-        <v/>
-      </c>
-      <c r="K34" s="20">
-        <f>F34-G34-H34-J34</f>
-        <v/>
-      </c>
-      <c r="L34" s="22">
-        <f>IF(F34=0,"",K34/F34)</f>
+      <c r="L34" s="20">
+        <f>K34*$B$4</f>
+        <v/>
+      </c>
+      <c r="M34" s="20">
+        <f>F34-I34-J34-L34</f>
+        <v/>
+      </c>
+      <c r="N34" s="22">
+        <f>IF(F34=0,"",M34/F34)</f>
         <v/>
       </c>
     </row>
@@ -3487,24 +3684,30 @@
         <v>316</v>
       </c>
       <c r="G35" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H35" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I35" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="H35" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I35" s="21" t="n">
+      <c r="J35" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K35" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J35" s="20">
-        <f>I35*$B$4</f>
-        <v/>
-      </c>
-      <c r="K35" s="20">
-        <f>F35-G35-H35-J35</f>
-        <v/>
-      </c>
-      <c r="L35" s="22">
-        <f>IF(F35=0,"",K35/F35)</f>
+      <c r="L35" s="20">
+        <f>K35*$B$4</f>
+        <v/>
+      </c>
+      <c r="M35" s="20">
+        <f>F35-I35-J35-L35</f>
+        <v/>
+      </c>
+      <c r="N35" s="22">
+        <f>IF(F35=0,"",M35/F35)</f>
         <v/>
       </c>
     </row>
@@ -3534,24 +3737,30 @@
         <v>335</v>
       </c>
       <c r="G36" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H36" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I36" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H36" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I36" s="21" t="n">
+      <c r="J36" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K36" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J36" s="20">
-        <f>I36*$B$4</f>
-        <v/>
-      </c>
-      <c r="K36" s="20">
-        <f>F36-G36-H36-J36</f>
-        <v/>
-      </c>
-      <c r="L36" s="22">
-        <f>IF(F36=0,"",K36/F36)</f>
+      <c r="L36" s="20">
+        <f>K36*$B$4</f>
+        <v/>
+      </c>
+      <c r="M36" s="20">
+        <f>F36-I36-J36-L36</f>
+        <v/>
+      </c>
+      <c r="N36" s="22">
+        <f>IF(F36=0,"",M36/F36)</f>
         <v/>
       </c>
     </row>
@@ -3581,24 +3790,30 @@
         <v>322</v>
       </c>
       <c r="G37" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H37" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I37" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H37" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I37" s="21" t="n">
+      <c r="J37" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K37" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J37" s="20">
-        <f>I37*$B$4</f>
-        <v/>
-      </c>
-      <c r="K37" s="20">
-        <f>F37-G37-H37-J37</f>
-        <v/>
-      </c>
-      <c r="L37" s="22">
-        <f>IF(F37=0,"",K37/F37)</f>
+      <c r="L37" s="20">
+        <f>K37*$B$4</f>
+        <v/>
+      </c>
+      <c r="M37" s="20">
+        <f>F37-I37-J37-L37</f>
+        <v/>
+      </c>
+      <c r="N37" s="22">
+        <f>IF(F37=0,"",M37/F37)</f>
         <v/>
       </c>
     </row>
@@ -3628,24 +3843,30 @@
         <v>381</v>
       </c>
       <c r="G38" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H38" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I38" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H38" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I38" s="21" t="n">
+      <c r="J38" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K38" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J38" s="20">
-        <f>I38*$B$4</f>
-        <v/>
-      </c>
-      <c r="K38" s="20">
-        <f>F38-G38-H38-J38</f>
-        <v/>
-      </c>
-      <c r="L38" s="22">
-        <f>IF(F38=0,"",K38/F38)</f>
+      <c r="L38" s="20">
+        <f>K38*$B$4</f>
+        <v/>
+      </c>
+      <c r="M38" s="20">
+        <f>F38-I38-J38-L38</f>
+        <v/>
+      </c>
+      <c r="N38" s="22">
+        <f>IF(F38=0,"",M38/F38)</f>
         <v/>
       </c>
     </row>
@@ -3675,24 +3896,30 @@
         <v>262</v>
       </c>
       <c r="G39" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H39" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I39" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H39" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I39" s="21" t="n">
+      <c r="J39" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K39" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J39" s="20">
-        <f>I39*$B$4</f>
-        <v/>
-      </c>
-      <c r="K39" s="20">
-        <f>F39-G39-H39-J39</f>
-        <v/>
-      </c>
-      <c r="L39" s="22">
-        <f>IF(F39=0,"",K39/F39)</f>
+      <c r="L39" s="20">
+        <f>K39*$B$4</f>
+        <v/>
+      </c>
+      <c r="M39" s="20">
+        <f>F39-I39-J39-L39</f>
+        <v/>
+      </c>
+      <c r="N39" s="22">
+        <f>IF(F39=0,"",M39/F39)</f>
         <v/>
       </c>
     </row>
@@ -3722,24 +3949,30 @@
         <v>472</v>
       </c>
       <c r="G40" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H40" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I40" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H40" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I40" s="21" t="n">
+      <c r="J40" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K40" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J40" s="20">
-        <f>I40*$B$4</f>
-        <v/>
-      </c>
-      <c r="K40" s="20">
-        <f>F40-G40-H40-J40</f>
-        <v/>
-      </c>
-      <c r="L40" s="22">
-        <f>IF(F40=0,"",K40/F40)</f>
+      <c r="L40" s="20">
+        <f>K40*$B$4</f>
+        <v/>
+      </c>
+      <c r="M40" s="20">
+        <f>F40-I40-J40-L40</f>
+        <v/>
+      </c>
+      <c r="N40" s="22">
+        <f>IF(F40=0,"",M40/F40)</f>
         <v/>
       </c>
     </row>
@@ -3769,24 +4002,30 @@
         <v>623</v>
       </c>
       <c r="G41" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H41" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I41" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H41" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I41" s="21" t="n">
+      <c r="J41" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K41" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J41" s="20">
-        <f>I41*$B$4</f>
-        <v/>
-      </c>
-      <c r="K41" s="20">
-        <f>F41-G41-H41-J41</f>
-        <v/>
-      </c>
-      <c r="L41" s="22">
-        <f>IF(F41=0,"",K41/F41)</f>
+      <c r="L41" s="20">
+        <f>K41*$B$4</f>
+        <v/>
+      </c>
+      <c r="M41" s="20">
+        <f>F41-I41-J41-L41</f>
+        <v/>
+      </c>
+      <c r="N41" s="22">
+        <f>IF(F41=0,"",M41/F41)</f>
         <v/>
       </c>
     </row>
@@ -3816,24 +4055,30 @@
         <v>288</v>
       </c>
       <c r="G42" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H42" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="I42" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="H42" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I42" s="21" t="n">
+      <c r="J42" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K42" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J42" s="20">
-        <f>I42*$B$4</f>
-        <v/>
-      </c>
-      <c r="K42" s="20">
-        <f>F42-G42-H42-J42</f>
-        <v/>
-      </c>
-      <c r="L42" s="22">
-        <f>IF(F42=0,"",K42/F42)</f>
+      <c r="L42" s="20">
+        <f>K42*$B$4</f>
+        <v/>
+      </c>
+      <c r="M42" s="20">
+        <f>F42-I42-J42-L42</f>
+        <v/>
+      </c>
+      <c r="N42" s="22">
+        <f>IF(F42=0,"",M42/F42)</f>
         <v/>
       </c>
     </row>
@@ -3863,24 +4108,30 @@
         <v>552</v>
       </c>
       <c r="G43" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H43" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I43" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H43" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I43" s="21" t="n">
+      <c r="J43" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K43" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J43" s="20">
-        <f>I43*$B$4</f>
-        <v/>
-      </c>
-      <c r="K43" s="20">
-        <f>F43-G43-H43-J43</f>
-        <v/>
-      </c>
-      <c r="L43" s="22">
-        <f>IF(F43=0,"",K43/F43)</f>
+      <c r="L43" s="20">
+        <f>K43*$B$4</f>
+        <v/>
+      </c>
+      <c r="M43" s="20">
+        <f>F43-I43-J43-L43</f>
+        <v/>
+      </c>
+      <c r="N43" s="22">
+        <f>IF(F43=0,"",M43/F43)</f>
         <v/>
       </c>
     </row>
@@ -3910,24 +4161,30 @@
         <v>270</v>
       </c>
       <c r="G44" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H44" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I44" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H44" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I44" s="21" t="n">
+      <c r="J44" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K44" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J44" s="20">
-        <f>I44*$B$4</f>
-        <v/>
-      </c>
-      <c r="K44" s="20">
-        <f>F44-G44-H44-J44</f>
-        <v/>
-      </c>
-      <c r="L44" s="22">
-        <f>IF(F44=0,"",K44/F44)</f>
+      <c r="L44" s="20">
+        <f>K44*$B$4</f>
+        <v/>
+      </c>
+      <c r="M44" s="20">
+        <f>F44-I44-J44-L44</f>
+        <v/>
+      </c>
+      <c r="N44" s="22">
+        <f>IF(F44=0,"",M44/F44)</f>
         <v/>
       </c>
     </row>
@@ -3957,24 +4214,30 @@
         <v>684</v>
       </c>
       <c r="G45" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H45" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I45" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H45" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I45" s="21" t="n">
+      <c r="J45" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K45" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J45" s="20">
-        <f>I45*$B$4</f>
-        <v/>
-      </c>
-      <c r="K45" s="20">
-        <f>F45-G45-H45-J45</f>
-        <v/>
-      </c>
-      <c r="L45" s="22">
-        <f>IF(F45=0,"",K45/F45)</f>
+      <c r="L45" s="20">
+        <f>K45*$B$4</f>
+        <v/>
+      </c>
+      <c r="M45" s="20">
+        <f>F45-I45-J45-L45</f>
+        <v/>
+      </c>
+      <c r="N45" s="22">
+        <f>IF(F45=0,"",M45/F45)</f>
         <v/>
       </c>
     </row>
@@ -4004,24 +4267,30 @@
         <v>645</v>
       </c>
       <c r="G46" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H46" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I46" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H46" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I46" s="21" t="n">
+      <c r="J46" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K46" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J46" s="20">
-        <f>I46*$B$4</f>
-        <v/>
-      </c>
-      <c r="K46" s="20">
-        <f>F46-G46-H46-J46</f>
-        <v/>
-      </c>
-      <c r="L46" s="22">
-        <f>IF(F46=0,"",K46/F46)</f>
+      <c r="L46" s="20">
+        <f>K46*$B$4</f>
+        <v/>
+      </c>
+      <c r="M46" s="20">
+        <f>F46-I46-J46-L46</f>
+        <v/>
+      </c>
+      <c r="N46" s="22">
+        <f>IF(F46=0,"",M46/F46)</f>
         <v/>
       </c>
     </row>
@@ -4051,24 +4320,30 @@
         <v>565</v>
       </c>
       <c r="G47" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H47" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I47" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H47" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I47" s="21" t="n">
+      <c r="J47" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K47" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J47" s="20">
-        <f>I47*$B$4</f>
-        <v/>
-      </c>
-      <c r="K47" s="20">
-        <f>F47-G47-H47-J47</f>
-        <v/>
-      </c>
-      <c r="L47" s="22">
-        <f>IF(F47=0,"",K47/F47)</f>
+      <c r="L47" s="20">
+        <f>K47*$B$4</f>
+        <v/>
+      </c>
+      <c r="M47" s="20">
+        <f>F47-I47-J47-L47</f>
+        <v/>
+      </c>
+      <c r="N47" s="22">
+        <f>IF(F47=0,"",M47/F47)</f>
         <v/>
       </c>
     </row>
@@ -4098,24 +4373,30 @@
         <v>441</v>
       </c>
       <c r="G48" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H48" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I48" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H48" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I48" s="21" t="n">
+      <c r="J48" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K48" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J48" s="20">
-        <f>I48*$B$4</f>
-        <v/>
-      </c>
-      <c r="K48" s="20">
-        <f>F48-G48-H48-J48</f>
-        <v/>
-      </c>
-      <c r="L48" s="22">
-        <f>IF(F48=0,"",K48/F48)</f>
+      <c r="L48" s="20">
+        <f>K48*$B$4</f>
+        <v/>
+      </c>
+      <c r="M48" s="20">
+        <f>F48-I48-J48-L48</f>
+        <v/>
+      </c>
+      <c r="N48" s="22">
+        <f>IF(F48=0,"",M48/F48)</f>
         <v/>
       </c>
     </row>
@@ -4145,24 +4426,30 @@
         <v>327</v>
       </c>
       <c r="G49" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H49" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I49" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H49" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I49" s="21" t="n">
+      <c r="J49" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K49" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J49" s="20">
-        <f>I49*$B$4</f>
-        <v/>
-      </c>
-      <c r="K49" s="20">
-        <f>F49-G49-H49-J49</f>
-        <v/>
-      </c>
-      <c r="L49" s="22">
-        <f>IF(F49=0,"",K49/F49)</f>
+      <c r="L49" s="20">
+        <f>K49*$B$4</f>
+        <v/>
+      </c>
+      <c r="M49" s="20">
+        <f>F49-I49-J49-L49</f>
+        <v/>
+      </c>
+      <c r="N49" s="22">
+        <f>IF(F49=0,"",M49/F49)</f>
         <v/>
       </c>
     </row>
@@ -4192,24 +4479,30 @@
         <v>550</v>
       </c>
       <c r="G50" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H50" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I50" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H50" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I50" s="21" t="n">
+      <c r="J50" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K50" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J50" s="20">
-        <f>I50*$B$4</f>
-        <v/>
-      </c>
-      <c r="K50" s="20">
-        <f>F50-G50-H50-J50</f>
-        <v/>
-      </c>
-      <c r="L50" s="22">
-        <f>IF(F50=0,"",K50/F50)</f>
+      <c r="L50" s="20">
+        <f>K50*$B$4</f>
+        <v/>
+      </c>
+      <c r="M50" s="20">
+        <f>F50-I50-J50-L50</f>
+        <v/>
+      </c>
+      <c r="N50" s="22">
+        <f>IF(F50=0,"",M50/F50)</f>
         <v/>
       </c>
     </row>
@@ -4239,24 +4532,30 @@
         <v>472</v>
       </c>
       <c r="G51" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H51" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I51" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H51" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I51" s="21" t="n">
+      <c r="J51" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K51" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J51" s="20">
-        <f>I51*$B$4</f>
-        <v/>
-      </c>
-      <c r="K51" s="20">
-        <f>F51-G51-H51-J51</f>
-        <v/>
-      </c>
-      <c r="L51" s="22">
-        <f>IF(F51=0,"",K51/F51)</f>
+      <c r="L51" s="20">
+        <f>K51*$B$4</f>
+        <v/>
+      </c>
+      <c r="M51" s="20">
+        <f>F51-I51-J51-L51</f>
+        <v/>
+      </c>
+      <c r="N51" s="22">
+        <f>IF(F51=0,"",M51/F51)</f>
         <v/>
       </c>
     </row>
@@ -4286,24 +4585,30 @@
         <v>517</v>
       </c>
       <c r="G52" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H52" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I52" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H52" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I52" s="21" t="n">
+      <c r="J52" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K52" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J52" s="20">
-        <f>I52*$B$4</f>
-        <v/>
-      </c>
-      <c r="K52" s="20">
-        <f>F52-G52-H52-J52</f>
-        <v/>
-      </c>
-      <c r="L52" s="22">
-        <f>IF(F52=0,"",K52/F52)</f>
+      <c r="L52" s="20">
+        <f>K52*$B$4</f>
+        <v/>
+      </c>
+      <c r="M52" s="20">
+        <f>F52-I52-J52-L52</f>
+        <v/>
+      </c>
+      <c r="N52" s="22">
+        <f>IF(F52=0,"",M52/F52)</f>
         <v/>
       </c>
     </row>
@@ -4333,24 +4638,30 @@
         <v>643</v>
       </c>
       <c r="G53" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H53" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="I53" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H53" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I53" s="21" t="n">
+      <c r="J53" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K53" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J53" s="20">
-        <f>I53*$B$4</f>
-        <v/>
-      </c>
-      <c r="K53" s="20">
-        <f>F53-G53-H53-J53</f>
-        <v/>
-      </c>
-      <c r="L53" s="22">
-        <f>IF(F53=0,"",K53/F53)</f>
+      <c r="L53" s="20">
+        <f>K53*$B$4</f>
+        <v/>
+      </c>
+      <c r="M53" s="20">
+        <f>F53-I53-J53-L53</f>
+        <v/>
+      </c>
+      <c r="N53" s="22">
+        <f>IF(F53=0,"",M53/F53)</f>
         <v/>
       </c>
     </row>
@@ -4380,24 +4691,30 @@
         <v>420</v>
       </c>
       <c r="G54" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H54" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I54" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H54" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I54" s="21" t="n">
+      <c r="J54" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K54" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J54" s="20">
-        <f>I54*$B$4</f>
-        <v/>
-      </c>
-      <c r="K54" s="20">
-        <f>F54-G54-H54-J54</f>
-        <v/>
-      </c>
-      <c r="L54" s="22">
-        <f>IF(F54=0,"",K54/F54)</f>
+      <c r="L54" s="20">
+        <f>K54*$B$4</f>
+        <v/>
+      </c>
+      <c r="M54" s="20">
+        <f>F54-I54-J54-L54</f>
+        <v/>
+      </c>
+      <c r="N54" s="22">
+        <f>IF(F54=0,"",M54/F54)</f>
         <v/>
       </c>
     </row>
@@ -4427,24 +4744,30 @@
         <v>309</v>
       </c>
       <c r="G55" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H55" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I55" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H55" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I55" s="21" t="n">
+      <c r="J55" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K55" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J55" s="20">
-        <f>I55*$B$4</f>
-        <v/>
-      </c>
-      <c r="K55" s="20">
-        <f>F55-G55-H55-J55</f>
-        <v/>
-      </c>
-      <c r="L55" s="22">
-        <f>IF(F55=0,"",K55/F55)</f>
+      <c r="L55" s="20">
+        <f>K55*$B$4</f>
+        <v/>
+      </c>
+      <c r="M55" s="20">
+        <f>F55-I55-J55-L55</f>
+        <v/>
+      </c>
+      <c r="N55" s="22">
+        <f>IF(F55=0,"",M55/F55)</f>
         <v/>
       </c>
     </row>
@@ -4474,24 +4797,30 @@
         <v>446</v>
       </c>
       <c r="G56" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H56" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I56" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H56" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I56" s="21" t="n">
+      <c r="J56" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K56" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J56" s="20">
-        <f>I56*$B$4</f>
-        <v/>
-      </c>
-      <c r="K56" s="20">
-        <f>F56-G56-H56-J56</f>
-        <v/>
-      </c>
-      <c r="L56" s="22">
-        <f>IF(F56=0,"",K56/F56)</f>
+      <c r="L56" s="20">
+        <f>K56*$B$4</f>
+        <v/>
+      </c>
+      <c r="M56" s="20">
+        <f>F56-I56-J56-L56</f>
+        <v/>
+      </c>
+      <c r="N56" s="22">
+        <f>IF(F56=0,"",M56/F56)</f>
         <v/>
       </c>
     </row>
@@ -4521,24 +4850,30 @@
         <v>171</v>
       </c>
       <c r="G57" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H57" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I57" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="H57" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I57" s="21" t="n">
+      <c r="J57" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K57" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J57" s="20">
-        <f>I57*$B$4</f>
-        <v/>
-      </c>
-      <c r="K57" s="20">
-        <f>F57-G57-H57-J57</f>
-        <v/>
-      </c>
-      <c r="L57" s="22">
-        <f>IF(F57=0,"",K57/F57)</f>
+      <c r="L57" s="20">
+        <f>K57*$B$4</f>
+        <v/>
+      </c>
+      <c r="M57" s="20">
+        <f>F57-I57-J57-L57</f>
+        <v/>
+      </c>
+      <c r="N57" s="22">
+        <f>IF(F57=0,"",M57/F57)</f>
         <v/>
       </c>
     </row>
@@ -4568,24 +4903,30 @@
         <v>736</v>
       </c>
       <c r="G58" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H58" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I58" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H58" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I58" s="21" t="n">
+      <c r="J58" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K58" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J58" s="20">
-        <f>I58*$B$4</f>
-        <v/>
-      </c>
-      <c r="K58" s="20">
-        <f>F58-G58-H58-J58</f>
-        <v/>
-      </c>
-      <c r="L58" s="22">
-        <f>IF(F58=0,"",K58/F58)</f>
+      <c r="L58" s="20">
+        <f>K58*$B$4</f>
+        <v/>
+      </c>
+      <c r="M58" s="20">
+        <f>F58-I58-J58-L58</f>
+        <v/>
+      </c>
+      <c r="N58" s="22">
+        <f>IF(F58=0,"",M58/F58)</f>
         <v/>
       </c>
     </row>
@@ -4615,24 +4956,30 @@
         <v>550</v>
       </c>
       <c r="G59" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H59" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I59" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H59" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I59" s="21" t="n">
+      <c r="J59" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K59" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J59" s="20">
-        <f>I59*$B$4</f>
-        <v/>
-      </c>
-      <c r="K59" s="20">
-        <f>F59-G59-H59-J59</f>
-        <v/>
-      </c>
-      <c r="L59" s="22">
-        <f>IF(F59=0,"",K59/F59)</f>
+      <c r="L59" s="20">
+        <f>K59*$B$4</f>
+        <v/>
+      </c>
+      <c r="M59" s="20">
+        <f>F59-I59-J59-L59</f>
+        <v/>
+      </c>
+      <c r="N59" s="22">
+        <f>IF(F59=0,"",M59/F59)</f>
         <v/>
       </c>
     </row>
@@ -4662,24 +5009,30 @@
         <v>322</v>
       </c>
       <c r="G60" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H60" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I60" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H60" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I60" s="21" t="n">
+      <c r="J60" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K60" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J60" s="20">
-        <f>I60*$B$4</f>
-        <v/>
-      </c>
-      <c r="K60" s="20">
-        <f>F60-G60-H60-J60</f>
-        <v/>
-      </c>
-      <c r="L60" s="22">
-        <f>IF(F60=0,"",K60/F60)</f>
+      <c r="L60" s="20">
+        <f>K60*$B$4</f>
+        <v/>
+      </c>
+      <c r="M60" s="20">
+        <f>F60-I60-J60-L60</f>
+        <v/>
+      </c>
+      <c r="N60" s="22">
+        <f>IF(F60=0,"",M60/F60)</f>
         <v/>
       </c>
     </row>
@@ -4709,24 +5062,30 @@
         <v>348</v>
       </c>
       <c r="G61" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H61" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I61" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H61" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I61" s="21" t="n">
+      <c r="J61" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K61" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J61" s="20">
-        <f>I61*$B$4</f>
-        <v/>
-      </c>
-      <c r="K61" s="20">
-        <f>F61-G61-H61-J61</f>
-        <v/>
-      </c>
-      <c r="L61" s="22">
-        <f>IF(F61=0,"",K61/F61)</f>
+      <c r="L61" s="20">
+        <f>K61*$B$4</f>
+        <v/>
+      </c>
+      <c r="M61" s="20">
+        <f>F61-I61-J61-L61</f>
+        <v/>
+      </c>
+      <c r="N61" s="22">
+        <f>IF(F61=0,"",M61/F61)</f>
         <v/>
       </c>
     </row>
@@ -4756,24 +5115,30 @@
         <v>454</v>
       </c>
       <c r="G62" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H62" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I62" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H62" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I62" s="21" t="n">
+      <c r="J62" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K62" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J62" s="20">
-        <f>I62*$B$4</f>
-        <v/>
-      </c>
-      <c r="K62" s="20">
-        <f>F62-G62-H62-J62</f>
-        <v/>
-      </c>
-      <c r="L62" s="22">
-        <f>IF(F62=0,"",K62/F62)</f>
+      <c r="L62" s="20">
+        <f>K62*$B$4</f>
+        <v/>
+      </c>
+      <c r="M62" s="20">
+        <f>F62-I62-J62-L62</f>
+        <v/>
+      </c>
+      <c r="N62" s="22">
+        <f>IF(F62=0,"",M62/F62)</f>
         <v/>
       </c>
     </row>
@@ -4803,24 +5168,30 @@
         <v>381</v>
       </c>
       <c r="G63" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H63" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I63" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H63" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I63" s="21" t="n">
+      <c r="J63" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K63" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J63" s="20">
-        <f>I63*$B$4</f>
-        <v/>
-      </c>
-      <c r="K63" s="20">
-        <f>F63-G63-H63-J63</f>
-        <v/>
-      </c>
-      <c r="L63" s="22">
-        <f>IF(F63=0,"",K63/F63)</f>
+      <c r="L63" s="20">
+        <f>K63*$B$4</f>
+        <v/>
+      </c>
+      <c r="M63" s="20">
+        <f>F63-I63-J63-L63</f>
+        <v/>
+      </c>
+      <c r="N63" s="22">
+        <f>IF(F63=0,"",M63/F63)</f>
         <v/>
       </c>
     </row>
@@ -4850,24 +5221,30 @@
         <v>301</v>
       </c>
       <c r="G64" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H64" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I64" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H64" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I64" s="21" t="n">
+      <c r="J64" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K64" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J64" s="20">
-        <f>I64*$B$4</f>
-        <v/>
-      </c>
-      <c r="K64" s="20">
-        <f>F64-G64-H64-J64</f>
-        <v/>
-      </c>
-      <c r="L64" s="22">
-        <f>IF(F64=0,"",K64/F64)</f>
+      <c r="L64" s="20">
+        <f>K64*$B$4</f>
+        <v/>
+      </c>
+      <c r="M64" s="20">
+        <f>F64-I64-J64-L64</f>
+        <v/>
+      </c>
+      <c r="N64" s="22">
+        <f>IF(F64=0,"",M64/F64)</f>
         <v/>
       </c>
     </row>
@@ -4897,24 +5274,30 @@
         <v>335</v>
       </c>
       <c r="G65" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H65" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I65" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H65" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I65" s="21" t="n">
+      <c r="J65" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K65" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J65" s="20">
-        <f>I65*$B$4</f>
-        <v/>
-      </c>
-      <c r="K65" s="20">
-        <f>F65-G65-H65-J65</f>
-        <v/>
-      </c>
-      <c r="L65" s="22">
-        <f>IF(F65=0,"",K65/F65)</f>
+      <c r="L65" s="20">
+        <f>K65*$B$4</f>
+        <v/>
+      </c>
+      <c r="M65" s="20">
+        <f>F65-I65-J65-L65</f>
+        <v/>
+      </c>
+      <c r="N65" s="22">
+        <f>IF(F65=0,"",M65/F65)</f>
         <v/>
       </c>
     </row>
@@ -4944,24 +5327,30 @@
         <v>532</v>
       </c>
       <c r="G66" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H66" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I66" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H66" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I66" s="21" t="n">
+      <c r="J66" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K66" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J66" s="20">
-        <f>I66*$B$4</f>
-        <v/>
-      </c>
-      <c r="K66" s="20">
-        <f>F66-G66-H66-J66</f>
-        <v/>
-      </c>
-      <c r="L66" s="22">
-        <f>IF(F66=0,"",K66/F66)</f>
+      <c r="L66" s="20">
+        <f>K66*$B$4</f>
+        <v/>
+      </c>
+      <c r="M66" s="20">
+        <f>F66-I66-J66-L66</f>
+        <v/>
+      </c>
+      <c r="N66" s="22">
+        <f>IF(F66=0,"",M66/F66)</f>
         <v/>
       </c>
     </row>
@@ -4991,24 +5380,30 @@
         <v>459</v>
       </c>
       <c r="G67" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H67" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I67" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H67" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I67" s="21" t="n">
+      <c r="J67" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K67" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J67" s="20">
-        <f>I67*$B$4</f>
-        <v/>
-      </c>
-      <c r="K67" s="20">
-        <f>F67-G67-H67-J67</f>
-        <v/>
-      </c>
-      <c r="L67" s="22">
-        <f>IF(F67=0,"",K67/F67)</f>
+      <c r="L67" s="20">
+        <f>K67*$B$4</f>
+        <v/>
+      </c>
+      <c r="M67" s="20">
+        <f>F67-I67-J67-L67</f>
+        <v/>
+      </c>
+      <c r="N67" s="22">
+        <f>IF(F67=0,"",M67/F67)</f>
         <v/>
       </c>
     </row>
@@ -5038,24 +5433,30 @@
         <v>734</v>
       </c>
       <c r="G68" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H68" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I68" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H68" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I68" s="21" t="n">
+      <c r="J68" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K68" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J68" s="20">
-        <f>I68*$B$4</f>
-        <v/>
-      </c>
-      <c r="K68" s="20">
-        <f>F68-G68-H68-J68</f>
-        <v/>
-      </c>
-      <c r="L68" s="22">
-        <f>IF(F68=0,"",K68/F68)</f>
+      <c r="L68" s="20">
+        <f>K68*$B$4</f>
+        <v/>
+      </c>
+      <c r="M68" s="20">
+        <f>F68-I68-J68-L68</f>
+        <v/>
+      </c>
+      <c r="N68" s="22">
+        <f>IF(F68=0,"",M68/F68)</f>
         <v/>
       </c>
     </row>
@@ -5085,24 +5486,30 @@
         <v>444</v>
       </c>
       <c r="G69" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H69" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I69" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H69" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I69" s="21" t="n">
+      <c r="J69" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K69" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J69" s="20">
-        <f>I69*$B$4</f>
-        <v/>
-      </c>
-      <c r="K69" s="20">
-        <f>F69-G69-H69-J69</f>
-        <v/>
-      </c>
-      <c r="L69" s="22">
-        <f>IF(F69=0,"",K69/F69)</f>
+      <c r="L69" s="20">
+        <f>K69*$B$4</f>
+        <v/>
+      </c>
+      <c r="M69" s="20">
+        <f>F69-I69-J69-L69</f>
+        <v/>
+      </c>
+      <c r="N69" s="22">
+        <f>IF(F69=0,"",M69/F69)</f>
         <v/>
       </c>
     </row>
@@ -5132,24 +5539,30 @@
         <v>762</v>
       </c>
       <c r="G70" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H70" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I70" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H70" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I70" s="21" t="n">
+      <c r="J70" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K70" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J70" s="20">
-        <f>I70*$B$4</f>
-        <v/>
-      </c>
-      <c r="K70" s="20">
-        <f>F70-G70-H70-J70</f>
-        <v/>
-      </c>
-      <c r="L70" s="22">
-        <f>IF(F70=0,"",K70/F70)</f>
+      <c r="L70" s="20">
+        <f>K70*$B$4</f>
+        <v/>
+      </c>
+      <c r="M70" s="20">
+        <f>F70-I70-J70-L70</f>
+        <v/>
+      </c>
+      <c r="N70" s="22">
+        <f>IF(F70=0,"",M70/F70)</f>
         <v/>
       </c>
     </row>
@@ -5178,25 +5591,27 @@
       <c r="F71" s="20" t="n">
         <v>9800</v>
       </c>
-      <c r="G71" s="20" t="n">
+      <c r="G71" s="20" t="n"/>
+      <c r="H71" s="20" t="n"/>
+      <c r="I71" s="20" t="n">
         <v>3600</v>
       </c>
-      <c r="H71" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I71" s="21" t="n">
+      <c r="J71" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K71" s="21" t="n">
         <v>26</v>
       </c>
-      <c r="J71" s="20">
-        <f>I71*$B$4</f>
-        <v/>
-      </c>
-      <c r="K71" s="20">
-        <f>F71-G71-H71-J71</f>
-        <v/>
-      </c>
-      <c r="L71" s="22">
-        <f>IF(F71=0,"",K71/F71)</f>
+      <c r="L71" s="20">
+        <f>K71*$B$4</f>
+        <v/>
+      </c>
+      <c r="M71" s="20">
+        <f>F71-I71-J71-L71</f>
+        <v/>
+      </c>
+      <c r="N71" s="22">
+        <f>IF(F71=0,"",M71/F71)</f>
         <v/>
       </c>
     </row>
@@ -5225,25 +5640,27 @@
       <c r="F72" s="20" t="n">
         <v>27400</v>
       </c>
-      <c r="G72" s="20" t="n">
+      <c r="G72" s="20" t="n"/>
+      <c r="H72" s="20" t="n"/>
+      <c r="I72" s="20" t="n">
         <v>13800</v>
       </c>
-      <c r="H72" s="20" t="n">
+      <c r="J72" s="20" t="n">
         <v>3100</v>
       </c>
-      <c r="I72" s="21" t="n">
+      <c r="K72" s="21" t="n">
         <v>46</v>
       </c>
-      <c r="J72" s="20">
-        <f>I72*$B$4</f>
-        <v/>
-      </c>
-      <c r="K72" s="20">
-        <f>F72-G72-H72-J72</f>
-        <v/>
-      </c>
-      <c r="L72" s="22">
-        <f>IF(F72=0,"",K72/F72)</f>
+      <c r="L72" s="20">
+        <f>K72*$B$4</f>
+        <v/>
+      </c>
+      <c r="M72" s="20">
+        <f>F72-I72-J72-L72</f>
+        <v/>
+      </c>
+      <c r="N72" s="22">
+        <f>IF(F72=0,"",M72/F72)</f>
         <v/>
       </c>
     </row>
@@ -5272,25 +5689,27 @@
       <c r="F73" s="20" t="n">
         <v>15200</v>
       </c>
-      <c r="G73" s="20" t="n">
+      <c r="G73" s="20" t="n"/>
+      <c r="H73" s="20" t="n"/>
+      <c r="I73" s="20" t="n">
         <v>4300</v>
       </c>
-      <c r="H73" s="20" t="n">
+      <c r="J73" s="20" t="n">
         <v>1800</v>
       </c>
-      <c r="I73" s="21" t="n">
+      <c r="K73" s="21" t="n">
         <v>52</v>
       </c>
-      <c r="J73" s="20">
-        <f>I73*$B$4</f>
-        <v/>
-      </c>
-      <c r="K73" s="20">
-        <f>F73-G73-H73-J73</f>
-        <v/>
-      </c>
-      <c r="L73" s="22">
-        <f>IF(F73=0,"",K73/F73)</f>
+      <c r="L73" s="20">
+        <f>K73*$B$4</f>
+        <v/>
+      </c>
+      <c r="M73" s="20">
+        <f>F73-I73-J73-L73</f>
+        <v/>
+      </c>
+      <c r="N73" s="22">
+        <f>IF(F73=0,"",M73/F73)</f>
         <v/>
       </c>
     </row>
@@ -5319,25 +5738,27 @@
       <c r="F74" s="20" t="n">
         <v>18600</v>
       </c>
-      <c r="G74" s="20" t="n">
+      <c r="G74" s="20" t="n"/>
+      <c r="H74" s="20" t="n"/>
+      <c r="I74" s="20" t="n">
         <v>6900</v>
       </c>
-      <c r="H74" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I74" s="21" t="n">
+      <c r="J74" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K74" s="21" t="n">
         <v>64</v>
       </c>
-      <c r="J74" s="20">
-        <f>I74*$B$4</f>
-        <v/>
-      </c>
-      <c r="K74" s="20">
-        <f>F74-G74-H74-J74</f>
-        <v/>
-      </c>
-      <c r="L74" s="22">
-        <f>IF(F74=0,"",K74/F74)</f>
+      <c r="L74" s="20">
+        <f>K74*$B$4</f>
+        <v/>
+      </c>
+      <c r="M74" s="20">
+        <f>F74-I74-J74-L74</f>
+        <v/>
+      </c>
+      <c r="N74" s="22">
+        <f>IF(F74=0,"",M74/F74)</f>
         <v/>
       </c>
     </row>
@@ -5366,25 +5787,27 @@
       <c r="F75" s="20" t="n">
         <v>46800</v>
       </c>
-      <c r="G75" s="20" t="n">
+      <c r="G75" s="20" t="n"/>
+      <c r="H75" s="20" t="n"/>
+      <c r="I75" s="20" t="n">
         <v>22900</v>
       </c>
-      <c r="H75" s="20" t="n">
+      <c r="J75" s="20" t="n">
         <v>7400</v>
       </c>
-      <c r="I75" s="21" t="n">
+      <c r="K75" s="21" t="n">
         <v>150</v>
       </c>
-      <c r="J75" s="20">
-        <f>I75*$B$4</f>
-        <v/>
-      </c>
-      <c r="K75" s="20">
-        <f>F75-G75-H75-J75</f>
-        <v/>
-      </c>
-      <c r="L75" s="22">
-        <f>IF(F75=0,"",K75/F75)</f>
+      <c r="L75" s="20">
+        <f>K75*$B$4</f>
+        <v/>
+      </c>
+      <c r="M75" s="20">
+        <f>F75-I75-J75-L75</f>
+        <v/>
+      </c>
+      <c r="N75" s="22">
+        <f>IF(F75=0,"",M75/F75)</f>
         <v/>
       </c>
     </row>
@@ -5413,25 +5836,27 @@
       <c r="F76" s="20" t="n">
         <v>12900</v>
       </c>
-      <c r="G76" s="20" t="n">
+      <c r="G76" s="20" t="n"/>
+      <c r="H76" s="20" t="n"/>
+      <c r="I76" s="20" t="n">
         <v>5100</v>
       </c>
-      <c r="H76" s="20" t="n">
+      <c r="J76" s="20" t="n">
         <v>900</v>
       </c>
-      <c r="I76" s="21" t="n">
+      <c r="K76" s="21" t="n">
         <v>38</v>
       </c>
-      <c r="J76" s="20">
-        <f>I76*$B$4</f>
-        <v/>
-      </c>
-      <c r="K76" s="20">
-        <f>F76-G76-H76-J76</f>
-        <v/>
-      </c>
-      <c r="L76" s="22">
-        <f>IF(F76=0,"",K76/F76)</f>
+      <c r="L76" s="20">
+        <f>K76*$B$4</f>
+        <v/>
+      </c>
+      <c r="M76" s="20">
+        <f>F76-I76-J76-L76</f>
+        <v/>
+      </c>
+      <c r="N76" s="22">
+        <f>IF(F76=0,"",M76/F76)</f>
         <v/>
       </c>
     </row>
@@ -5460,25 +5885,27 @@
       <c r="F77" s="20" t="n">
         <v>3600</v>
       </c>
-      <c r="G77" s="20" t="n">
+      <c r="G77" s="20" t="n"/>
+      <c r="H77" s="20" t="n"/>
+      <c r="I77" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H77" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I77" s="21" t="n">
+      <c r="J77" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K77" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="J77" s="20">
-        <f>I77*$B$4</f>
-        <v/>
-      </c>
-      <c r="K77" s="20">
-        <f>F77-G77-H77-J77</f>
-        <v/>
-      </c>
-      <c r="L77" s="22">
-        <f>IF(F77=0,"",K77/F77)</f>
+      <c r="L77" s="20">
+        <f>K77*$B$4</f>
+        <v/>
+      </c>
+      <c r="M77" s="20">
+        <f>F77-I77-J77-L77</f>
+        <v/>
+      </c>
+      <c r="N77" s="22">
+        <f>IF(F77=0,"",M77/F77)</f>
         <v/>
       </c>
     </row>
@@ -5507,25 +5934,27 @@
       <c r="F78" s="20" t="n">
         <v>2800</v>
       </c>
-      <c r="G78" s="20" t="n">
+      <c r="G78" s="20" t="n"/>
+      <c r="H78" s="20" t="n"/>
+      <c r="I78" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H78" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I78" s="21" t="n">
+      <c r="J78" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K78" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="J78" s="20">
-        <f>I78*$B$4</f>
-        <v/>
-      </c>
-      <c r="K78" s="20">
-        <f>F78-G78-H78-J78</f>
-        <v/>
-      </c>
-      <c r="L78" s="22">
-        <f>IF(F78=0,"",K78/F78)</f>
+      <c r="L78" s="20">
+        <f>K78*$B$4</f>
+        <v/>
+      </c>
+      <c r="M78" s="20">
+        <f>F78-I78-J78-L78</f>
+        <v/>
+      </c>
+      <c r="N78" s="22">
+        <f>IF(F78=0,"",M78/F78)</f>
         <v/>
       </c>
     </row>
@@ -5554,25 +5983,27 @@
       <c r="F79" s="20" t="n">
         <v>1700</v>
       </c>
-      <c r="G79" s="20" t="n">
+      <c r="G79" s="20" t="n"/>
+      <c r="H79" s="20" t="n"/>
+      <c r="I79" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H79" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I79" s="21" t="n">
+      <c r="J79" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K79" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="J79" s="20">
-        <f>I79*$B$4</f>
-        <v/>
-      </c>
-      <c r="K79" s="20">
-        <f>F79-G79-H79-J79</f>
-        <v/>
-      </c>
-      <c r="L79" s="22">
-        <f>IF(F79=0,"",K79/F79)</f>
+      <c r="L79" s="20">
+        <f>K79*$B$4</f>
+        <v/>
+      </c>
+      <c r="M79" s="20">
+        <f>F79-I79-J79-L79</f>
+        <v/>
+      </c>
+      <c r="N79" s="22">
+        <f>IF(F79=0,"",M79/F79)</f>
         <v/>
       </c>
     </row>
@@ -5601,25 +6032,27 @@
       <c r="F80" s="20" t="n">
         <v>4100</v>
       </c>
-      <c r="G80" s="20" t="n">
+      <c r="G80" s="20" t="n"/>
+      <c r="H80" s="20" t="n"/>
+      <c r="I80" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H80" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I80" s="21" t="n">
+      <c r="J80" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K80" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="J80" s="20">
-        <f>I80*$B$4</f>
-        <v/>
-      </c>
-      <c r="K80" s="20">
-        <f>F80-G80-H80-J80</f>
-        <v/>
-      </c>
-      <c r="L80" s="22">
-        <f>IF(F80=0,"",K80/F80)</f>
+      <c r="L80" s="20">
+        <f>K80*$B$4</f>
+        <v/>
+      </c>
+      <c r="M80" s="20">
+        <f>F80-I80-J80-L80</f>
+        <v/>
+      </c>
+      <c r="N80" s="22">
+        <f>IF(F80=0,"",M80/F80)</f>
         <v/>
       </c>
     </row>
@@ -5648,25 +6081,27 @@
       <c r="F81" s="20" t="n">
         <v>3400</v>
       </c>
-      <c r="G81" s="20" t="n">
+      <c r="G81" s="20" t="n"/>
+      <c r="H81" s="20" t="n"/>
+      <c r="I81" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H81" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I81" s="21" t="n">
+      <c r="J81" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K81" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="J81" s="20">
-        <f>I81*$B$4</f>
-        <v/>
-      </c>
-      <c r="K81" s="20">
-        <f>F81-G81-H81-J81</f>
-        <v/>
-      </c>
-      <c r="L81" s="22">
-        <f>IF(F81=0,"",K81/F81)</f>
+      <c r="L81" s="20">
+        <f>K81*$B$4</f>
+        <v/>
+      </c>
+      <c r="M81" s="20">
+        <f>F81-I81-J81-L81</f>
+        <v/>
+      </c>
+      <c r="N81" s="22">
+        <f>IF(F81=0,"",M81/F81)</f>
         <v/>
       </c>
     </row>
@@ -5695,25 +6130,27 @@
       <c r="F82" s="20" t="n">
         <v>2400</v>
       </c>
-      <c r="G82" s="20" t="n">
+      <c r="G82" s="20" t="n"/>
+      <c r="H82" s="20" t="n"/>
+      <c r="I82" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H82" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I82" s="21" t="n">
+      <c r="J82" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K82" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="J82" s="20">
-        <f>I82*$B$4</f>
-        <v/>
-      </c>
-      <c r="K82" s="20">
-        <f>F82-G82-H82-J82</f>
-        <v/>
-      </c>
-      <c r="L82" s="22">
-        <f>IF(F82=0,"",K82/F82)</f>
+      <c r="L82" s="20">
+        <f>K82*$B$4</f>
+        <v/>
+      </c>
+      <c r="M82" s="20">
+        <f>F82-I82-J82-L82</f>
+        <v/>
+      </c>
+      <c r="N82" s="22">
+        <f>IF(F82=0,"",M82/F82)</f>
         <v/>
       </c>
     </row>
@@ -5742,25 +6179,27 @@
       <c r="F83" s="20" t="n">
         <v>4200</v>
       </c>
-      <c r="G83" s="20" t="n">
+      <c r="G83" s="20" t="n"/>
+      <c r="H83" s="20" t="n"/>
+      <c r="I83" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H83" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I83" s="21" t="n">
+      <c r="J83" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K83" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="J83" s="20">
-        <f>I83*$B$4</f>
-        <v/>
-      </c>
-      <c r="K83" s="20">
-        <f>F83-G83-H83-J83</f>
-        <v/>
-      </c>
-      <c r="L83" s="22">
-        <f>IF(F83=0,"",K83/F83)</f>
+      <c r="L83" s="20">
+        <f>K83*$B$4</f>
+        <v/>
+      </c>
+      <c r="M83" s="20">
+        <f>F83-I83-J83-L83</f>
+        <v/>
+      </c>
+      <c r="N83" s="22">
+        <f>IF(F83=0,"",M83/F83)</f>
         <v/>
       </c>
     </row>
@@ -5789,25 +6228,27 @@
       <c r="F84" s="20" t="n">
         <v>1600</v>
       </c>
-      <c r="G84" s="20" t="n">
+      <c r="G84" s="20" t="n"/>
+      <c r="H84" s="20" t="n"/>
+      <c r="I84" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H84" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I84" s="21" t="n">
+      <c r="J84" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K84" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="J84" s="20">
-        <f>I84*$B$4</f>
-        <v/>
-      </c>
-      <c r="K84" s="20">
-        <f>F84-G84-H84-J84</f>
-        <v/>
-      </c>
-      <c r="L84" s="22">
-        <f>IF(F84=0,"",K84/F84)</f>
+      <c r="L84" s="20">
+        <f>K84*$B$4</f>
+        <v/>
+      </c>
+      <c r="M84" s="20">
+        <f>F84-I84-J84-L84</f>
+        <v/>
+      </c>
+      <c r="N84" s="22">
+        <f>IF(F84=0,"",M84/F84)</f>
         <v/>
       </c>
     </row>
@@ -5836,25 +6277,27 @@
       <c r="F85" s="20" t="n">
         <v>3200</v>
       </c>
-      <c r="G85" s="20" t="n">
+      <c r="G85" s="20" t="n"/>
+      <c r="H85" s="20" t="n"/>
+      <c r="I85" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H85" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I85" s="21" t="n">
+      <c r="J85" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K85" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="J85" s="20">
-        <f>I85*$B$4</f>
-        <v/>
-      </c>
-      <c r="K85" s="20">
-        <f>F85-G85-H85-J85</f>
-        <v/>
-      </c>
-      <c r="L85" s="22">
-        <f>IF(F85=0,"",K85/F85)</f>
+      <c r="L85" s="20">
+        <f>K85*$B$4</f>
+        <v/>
+      </c>
+      <c r="M85" s="20">
+        <f>F85-I85-J85-L85</f>
+        <v/>
+      </c>
+      <c r="N85" s="22">
+        <f>IF(F85=0,"",M85/F85)</f>
         <v/>
       </c>
     </row>
@@ -5883,25 +6326,27 @@
       <c r="F86" s="20" t="n">
         <v>3900</v>
       </c>
-      <c r="G86" s="20" t="n">
+      <c r="G86" s="20" t="n"/>
+      <c r="H86" s="20" t="n"/>
+      <c r="I86" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="H86" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I86" s="21" t="n">
+      <c r="J86" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K86" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="J86" s="20">
-        <f>I86*$B$4</f>
-        <v/>
-      </c>
-      <c r="K86" s="20">
-        <f>F86-G86-H86-J86</f>
-        <v/>
-      </c>
-      <c r="L86" s="22">
-        <f>IF(F86=0,"",K86/F86)</f>
+      <c r="L86" s="20">
+        <f>K86*$B$4</f>
+        <v/>
+      </c>
+      <c r="M86" s="20">
+        <f>F86-I86-J86-L86</f>
+        <v/>
+      </c>
+      <c r="N86" s="22">
+        <f>IF(F86=0,"",M86/F86)</f>
         <v/>
       </c>
     </row>
@@ -5930,25 +6375,27 @@
       <c r="F87" s="20" t="n">
         <v>1800</v>
       </c>
-      <c r="G87" s="20" t="n">
+      <c r="G87" s="20" t="n"/>
+      <c r="H87" s="20" t="n"/>
+      <c r="I87" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H87" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I87" s="21" t="n">
+      <c r="J87" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K87" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="J87" s="20">
-        <f>I87*$B$4</f>
-        <v/>
-      </c>
-      <c r="K87" s="20">
-        <f>F87-G87-H87-J87</f>
-        <v/>
-      </c>
-      <c r="L87" s="22">
-        <f>IF(F87=0,"",K87/F87)</f>
+      <c r="L87" s="20">
+        <f>K87*$B$4</f>
+        <v/>
+      </c>
+      <c r="M87" s="20">
+        <f>F87-I87-J87-L87</f>
+        <v/>
+      </c>
+      <c r="N87" s="22">
+        <f>IF(F87=0,"",M87/F87)</f>
         <v/>
       </c>
     </row>
@@ -5977,25 +6424,27 @@
       <c r="F88" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="G88" s="20" t="n">
+      <c r="G88" s="20" t="n"/>
+      <c r="H88" s="20" t="n"/>
+      <c r="I88" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H88" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I88" s="21" t="n">
+      <c r="J88" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K88" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="J88" s="20">
-        <f>I88*$B$4</f>
-        <v/>
-      </c>
-      <c r="K88" s="20">
-        <f>F88-G88-H88-J88</f>
-        <v/>
-      </c>
-      <c r="L88" s="22">
-        <f>IF(F88=0,"",K88/F88)</f>
+      <c r="L88" s="20">
+        <f>K88*$B$4</f>
+        <v/>
+      </c>
+      <c r="M88" s="20">
+        <f>F88-I88-J88-L88</f>
+        <v/>
+      </c>
+      <c r="N88" s="22">
+        <f>IF(F88=0,"",M88/F88)</f>
         <v/>
       </c>
     </row>
@@ -6024,25 +6473,27 @@
       <c r="F89" s="20" t="n">
         <v>2600</v>
       </c>
-      <c r="G89" s="20" t="n">
+      <c r="G89" s="20" t="n"/>
+      <c r="H89" s="20" t="n"/>
+      <c r="I89" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H89" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I89" s="21" t="n">
+      <c r="J89" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K89" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="J89" s="20">
-        <f>I89*$B$4</f>
-        <v/>
-      </c>
-      <c r="K89" s="20">
-        <f>F89-G89-H89-J89</f>
-        <v/>
-      </c>
-      <c r="L89" s="22">
-        <f>IF(F89=0,"",K89/F89)</f>
+      <c r="L89" s="20">
+        <f>K89*$B$4</f>
+        <v/>
+      </c>
+      <c r="M89" s="20">
+        <f>F89-I89-J89-L89</f>
+        <v/>
+      </c>
+      <c r="N89" s="22">
+        <f>IF(F89=0,"",M89/F89)</f>
         <v/>
       </c>
     </row>
@@ -6071,25 +6522,27 @@
       <c r="F90" s="20" t="n">
         <v>2200</v>
       </c>
-      <c r="G90" s="20" t="n">
+      <c r="G90" s="20" t="n"/>
+      <c r="H90" s="20" t="n"/>
+      <c r="I90" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H90" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I90" s="21" t="n">
+      <c r="J90" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K90" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="J90" s="20">
-        <f>I90*$B$4</f>
-        <v/>
-      </c>
-      <c r="K90" s="20">
-        <f>F90-G90-H90-J90</f>
-        <v/>
-      </c>
-      <c r="L90" s="22">
-        <f>IF(F90=0,"",K90/F90)</f>
+      <c r="L90" s="20">
+        <f>K90*$B$4</f>
+        <v/>
+      </c>
+      <c r="M90" s="20">
+        <f>F90-I90-J90-L90</f>
+        <v/>
+      </c>
+      <c r="N90" s="22">
+        <f>IF(F90=0,"",M90/F90)</f>
         <v/>
       </c>
     </row>
@@ -6119,24 +6572,30 @@
         <v>853</v>
       </c>
       <c r="G91" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H91" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="I91" s="20" t="n">
         <v>210</v>
       </c>
-      <c r="H91" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I91" s="21" t="n">
+      <c r="J91" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K91" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J91" s="20">
-        <f>I91*$B$4</f>
-        <v/>
-      </c>
-      <c r="K91" s="20">
-        <f>F91-G91-H91-J91</f>
-        <v/>
-      </c>
-      <c r="L91" s="22">
-        <f>IF(F91=0,"",K91/F91)</f>
+      <c r="L91" s="20">
+        <f>K91*$B$4</f>
+        <v/>
+      </c>
+      <c r="M91" s="20">
+        <f>F91-I91-J91-L91</f>
+        <v/>
+      </c>
+      <c r="N91" s="22">
+        <f>IF(F91=0,"",M91/F91)</f>
         <v/>
       </c>
     </row>
@@ -6166,24 +6625,30 @@
         <v>342</v>
       </c>
       <c r="G92" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H92" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I92" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H92" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I92" s="21" t="n">
+      <c r="J92" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K92" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J92" s="20">
-        <f>I92*$B$4</f>
-        <v/>
-      </c>
-      <c r="K92" s="20">
-        <f>F92-G92-H92-J92</f>
-        <v/>
-      </c>
-      <c r="L92" s="22">
-        <f>IF(F92=0,"",K92/F92)</f>
+      <c r="L92" s="20">
+        <f>K92*$B$4</f>
+        <v/>
+      </c>
+      <c r="M92" s="20">
+        <f>F92-I92-J92-L92</f>
+        <v/>
+      </c>
+      <c r="N92" s="22">
+        <f>IF(F92=0,"",M92/F92)</f>
         <v/>
       </c>
     </row>
@@ -6213,24 +6678,30 @@
         <v>474</v>
       </c>
       <c r="G93" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H93" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="I93" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H93" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I93" s="21" t="n">
+      <c r="J93" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K93" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J93" s="20">
-        <f>I93*$B$4</f>
-        <v/>
-      </c>
-      <c r="K93" s="20">
-        <f>F93-G93-H93-J93</f>
-        <v/>
-      </c>
-      <c r="L93" s="22">
-        <f>IF(F93=0,"",K93/F93)</f>
+      <c r="L93" s="20">
+        <f>K93*$B$4</f>
+        <v/>
+      </c>
+      <c r="M93" s="20">
+        <f>F93-I93-J93-L93</f>
+        <v/>
+      </c>
+      <c r="N93" s="22">
+        <f>IF(F93=0,"",M93/F93)</f>
         <v/>
       </c>
     </row>
@@ -6260,24 +6731,30 @@
         <v>708</v>
       </c>
       <c r="G94" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H94" s="20" t="n">
+        <v>273</v>
+      </c>
+      <c r="I94" s="20" t="n">
         <v>210</v>
       </c>
-      <c r="H94" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I94" s="21" t="n">
+      <c r="J94" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K94" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J94" s="20">
-        <f>I94*$B$4</f>
-        <v/>
-      </c>
-      <c r="K94" s="20">
-        <f>F94-G94-H94-J94</f>
-        <v/>
-      </c>
-      <c r="L94" s="22">
-        <f>IF(F94=0,"",K94/F94)</f>
+      <c r="L94" s="20">
+        <f>K94*$B$4</f>
+        <v/>
+      </c>
+      <c r="M94" s="20">
+        <f>F94-I94-J94-L94</f>
+        <v/>
+      </c>
+      <c r="N94" s="22">
+        <f>IF(F94=0,"",M94/F94)</f>
         <v/>
       </c>
     </row>
@@ -6307,24 +6784,30 @@
         <v>381</v>
       </c>
       <c r="G95" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H95" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I95" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H95" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I95" s="21" t="n">
+      <c r="J95" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K95" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J95" s="20">
-        <f>I95*$B$4</f>
-        <v/>
-      </c>
-      <c r="K95" s="20">
-        <f>F95-G95-H95-J95</f>
-        <v/>
-      </c>
-      <c r="L95" s="22">
-        <f>IF(F95=0,"",K95/F95)</f>
+      <c r="L95" s="20">
+        <f>K95*$B$4</f>
+        <v/>
+      </c>
+      <c r="M95" s="20">
+        <f>F95-I95-J95-L95</f>
+        <v/>
+      </c>
+      <c r="N95" s="22">
+        <f>IF(F95=0,"",M95/F95)</f>
         <v/>
       </c>
     </row>
@@ -6354,24 +6837,30 @@
         <v>695</v>
       </c>
       <c r="G96" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H96" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I96" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H96" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I96" s="21" t="n">
+      <c r="J96" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K96" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J96" s="20">
-        <f>I96*$B$4</f>
-        <v/>
-      </c>
-      <c r="K96" s="20">
-        <f>F96-G96-H96-J96</f>
-        <v/>
-      </c>
-      <c r="L96" s="22">
-        <f>IF(F96=0,"",K96/F96)</f>
+      <c r="L96" s="20">
+        <f>K96*$B$4</f>
+        <v/>
+      </c>
+      <c r="M96" s="20">
+        <f>F96-I96-J96-L96</f>
+        <v/>
+      </c>
+      <c r="N96" s="22">
+        <f>IF(F96=0,"",M96/F96)</f>
         <v/>
       </c>
     </row>
@@ -6401,24 +6890,30 @@
         <v>539</v>
       </c>
       <c r="G97" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H97" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I97" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H97" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I97" s="21" t="n">
+      <c r="J97" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K97" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J97" s="20">
-        <f>I97*$B$4</f>
-        <v/>
-      </c>
-      <c r="K97" s="20">
-        <f>F97-G97-H97-J97</f>
-        <v/>
-      </c>
-      <c r="L97" s="22">
-        <f>IF(F97=0,"",K97/F97)</f>
+      <c r="L97" s="20">
+        <f>K97*$B$4</f>
+        <v/>
+      </c>
+      <c r="M97" s="20">
+        <f>F97-I97-J97-L97</f>
+        <v/>
+      </c>
+      <c r="N97" s="22">
+        <f>IF(F97=0,"",M97/F97)</f>
         <v/>
       </c>
     </row>
@@ -6448,24 +6943,30 @@
         <v>840</v>
       </c>
       <c r="G98" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H98" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I98" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H98" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I98" s="21" t="n">
+      <c r="J98" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K98" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J98" s="20">
-        <f>I98*$B$4</f>
-        <v/>
-      </c>
-      <c r="K98" s="20">
-        <f>F98-G98-H98-J98</f>
-        <v/>
-      </c>
-      <c r="L98" s="22">
-        <f>IF(F98=0,"",K98/F98)</f>
+      <c r="L98" s="20">
+        <f>K98*$B$4</f>
+        <v/>
+      </c>
+      <c r="M98" s="20">
+        <f>F98-I98-J98-L98</f>
+        <v/>
+      </c>
+      <c r="N98" s="22">
+        <f>IF(F98=0,"",M98/F98)</f>
         <v/>
       </c>
     </row>
@@ -6495,24 +6996,30 @@
         <v>866</v>
       </c>
       <c r="G99" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H99" s="20" t="n">
+        <v>286</v>
+      </c>
+      <c r="I99" s="20" t="n">
         <v>220</v>
       </c>
-      <c r="H99" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I99" s="21" t="n">
+      <c r="J99" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K99" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J99" s="20">
-        <f>I99*$B$4</f>
-        <v/>
-      </c>
-      <c r="K99" s="20">
-        <f>F99-G99-H99-J99</f>
-        <v/>
-      </c>
-      <c r="L99" s="22">
-        <f>IF(F99=0,"",K99/F99)</f>
+      <c r="L99" s="20">
+        <f>K99*$B$4</f>
+        <v/>
+      </c>
+      <c r="M99" s="20">
+        <f>F99-I99-J99-L99</f>
+        <v/>
+      </c>
+      <c r="N99" s="22">
+        <f>IF(F99=0,"",M99/F99)</f>
         <v/>
       </c>
     </row>
@@ -6542,24 +7049,30 @@
         <v>604</v>
       </c>
       <c r="G100" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H100" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I100" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H100" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I100" s="21" t="n">
+      <c r="J100" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K100" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J100" s="20">
-        <f>I100*$B$4</f>
-        <v/>
-      </c>
-      <c r="K100" s="20">
-        <f>F100-G100-H100-J100</f>
-        <v/>
-      </c>
-      <c r="L100" s="22">
-        <f>IF(F100=0,"",K100/F100)</f>
+      <c r="L100" s="20">
+        <f>K100*$B$4</f>
+        <v/>
+      </c>
+      <c r="M100" s="20">
+        <f>F100-I100-J100-L100</f>
+        <v/>
+      </c>
+      <c r="N100" s="22">
+        <f>IF(F100=0,"",M100/F100)</f>
         <v/>
       </c>
     </row>
@@ -6589,24 +7102,30 @@
         <v>524</v>
       </c>
       <c r="G101" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H101" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="I101" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="H101" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I101" s="21" t="n">
+      <c r="J101" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K101" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J101" s="20">
-        <f>I101*$B$4</f>
-        <v/>
-      </c>
-      <c r="K101" s="20">
-        <f>F101-G101-H101-J101</f>
-        <v/>
-      </c>
-      <c r="L101" s="22">
-        <f>IF(F101=0,"",K101/F101)</f>
+      <c r="L101" s="20">
+        <f>K101*$B$4</f>
+        <v/>
+      </c>
+      <c r="M101" s="20">
+        <f>F101-I101-J101-L101</f>
+        <v/>
+      </c>
+      <c r="N101" s="22">
+        <f>IF(F101=0,"",M101/F101)</f>
         <v/>
       </c>
     </row>
@@ -6636,24 +7155,30 @@
         <v>368</v>
       </c>
       <c r="G102" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H102" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I102" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H102" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I102" s="21" t="n">
+      <c r="J102" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K102" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J102" s="20">
-        <f>I102*$B$4</f>
-        <v/>
-      </c>
-      <c r="K102" s="20">
-        <f>F102-G102-H102-J102</f>
-        <v/>
-      </c>
-      <c r="L102" s="22">
-        <f>IF(F102=0,"",K102/F102)</f>
+      <c r="L102" s="20">
+        <f>K102*$B$4</f>
+        <v/>
+      </c>
+      <c r="M102" s="20">
+        <f>F102-I102-J102-L102</f>
+        <v/>
+      </c>
+      <c r="N102" s="22">
+        <f>IF(F102=0,"",M102/F102)</f>
         <v/>
       </c>
     </row>
@@ -6683,24 +7208,30 @@
         <v>658</v>
       </c>
       <c r="G103" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H103" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I103" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H103" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I103" s="21" t="n">
+      <c r="J103" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K103" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J103" s="20">
-        <f>I103*$B$4</f>
-        <v/>
-      </c>
-      <c r="K103" s="20">
-        <f>F103-G103-H103-J103</f>
-        <v/>
-      </c>
-      <c r="L103" s="22">
-        <f>IF(F103=0,"",K103/F103)</f>
+      <c r="L103" s="20">
+        <f>K103*$B$4</f>
+        <v/>
+      </c>
+      <c r="M103" s="20">
+        <f>F103-I103-J103-L103</f>
+        <v/>
+      </c>
+      <c r="N103" s="22">
+        <f>IF(F103=0,"",M103/F103)</f>
         <v/>
       </c>
     </row>
@@ -6730,24 +7261,30 @@
         <v>511</v>
       </c>
       <c r="G104" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H104" s="20" t="n">
+        <v>221</v>
+      </c>
+      <c r="I104" s="20" t="n">
         <v>170</v>
       </c>
-      <c r="H104" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I104" s="21" t="n">
+      <c r="J104" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K104" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J104" s="20">
-        <f>I104*$B$4</f>
-        <v/>
-      </c>
-      <c r="K104" s="20">
-        <f>F104-G104-H104-J104</f>
-        <v/>
-      </c>
-      <c r="L104" s="22">
-        <f>IF(F104=0,"",K104/F104)</f>
+      <c r="L104" s="20">
+        <f>K104*$B$4</f>
+        <v/>
+      </c>
+      <c r="M104" s="20">
+        <f>F104-I104-J104-L104</f>
+        <v/>
+      </c>
+      <c r="N104" s="22">
+        <f>IF(F104=0,"",M104/F104)</f>
         <v/>
       </c>
     </row>
@@ -6777,24 +7314,30 @@
         <v>433</v>
       </c>
       <c r="G105" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H105" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="I105" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="H105" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I105" s="21" t="n">
+      <c r="J105" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K105" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J105" s="20">
-        <f>I105*$B$4</f>
-        <v/>
-      </c>
-      <c r="K105" s="20">
-        <f>F105-G105-H105-J105</f>
-        <v/>
-      </c>
-      <c r="L105" s="22">
-        <f>IF(F105=0,"",K105/F105)</f>
+      <c r="L105" s="20">
+        <f>K105*$B$4</f>
+        <v/>
+      </c>
+      <c r="M105" s="20">
+        <f>F105-I105-J105-L105</f>
+        <v/>
+      </c>
+      <c r="N105" s="22">
+        <f>IF(F105=0,"",M105/F105)</f>
         <v/>
       </c>
     </row>
@@ -6824,24 +7367,30 @@
         <v>439</v>
       </c>
       <c r="G106" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H106" s="20" t="n">
+        <v>221</v>
+      </c>
+      <c r="I106" s="20" t="n">
         <v>170</v>
       </c>
-      <c r="H106" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I106" s="21" t="n">
+      <c r="J106" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K106" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J106" s="20">
-        <f>I106*$B$4</f>
-        <v/>
-      </c>
-      <c r="K106" s="20">
-        <f>F106-G106-H106-J106</f>
-        <v/>
-      </c>
-      <c r="L106" s="22">
-        <f>IF(F106=0,"",K106/F106)</f>
+      <c r="L106" s="20">
+        <f>K106*$B$4</f>
+        <v/>
+      </c>
+      <c r="M106" s="20">
+        <f>F106-I106-J106-L106</f>
+        <v/>
+      </c>
+      <c r="N106" s="22">
+        <f>IF(F106=0,"",M106/F106)</f>
         <v/>
       </c>
     </row>
@@ -6871,24 +7420,30 @@
         <v>617</v>
       </c>
       <c r="G107" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H107" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I107" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H107" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I107" s="21" t="n">
+      <c r="J107" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K107" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J107" s="20">
-        <f>I107*$B$4</f>
-        <v/>
-      </c>
-      <c r="K107" s="20">
-        <f>F107-G107-H107-J107</f>
-        <v/>
-      </c>
-      <c r="L107" s="22">
-        <f>IF(F107=0,"",K107/F107)</f>
+      <c r="L107" s="20">
+        <f>K107*$B$4</f>
+        <v/>
+      </c>
+      <c r="M107" s="20">
+        <f>F107-I107-J107-L107</f>
+        <v/>
+      </c>
+      <c r="N107" s="22">
+        <f>IF(F107=0,"",M107/F107)</f>
         <v/>
       </c>
     </row>
@@ -6918,24 +7473,30 @@
         <v>478</v>
       </c>
       <c r="G108" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H108" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I108" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H108" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I108" s="21" t="n">
+      <c r="J108" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K108" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J108" s="20">
-        <f>I108*$B$4</f>
-        <v/>
-      </c>
-      <c r="K108" s="20">
-        <f>F108-G108-H108-J108</f>
-        <v/>
-      </c>
-      <c r="L108" s="22">
-        <f>IF(F108=0,"",K108/F108)</f>
+      <c r="L108" s="20">
+        <f>K108*$B$4</f>
+        <v/>
+      </c>
+      <c r="M108" s="20">
+        <f>F108-I108-J108-L108</f>
+        <v/>
+      </c>
+      <c r="N108" s="22">
+        <f>IF(F108=0,"",M108/F108)</f>
         <v/>
       </c>
     </row>
@@ -6965,24 +7526,30 @@
         <v>682</v>
       </c>
       <c r="G109" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H109" s="20" t="n">
+        <v>247</v>
+      </c>
+      <c r="I109" s="20" t="n">
         <v>190</v>
       </c>
-      <c r="H109" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I109" s="21" t="n">
+      <c r="J109" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K109" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J109" s="20">
-        <f>I109*$B$4</f>
-        <v/>
-      </c>
-      <c r="K109" s="20">
-        <f>F109-G109-H109-J109</f>
-        <v/>
-      </c>
-      <c r="L109" s="22">
-        <f>IF(F109=0,"",K109/F109)</f>
+      <c r="L109" s="20">
+        <f>K109*$B$4</f>
+        <v/>
+      </c>
+      <c r="M109" s="20">
+        <f>F109-I109-J109-L109</f>
+        <v/>
+      </c>
+      <c r="N109" s="22">
+        <f>IF(F109=0,"",M109/F109)</f>
         <v/>
       </c>
     </row>
@@ -7012,24 +7579,30 @@
         <v>571</v>
       </c>
       <c r="G110" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H110" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="I110" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H110" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I110" s="21" t="n">
+      <c r="J110" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K110" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J110" s="20">
-        <f>I110*$B$4</f>
-        <v/>
-      </c>
-      <c r="K110" s="20">
-        <f>F110-G110-H110-J110</f>
-        <v/>
-      </c>
-      <c r="L110" s="22">
-        <f>IF(F110=0,"",K110/F110)</f>
+      <c r="L110" s="20">
+        <f>K110*$B$4</f>
+        <v/>
+      </c>
+      <c r="M110" s="20">
+        <f>F110-I110-J110-L110</f>
+        <v/>
+      </c>
+      <c r="N110" s="22">
+        <f>IF(F110=0,"",M110/F110)</f>
         <v/>
       </c>
     </row>
@@ -7059,24 +7632,30 @@
         <v>493</v>
       </c>
       <c r="G111" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H111" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I111" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H111" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I111" s="21" t="n">
+      <c r="J111" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K111" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J111" s="20">
-        <f>I111*$B$4</f>
-        <v/>
-      </c>
-      <c r="K111" s="20">
-        <f>F111-G111-H111-J111</f>
-        <v/>
-      </c>
-      <c r="L111" s="22">
-        <f>IF(F111=0,"",K111/F111)</f>
+      <c r="L111" s="20">
+        <f>K111*$B$4</f>
+        <v/>
+      </c>
+      <c r="M111" s="20">
+        <f>F111-I111-J111-L111</f>
+        <v/>
+      </c>
+      <c r="N111" s="22">
+        <f>IF(F111=0,"",M111/F111)</f>
         <v/>
       </c>
     </row>
@@ -7106,24 +7685,30 @@
         <v>669</v>
       </c>
       <c r="G112" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H112" s="20" t="n">
+        <v>234</v>
+      </c>
+      <c r="I112" s="20" t="n">
         <v>180</v>
       </c>
-      <c r="H112" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I112" s="21" t="n">
+      <c r="J112" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K112" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J112" s="20">
-        <f>I112*$B$4</f>
-        <v/>
-      </c>
-      <c r="K112" s="20">
-        <f>F112-G112-H112-J112</f>
-        <v/>
-      </c>
-      <c r="L112" s="22">
-        <f>IF(F112=0,"",K112/F112)</f>
+      <c r="L112" s="20">
+        <f>K112*$B$4</f>
+        <v/>
+      </c>
+      <c r="M112" s="20">
+        <f>F112-I112-J112-L112</f>
+        <v/>
+      </c>
+      <c r="N112" s="22">
+        <f>IF(F112=0,"",M112/F112)</f>
         <v/>
       </c>
     </row>
@@ -7153,24 +7738,30 @@
         <v>322</v>
       </c>
       <c r="G113" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H113" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I113" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H113" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I113" s="21" t="n">
+      <c r="J113" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K113" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J113" s="20">
-        <f>I113*$B$4</f>
-        <v/>
-      </c>
-      <c r="K113" s="20">
-        <f>F113-G113-H113-J113</f>
-        <v/>
-      </c>
-      <c r="L113" s="22">
-        <f>IF(F113=0,"",K113/F113)</f>
+      <c r="L113" s="20">
+        <f>K113*$B$4</f>
+        <v/>
+      </c>
+      <c r="M113" s="20">
+        <f>F113-I113-J113-L113</f>
+        <v/>
+      </c>
+      <c r="N113" s="22">
+        <f>IF(F113=0,"",M113/F113)</f>
         <v/>
       </c>
     </row>
@@ -7200,24 +7791,30 @@
         <v>467</v>
       </c>
       <c r="G114" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H114" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I114" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H114" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I114" s="21" t="n">
+      <c r="J114" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K114" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J114" s="20">
-        <f>I114*$B$4</f>
-        <v/>
-      </c>
-      <c r="K114" s="20">
-        <f>F114-G114-H114-J114</f>
-        <v/>
-      </c>
-      <c r="L114" s="22">
-        <f>IF(F114=0,"",K114/F114)</f>
+      <c r="L114" s="20">
+        <f>K114*$B$4</f>
+        <v/>
+      </c>
+      <c r="M114" s="20">
+        <f>F114-I114-J114-L114</f>
+        <v/>
+      </c>
+      <c r="N114" s="22">
+        <f>IF(F114=0,"",M114/F114)</f>
         <v/>
       </c>
     </row>
@@ -7247,24 +7844,30 @@
         <v>537</v>
       </c>
       <c r="G115" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H115" s="20" t="n">
+        <v>247</v>
+      </c>
+      <c r="I115" s="20" t="n">
         <v>190</v>
       </c>
-      <c r="H115" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I115" s="21" t="n">
+      <c r="J115" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K115" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J115" s="20">
-        <f>I115*$B$4</f>
-        <v/>
-      </c>
-      <c r="K115" s="20">
-        <f>F115-G115-H115-J115</f>
-        <v/>
-      </c>
-      <c r="L115" s="22">
-        <f>IF(F115=0,"",K115/F115)</f>
+      <c r="L115" s="20">
+        <f>K115*$B$4</f>
+        <v/>
+      </c>
+      <c r="M115" s="20">
+        <f>F115-I115-J115-L115</f>
+        <v/>
+      </c>
+      <c r="N115" s="22">
+        <f>IF(F115=0,"",M115/F115)</f>
         <v/>
       </c>
     </row>
@@ -7294,24 +7897,30 @@
         <v>623</v>
       </c>
       <c r="G116" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H116" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I116" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H116" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I116" s="21" t="n">
+      <c r="J116" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K116" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J116" s="20">
-        <f>I116*$B$4</f>
-        <v/>
-      </c>
-      <c r="K116" s="20">
-        <f>F116-G116-H116-J116</f>
-        <v/>
-      </c>
-      <c r="L116" s="22">
-        <f>IF(F116=0,"",K116/F116)</f>
+      <c r="L116" s="20">
+        <f>K116*$B$4</f>
+        <v/>
+      </c>
+      <c r="M116" s="20">
+        <f>F116-I116-J116-L116</f>
+        <v/>
+      </c>
+      <c r="N116" s="22">
+        <f>IF(F116=0,"",M116/F116)</f>
         <v/>
       </c>
     </row>
@@ -7341,24 +7950,30 @@
         <v>472</v>
       </c>
       <c r="G117" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H117" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I117" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H117" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I117" s="21" t="n">
+      <c r="J117" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K117" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J117" s="20">
-        <f>I117*$B$4</f>
-        <v/>
-      </c>
-      <c r="K117" s="20">
-        <f>F117-G117-H117-J117</f>
-        <v/>
-      </c>
-      <c r="L117" s="22">
-        <f>IF(F117=0,"",K117/F117)</f>
+      <c r="L117" s="20">
+        <f>K117*$B$4</f>
+        <v/>
+      </c>
+      <c r="M117" s="20">
+        <f>F117-I117-J117-L117</f>
+        <v/>
+      </c>
+      <c r="N117" s="22">
+        <f>IF(F117=0,"",M117/F117)</f>
         <v/>
       </c>
     </row>
@@ -7388,24 +8003,30 @@
         <v>517</v>
       </c>
       <c r="G118" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H118" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I118" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H118" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I118" s="21" t="n">
+      <c r="J118" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K118" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J118" s="20">
-        <f>I118*$B$4</f>
-        <v/>
-      </c>
-      <c r="K118" s="20">
-        <f>F118-G118-H118-J118</f>
-        <v/>
-      </c>
-      <c r="L118" s="22">
-        <f>IF(F118=0,"",K118/F118)</f>
+      <c r="L118" s="20">
+        <f>K118*$B$4</f>
+        <v/>
+      </c>
+      <c r="M118" s="20">
+        <f>F118-I118-J118-L118</f>
+        <v/>
+      </c>
+      <c r="N118" s="22">
+        <f>IF(F118=0,"",M118/F118)</f>
         <v/>
       </c>
     </row>
@@ -7435,24 +8056,30 @@
         <v>526</v>
       </c>
       <c r="G119" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H119" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I119" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H119" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I119" s="21" t="n">
+      <c r="J119" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K119" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J119" s="20">
-        <f>I119*$B$4</f>
-        <v/>
-      </c>
-      <c r="K119" s="20">
-        <f>F119-G119-H119-J119</f>
-        <v/>
-      </c>
-      <c r="L119" s="22">
-        <f>IF(F119=0,"",K119/F119)</f>
+      <c r="L119" s="20">
+        <f>K119*$B$4</f>
+        <v/>
+      </c>
+      <c r="M119" s="20">
+        <f>F119-I119-J119-L119</f>
+        <v/>
+      </c>
+      <c r="N119" s="22">
+        <f>IF(F119=0,"",M119/F119)</f>
         <v/>
       </c>
     </row>
@@ -7482,24 +8109,30 @@
         <v>658</v>
       </c>
       <c r="G120" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H120" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I120" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H120" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I120" s="21" t="n">
+      <c r="J120" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K120" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J120" s="20">
-        <f>I120*$B$4</f>
-        <v/>
-      </c>
-      <c r="K120" s="20">
-        <f>F120-G120-H120-J120</f>
-        <v/>
-      </c>
-      <c r="L120" s="22">
-        <f>IF(F120=0,"",K120/F120)</f>
+      <c r="L120" s="20">
+        <f>K120*$B$4</f>
+        <v/>
+      </c>
+      <c r="M120" s="20">
+        <f>F120-I120-J120-L120</f>
+        <v/>
+      </c>
+      <c r="N120" s="22">
+        <f>IF(F120=0,"",M120/F120)</f>
         <v/>
       </c>
     </row>
@@ -7529,24 +8162,30 @@
         <v>420</v>
       </c>
       <c r="G121" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H121" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I121" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H121" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I121" s="21" t="n">
+      <c r="J121" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K121" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J121" s="20">
-        <f>I121*$B$4</f>
-        <v/>
-      </c>
-      <c r="K121" s="20">
-        <f>F121-G121-H121-J121</f>
-        <v/>
-      </c>
-      <c r="L121" s="22">
-        <f>IF(F121=0,"",K121/F121)</f>
+      <c r="L121" s="20">
+        <f>K121*$B$4</f>
+        <v/>
+      </c>
+      <c r="M121" s="20">
+        <f>F121-I121-J121-L121</f>
+        <v/>
+      </c>
+      <c r="N121" s="22">
+        <f>IF(F121=0,"",M121/F121)</f>
         <v/>
       </c>
     </row>
@@ -7576,24 +8215,30 @@
         <v>656</v>
       </c>
       <c r="G122" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H122" s="20" t="n">
+        <v>221</v>
+      </c>
+      <c r="I122" s="20" t="n">
         <v>170</v>
       </c>
-      <c r="H122" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I122" s="21" t="n">
+      <c r="J122" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K122" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J122" s="20">
-        <f>I122*$B$4</f>
-        <v/>
-      </c>
-      <c r="K122" s="20">
-        <f>F122-G122-H122-J122</f>
-        <v/>
-      </c>
-      <c r="L122" s="22">
-        <f>IF(F122=0,"",K122/F122)</f>
+      <c r="L122" s="20">
+        <f>K122*$B$4</f>
+        <v/>
+      </c>
+      <c r="M122" s="20">
+        <f>F122-I122-J122-L122</f>
+        <v/>
+      </c>
+      <c r="N122" s="22">
+        <f>IF(F122=0,"",M122/F122)</f>
         <v/>
       </c>
     </row>
@@ -7623,24 +8268,30 @@
         <v>446</v>
       </c>
       <c r="G123" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H123" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I123" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H123" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I123" s="21" t="n">
+      <c r="J123" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K123" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J123" s="20">
-        <f>I123*$B$4</f>
-        <v/>
-      </c>
-      <c r="K123" s="20">
-        <f>F123-G123-H123-J123</f>
-        <v/>
-      </c>
-      <c r="L123" s="22">
-        <f>IF(F123=0,"",K123/F123)</f>
+      <c r="L123" s="20">
+        <f>K123*$B$4</f>
+        <v/>
+      </c>
+      <c r="M123" s="20">
+        <f>F123-I123-J123-L123</f>
+        <v/>
+      </c>
+      <c r="N123" s="22">
+        <f>IF(F123=0,"",M123/F123)</f>
         <v/>
       </c>
     </row>
@@ -7670,24 +8321,30 @@
         <v>327</v>
       </c>
       <c r="G124" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H124" s="20" t="n">
+        <v>182</v>
+      </c>
+      <c r="I124" s="20" t="n">
         <v>140</v>
       </c>
-      <c r="H124" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I124" s="21" t="n">
+      <c r="J124" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K124" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J124" s="20">
-        <f>I124*$B$4</f>
-        <v/>
-      </c>
-      <c r="K124" s="20">
-        <f>F124-G124-H124-J124</f>
-        <v/>
-      </c>
-      <c r="L124" s="22">
-        <f>IF(F124=0,"",K124/F124)</f>
+      <c r="L124" s="20">
+        <f>K124*$B$4</f>
+        <v/>
+      </c>
+      <c r="M124" s="20">
+        <f>F124-I124-J124-L124</f>
+        <v/>
+      </c>
+      <c r="N124" s="22">
+        <f>IF(F124=0,"",M124/F124)</f>
         <v/>
       </c>
     </row>
@@ -7717,24 +8374,30 @@
         <v>441</v>
       </c>
       <c r="G125" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H125" s="20" t="n">
+        <v>78</v>
+      </c>
+      <c r="I125" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H125" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I125" s="21" t="n">
+      <c r="J125" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K125" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J125" s="20">
-        <f>I125*$B$4</f>
-        <v/>
-      </c>
-      <c r="K125" s="20">
-        <f>F125-G125-H125-J125</f>
-        <v/>
-      </c>
-      <c r="L125" s="22">
-        <f>IF(F125=0,"",K125/F125)</f>
+      <c r="L125" s="20">
+        <f>K125*$B$4</f>
+        <v/>
+      </c>
+      <c r="M125" s="20">
+        <f>F125-I125-J125-L125</f>
+        <v/>
+      </c>
+      <c r="N125" s="22">
+        <f>IF(F125=0,"",M125/F125)</f>
         <v/>
       </c>
     </row>
@@ -7764,24 +8427,30 @@
         <v>402</v>
       </c>
       <c r="G126" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H126" s="20" t="n">
+        <v>39</v>
+      </c>
+      <c r="I126" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H126" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I126" s="21" t="n">
+      <c r="J126" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K126" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J126" s="20">
-        <f>I126*$B$4</f>
-        <v/>
-      </c>
-      <c r="K126" s="20">
-        <f>F126-G126-H126-J126</f>
-        <v/>
-      </c>
-      <c r="L126" s="22">
-        <f>IF(F126=0,"",K126/F126)</f>
+      <c r="L126" s="20">
+        <f>K126*$B$4</f>
+        <v/>
+      </c>
+      <c r="M126" s="20">
+        <f>F126-I126-J126-L126</f>
+        <v/>
+      </c>
+      <c r="N126" s="22">
+        <f>IF(F126=0,"",M126/F126)</f>
         <v/>
       </c>
     </row>
@@ -7811,24 +8480,30 @@
         <v>710</v>
       </c>
       <c r="G127" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H127" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I127" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H127" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I127" s="21" t="n">
+      <c r="J127" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K127" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J127" s="20">
-        <f>I127*$B$4</f>
-        <v/>
-      </c>
-      <c r="K127" s="20">
-        <f>F127-G127-H127-J127</f>
-        <v/>
-      </c>
-      <c r="L127" s="22">
-        <f>IF(F127=0,"",K127/F127)</f>
+      <c r="L127" s="20">
+        <f>K127*$B$4</f>
+        <v/>
+      </c>
+      <c r="M127" s="20">
+        <f>F127-I127-J127-L127</f>
+        <v/>
+      </c>
+      <c r="N127" s="22">
+        <f>IF(F127=0,"",M127/F127)</f>
         <v/>
       </c>
     </row>
@@ -7858,24 +8533,30 @@
         <v>355</v>
       </c>
       <c r="G128" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H128" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I128" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H128" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I128" s="21" t="n">
+      <c r="J128" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K128" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J128" s="20">
-        <f>I128*$B$4</f>
-        <v/>
-      </c>
-      <c r="K128" s="20">
-        <f>F128-G128-H128-J128</f>
-        <v/>
-      </c>
-      <c r="L128" s="22">
-        <f>IF(F128=0,"",K128/F128)</f>
+      <c r="L128" s="20">
+        <f>K128*$B$4</f>
+        <v/>
+      </c>
+      <c r="M128" s="20">
+        <f>F128-I128-J128-L128</f>
+        <v/>
+      </c>
+      <c r="N128" s="22">
+        <f>IF(F128=0,"",M128/F128)</f>
         <v/>
       </c>
     </row>
@@ -7905,24 +8586,30 @@
         <v>335</v>
       </c>
       <c r="G129" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H129" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I129" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H129" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I129" s="21" t="n">
+      <c r="J129" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K129" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J129" s="20">
-        <f>I129*$B$4</f>
-        <v/>
-      </c>
-      <c r="K129" s="20">
-        <f>F129-G129-H129-J129</f>
-        <v/>
-      </c>
-      <c r="L129" s="22">
-        <f>IF(F129=0,"",K129/F129)</f>
+      <c r="L129" s="20">
+        <f>K129*$B$4</f>
+        <v/>
+      </c>
+      <c r="M129" s="20">
+        <f>F129-I129-J129-L129</f>
+        <v/>
+      </c>
+      <c r="N129" s="22">
+        <f>IF(F129=0,"",M129/F129)</f>
         <v/>
       </c>
     </row>
@@ -7952,24 +8639,30 @@
         <v>301</v>
       </c>
       <c r="G130" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H130" s="20" t="n">
+        <v>156</v>
+      </c>
+      <c r="I130" s="20" t="n">
         <v>120</v>
       </c>
-      <c r="H130" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I130" s="21" t="n">
+      <c r="J130" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K130" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J130" s="20">
-        <f>I130*$B$4</f>
-        <v/>
-      </c>
-      <c r="K130" s="20">
-        <f>F130-G130-H130-J130</f>
-        <v/>
-      </c>
-      <c r="L130" s="22">
-        <f>IF(F130=0,"",K130/F130)</f>
+      <c r="L130" s="20">
+        <f>K130*$B$4</f>
+        <v/>
+      </c>
+      <c r="M130" s="20">
+        <f>F130-I130-J130-L130</f>
+        <v/>
+      </c>
+      <c r="N130" s="22">
+        <f>IF(F130=0,"",M130/F130)</f>
         <v/>
       </c>
     </row>
@@ -7999,24 +8692,30 @@
         <v>734</v>
       </c>
       <c r="G131" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H131" s="20" t="n">
+        <v>299</v>
+      </c>
+      <c r="I131" s="20" t="n">
         <v>230</v>
       </c>
-      <c r="H131" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I131" s="21" t="n">
+      <c r="J131" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K131" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J131" s="20">
-        <f>I131*$B$4</f>
-        <v/>
-      </c>
-      <c r="K131" s="20">
-        <f>F131-G131-H131-J131</f>
-        <v/>
-      </c>
-      <c r="L131" s="22">
-        <f>IF(F131=0,"",K131/F131)</f>
+      <c r="L131" s="20">
+        <f>K131*$B$4</f>
+        <v/>
+      </c>
+      <c r="M131" s="20">
+        <f>F131-I131-J131-L131</f>
+        <v/>
+      </c>
+      <c r="N131" s="22">
+        <f>IF(F131=0,"",M131/F131)</f>
         <v/>
       </c>
     </row>
@@ -8046,24 +8745,30 @@
         <v>270</v>
       </c>
       <c r="G132" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H132" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I132" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H132" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I132" s="21" t="n">
+      <c r="J132" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K132" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J132" s="20">
-        <f>I132*$B$4</f>
-        <v/>
-      </c>
-      <c r="K132" s="20">
-        <f>F132-G132-H132-J132</f>
-        <v/>
-      </c>
-      <c r="L132" s="22">
-        <f>IF(F132=0,"",K132/F132)</f>
+      <c r="L132" s="20">
+        <f>K132*$B$4</f>
+        <v/>
+      </c>
+      <c r="M132" s="20">
+        <f>F132-I132-J132-L132</f>
+        <v/>
+      </c>
+      <c r="N132" s="22">
+        <f>IF(F132=0,"",M132/F132)</f>
         <v/>
       </c>
     </row>
@@ -8093,24 +8798,30 @@
         <v>394</v>
       </c>
       <c r="G133" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H133" s="20" t="n">
+        <v>104</v>
+      </c>
+      <c r="I133" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H133" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I133" s="21" t="n">
+      <c r="J133" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K133" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J133" s="20">
-        <f>I133*$B$4</f>
-        <v/>
-      </c>
-      <c r="K133" s="20">
-        <f>F133-G133-H133-J133</f>
-        <v/>
-      </c>
-      <c r="L133" s="22">
-        <f>IF(F133=0,"",K133/F133)</f>
+      <c r="L133" s="20">
+        <f>K133*$B$4</f>
+        <v/>
+      </c>
+      <c r="M133" s="20">
+        <f>F133-I133-J133-L133</f>
+        <v/>
+      </c>
+      <c r="N133" s="22">
+        <f>IF(F133=0,"",M133/F133)</f>
         <v/>
       </c>
     </row>
@@ -8140,24 +8851,30 @@
         <v>288</v>
       </c>
       <c r="G134" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H134" s="20" t="n">
+        <v>143</v>
+      </c>
+      <c r="I134" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="H134" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I134" s="21" t="n">
+      <c r="J134" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K134" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J134" s="20">
-        <f>I134*$B$4</f>
-        <v/>
-      </c>
-      <c r="K134" s="20">
-        <f>F134-G134-H134-J134</f>
-        <v/>
-      </c>
-      <c r="L134" s="22">
-        <f>IF(F134=0,"",K134/F134)</f>
+      <c r="L134" s="20">
+        <f>K134*$B$4</f>
+        <v/>
+      </c>
+      <c r="M134" s="20">
+        <f>F134-I134-J134-L134</f>
+        <v/>
+      </c>
+      <c r="N134" s="22">
+        <f>IF(F134=0,"",M134/F134)</f>
         <v/>
       </c>
     </row>
@@ -8187,24 +8904,30 @@
         <v>493</v>
       </c>
       <c r="G135" s="20" t="n">
+        <v>363</v>
+      </c>
+      <c r="H135" s="20" t="n">
+        <v>130</v>
+      </c>
+      <c r="I135" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H135" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I135" s="21" t="n">
+      <c r="J135" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K135" s="21" t="n">
         <v>2.5</v>
       </c>
-      <c r="J135" s="20">
-        <f>I135*$B$4</f>
-        <v/>
-      </c>
-      <c r="K135" s="20">
-        <f>F135-G135-H135-J135</f>
-        <v/>
-      </c>
-      <c r="L135" s="22">
-        <f>IF(F135=0,"",K135/F135)</f>
+      <c r="L135" s="20">
+        <f>K135*$B$4</f>
+        <v/>
+      </c>
+      <c r="M135" s="20">
+        <f>F135-I135-J135-L135</f>
+        <v/>
+      </c>
+      <c r="N135" s="22">
+        <f>IF(F135=0,"",M135/F135)</f>
         <v/>
       </c>
     </row>
@@ -8234,24 +8957,30 @@
         <v>314</v>
       </c>
       <c r="G136" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H136" s="20" t="n">
+        <v>169</v>
+      </c>
+      <c r="I136" s="20" t="n">
         <v>130</v>
       </c>
-      <c r="H136" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I136" s="21" t="n">
+      <c r="J136" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K136" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J136" s="20">
-        <f>I136*$B$4</f>
-        <v/>
-      </c>
-      <c r="K136" s="20">
-        <f>F136-G136-H136-J136</f>
-        <v/>
-      </c>
-      <c r="L136" s="22">
-        <f>IF(F136=0,"",K136/F136)</f>
+      <c r="L136" s="20">
+        <f>K136*$B$4</f>
+        <v/>
+      </c>
+      <c r="M136" s="20">
+        <f>F136-I136-J136-L136</f>
+        <v/>
+      </c>
+      <c r="N136" s="22">
+        <f>IF(F136=0,"",M136/F136)</f>
         <v/>
       </c>
     </row>
@@ -8281,24 +9010,30 @@
         <v>340</v>
       </c>
       <c r="G137" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H137" s="20" t="n">
+        <v>195</v>
+      </c>
+      <c r="I137" s="20" t="n">
         <v>150</v>
       </c>
-      <c r="H137" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I137" s="21" t="n">
+      <c r="J137" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K137" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J137" s="20">
-        <f>I137*$B$4</f>
-        <v/>
-      </c>
-      <c r="K137" s="20">
-        <f>F137-G137-H137-J137</f>
-        <v/>
-      </c>
-      <c r="L137" s="22">
-        <f>IF(F137=0,"",K137/F137)</f>
+      <c r="L137" s="20">
+        <f>K137*$B$4</f>
+        <v/>
+      </c>
+      <c r="M137" s="20">
+        <f>F137-I137-J137-L137</f>
+        <v/>
+      </c>
+      <c r="N137" s="22">
+        <f>IF(F137=0,"",M137/F137)</f>
         <v/>
       </c>
     </row>
@@ -8328,24 +9063,30 @@
         <v>262</v>
       </c>
       <c r="G138" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H138" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I138" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H138" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I138" s="21" t="n">
+      <c r="J138" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K138" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J138" s="20">
-        <f>I138*$B$4</f>
-        <v/>
-      </c>
-      <c r="K138" s="20">
-        <f>F138-G138-H138-J138</f>
-        <v/>
-      </c>
-      <c r="L138" s="22">
-        <f>IF(F138=0,"",K138/F138)</f>
+      <c r="L138" s="20">
+        <f>K138*$B$4</f>
+        <v/>
+      </c>
+      <c r="M138" s="20">
+        <f>F138-I138-J138-L138</f>
+        <v/>
+      </c>
+      <c r="N138" s="22">
+        <f>IF(F138=0,"",M138/F138)</f>
         <v/>
       </c>
     </row>
@@ -8375,24 +9116,30 @@
         <v>643</v>
       </c>
       <c r="G139" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H139" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="I139" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H139" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I139" s="21" t="n">
+      <c r="J139" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K139" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J139" s="20">
-        <f>I139*$B$4</f>
-        <v/>
-      </c>
-      <c r="K139" s="20">
-        <f>F139-G139-H139-J139</f>
-        <v/>
-      </c>
-      <c r="L139" s="22">
-        <f>IF(F139=0,"",K139/F139)</f>
+      <c r="L139" s="20">
+        <f>K139*$B$4</f>
+        <v/>
+      </c>
+      <c r="M139" s="20">
+        <f>F139-I139-J139-L139</f>
+        <v/>
+      </c>
+      <c r="N139" s="22">
+        <f>IF(F139=0,"",M139/F139)</f>
         <v/>
       </c>
     </row>
@@ -8422,24 +9169,30 @@
         <v>210</v>
       </c>
       <c r="G140" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H140" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I140" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H140" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I140" s="21" t="n">
+      <c r="J140" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K140" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J140" s="20">
-        <f>I140*$B$4</f>
-        <v/>
-      </c>
-      <c r="K140" s="20">
-        <f>F140-G140-H140-J140</f>
-        <v/>
-      </c>
-      <c r="L140" s="22">
-        <f>IF(F140=0,"",K140/F140)</f>
+      <c r="L140" s="20">
+        <f>K140*$B$4</f>
+        <v/>
+      </c>
+      <c r="M140" s="20">
+        <f>F140-I140-J140-L140</f>
+        <v/>
+      </c>
+      <c r="N140" s="22">
+        <f>IF(F140=0,"",M140/F140)</f>
         <v/>
       </c>
     </row>
@@ -8469,24 +9222,30 @@
         <v>526</v>
       </c>
       <c r="G141" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H141" s="20" t="n">
+        <v>91</v>
+      </c>
+      <c r="I141" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H141" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I141" s="21" t="n">
+      <c r="J141" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K141" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J141" s="20">
-        <f>I141*$B$4</f>
-        <v/>
-      </c>
-      <c r="K141" s="20">
-        <f>F141-G141-H141-J141</f>
-        <v/>
-      </c>
-      <c r="L141" s="22">
-        <f>IF(F141=0,"",K141/F141)</f>
+      <c r="L141" s="20">
+        <f>K141*$B$4</f>
+        <v/>
+      </c>
+      <c r="M141" s="20">
+        <f>F141-I141-J141-L141</f>
+        <v/>
+      </c>
+      <c r="N141" s="22">
+        <f>IF(F141=0,"",M141/F141)</f>
         <v/>
       </c>
     </row>
@@ -8516,24 +9275,30 @@
         <v>270</v>
       </c>
       <c r="G142" s="20" t="n">
+        <v>218</v>
+      </c>
+      <c r="H142" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I142" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H142" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I142" s="21" t="n">
+      <c r="J142" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K142" s="21" t="n">
         <v>1.5</v>
       </c>
-      <c r="J142" s="20">
-        <f>I142*$B$4</f>
-        <v/>
-      </c>
-      <c r="K142" s="20">
-        <f>F142-G142-H142-J142</f>
-        <v/>
-      </c>
-      <c r="L142" s="22">
-        <f>IF(F142=0,"",K142/F142)</f>
+      <c r="L142" s="20">
+        <f>K142*$B$4</f>
+        <v/>
+      </c>
+      <c r="M142" s="20">
+        <f>F142-I142-J142-L142</f>
+        <v/>
+      </c>
+      <c r="N142" s="22">
+        <f>IF(F142=0,"",M142/F142)</f>
         <v/>
       </c>
     </row>
@@ -8563,24 +9328,30 @@
         <v>342</v>
       </c>
       <c r="G143" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H143" s="20" t="n">
+        <v>52</v>
+      </c>
+      <c r="I143" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H143" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I143" s="21" t="n">
+      <c r="J143" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K143" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J143" s="20">
-        <f>I143*$B$4</f>
-        <v/>
-      </c>
-      <c r="K143" s="20">
-        <f>F143-G143-H143-J143</f>
-        <v/>
-      </c>
-      <c r="L143" s="22">
-        <f>IF(F143=0,"",K143/F143)</f>
+      <c r="L143" s="20">
+        <f>K143*$B$4</f>
+        <v/>
+      </c>
+      <c r="M143" s="20">
+        <f>F143-I143-J143-L143</f>
+        <v/>
+      </c>
+      <c r="N143" s="22">
+        <f>IF(F143=0,"",M143/F143)</f>
         <v/>
       </c>
     </row>
@@ -8610,24 +9381,30 @@
         <v>355</v>
       </c>
       <c r="G144" s="20" t="n">
+        <v>290</v>
+      </c>
+      <c r="H144" s="20" t="n">
+        <v>65</v>
+      </c>
+      <c r="I144" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H144" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I144" s="21" t="n">
+      <c r="J144" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K144" s="21" t="n">
         <v>2</v>
       </c>
-      <c r="J144" s="20">
-        <f>I144*$B$4</f>
-        <v/>
-      </c>
-      <c r="K144" s="20">
-        <f>F144-G144-H144-J144</f>
-        <v/>
-      </c>
-      <c r="L144" s="22">
-        <f>IF(F144=0,"",K144/F144)</f>
+      <c r="L144" s="20">
+        <f>K144*$B$4</f>
+        <v/>
+      </c>
+      <c r="M144" s="20">
+        <f>F144-I144-J144-L144</f>
+        <v/>
+      </c>
+      <c r="N144" s="22">
+        <f>IF(F144=0,"",M144/F144)</f>
         <v/>
       </c>
     </row>
@@ -8657,24 +9434,30 @@
         <v>552</v>
       </c>
       <c r="G145" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H145" s="20" t="n">
+        <v>117</v>
+      </c>
+      <c r="I145" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H145" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I145" s="21" t="n">
+      <c r="J145" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K145" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J145" s="20">
-        <f>I145*$B$4</f>
-        <v/>
-      </c>
-      <c r="K145" s="20">
-        <f>F145-G145-H145-J145</f>
-        <v/>
-      </c>
-      <c r="L145" s="22">
-        <f>IF(F145=0,"",K145/F145)</f>
+      <c r="L145" s="20">
+        <f>K145*$B$4</f>
+        <v/>
+      </c>
+      <c r="M145" s="20">
+        <f>F145-I145-J145-L145</f>
+        <v/>
+      </c>
+      <c r="N145" s="22">
+        <f>IF(F145=0,"",M145/F145)</f>
         <v/>
       </c>
     </row>
@@ -8704,24 +9487,30 @@
         <v>171</v>
       </c>
       <c r="G146" s="20" t="n">
+        <v>145</v>
+      </c>
+      <c r="H146" s="20" t="n">
+        <v>26</v>
+      </c>
+      <c r="I146" s="20" t="n">
         <v>20</v>
       </c>
-      <c r="H146" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I146" s="21" t="n">
+      <c r="J146" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K146" s="21" t="n">
         <v>1</v>
       </c>
-      <c r="J146" s="20">
-        <f>I146*$B$4</f>
-        <v/>
-      </c>
-      <c r="K146" s="20">
-        <f>F146-G146-H146-J146</f>
-        <v/>
-      </c>
-      <c r="L146" s="22">
-        <f>IF(F146=0,"",K146/F146)</f>
+      <c r="L146" s="20">
+        <f>K146*$B$4</f>
+        <v/>
+      </c>
+      <c r="M146" s="20">
+        <f>F146-I146-J146-L146</f>
+        <v/>
+      </c>
+      <c r="N146" s="22">
+        <f>IF(F146=0,"",M146/F146)</f>
         <v/>
       </c>
     </row>
@@ -8751,24 +9540,30 @@
         <v>695</v>
       </c>
       <c r="G147" s="20" t="n">
+        <v>435</v>
+      </c>
+      <c r="H147" s="20" t="n">
+        <v>260</v>
+      </c>
+      <c r="I147" s="20" t="n">
         <v>200</v>
       </c>
-      <c r="H147" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I147" s="21" t="n">
+      <c r="J147" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K147" s="21" t="n">
         <v>3</v>
       </c>
-      <c r="J147" s="20">
-        <f>I147*$B$4</f>
-        <v/>
-      </c>
-      <c r="K147" s="20">
-        <f>F147-G147-H147-J147</f>
-        <v/>
-      </c>
-      <c r="L147" s="22">
-        <f>IF(F147=0,"",K147/F147)</f>
+      <c r="L147" s="20">
+        <f>K147*$B$4</f>
+        <v/>
+      </c>
+      <c r="M147" s="20">
+        <f>F147-I147-J147-L147</f>
+        <v/>
+      </c>
+      <c r="N147" s="22">
+        <f>IF(F147=0,"",M147/F147)</f>
         <v/>
       </c>
     </row>
@@ -8798,24 +9593,30 @@
         <v>788</v>
       </c>
       <c r="G148" s="20" t="n">
+        <v>580</v>
+      </c>
+      <c r="H148" s="20" t="n">
+        <v>208</v>
+      </c>
+      <c r="I148" s="20" t="n">
         <v>160</v>
       </c>
-      <c r="H148" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I148" s="21" t="n">
+      <c r="J148" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K148" s="21" t="n">
         <v>4</v>
       </c>
-      <c r="J148" s="20">
-        <f>I148*$B$4</f>
-        <v/>
-      </c>
-      <c r="K148" s="20">
-        <f>F148-G148-H148-J148</f>
-        <v/>
-      </c>
-      <c r="L148" s="22">
-        <f>IF(F148=0,"",K148/F148)</f>
+      <c r="L148" s="20">
+        <f>K148*$B$4</f>
+        <v/>
+      </c>
+      <c r="M148" s="20">
+        <f>F148-I148-J148-L148</f>
+        <v/>
+      </c>
+      <c r="N148" s="22">
+        <f>IF(F148=0,"",M148/F148)</f>
         <v/>
       </c>
     </row>
@@ -8844,25 +9645,27 @@
       <c r="F149" s="20" t="n">
         <v>21300</v>
       </c>
-      <c r="G149" s="20" t="n">
+      <c r="G149" s="20" t="n"/>
+      <c r="H149" s="20" t="n"/>
+      <c r="I149" s="20" t="n">
         <v>8100</v>
       </c>
-      <c r="H149" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I149" s="21" t="n">
+      <c r="J149" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K149" s="21" t="n">
         <v>70</v>
       </c>
-      <c r="J149" s="20">
-        <f>I149*$B$4</f>
-        <v/>
-      </c>
-      <c r="K149" s="20">
-        <f>F149-G149-H149-J149</f>
-        <v/>
-      </c>
-      <c r="L149" s="22">
-        <f>IF(F149=0,"",K149/F149)</f>
+      <c r="L149" s="20">
+        <f>K149*$B$4</f>
+        <v/>
+      </c>
+      <c r="M149" s="20">
+        <f>F149-I149-J149-L149</f>
+        <v/>
+      </c>
+      <c r="N149" s="22">
+        <f>IF(F149=0,"",M149/F149)</f>
         <v/>
       </c>
     </row>
@@ -8891,25 +9694,27 @@
       <c r="F150" s="20" t="n">
         <v>16800</v>
       </c>
-      <c r="G150" s="20" t="n">
+      <c r="G150" s="20" t="n"/>
+      <c r="H150" s="20" t="n"/>
+      <c r="I150" s="20" t="n">
         <v>6700</v>
       </c>
-      <c r="H150" s="20" t="n">
+      <c r="J150" s="20" t="n">
         <v>1200</v>
       </c>
-      <c r="I150" s="21" t="n">
+      <c r="K150" s="21" t="n">
         <v>44</v>
       </c>
-      <c r="J150" s="20">
-        <f>I150*$B$4</f>
-        <v/>
-      </c>
-      <c r="K150" s="20">
-        <f>F150-G150-H150-J150</f>
-        <v/>
-      </c>
-      <c r="L150" s="22">
-        <f>IF(F150=0,"",K150/F150)</f>
+      <c r="L150" s="20">
+        <f>K150*$B$4</f>
+        <v/>
+      </c>
+      <c r="M150" s="20">
+        <f>F150-I150-J150-L150</f>
+        <v/>
+      </c>
+      <c r="N150" s="22">
+        <f>IF(F150=0,"",M150/F150)</f>
         <v/>
       </c>
     </row>
@@ -8938,25 +9743,27 @@
       <c r="F151" s="20" t="n">
         <v>38500</v>
       </c>
-      <c r="G151" s="20" t="n">
+      <c r="G151" s="20" t="n"/>
+      <c r="H151" s="20" t="n"/>
+      <c r="I151" s="20" t="n">
         <v>15600</v>
       </c>
-      <c r="H151" s="20" t="n">
+      <c r="J151" s="20" t="n">
         <v>4800</v>
       </c>
-      <c r="I151" s="21" t="n">
+      <c r="K151" s="21" t="n">
         <v>92</v>
       </c>
-      <c r="J151" s="20">
-        <f>I151*$B$4</f>
-        <v/>
-      </c>
-      <c r="K151" s="20">
-        <f>F151-G151-H151-J151</f>
-        <v/>
-      </c>
-      <c r="L151" s="22">
-        <f>IF(F151=0,"",K151/F151)</f>
+      <c r="L151" s="20">
+        <f>K151*$B$4</f>
+        <v/>
+      </c>
+      <c r="M151" s="20">
+        <f>F151-I151-J151-L151</f>
+        <v/>
+      </c>
+      <c r="N151" s="22">
+        <f>IF(F151=0,"",M151/F151)</f>
         <v/>
       </c>
     </row>
@@ -8985,25 +9792,27 @@
       <c r="F152" s="20" t="n">
         <v>13400</v>
       </c>
-      <c r="G152" s="20" t="n">
+      <c r="G152" s="20" t="n"/>
+      <c r="H152" s="20" t="n"/>
+      <c r="I152" s="20" t="n">
         <v>3900</v>
       </c>
-      <c r="H152" s="20" t="n">
+      <c r="J152" s="20" t="n">
         <v>1100</v>
       </c>
-      <c r="I152" s="21" t="n">
+      <c r="K152" s="21" t="n">
         <v>48</v>
       </c>
-      <c r="J152" s="20">
-        <f>I152*$B$4</f>
-        <v/>
-      </c>
-      <c r="K152" s="20">
-        <f>F152-G152-H152-J152</f>
-        <v/>
-      </c>
-      <c r="L152" s="22">
-        <f>IF(F152=0,"",K152/F152)</f>
+      <c r="L152" s="20">
+        <f>K152*$B$4</f>
+        <v/>
+      </c>
+      <c r="M152" s="20">
+        <f>F152-I152-J152-L152</f>
+        <v/>
+      </c>
+      <c r="N152" s="22">
+        <f>IF(F152=0,"",M152/F152)</f>
         <v/>
       </c>
     </row>
@@ -9032,25 +9841,27 @@
       <c r="F153" s="20" t="n">
         <v>19600</v>
       </c>
-      <c r="G153" s="20" t="n">
+      <c r="G153" s="20" t="n"/>
+      <c r="H153" s="20" t="n"/>
+      <c r="I153" s="20" t="n">
         <v>9400</v>
       </c>
-      <c r="H153" s="20" t="n">
+      <c r="J153" s="20" t="n">
         <v>2200</v>
       </c>
-      <c r="I153" s="21" t="n">
+      <c r="K153" s="21" t="n">
         <v>36</v>
       </c>
-      <c r="J153" s="20">
-        <f>I153*$B$4</f>
-        <v/>
-      </c>
-      <c r="K153" s="20">
-        <f>F153-G153-H153-J153</f>
-        <v/>
-      </c>
-      <c r="L153" s="22">
-        <f>IF(F153=0,"",K153/F153)</f>
+      <c r="L153" s="20">
+        <f>K153*$B$4</f>
+        <v/>
+      </c>
+      <c r="M153" s="20">
+        <f>F153-I153-J153-L153</f>
+        <v/>
+      </c>
+      <c r="N153" s="22">
+        <f>IF(F153=0,"",M153/F153)</f>
         <v/>
       </c>
     </row>
@@ -9079,25 +9890,27 @@
       <c r="F154" s="20" t="n">
         <v>3600</v>
       </c>
-      <c r="G154" s="20" t="n">
+      <c r="G154" s="20" t="n"/>
+      <c r="H154" s="20" t="n"/>
+      <c r="I154" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H154" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I154" s="21" t="n">
+      <c r="J154" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K154" s="21" t="n">
         <v>20</v>
       </c>
-      <c r="J154" s="20">
-        <f>I154*$B$4</f>
-        <v/>
-      </c>
-      <c r="K154" s="20">
-        <f>F154-G154-H154-J154</f>
-        <v/>
-      </c>
-      <c r="L154" s="22">
-        <f>IF(F154=0,"",K154/F154)</f>
+      <c r="L154" s="20">
+        <f>K154*$B$4</f>
+        <v/>
+      </c>
+      <c r="M154" s="20">
+        <f>F154-I154-J154-L154</f>
+        <v/>
+      </c>
+      <c r="N154" s="22">
+        <f>IF(F154=0,"",M154/F154)</f>
         <v/>
       </c>
     </row>
@@ -9126,25 +9939,27 @@
       <c r="F155" s="20" t="n">
         <v>2800</v>
       </c>
-      <c r="G155" s="20" t="n">
+      <c r="G155" s="20" t="n"/>
+      <c r="H155" s="20" t="n"/>
+      <c r="I155" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H155" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I155" s="21" t="n">
+      <c r="J155" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K155" s="21" t="n">
         <v>16</v>
       </c>
-      <c r="J155" s="20">
-        <f>I155*$B$4</f>
-        <v/>
-      </c>
-      <c r="K155" s="20">
-        <f>F155-G155-H155-J155</f>
-        <v/>
-      </c>
-      <c r="L155" s="22">
-        <f>IF(F155=0,"",K155/F155)</f>
+      <c r="L155" s="20">
+        <f>K155*$B$4</f>
+        <v/>
+      </c>
+      <c r="M155" s="20">
+        <f>F155-I155-J155-L155</f>
+        <v/>
+      </c>
+      <c r="N155" s="22">
+        <f>IF(F155=0,"",M155/F155)</f>
         <v/>
       </c>
     </row>
@@ -9173,25 +9988,27 @@
       <c r="F156" s="20" t="n">
         <v>1700</v>
       </c>
-      <c r="G156" s="20" t="n">
+      <c r="G156" s="20" t="n"/>
+      <c r="H156" s="20" t="n"/>
+      <c r="I156" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H156" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I156" s="21" t="n">
+      <c r="J156" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K156" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="J156" s="20">
-        <f>I156*$B$4</f>
-        <v/>
-      </c>
-      <c r="K156" s="20">
-        <f>F156-G156-H156-J156</f>
-        <v/>
-      </c>
-      <c r="L156" s="22">
-        <f>IF(F156=0,"",K156/F156)</f>
+      <c r="L156" s="20">
+        <f>K156*$B$4</f>
+        <v/>
+      </c>
+      <c r="M156" s="20">
+        <f>F156-I156-J156-L156</f>
+        <v/>
+      </c>
+      <c r="N156" s="22">
+        <f>IF(F156=0,"",M156/F156)</f>
         <v/>
       </c>
     </row>
@@ -9220,25 +10037,27 @@
       <c r="F157" s="20" t="n">
         <v>4100</v>
       </c>
-      <c r="G157" s="20" t="n">
+      <c r="G157" s="20" t="n"/>
+      <c r="H157" s="20" t="n"/>
+      <c r="I157" s="20" t="n">
         <v>100</v>
       </c>
-      <c r="H157" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I157" s="21" t="n">
+      <c r="J157" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K157" s="21" t="n">
         <v>23</v>
       </c>
-      <c r="J157" s="20">
-        <f>I157*$B$4</f>
-        <v/>
-      </c>
-      <c r="K157" s="20">
-        <f>F157-G157-H157-J157</f>
-        <v/>
-      </c>
-      <c r="L157" s="22">
-        <f>IF(F157=0,"",K157/F157)</f>
+      <c r="L157" s="20">
+        <f>K157*$B$4</f>
+        <v/>
+      </c>
+      <c r="M157" s="20">
+        <f>F157-I157-J157-L157</f>
+        <v/>
+      </c>
+      <c r="N157" s="22">
+        <f>IF(F157=0,"",M157/F157)</f>
         <v/>
       </c>
     </row>
@@ -9267,25 +10086,27 @@
       <c r="F158" s="20" t="n">
         <v>3400</v>
       </c>
-      <c r="G158" s="20" t="n">
+      <c r="G158" s="20" t="n"/>
+      <c r="H158" s="20" t="n"/>
+      <c r="I158" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H158" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I158" s="21" t="n">
+      <c r="J158" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K158" s="21" t="n">
         <v>19</v>
       </c>
-      <c r="J158" s="20">
-        <f>I158*$B$4</f>
-        <v/>
-      </c>
-      <c r="K158" s="20">
-        <f>F158-G158-H158-J158</f>
-        <v/>
-      </c>
-      <c r="L158" s="22">
-        <f>IF(F158=0,"",K158/F158)</f>
+      <c r="L158" s="20">
+        <f>K158*$B$4</f>
+        <v/>
+      </c>
+      <c r="M158" s="20">
+        <f>F158-I158-J158-L158</f>
+        <v/>
+      </c>
+      <c r="N158" s="22">
+        <f>IF(F158=0,"",M158/F158)</f>
         <v/>
       </c>
     </row>
@@ -9314,25 +10135,27 @@
       <c r="F159" s="20" t="n">
         <v>2400</v>
       </c>
-      <c r="G159" s="20" t="n">
+      <c r="G159" s="20" t="n"/>
+      <c r="H159" s="20" t="n"/>
+      <c r="I159" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H159" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I159" s="21" t="n">
+      <c r="J159" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K159" s="21" t="n">
         <v>14</v>
       </c>
-      <c r="J159" s="20">
-        <f>I159*$B$4</f>
-        <v/>
-      </c>
-      <c r="K159" s="20">
-        <f>F159-G159-H159-J159</f>
-        <v/>
-      </c>
-      <c r="L159" s="22">
-        <f>IF(F159=0,"",K159/F159)</f>
+      <c r="L159" s="20">
+        <f>K159*$B$4</f>
+        <v/>
+      </c>
+      <c r="M159" s="20">
+        <f>F159-I159-J159-L159</f>
+        <v/>
+      </c>
+      <c r="N159" s="22">
+        <f>IF(F159=0,"",M159/F159)</f>
         <v/>
       </c>
     </row>
@@ -9361,25 +10184,27 @@
       <c r="F160" s="20" t="n">
         <v>4200</v>
       </c>
-      <c r="G160" s="20" t="n">
+      <c r="G160" s="20" t="n"/>
+      <c r="H160" s="20" t="n"/>
+      <c r="I160" s="20" t="n">
         <v>90</v>
       </c>
-      <c r="H160" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I160" s="21" t="n">
+      <c r="J160" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K160" s="21" t="n">
         <v>24</v>
       </c>
-      <c r="J160" s="20">
-        <f>I160*$B$4</f>
-        <v/>
-      </c>
-      <c r="K160" s="20">
-        <f>F160-G160-H160-J160</f>
-        <v/>
-      </c>
-      <c r="L160" s="22">
-        <f>IF(F160=0,"",K160/F160)</f>
+      <c r="L160" s="20">
+        <f>K160*$B$4</f>
+        <v/>
+      </c>
+      <c r="M160" s="20">
+        <f>F160-I160-J160-L160</f>
+        <v/>
+      </c>
+      <c r="N160" s="22">
+        <f>IF(F160=0,"",M160/F160)</f>
         <v/>
       </c>
     </row>
@@ -9408,25 +10233,27 @@
       <c r="F161" s="20" t="n">
         <v>1600</v>
       </c>
-      <c r="G161" s="20" t="n">
+      <c r="G161" s="20" t="n"/>
+      <c r="H161" s="20" t="n"/>
+      <c r="I161" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H161" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I161" s="21" t="n">
+      <c r="J161" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K161" s="21" t="n">
         <v>9</v>
       </c>
-      <c r="J161" s="20">
-        <f>I161*$B$4</f>
-        <v/>
-      </c>
-      <c r="K161" s="20">
-        <f>F161-G161-H161-J161</f>
-        <v/>
-      </c>
-      <c r="L161" s="22">
-        <f>IF(F161=0,"",K161/F161)</f>
+      <c r="L161" s="20">
+        <f>K161*$B$4</f>
+        <v/>
+      </c>
+      <c r="M161" s="20">
+        <f>F161-I161-J161-L161</f>
+        <v/>
+      </c>
+      <c r="N161" s="22">
+        <f>IF(F161=0,"",M161/F161)</f>
         <v/>
       </c>
     </row>
@@ -9455,25 +10282,27 @@
       <c r="F162" s="20" t="n">
         <v>3200</v>
       </c>
-      <c r="G162" s="20" t="n">
+      <c r="G162" s="20" t="n"/>
+      <c r="H162" s="20" t="n"/>
+      <c r="I162" s="20" t="n">
         <v>60</v>
       </c>
-      <c r="H162" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I162" s="21" t="n">
+      <c r="J162" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K162" s="21" t="n">
         <v>18</v>
       </c>
-      <c r="J162" s="20">
-        <f>I162*$B$4</f>
-        <v/>
-      </c>
-      <c r="K162" s="20">
-        <f>F162-G162-H162-J162</f>
-        <v/>
-      </c>
-      <c r="L162" s="22">
-        <f>IF(F162=0,"",K162/F162)</f>
+      <c r="L162" s="20">
+        <f>K162*$B$4</f>
+        <v/>
+      </c>
+      <c r="M162" s="20">
+        <f>F162-I162-J162-L162</f>
+        <v/>
+      </c>
+      <c r="N162" s="22">
+        <f>IF(F162=0,"",M162/F162)</f>
         <v/>
       </c>
     </row>
@@ -9502,25 +10331,27 @@
       <c r="F163" s="20" t="n">
         <v>3900</v>
       </c>
-      <c r="G163" s="20" t="n">
+      <c r="G163" s="20" t="n"/>
+      <c r="H163" s="20" t="n"/>
+      <c r="I163" s="20" t="n">
         <v>110</v>
       </c>
-      <c r="H163" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I163" s="21" t="n">
+      <c r="J163" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K163" s="21" t="n">
         <v>22</v>
       </c>
-      <c r="J163" s="20">
-        <f>I163*$B$4</f>
-        <v/>
-      </c>
-      <c r="K163" s="20">
-        <f>F163-G163-H163-J163</f>
-        <v/>
-      </c>
-      <c r="L163" s="22">
-        <f>IF(F163=0,"",K163/F163)</f>
+      <c r="L163" s="20">
+        <f>K163*$B$4</f>
+        <v/>
+      </c>
+      <c r="M163" s="20">
+        <f>F163-I163-J163-L163</f>
+        <v/>
+      </c>
+      <c r="N163" s="22">
+        <f>IF(F163=0,"",M163/F163)</f>
         <v/>
       </c>
     </row>
@@ -9549,25 +10380,27 @@
       <c r="F164" s="20" t="n">
         <v>1800</v>
       </c>
-      <c r="G164" s="20" t="n">
+      <c r="G164" s="20" t="n"/>
+      <c r="H164" s="20" t="n"/>
+      <c r="I164" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H164" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I164" s="21" t="n">
+      <c r="J164" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K164" s="21" t="n">
         <v>10</v>
       </c>
-      <c r="J164" s="20">
-        <f>I164*$B$4</f>
-        <v/>
-      </c>
-      <c r="K164" s="20">
-        <f>F164-G164-H164-J164</f>
-        <v/>
-      </c>
-      <c r="L164" s="22">
-        <f>IF(F164=0,"",K164/F164)</f>
+      <c r="L164" s="20">
+        <f>K164*$B$4</f>
+        <v/>
+      </c>
+      <c r="M164" s="20">
+        <f>F164-I164-J164-L164</f>
+        <v/>
+      </c>
+      <c r="N164" s="22">
+        <f>IF(F164=0,"",M164/F164)</f>
         <v/>
       </c>
     </row>
@@ -9596,25 +10429,27 @@
       <c r="F165" s="20" t="n">
         <v>3000</v>
       </c>
-      <c r="G165" s="20" t="n">
+      <c r="G165" s="20" t="n"/>
+      <c r="H165" s="20" t="n"/>
+      <c r="I165" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="H165" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I165" s="21" t="n">
+      <c r="J165" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K165" s="21" t="n">
         <v>17</v>
       </c>
-      <c r="J165" s="20">
-        <f>I165*$B$4</f>
-        <v/>
-      </c>
-      <c r="K165" s="20">
-        <f>F165-G165-H165-J165</f>
-        <v/>
-      </c>
-      <c r="L165" s="22">
-        <f>IF(F165=0,"",K165/F165)</f>
+      <c r="L165" s="20">
+        <f>K165*$B$4</f>
+        <v/>
+      </c>
+      <c r="M165" s="20">
+        <f>F165-I165-J165-L165</f>
+        <v/>
+      </c>
+      <c r="N165" s="22">
+        <f>IF(F165=0,"",M165/F165)</f>
         <v/>
       </c>
     </row>
@@ -9643,25 +10478,27 @@
       <c r="F166" s="20" t="n">
         <v>2600</v>
       </c>
-      <c r="G166" s="20" t="n">
+      <c r="G166" s="20" t="n"/>
+      <c r="H166" s="20" t="n"/>
+      <c r="I166" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H166" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I166" s="21" t="n">
+      <c r="J166" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K166" s="21" t="n">
         <v>15</v>
       </c>
-      <c r="J166" s="20">
-        <f>I166*$B$4</f>
-        <v/>
-      </c>
-      <c r="K166" s="20">
-        <f>F166-G166-H166-J166</f>
-        <v/>
-      </c>
-      <c r="L166" s="22">
-        <f>IF(F166=0,"",K166/F166)</f>
+      <c r="L166" s="20">
+        <f>K166*$B$4</f>
+        <v/>
+      </c>
+      <c r="M166" s="20">
+        <f>F166-I166-J166-L166</f>
+        <v/>
+      </c>
+      <c r="N166" s="22">
+        <f>IF(F166=0,"",M166/F166)</f>
         <v/>
       </c>
     </row>
@@ -9690,25 +10527,27 @@
       <c r="F167" s="20" t="n">
         <v>2200</v>
       </c>
-      <c r="G167" s="20" t="n">
+      <c r="G167" s="20" t="n"/>
+      <c r="H167" s="20" t="n"/>
+      <c r="I167" s="20" t="n">
         <v>40</v>
       </c>
-      <c r="H167" s="20" t="n">
-        <v>0</v>
-      </c>
-      <c r="I167" s="21" t="n">
+      <c r="J167" s="20" t="n">
+        <v>0</v>
+      </c>
+      <c r="K167" s="21" t="n">
         <v>12</v>
       </c>
-      <c r="J167" s="20">
-        <f>I167*$B$4</f>
-        <v/>
-      </c>
-      <c r="K167" s="20">
-        <f>F167-G167-H167-J167</f>
-        <v/>
-      </c>
-      <c r="L167" s="22">
-        <f>IF(F167=0,"",K167/F167)</f>
+      <c r="L167" s="20">
+        <f>K167*$B$4</f>
+        <v/>
+      </c>
+      <c r="M167" s="20">
+        <f>F167-I167-J167-L167</f>
+        <v/>
+      </c>
+      <c r="N167" s="22">
+        <f>IF(F167=0,"",M167/F167)</f>
         <v/>
       </c>
     </row>
@@ -9730,7 +10569,7 @@
         <f>SUM(H7:H167)</f>
         <v/>
       </c>
-      <c r="I168" s="25">
+      <c r="I168" s="24">
         <f>SUM(I7:I167)</f>
         <v/>
       </c>
@@ -9738,13 +10577,21 @@
         <f>SUM(J7:J167)</f>
         <v/>
       </c>
-      <c r="K168" s="24">
+      <c r="K168" s="25">
         <f>SUM(K7:K167)</f>
         <v/>
       </c>
+      <c r="L168" s="24">
+        <f>SUM(L7:L167)</f>
+        <v/>
+      </c>
+      <c r="M168" s="24">
+        <f>SUM(M7:M167)</f>
+        <v/>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A6:L167"/>
+  <autoFilter ref="A6:N167"/>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -9757,10 +10604,10 @@
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="4" manualBreakCount="4">
-    <brk id="39" min="0" max="16383" man="1"/>
-    <brk id="78" min="0" max="16383" man="1"/>
+    <brk id="45" min="0" max="16383" man="1"/>
+    <brk id="89" min="0" max="16383" man="1"/>
     <brk id="90" min="0" max="16383" man="1"/>
-    <brk id="129" min="0" max="16383" man="1"/>
+    <brk id="134" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
@@ -11130,7 +11977,7 @@
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>✓ Jobs: 5 pages, 79% scale, no block split</t>
+          <t>✓ Jobs: 5 pages, 69% scale, no block split</t>
         </is>
       </c>
     </row>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -36,57 +36,69 @@
     <numFmt numFmtId="167" formatCode="yyyy-mm-dd"/>
     <numFmt numFmtId="168" formatCode="d mmm yyyy"/>
   </numFmts>
-  <fonts count="12">
+  <fonts count="13">
     <font>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <color theme="1"/>
+      <name val="Roboto"/>
       <sz val="11"/>
-      <scheme val="minor"/>
     </font>
     <font>
+      <name val="Roboto"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
       <sz val="14"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
       <sz val="9"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
       <sz val="12"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <i val="1"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <color rgb="002F7A5D"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <color rgb="005F6F63"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="0025342A"/>
     </font>
     <font>
+      <name val="Roboto"/>
       <b val="1"/>
       <i val="1"/>
       <color rgb="002F7A5D"/>
@@ -133,33 +145,33 @@
     </border>
   </borders>
   <cellStyleXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment indent="1"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="10" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="8" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="11" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="9" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="12" fillId="3" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="168" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
@@ -173,15 +185,15 @@
     <xf numFmtId="165" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="165" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="166" fontId="7" fillId="0" borderId="2" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="164" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -799,8 +811,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1315,8 +1327,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1710,8 +1722,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2035,8 +2047,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -10596,8 +10608,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11603,8 +11615,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12000,8 +12012,8 @@
   <pageMargins left="0.5" right="0.5" top="0.75" bottom="0.75" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
-    <oddHeader>&amp;L&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;8 trades-sample-statements.xlsx&amp;C&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -8,12 +8,13 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="The fourth sheet" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit and loss" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Chart lines" sheetId="2" state="hidden" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit and loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance sheet" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash flow" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Jobs" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Workings" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Assumptions" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames>
     <definedName name="Gross_margin_P_L">'The fourth sheet'!$B$6</definedName>
@@ -21,16 +22,16 @@
     <definedName name="Technician_time_on_jobs">'The fourth sheet'!$B$8</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'The fourth sheet'!$5:$5</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'The fourth sheet'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="1">'Profit and loss'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'Profit and loss'!$A$1:$D$31</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Balance sheet'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'Balance sheet'!$A$1:$D$24</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Cash flow'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Cash flow'!$A$1:$D$20</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Jobs'!$6:$6</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'Jobs'!$A$1:$N$168</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'Workings'!$A$1:$C$112</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="6">'Assumptions'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="2">'Profit and loss'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'Profit and loss'!$A$1:$D$31</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="3">'Balance sheet'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cash flow'!$4:$4</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow'!$A$1:$D$20</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'Jobs'!$6:$6</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'Jobs'!$A$1:$N$168</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'Workings'!$A$1:$C$112</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -331,7 +332,7 @@
                 </a:solidFill>
                 <a:latin typeface="Roboto"/>
               </a:rPr>
-              <a:t>Job gross margin on each installation invoiced in September 2026 · target 35.0%</a:t>
+              <a:t>Job gross margin on each installation invoiced in September 2026</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -426,6 +427,82 @@
         <axId val="10"/>
         <axId val="100"/>
       </barChart>
+      <scatterChart>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <v>Target 35.0%</v>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" w="19050">
+              <a:solidFill>
+                <a:srgbClr val="25342A"/>
+              </a:solidFill>
+              <a:prstDash val="dash"/>
+            </a:ln>
+          </spPr>
+          <marker>
+            <symbol val="none"/>
+            <spPr>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:prstDash val="solid"/>
+              </a:ln>
+            </spPr>
+          </marker>
+          <dLbls>
+            <dLbl>
+              <idx val="1"/>
+              <txPr>
+                <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+                <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                  <a:pPr>
+                    <a:defRPr sz="900" b="1">
+                      <a:solidFill>
+                        <a:srgbClr val="25342A"/>
+                      </a:solidFill>
+                      <a:latin typeface="Roboto"/>
+                    </a:defRPr>
+                  </a:pPr>
+                  <a:r>
+                    <a:t/>
+                  </a:r>
+                  <a:endParaRPr sz="900" b="1">
+                    <a:solidFill>
+                      <a:srgbClr val="25342A"/>
+                    </a:solidFill>
+                    <a:latin typeface="Roboto"/>
+                  </a:endParaRPr>
+                </a:p>
+              </txPr>
+              <dLblPos val="r"/>
+              <showLegendKey val="0"/>
+              <showVal val="0"/>
+              <showCatName val="0"/>
+              <showSerName val="1"/>
+              <showPercent val="0"/>
+            </dLbl>
+            <showLegendKey val="0"/>
+            <showVal val="0"/>
+            <showCatName val="0"/>
+            <showSerName val="0"/>
+            <showPercent val="0"/>
+          </dLbls>
+          <xVal>
+            <numRef>
+              <f>'Chart lines'!$B$4:$B$5</f>
+            </numRef>
+          </xVal>
+          <yVal>
+            <numRef>
+              <f>'Chart lines'!$C$4:$C$5</f>
+            </numRef>
+          </yVal>
+          <smooth val="0"/>
+        </ser>
+        <axId val="500"/>
+        <axId val="600"/>
+      </scatterChart>
       <catAx>
         <axId val="10"/>
         <scaling>
@@ -441,6 +518,8 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
+          <max val="0.5197999999999999"/>
+          <min val="0"/>
         </scaling>
         <delete val="1"/>
         <axPos val="l"/>
@@ -448,6 +527,33 @@
         <majorTickMark val="none"/>
         <minorTickMark val="none"/>
         <crossAx val="10"/>
+      </valAx>
+      <valAx>
+        <axId val="500"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="0.5197999999999999"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="t"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="600"/>
+      </valAx>
+      <valAx>
+        <axId val="600"/>
+        <scaling>
+          <orientation val="minMax"/>
+          <max val="1.08"/>
+          <min val="0"/>
+        </scaling>
+        <delete val="1"/>
+        <axPos val="r"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="500"/>
+        <crosses val="max"/>
       </valAx>
     </plotArea>
     <plotVisOnly val="1"/>
@@ -572,7 +678,7 @@
       <row>11</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="5400000" cy="2340000"/>
+    <ext cx="5400000" cy="2556000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="1" name="Chart 1"/>
@@ -955,7 +1061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -1198,7 +1304,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1209,6 +1315,51 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:C5"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Points for the target and break-even lines drawn on the charts (hidden sheet; edit the values on the chart's own sheet).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2"/>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>The fourth sheet: Job gross margin on each installation invoiced in September 2026: Target 35.0%</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="B4" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C4" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="B5" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1240,7 +1391,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -1907,7 +2058,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1916,7 +2067,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1948,7 +2099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -2302,7 +2453,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2311,7 +2462,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2343,7 +2494,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -2731,7 +2882,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2740,7 +2891,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2782,7 +2933,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -11291,7 +11442,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11310,7 +11461,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -11342,7 +11493,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -12302,7 +12453,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12317,7 +12468,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -12347,7 +12498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:35am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
         </is>
       </c>
     </row>
@@ -12700,7 +12851,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:35am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -1061,7 +1061,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1304,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1391,7 +1391,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2058,7 +2058,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2099,7 +2099,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2453,7 +2453,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2494,7 +2494,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -2882,7 +2882,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2933,7 +2933,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -11442,7 +11442,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11493,7 +11493,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -12453,7 +12453,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12498,7 +12498,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 10:07am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
         </is>
       </c>
     </row>
@@ -12598,7 +12598,7 @@
       </c>
       <c r="B14" s="33" t="inlineStr">
         <is>
-          <t>84 in total (every one is in the Excel download and CSV)</t>
+          <t>84 in total (every one is in the spreadsheet download and CSV)</t>
         </is>
       </c>
     </row>
@@ -12851,7 +12851,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 10:07am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>

--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -25,13 +25,13 @@
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Profit and loss'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'Profit and loss'!$A$1:$D$31</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Balance sheet'!$4:$4</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'Balance sheet'!$A$1:$D$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Cash flow'!$4:$4</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'Cash flow'!$A$1:$D$20</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="5">'Jobs'!$6:$6</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="5">'Jobs'!$A$1:$N$168</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="6">'Workings'!$A$1:$C$112</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="7">'Assumptions'!$A$1:$B$43</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -363,20 +363,6 @@
           </spPr>
           <invertIfNegative val="0"/>
           <dPt>
-            <idx val="3"/>
-            <spPr>
-              <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:srgbClr val="7D8790"/>
-              </a:solidFill>
-              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-                <a:solidFill>
-                  <a:srgbClr val="7D8790"/>
-                </a:solidFill>
-                <a:prstDash val="solid"/>
-              </a:ln>
-            </spPr>
-          </dPt>
-          <dPt>
             <idx val="4"/>
             <spPr>
               <a:solidFill xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
@@ -518,7 +504,7 @@
         <axId val="100"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5197999999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -532,7 +518,7 @@
         <axId val="500"/>
         <scaling>
           <orientation val="minMax"/>
-          <max val="0.5197999999999999"/>
+          <max val="0.5888"/>
           <min val="0"/>
         </scaling>
         <delete val="1"/>
@@ -1061,7 +1047,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -1304,7 +1290,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1391,7 +1377,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -1431,10 +1417,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>40500</v>
+        <v>45350</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -1448,10 +1434,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>130700</v>
+        <v>146300</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>109600</v>
+        <v>122800</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -1465,10 +1451,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>21543</v>
+        <v>24216</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>19872</v>
+        <v>22338</v>
       </c>
       <c r="D8" s="13">
         <f>B8-C8</f>
@@ -1559,10 +1545,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>-54600</v>
+        <v>-79587</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>-54600</v>
+        <v>-72352</v>
       </c>
       <c r="D14" s="13">
         <f>B14-C14</f>
@@ -1831,10 +1817,10 @@
         </is>
       </c>
       <c r="B30" s="15" t="n">
-        <v>-2524</v>
+        <v>-2058</v>
       </c>
       <c r="C30" s="15" t="n">
-        <v>-1019</v>
+        <v>-1710</v>
       </c>
       <c r="D30" s="16">
         <f>B30-C30</f>
@@ -2058,7 +2044,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2073,7 +2059,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D24"/>
+  <dimension ref="A1:D28"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="52" customWidth="1" min="1" max="1"/>
@@ -2099,7 +2085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -2139,10 +2125,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>59746</v>
+        <v>120228</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>65263</v>
+        <v>92859</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -2156,10 +2142,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>151063</v>
+        <v>185678</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>129819</v>
+        <v>159756</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -2269,10 +2255,10 @@
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>78060</v>
+        <v>85866</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>60830</v>
+        <v>66913</v>
       </c>
       <c r="D14" s="13">
         <f>B14-C14</f>
@@ -2282,14 +2268,14 @@
     <row r="15">
       <c r="A15" s="12" t="inlineStr">
         <is>
-          <t>Employee leave provisions</t>
+          <t>Wages owed (since the last pay run)</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>106000</v>
+        <v>37678</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>105100</v>
+        <v>27458</v>
       </c>
       <c r="D15" s="13">
         <f>B15-C15</f>
@@ -2299,14 +2285,14 @@
     <row r="16">
       <c r="A16" s="12" t="inlineStr">
         <is>
-          <t>Income tax payable</t>
+          <t>Super payable</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>35043</v>
+        <v>4523</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>32519</v>
+        <v>3296</v>
       </c>
       <c r="D16" s="13">
         <f>B16-C16</f>
@@ -2314,116 +2300,124 @@
       </c>
     </row>
     <row r="17">
-      <c r="A17" s="14" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>PAYG withholding payable</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="n">
+        <v>47754</v>
+      </c>
+      <c r="C17" s="7" t="n">
+        <v>31836</v>
+      </c>
+      <c r="D17" s="13">
+        <f>B17-C17</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>GST payable (net)</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="n">
+        <v>32817</v>
+      </c>
+      <c r="C18" s="7" t="n">
+        <v>22477</v>
+      </c>
+      <c r="D18" s="13">
+        <f>B18-C18</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>Employee leave provisions</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="n">
+        <v>106000</v>
+      </c>
+      <c r="C19" s="7" t="n">
+        <v>105100</v>
+      </c>
+      <c r="D19" s="13">
+        <f>B19-C19</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>Income tax payable</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="n">
+        <v>35268</v>
+      </c>
+      <c r="C20" s="7" t="n">
+        <v>33210</v>
+      </c>
+      <c r="D20" s="13">
+        <f>B20-C20</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>Total current liabilities</t>
         </is>
       </c>
-      <c r="B17" s="15">
-        <f>SUM(B14:B16)</f>
-        <v/>
-      </c>
-      <c r="C17" s="15">
-        <f>SUM(C14:C16)</f>
-        <v/>
-      </c>
-      <c r="D17" s="16">
-        <f>B17-C17</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" s="14" t="inlineStr">
+      <c r="B21" s="15">
+        <f>SUM(B14:B20)</f>
+        <v/>
+      </c>
+      <c r="C21" s="15">
+        <f>SUM(C14:C20)</f>
+        <v/>
+      </c>
+      <c r="D21" s="16">
+        <f>B21-C21</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="14" t="inlineStr">
         <is>
           <t>Equipment finance</t>
         </is>
       </c>
-      <c r="B18" s="15" t="n">
+      <c r="B22" s="15" t="n">
         <v>95000</v>
       </c>
-      <c r="C18" s="15" t="n">
+      <c r="C22" s="15" t="n">
         <v>100000</v>
       </c>
-      <c r="D18" s="16">
-        <f>B18-C18</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="14" t="inlineStr">
+      <c r="D22" s="16">
+        <f>B22-C22</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="14" t="inlineStr">
         <is>
           <t>Total liabilities</t>
         </is>
       </c>
-      <c r="B19" s="15">
-        <f>B17+B18</f>
-        <v/>
-      </c>
-      <c r="C19" s="15">
-        <f>C17+C18</f>
-        <v/>
-      </c>
-      <c r="D19" s="16">
-        <f>B19-C19</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" s="17" t="inlineStr">
-        <is>
-          <t>Net assets</t>
-        </is>
-      </c>
-      <c r="B20" s="18">
-        <f>B12-B19</f>
-        <v/>
-      </c>
-      <c r="C20" s="18">
-        <f>C12-C19</f>
-        <v/>
-      </c>
-      <c r="D20" s="19">
-        <f>B20-C20</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" s="11" t="inlineStr">
-        <is>
-          <t>Equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="12" t="inlineStr">
-        <is>
-          <t>Share capital</t>
-        </is>
-      </c>
-      <c r="B22" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="C22" s="7" t="n">
-        <v>10000</v>
-      </c>
-      <c r="D22" s="13">
-        <f>B22-C22</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" s="12" t="inlineStr">
-        <is>
-          <t>Retained earnings</t>
-        </is>
-      </c>
-      <c r="B23" s="7" t="n">
-        <v>228906</v>
-      </c>
-      <c r="C23" s="7" t="n">
-        <v>221333</v>
-      </c>
-      <c r="D23" s="13">
+      <c r="B23" s="15">
+        <f>B21+B22</f>
+        <v/>
+      </c>
+      <c r="C23" s="15">
+        <f>C21+C22</f>
+        <v/>
+      </c>
+      <c r="D23" s="16">
         <f>B23-C23</f>
         <v/>
       </c>
@@ -2431,19 +2425,79 @@
     <row r="24">
       <c r="A24" s="17" t="inlineStr">
         <is>
-          <t>Total equity</t>
+          <t>Net assets</t>
         </is>
       </c>
       <c r="B24" s="18">
-        <f>SUM(B22:B23)</f>
+        <f>B12-B23</f>
         <v/>
       </c>
       <c r="C24" s="18">
-        <f>SUM(C22:C23)</f>
+        <f>C12-C23</f>
         <v/>
       </c>
       <c r="D24" s="19">
         <f>B24-C24</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="11" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>Share capital</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="C26" s="7" t="n">
+        <v>10000</v>
+      </c>
+      <c r="D26" s="13">
+        <f>B26-C26</f>
+        <v/>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="n">
+        <v>193200</v>
+      </c>
+      <c r="C27" s="7" t="n">
+        <v>187025</v>
+      </c>
+      <c r="D27" s="13">
+        <f>B27-C27</f>
+        <v/>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="17" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B28" s="18">
+        <f>SUM(B26:B27)</f>
+        <v/>
+      </c>
+      <c r="C28" s="18">
+        <f>SUM(C26:C27)</f>
+        <v/>
+      </c>
+      <c r="D28" s="19">
+        <f>B28-C28</f>
         <v/>
       </c>
     </row>
@@ -2453,7 +2507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2494,7 +2548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -2534,10 +2588,10 @@
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>181093</v>
+        <v>222094</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>156273</v>
+        <v>191442</v>
       </c>
       <c r="D6" s="13">
         <f>B6-C6</f>
@@ -2551,10 +2605,10 @@
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>-92930</v>
+        <v>-102223</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>-97510</v>
+        <v>-107261</v>
       </c>
       <c r="D7" s="13">
         <f>B7-C7</f>
@@ -2568,10 +2622,10 @@
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>-75600</v>
+        <v>-73222</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>-75400</v>
+        <v>-73222</v>
       </c>
       <c r="D8" s="13">
         <f>B8-C8</f>
@@ -2598,7 +2652,7 @@
     <row r="10">
       <c r="A10" s="12" t="inlineStr">
         <is>
-          <t>Income tax paid</t>
+          <t>GST, PAYG and income tax paid (BAS)</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
@@ -2645,7 +2699,7 @@
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>-12000</v>
+        <v>-13200</v>
       </c>
       <c r="C13" s="7" t="n">
         <v>0</v>
@@ -2743,7 +2797,7 @@
         </is>
       </c>
       <c r="B19" s="15" t="n">
-        <v>65263</v>
+        <v>92859</v>
       </c>
       <c r="C19" s="15" t="n">
         <v>88000</v>
@@ -2882,7 +2936,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2933,7 +2987,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -3043,10 +3097,10 @@
         <v>46273</v>
       </c>
       <c r="F7" s="22" t="n">
-        <v>589</v>
+        <v>625</v>
       </c>
       <c r="G7" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H7" s="22" t="n">
         <v>299</v>
@@ -3093,13 +3147,13 @@
         <v>46282</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>539</v>
+        <v>593</v>
       </c>
       <c r="G8" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H8" s="22" t="n">
         <v>104</v>
@@ -3149,10 +3203,10 @@
         <v>46296</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="G9" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H9" s="22" t="n">
         <v>91</v>
@@ -3202,10 +3256,10 @@
         <v>46289</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>413</v>
+        <v>440</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H10" s="22" t="n">
         <v>195</v>
@@ -3255,10 +3309,10 @@
         <v>46269</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>775</v>
+        <v>847</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H11" s="22" t="n">
         <v>195</v>
@@ -3308,10 +3362,10 @@
         <v>46269</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H12" s="22" t="n">
         <v>130</v>
@@ -3361,10 +3415,10 @@
         <v>46310</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>775</v>
+        <v>847</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H13" s="22" t="n">
         <v>195</v>
@@ -3414,10 +3468,10 @@
         <v>46273</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H14" s="22" t="n">
         <v>78</v>
@@ -3467,10 +3521,10 @@
         <v>46280</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H15" s="22" t="n">
         <v>91</v>
@@ -3517,13 +3571,13 @@
         <v>46271</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H16" s="22" t="n">
         <v>104</v>
@@ -3573,10 +3627,10 @@
         <v>46288</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>589</v>
+        <v>625</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H17" s="22" t="n">
         <v>299</v>
@@ -3626,10 +3680,10 @@
         <v>46280</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>604</v>
+        <v>658</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H18" s="22" t="n">
         <v>169</v>
@@ -3679,10 +3733,10 @@
         <v>46296</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H19" s="22" t="n">
         <v>52</v>
@@ -3732,10 +3786,10 @@
         <v>46297</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>461</v>
+        <v>515</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H20" s="22" t="n">
         <v>26</v>
@@ -3782,13 +3836,13 @@
         <v>46282</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>46312</v>
+        <v>46314</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H21" s="22" t="n">
         <v>78</v>
@@ -3838,10 +3892,10 @@
         <v>46287</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>749</v>
+        <v>821</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H22" s="22" t="n">
         <v>169</v>
@@ -3891,10 +3945,10 @@
         <v>46293</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>801</v>
+        <v>873</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H23" s="22" t="n">
         <v>221</v>
@@ -3941,13 +3995,13 @@
         <v>46291</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H24" s="22" t="n">
         <v>104</v>
@@ -3994,13 +4048,13 @@
         <v>46291</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>46305</v>
+        <v>46307</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>374</v>
+        <v>401</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H25" s="22" t="n">
         <v>156</v>
@@ -4050,10 +4104,10 @@
         <v>46276</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="G26" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H26" s="22" t="n">
         <v>260</v>
@@ -4103,10 +4157,10 @@
         <v>46304</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>563</v>
+        <v>599</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H27" s="22" t="n">
         <v>273</v>
@@ -4153,13 +4207,13 @@
         <v>46293</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>46300</v>
+        <v>46301</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>606</v>
+        <v>678</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H28" s="22" t="n">
         <v>26</v>
@@ -4209,10 +4263,10 @@
         <v>46276</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>565</v>
+        <v>619</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H29" s="22" t="n">
         <v>130</v>
@@ -4259,13 +4313,13 @@
         <v>46278</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>643</v>
+        <v>697</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H30" s="22" t="n">
         <v>208</v>
@@ -4315,10 +4369,10 @@
         <v>46308</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H31" s="22" t="n">
         <v>52</v>
@@ -4368,10 +4422,10 @@
         <v>46316</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>597</v>
+        <v>642</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H32" s="22" t="n">
         <v>234</v>
@@ -4421,10 +4475,10 @@
         <v>46273</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>452</v>
+        <v>479</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H33" s="22" t="n">
         <v>234</v>
@@ -4474,10 +4528,10 @@
         <v>46274</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H34" s="22" t="n">
         <v>78</v>
@@ -4524,13 +4578,13 @@
         <v>46270</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>316</v>
+        <v>352</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H35" s="22" t="n">
         <v>26</v>
@@ -4577,13 +4631,13 @@
         <v>46278</v>
       </c>
       <c r="E36" s="21" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H36" s="22" t="n">
         <v>117</v>
@@ -4630,13 +4684,13 @@
         <v>46283</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>46285</v>
+        <v>46286</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="G37" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H37" s="22" t="n">
         <v>104</v>
@@ -4686,10 +4740,10 @@
         <v>46302</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H38" s="22" t="n">
         <v>91</v>
@@ -4739,10 +4793,10 @@
         <v>46288</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="G39" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H39" s="22" t="n">
         <v>117</v>
@@ -4789,13 +4843,13 @@
         <v>46277</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H40" s="22" t="n">
         <v>182</v>
@@ -4845,10 +4899,10 @@
         <v>46296</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H41" s="22" t="n">
         <v>260</v>
@@ -4898,10 +4952,10 @@
         <v>46290</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="G42" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H42" s="22" t="n">
         <v>143</v>
@@ -4948,13 +5002,13 @@
         <v>46278</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H43" s="22" t="n">
         <v>117</v>
@@ -5004,10 +5058,10 @@
         <v>46311</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="G44" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H44" s="22" t="n">
         <v>52</v>
@@ -5057,10 +5111,10 @@
         <v>46293</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>684</v>
+        <v>756</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H45" s="22" t="n">
         <v>104</v>
@@ -5110,10 +5164,10 @@
         <v>46282</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>645</v>
+        <v>717</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H46" s="22" t="n">
         <v>65</v>
@@ -5163,10 +5217,10 @@
         <v>46273</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>565</v>
+        <v>619</v>
       </c>
       <c r="G47" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H47" s="22" t="n">
         <v>130</v>
@@ -5216,10 +5270,10 @@
         <v>46273</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H48" s="22" t="n">
         <v>78</v>
@@ -5269,10 +5323,10 @@
         <v>46283</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="G49" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H49" s="22" t="n">
         <v>182</v>
@@ -5319,13 +5373,13 @@
         <v>46292</v>
       </c>
       <c r="E50" s="21" t="n">
-        <v>46306</v>
+        <v>46307</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H50" s="22" t="n">
         <v>260</v>
@@ -5372,13 +5426,13 @@
         <v>46291</v>
       </c>
       <c r="E51" s="21" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H51" s="22" t="n">
         <v>182</v>
@@ -5428,10 +5482,10 @@
         <v>46323</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H52" s="22" t="n">
         <v>299</v>
@@ -5481,10 +5535,10 @@
         <v>46287</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>643</v>
+        <v>697</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H53" s="22" t="n">
         <v>208</v>
@@ -5534,10 +5588,10 @@
         <v>46294</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H54" s="22" t="n">
         <v>130</v>
@@ -5587,10 +5641,10 @@
         <v>46267</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>309</v>
+        <v>336</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H55" s="22" t="n">
         <v>91</v>
@@ -5637,13 +5691,13 @@
         <v>46271</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H56" s="22" t="n">
         <v>156</v>
@@ -5693,10 +5747,10 @@
         <v>46279</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="G57" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H57" s="22" t="n">
         <v>26</v>
@@ -5746,10 +5800,10 @@
         <v>46275</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>736</v>
+        <v>808</v>
       </c>
       <c r="G58" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H58" s="22" t="n">
         <v>156</v>
@@ -5796,13 +5850,13 @@
         <v>46292</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F59" s="22" t="n">
-        <v>550</v>
+        <v>586</v>
       </c>
       <c r="G59" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H59" s="22" t="n">
         <v>260</v>
@@ -5852,10 +5906,10 @@
         <v>46289</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="G60" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H60" s="22" t="n">
         <v>104</v>
@@ -5905,10 +5959,10 @@
         <v>46294</v>
       </c>
       <c r="F61" s="22" t="n">
-        <v>348</v>
+        <v>375</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H61" s="22" t="n">
         <v>130</v>
@@ -5958,10 +6012,10 @@
         <v>46282</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>454</v>
+        <v>499</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H62" s="22" t="n">
         <v>91</v>
@@ -6008,13 +6062,13 @@
         <v>46284</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>46284</v>
+        <v>46286</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="G63" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H63" s="22" t="n">
         <v>91</v>
@@ -6061,13 +6115,13 @@
         <v>46284</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>46298</v>
+        <v>46301</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H64" s="22" t="n">
         <v>156</v>
@@ -6117,10 +6171,10 @@
         <v>46281</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="G65" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H65" s="22" t="n">
         <v>117</v>
@@ -6170,10 +6224,10 @@
         <v>46310</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>532</v>
+        <v>577</v>
       </c>
       <c r="G66" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H66" s="22" t="n">
         <v>169</v>
@@ -6220,13 +6274,13 @@
         <v>46270</v>
       </c>
       <c r="E67" s="21" t="n">
-        <v>46277</v>
+        <v>46279</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>459</v>
+        <v>495</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H67" s="22" t="n">
         <v>169</v>
@@ -6276,10 +6330,10 @@
         <v>46294</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>734</v>
+        <v>788</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H68" s="22" t="n">
         <v>299</v>
@@ -6329,10 +6383,10 @@
         <v>46269</v>
       </c>
       <c r="F69" s="22" t="n">
-        <v>444</v>
+        <v>462</v>
       </c>
       <c r="G69" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H69" s="22" t="n">
         <v>299</v>
@@ -6382,10 +6436,10 @@
         <v>46317</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>762</v>
+        <v>834</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H70" s="22" t="n">
         <v>182</v>
@@ -6435,7 +6489,7 @@
         <v>46318</v>
       </c>
       <c r="F71" s="22" t="n">
-        <v>9800</v>
+        <v>11000</v>
       </c>
       <c r="G71" s="22" t="n"/>
       <c r="H71" s="22" t="n"/>
@@ -6484,7 +6538,7 @@
         <v>46294</v>
       </c>
       <c r="F72" s="22" t="n">
-        <v>27400</v>
+        <v>30700</v>
       </c>
       <c r="G72" s="22" t="n"/>
       <c r="H72" s="22" t="n"/>
@@ -6533,7 +6587,7 @@
         <v>46324</v>
       </c>
       <c r="F73" s="22" t="n">
-        <v>15200</v>
+        <v>17000</v>
       </c>
       <c r="G73" s="22" t="n"/>
       <c r="H73" s="22" t="n"/>
@@ -6582,7 +6636,7 @@
         <v>46304</v>
       </c>
       <c r="F74" s="22" t="n">
-        <v>18600</v>
+        <v>20800</v>
       </c>
       <c r="G74" s="22" t="n"/>
       <c r="H74" s="22" t="n"/>
@@ -6631,7 +6685,7 @@
         <v>46314</v>
       </c>
       <c r="F75" s="22" t="n">
-        <v>46800</v>
+        <v>52400</v>
       </c>
       <c r="G75" s="22" t="n"/>
       <c r="H75" s="22" t="n"/>
@@ -6680,7 +6734,7 @@
         <v>46304</v>
       </c>
       <c r="F76" s="22" t="n">
-        <v>12900</v>
+        <v>14400</v>
       </c>
       <c r="G76" s="22" t="n"/>
       <c r="H76" s="22" t="n"/>
@@ -6729,7 +6783,7 @@
         <v>46296</v>
       </c>
       <c r="F77" s="22" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="G77" s="22" t="n"/>
       <c r="H77" s="22" t="n"/>
@@ -6778,7 +6832,7 @@
         <v>46304</v>
       </c>
       <c r="F78" s="22" t="n">
-        <v>2800</v>
+        <v>3150</v>
       </c>
       <c r="G78" s="22" t="n"/>
       <c r="H78" s="22" t="n"/>
@@ -6824,10 +6878,10 @@
         <v>46266</v>
       </c>
       <c r="E79" s="21" t="n">
-        <v>46291</v>
+        <v>46293</v>
       </c>
       <c r="F79" s="22" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="G79" s="22" t="n"/>
       <c r="H79" s="22" t="n"/>
@@ -6873,10 +6927,10 @@
         <v>46266</v>
       </c>
       <c r="E80" s="21" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="F80" s="22" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
       <c r="G80" s="22" t="n"/>
       <c r="H80" s="22" t="n"/>
@@ -6925,7 +6979,7 @@
         <v>46296</v>
       </c>
       <c r="F81" s="22" t="n">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G81" s="22" t="n"/>
       <c r="H81" s="22" t="n"/>
@@ -6974,7 +7028,7 @@
         <v>46304</v>
       </c>
       <c r="F82" s="22" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="G82" s="22" t="n"/>
       <c r="H82" s="22" t="n"/>
@@ -7023,7 +7077,7 @@
         <v>46304</v>
       </c>
       <c r="F83" s="22" t="n">
-        <v>4200</v>
+        <v>4700</v>
       </c>
       <c r="G83" s="22" t="n"/>
       <c r="H83" s="22" t="n"/>
@@ -7072,7 +7126,7 @@
         <v>46304</v>
       </c>
       <c r="F84" s="22" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="G84" s="22" t="n"/>
       <c r="H84" s="22" t="n"/>
@@ -7121,7 +7175,7 @@
         <v>46296</v>
       </c>
       <c r="F85" s="22" t="n">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="G85" s="22" t="n"/>
       <c r="H85" s="22" t="n"/>
@@ -7170,7 +7224,7 @@
         <v>46304</v>
       </c>
       <c r="F86" s="22" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
       <c r="G86" s="22" t="n"/>
       <c r="H86" s="22" t="n"/>
@@ -7219,7 +7273,7 @@
         <v>46296</v>
       </c>
       <c r="F87" s="22" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="G87" s="22" t="n"/>
       <c r="H87" s="22" t="n"/>
@@ -7268,7 +7322,7 @@
         <v>46296</v>
       </c>
       <c r="F88" s="22" t="n">
-        <v>3000</v>
+        <v>3350</v>
       </c>
       <c r="G88" s="22" t="n"/>
       <c r="H88" s="22" t="n"/>
@@ -7317,7 +7371,7 @@
         <v>46304</v>
       </c>
       <c r="F89" s="22" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="G89" s="22" t="n"/>
       <c r="H89" s="22" t="n"/>
@@ -7363,10 +7417,10 @@
         <v>46266</v>
       </c>
       <c r="E90" s="21" t="n">
-        <v>46299</v>
+        <v>46301</v>
       </c>
       <c r="F90" s="22" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
       <c r="G90" s="22" t="n"/>
       <c r="H90" s="22" t="n"/>
@@ -7415,10 +7469,10 @@
         <v>46272</v>
       </c>
       <c r="F91" s="22" t="n">
-        <v>853</v>
+        <v>925</v>
       </c>
       <c r="G91" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H91" s="22" t="n">
         <v>273</v>
@@ -7468,10 +7522,10 @@
         <v>46272</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="G92" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H92" s="22" t="n">
         <v>52</v>
@@ -7521,10 +7575,10 @@
         <v>46244</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>474</v>
+        <v>528</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H93" s="22" t="n">
         <v>39</v>
@@ -7571,13 +7625,13 @@
         <v>46261</v>
       </c>
       <c r="E94" s="21" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>708</v>
+        <v>762</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H94" s="22" t="n">
         <v>273</v>
@@ -7624,13 +7678,13 @@
         <v>46246</v>
       </c>
       <c r="E95" s="21" t="n">
-        <v>46246</v>
+        <v>46247</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>381</v>
+        <v>417</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H95" s="22" t="n">
         <v>91</v>
@@ -7680,10 +7734,10 @@
         <v>46269</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>695</v>
+        <v>749</v>
       </c>
       <c r="G96" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H96" s="22" t="n">
         <v>260</v>
@@ -7730,13 +7784,13 @@
         <v>46243</v>
       </c>
       <c r="E97" s="21" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>539</v>
+        <v>593</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H97" s="22" t="n">
         <v>104</v>
@@ -7786,10 +7840,10 @@
         <v>46286</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>840</v>
+        <v>912</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H98" s="22" t="n">
         <v>260</v>
@@ -7839,10 +7893,10 @@
         <v>46251</v>
       </c>
       <c r="F99" s="22" t="n">
-        <v>866</v>
+        <v>938</v>
       </c>
       <c r="G99" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H99" s="22" t="n">
         <v>286</v>
@@ -7892,10 +7946,10 @@
         <v>46260</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>604</v>
+        <v>658</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H100" s="22" t="n">
         <v>169</v>
@@ -7945,10 +7999,10 @@
         <v>46259</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>524</v>
+        <v>560</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H101" s="22" t="n">
         <v>234</v>
@@ -7998,10 +8052,10 @@
         <v>46253</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>368</v>
+        <v>404</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H102" s="22" t="n">
         <v>78</v>
@@ -8051,10 +8105,10 @@
         <v>46262</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>658</v>
+        <v>730</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H103" s="22" t="n">
         <v>78</v>
@@ -8104,10 +8158,10 @@
         <v>46252</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>511</v>
+        <v>547</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H104" s="22" t="n">
         <v>221</v>
@@ -8157,10 +8211,10 @@
         <v>46266</v>
       </c>
       <c r="F105" s="22" t="n">
-        <v>433</v>
+        <v>469</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H105" s="22" t="n">
         <v>143</v>
@@ -8210,10 +8264,10 @@
         <v>46254</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>439</v>
+        <v>466</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H106" s="22" t="n">
         <v>221</v>
@@ -8260,13 +8314,13 @@
         <v>46256</v>
       </c>
       <c r="E107" s="21" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>617</v>
+        <v>671</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H107" s="22" t="n">
         <v>182</v>
@@ -8313,13 +8367,13 @@
         <v>46256</v>
       </c>
       <c r="E108" s="21" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>478</v>
+        <v>505</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H108" s="22" t="n">
         <v>260</v>
@@ -8369,10 +8423,10 @@
         <v>46248</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>682</v>
+        <v>736</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H109" s="22" t="n">
         <v>247</v>
@@ -8422,10 +8476,10 @@
         <v>46267</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>571</v>
+        <v>616</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H110" s="22" t="n">
         <v>208</v>
@@ -8472,13 +8526,13 @@
         <v>46256</v>
       </c>
       <c r="E111" s="21" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H111" s="22" t="n">
         <v>130</v>
@@ -8528,10 +8582,10 @@
         <v>46261</v>
       </c>
       <c r="F112" s="22" t="n">
-        <v>669</v>
+        <v>723</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H112" s="22" t="n">
         <v>234</v>
@@ -8578,13 +8632,13 @@
         <v>46235</v>
       </c>
       <c r="E113" s="21" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="F113" s="22" t="n">
-        <v>322</v>
+        <v>349</v>
       </c>
       <c r="G113" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H113" s="22" t="n">
         <v>104</v>
@@ -8634,10 +8688,10 @@
         <v>46245</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>467</v>
+        <v>512</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H114" s="22" t="n">
         <v>104</v>
@@ -8687,10 +8741,10 @@
         <v>46258</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>537</v>
+        <v>573</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H115" s="22" t="n">
         <v>247</v>
@@ -8740,10 +8794,10 @@
         <v>46252</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>623</v>
+        <v>668</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H116" s="22" t="n">
         <v>260</v>
@@ -8793,10 +8847,10 @@
         <v>46237</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>472</v>
+        <v>508</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H117" s="22" t="n">
         <v>182</v>
@@ -8843,13 +8897,13 @@
         <v>46249</v>
       </c>
       <c r="E118" s="21" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>517</v>
+        <v>544</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H118" s="22" t="n">
         <v>299</v>
@@ -8899,10 +8953,10 @@
         <v>46239</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="G119" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H119" s="22" t="n">
         <v>91</v>
@@ -8952,10 +9006,10 @@
         <v>46253</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>658</v>
+        <v>730</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H120" s="22" t="n">
         <v>78</v>
@@ -9005,10 +9059,10 @@
         <v>46245</v>
       </c>
       <c r="F121" s="22" t="n">
-        <v>420</v>
+        <v>456</v>
       </c>
       <c r="G121" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H121" s="22" t="n">
         <v>130</v>
@@ -9058,10 +9112,10 @@
         <v>46289</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>656</v>
+        <v>710</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H122" s="22" t="n">
         <v>221</v>
@@ -9111,10 +9165,10 @@
         <v>46266</v>
       </c>
       <c r="F123" s="22" t="n">
-        <v>446</v>
+        <v>482</v>
       </c>
       <c r="G123" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H123" s="22" t="n">
         <v>156</v>
@@ -9164,10 +9218,10 @@
         <v>46240</v>
       </c>
       <c r="F124" s="22" t="n">
-        <v>327</v>
+        <v>345</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H124" s="22" t="n">
         <v>182</v>
@@ -9217,10 +9271,10 @@
         <v>46262</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>441</v>
+        <v>486</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H125" s="22" t="n">
         <v>78</v>
@@ -9267,13 +9321,13 @@
         <v>46249</v>
       </c>
       <c r="E126" s="21" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>402</v>
+        <v>447</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H126" s="22" t="n">
         <v>39</v>
@@ -9320,13 +9374,13 @@
         <v>46257</v>
       </c>
       <c r="E127" s="21" t="n">
-        <v>46264</v>
+        <v>46265</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>710</v>
+        <v>782</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H127" s="22" t="n">
         <v>130</v>
@@ -9376,10 +9430,10 @@
         <v>46272</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H128" s="22" t="n">
         <v>65</v>
@@ -9429,10 +9483,10 @@
         <v>46268</v>
       </c>
       <c r="F129" s="22" t="n">
-        <v>335</v>
+        <v>362</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H129" s="22" t="n">
         <v>117</v>
@@ -9482,10 +9536,10 @@
         <v>46248</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>301</v>
+        <v>319</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H130" s="22" t="n">
         <v>156</v>
@@ -9535,10 +9589,10 @@
         <v>46260</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>734</v>
+        <v>788</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H131" s="22" t="n">
         <v>299</v>
@@ -9585,13 +9639,13 @@
         <v>46242</v>
       </c>
       <c r="E132" s="21" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H132" s="22" t="n">
         <v>52</v>
@@ -9641,10 +9695,10 @@
         <v>46252</v>
       </c>
       <c r="F133" s="22" t="n">
-        <v>394</v>
+        <v>430</v>
       </c>
       <c r="G133" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H133" s="22" t="n">
         <v>104</v>
@@ -9694,10 +9748,10 @@
         <v>46262</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H134" s="22" t="n">
         <v>143</v>
@@ -9747,10 +9801,10 @@
         <v>46267</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>493</v>
+        <v>538</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>363</v>
+        <v>408</v>
       </c>
       <c r="H135" s="22" t="n">
         <v>130</v>
@@ -9797,13 +9851,13 @@
         <v>46235</v>
       </c>
       <c r="E136" s="21" t="n">
-        <v>46249</v>
+        <v>46251</v>
       </c>
       <c r="F136" s="22" t="n">
-        <v>314</v>
+        <v>332</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H136" s="22" t="n">
         <v>169</v>
@@ -9853,10 +9907,10 @@
         <v>46258</v>
       </c>
       <c r="F137" s="22" t="n">
-        <v>340</v>
+        <v>358</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H137" s="22" t="n">
         <v>195</v>
@@ -9906,10 +9960,10 @@
         <v>46244</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>262</v>
+        <v>280</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H138" s="22" t="n">
         <v>117</v>
@@ -9959,10 +10013,10 @@
         <v>46258</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>643</v>
+        <v>697</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H139" s="22" t="n">
         <v>208</v>
@@ -10012,10 +10066,10 @@
         <v>46238</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>210</v>
+        <v>228</v>
       </c>
       <c r="G140" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H140" s="22" t="n">
         <v>65</v>
@@ -10062,13 +10116,13 @@
         <v>46240</v>
       </c>
       <c r="E141" s="21" t="n">
-        <v>46242</v>
+        <v>46244</v>
       </c>
       <c r="F141" s="22" t="n">
-        <v>526</v>
+        <v>580</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H141" s="22" t="n">
         <v>91</v>
@@ -10115,13 +10169,13 @@
         <v>46256</v>
       </c>
       <c r="E142" s="21" t="n">
-        <v>46256</v>
+        <v>46258</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>270</v>
+        <v>297</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>218</v>
+        <v>245</v>
       </c>
       <c r="H142" s="22" t="n">
         <v>52</v>
@@ -10168,13 +10222,13 @@
         <v>46257</v>
       </c>
       <c r="E143" s="21" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F143" s="22" t="n">
-        <v>342</v>
+        <v>378</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H143" s="22" t="n">
         <v>52</v>
@@ -10221,13 +10275,13 @@
         <v>46256</v>
       </c>
       <c r="E144" s="21" t="n">
-        <v>46263</v>
+        <v>46265</v>
       </c>
       <c r="F144" s="22" t="n">
-        <v>355</v>
+        <v>391</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>290</v>
+        <v>326</v>
       </c>
       <c r="H144" s="22" t="n">
         <v>65</v>
@@ -10277,10 +10331,10 @@
         <v>46245</v>
       </c>
       <c r="F145" s="22" t="n">
-        <v>552</v>
+        <v>606</v>
       </c>
       <c r="G145" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H145" s="22" t="n">
         <v>117</v>
@@ -10330,10 +10384,10 @@
         <v>46254</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>171</v>
+        <v>189</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>145</v>
+        <v>163</v>
       </c>
       <c r="H146" s="22" t="n">
         <v>26</v>
@@ -10383,10 +10437,10 @@
         <v>46251</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>695</v>
+        <v>749</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>435</v>
+        <v>489</v>
       </c>
       <c r="H147" s="22" t="n">
         <v>260</v>
@@ -10433,13 +10487,13 @@
         <v>46255</v>
       </c>
       <c r="E148" s="21" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>788</v>
+        <v>860</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>580</v>
+        <v>652</v>
       </c>
       <c r="H148" s="22" t="n">
         <v>208</v>
@@ -10486,10 +10540,10 @@
         <v>46248</v>
       </c>
       <c r="E149" s="21" t="n">
-        <v>46278</v>
+        <v>46279</v>
       </c>
       <c r="F149" s="22" t="n">
-        <v>21300</v>
+        <v>23900</v>
       </c>
       <c r="G149" s="22" t="n"/>
       <c r="H149" s="22" t="n"/>
@@ -10538,7 +10592,7 @@
         <v>46274</v>
       </c>
       <c r="F150" s="22" t="n">
-        <v>16800</v>
+        <v>18800</v>
       </c>
       <c r="G150" s="22" t="n"/>
       <c r="H150" s="22" t="n"/>
@@ -10584,10 +10638,10 @@
         <v>46241</v>
       </c>
       <c r="E151" s="21" t="n">
-        <v>46271</v>
+        <v>46272</v>
       </c>
       <c r="F151" s="22" t="n">
-        <v>38500</v>
+        <v>43100</v>
       </c>
       <c r="G151" s="22" t="n"/>
       <c r="H151" s="22" t="n"/>
@@ -10633,10 +10687,10 @@
         <v>46262</v>
       </c>
       <c r="E152" s="21" t="n">
-        <v>46292</v>
+        <v>46293</v>
       </c>
       <c r="F152" s="22" t="n">
-        <v>13400</v>
+        <v>15000</v>
       </c>
       <c r="G152" s="22" t="n"/>
       <c r="H152" s="22" t="n"/>
@@ -10685,7 +10739,7 @@
         <v>46272</v>
       </c>
       <c r="F153" s="22" t="n">
-        <v>19600</v>
+        <v>22000</v>
       </c>
       <c r="G153" s="22" t="n"/>
       <c r="H153" s="22" t="n"/>
@@ -10734,7 +10788,7 @@
         <v>46260</v>
       </c>
       <c r="F154" s="22" t="n">
-        <v>3600</v>
+        <v>4050</v>
       </c>
       <c r="G154" s="22" t="n"/>
       <c r="H154" s="22" t="n"/>
@@ -10783,7 +10837,7 @@
         <v>46265</v>
       </c>
       <c r="F155" s="22" t="n">
-        <v>2800</v>
+        <v>3150</v>
       </c>
       <c r="G155" s="22" t="n"/>
       <c r="H155" s="22" t="n"/>
@@ -10832,7 +10886,7 @@
         <v>46265</v>
       </c>
       <c r="F156" s="22" t="n">
-        <v>1700</v>
+        <v>1900</v>
       </c>
       <c r="G156" s="22" t="n"/>
       <c r="H156" s="22" t="n"/>
@@ -10881,7 +10935,7 @@
         <v>46268</v>
       </c>
       <c r="F157" s="22" t="n">
-        <v>4100</v>
+        <v>4600</v>
       </c>
       <c r="G157" s="22" t="n"/>
       <c r="H157" s="22" t="n"/>
@@ -10930,7 +10984,7 @@
         <v>46265</v>
       </c>
       <c r="F158" s="22" t="n">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G158" s="22" t="n"/>
       <c r="H158" s="22" t="n"/>
@@ -10979,7 +11033,7 @@
         <v>46265</v>
       </c>
       <c r="F159" s="22" t="n">
-        <v>2400</v>
+        <v>2700</v>
       </c>
       <c r="G159" s="22" t="n"/>
       <c r="H159" s="22" t="n"/>
@@ -11028,7 +11082,7 @@
         <v>46260</v>
       </c>
       <c r="F160" s="22" t="n">
-        <v>4200</v>
+        <v>4700</v>
       </c>
       <c r="G160" s="22" t="n"/>
       <c r="H160" s="22" t="n"/>
@@ -11077,7 +11131,7 @@
         <v>46260</v>
       </c>
       <c r="F161" s="22" t="n">
-        <v>1600</v>
+        <v>1800</v>
       </c>
       <c r="G161" s="22" t="n"/>
       <c r="H161" s="22" t="n"/>
@@ -11126,7 +11180,7 @@
         <v>46268</v>
       </c>
       <c r="F162" s="22" t="n">
-        <v>3200</v>
+        <v>3600</v>
       </c>
       <c r="G162" s="22" t="n"/>
       <c r="H162" s="22" t="n"/>
@@ -11175,7 +11229,7 @@
         <v>46273</v>
       </c>
       <c r="F163" s="22" t="n">
-        <v>3900</v>
+        <v>4350</v>
       </c>
       <c r="G163" s="22" t="n"/>
       <c r="H163" s="22" t="n"/>
@@ -11224,7 +11278,7 @@
         <v>46260</v>
       </c>
       <c r="F164" s="22" t="n">
-        <v>1800</v>
+        <v>2000</v>
       </c>
       <c r="G164" s="22" t="n"/>
       <c r="H164" s="22" t="n"/>
@@ -11273,7 +11327,7 @@
         <v>46268</v>
       </c>
       <c r="F165" s="22" t="n">
-        <v>3000</v>
+        <v>3350</v>
       </c>
       <c r="G165" s="22" t="n"/>
       <c r="H165" s="22" t="n"/>
@@ -11322,7 +11376,7 @@
         <v>46260</v>
       </c>
       <c r="F166" s="22" t="n">
-        <v>2600</v>
+        <v>2900</v>
       </c>
       <c r="G166" s="22" t="n"/>
       <c r="H166" s="22" t="n"/>
@@ -11371,7 +11425,7 @@
         <v>46260</v>
       </c>
       <c r="F167" s="22" t="n">
-        <v>2200</v>
+        <v>2450</v>
       </c>
       <c r="G167" s="22" t="n"/>
       <c r="H167" s="22" t="n"/>
@@ -11442,7 +11496,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11493,7 +11547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -11532,10 +11586,10 @@
         </is>
       </c>
       <c r="B8" s="22" t="n">
-        <v>202337</v>
+        <v>225460</v>
       </c>
       <c r="C8" s="22" t="n">
-        <v>179007</v>
+        <v>199523</v>
       </c>
     </row>
     <row r="9">
@@ -11571,10 +11625,10 @@
         </is>
       </c>
       <c r="B11" s="22" t="n">
-        <v>-54600</v>
+        <v>-79587</v>
       </c>
       <c r="C11" s="22" t="n">
-        <v>-54600</v>
+        <v>-72352</v>
       </c>
     </row>
     <row r="12">
@@ -11610,7 +11664,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Gross margin is before overheads (office wages, marketing, vehicles, rent and so on): it is not profit. Wages include all on-costs (super, payroll tax, workers' compensation, leave). Technicians are on salary, so a quiet month for jobs lowers gross margin even if every job is priced well.</t>
+          <t>Gross margin is before overheads (office wages, marketing, vehicles, rent and so on): it is not profit. Wages include their on-costs: super (12%) and leave as it's earned. No payroll tax: wages are under Queensland's $1.3 million threshold. Technicians are on salary, so a quiet month for jobs lowers gross margin even if every job is priced well.</t>
         </is>
       </c>
     </row>
@@ -11798,7 +11852,7 @@
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>August had one fewer working day for the Ekka show holiday. The rest is travel, training, quoting and waiting time.</t>
+          <t>August had 20 working days: 21 weekdays, less the Ekka People's Day holiday (Wed 12 Aug). The rest is travel, training, quoting and waiting time.</t>
         </is>
       </c>
     </row>
@@ -11833,7 +11887,7 @@
         </is>
       </c>
       <c r="B40" s="22" t="n">
-        <v>9800</v>
+        <v>11000</v>
       </c>
     </row>
     <row r="41">
@@ -11940,7 +11994,7 @@
         </is>
       </c>
       <c r="B53" s="22" t="n">
-        <v>18600</v>
+        <v>20800</v>
       </c>
     </row>
     <row r="54">
@@ -12047,7 +12101,7 @@
         </is>
       </c>
       <c r="B66" s="22" t="n">
-        <v>15200</v>
+        <v>17000</v>
       </c>
     </row>
     <row r="67">
@@ -12154,7 +12208,7 @@
         </is>
       </c>
       <c r="B79" s="22" t="n">
-        <v>12900</v>
+        <v>14400</v>
       </c>
     </row>
     <row r="80">
@@ -12261,7 +12315,7 @@
         </is>
       </c>
       <c r="B92" s="22" t="n">
-        <v>27400</v>
+        <v>30700</v>
       </c>
     </row>
     <row r="93">
@@ -12368,7 +12422,7 @@
         </is>
       </c>
       <c r="B105" s="22" t="n">
-        <v>46800</v>
+        <v>52400</v>
       </c>
     </row>
     <row r="106">
@@ -12453,7 +12507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12474,7 +12528,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:B45"/>
+  <dimension ref="A1:B52"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -12498,7 +12552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 8 Oct 2026, 9:30pm</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
         </is>
       </c>
     </row>
@@ -12586,7 +12640,7 @@
       </c>
       <c r="B13" s="33" t="inlineStr">
         <is>
-          <t>64 jobs at $145/hour plus materials marked up 30%</t>
+          <t>64 jobs at $163/hour plus materials marked up 30%</t>
         </is>
       </c>
     </row>
@@ -12618,7 +12672,7 @@
       </c>
       <c r="B17" s="33" t="inlineStr">
         <is>
-          <t>7 on salary: $54,600 a month incl. on-costs</t>
+          <t>7 employed full time: $79,587 in September incl. on-costs (every available hour at $68)</t>
         </is>
       </c>
     </row>
@@ -12630,7 +12684,7 @@
       </c>
       <c r="B18" s="33" t="inlineStr">
         <is>
-          <t>$68/hour for technician time charged to a job</t>
+          <t>$68/hour = technician wages incl. on-costs ÷ available hours, worked out each month; time charged to jobs + time not charged = technician wages</t>
         </is>
       </c>
     </row>
@@ -12642,7 +12696,7 @@
       </c>
       <c r="B19" s="33" t="inlineStr">
         <is>
-          <t>20 in August (Ekka show holiday), 22 in September; 7.6 hours a day</t>
+          <t>20 in August (21 weekdays, less the Ekka People's Day holiday, Wed 12 Aug), 22 in September; 7.6 hours a day</t>
         </is>
       </c>
     </row>
@@ -12666,7 +12720,7 @@
       </c>
       <c r="B21" s="33" t="inlineStr">
         <is>
-          <t>25% of profit, provided monthly; next PAYG instalment due October</t>
+          <t>25% of profit, provided monthly; the PAYG instalment is paid with each quarter's BAS</t>
         </is>
       </c>
     </row>
@@ -12726,120 +12780,188 @@
         </is>
       </c>
     </row>
-    <row r="28">
-      <c r="A28" s="32" t="inlineStr">
+    <row r="28"/>
+    <row r="29">
+      <c r="A29" s="11" t="inlineStr">
+        <is>
+          <t>GST, BAS and payroll</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="32" t="inlineStr">
         <is>
           <t>GST</t>
         </is>
       </c>
-      <c r="B28" s="33" t="inlineStr">
-        <is>
-          <t>excluded throughout, for simplicity</t>
-        </is>
-      </c>
-    </row>
-    <row r="29"/>
-    <row r="30">
-      <c r="A30" s="11" t="inlineStr">
+      <c r="B30" s="33" t="inlineStr">
+        <is>
+          <t>registered; 10%, accruals basis: GST on a sale is owed when it's invoiced, a credit on a bill is claimed when it's received. The P&amp;L excludes GST; invoices, bills, debtors, creditors and cash include it</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="32" t="inlineStr">
+        <is>
+          <t>BAS</t>
+        </is>
+      </c>
+      <c r="B31" s="33" t="inlineStr">
+        <is>
+          <t>quarterly, self-lodged: GST on sales − GST credits + PAYG withheld + PAYG instalment. July to September is due 28 October; October to December, 28 February</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="32" t="inlineStr">
+        <is>
+          <t>Pay runs</t>
+        </is>
+      </c>
+      <c r="B32" s="33" t="inlineStr">
+        <is>
+          <t>fortnightly on Thursdays: $39,795 gross (a 26th of the year's gross wages); net pay $31,836 and super $4,775 paid on the day; PAYG withheld (about 20% of gross, $7,959) goes with the BAS. Two months a year have three pay runs</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="32" t="inlineStr">
+        <is>
+          <t>Super</t>
+        </is>
+      </c>
+      <c r="B33" s="33" t="inlineStr">
+        <is>
+          <t>12% of gross wages, paid with each pay run (Payday Super, from 1 July 2026)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="32" t="inlineStr">
+        <is>
+          <t>Payroll tax</t>
+        </is>
+      </c>
+      <c r="B34" s="33" t="inlineStr">
+        <is>
+          <t>none: Queensland's threshold is $1.3 million of wages a year (rate 4.75% above it); this business pays about $1,159,000 including super</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="32" t="inlineStr">
+        <is>
+          <t>Banking days</t>
+        </is>
+      </c>
+      <c r="B35" s="33" t="inlineStr">
+        <is>
+          <t>money only moves on banking days: a payment due on a weekend or Queensland public holiday moves to the next banking day</t>
+        </is>
+      </c>
+    </row>
+    <row r="36"/>
+    <row r="37">
+      <c r="A37" s="11" t="inlineStr">
         <is>
           <t>Checks (all passed)</t>
         </is>
       </c>
     </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
+    <row r="38">
+      <c r="A38" t="inlineStr">
         <is>
           <t>✓ Every subtotal and total adds up</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>✓ Balance sheet balances: assets = liabilities + equity</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>✓ Cash flow ends at the cash in the bank</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>✓ Profit ties to the movement in retained earnings</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>✓ Every job's revenue, materials and subcontractors add up to the P&amp;L</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>✓ Trade debtors equal the invoices still unpaid at month end</t>
-        </is>
-      </c>
-    </row>
-    <row r="37"/>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
-        <is>
-          <t>Print check (done before this file was saved)</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
+          <t>✓ Balance sheet balances: assets = liabilities + equity</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>✓ Profit and loss: 1 page, 100% scale, no block split</t>
+          <t>✓ Cash flow ends at the cash in the bank</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
+          <t>✓ Profit ties to the movement in retained earnings</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+          <t>✓ Every job's revenue, materials and subcontractors add up to the P&amp;L</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
+          <t>✓ Trade debtors equal the invoices still unpaid at month end</t>
+        </is>
+      </c>
+    </row>
+    <row r="44"/>
+    <row r="45">
+      <c r="A45" s="11" t="inlineStr">
+        <is>
+          <t>Print check (done before this file was saved)</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="inlineStr">
+        <is>
+          <t>✓ The fourth sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="inlineStr">
+        <is>
+          <t>✓ Profit and loss: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>✓ Balance sheet: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>✓ Cash flow: 1 page, 100% scale, no block split</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="inlineStr">
+        <is>
           <t>✓ Jobs: 5 pages, 69% scale, no block split</t>
         </is>
       </c>
     </row>
-    <row r="44">
-      <c r="A44" t="inlineStr">
+    <row r="51">
+      <c r="A51" t="inlineStr">
         <is>
           <t>✓ Workings: 5 pages, 100% scale, no block split</t>
         </is>
       </c>
     </row>
-    <row r="45">
-      <c r="A45" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="inlineStr">
         <is>
           <t>✓ Assumptions: 2 pages, 100% scale, no block split</t>
         </is>
@@ -12851,14 +12973,14 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 8 Oct 2026, 9:30pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
     <firstFooter/>
   </headerFooter>
   <rowBreaks count="1" manualBreakCount="1">
-    <brk id="29" min="0" max="16383" man="1"/>
+    <brk id="28" min="0" max="16383" man="1"/>
   </rowBreaks>
 </worksheet>
 </file>
--- a/media/exports/trades-sample-statements.xlsx
+++ b/media/exports/trades-sample-statements.xlsx
@@ -1047,7 +1047,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -1290,7 +1290,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -1377,7 +1377,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -2044,7 +2044,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2085,7 +2085,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -2507,7 +2507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2548,7 +2548,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -2936,7 +2936,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -2987,7 +2987,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -3082,7 +3082,7 @@
       </c>
       <c r="B7" s="20" t="inlineStr">
         <is>
-          <t>Call-out 1, September</t>
+          <t>Call-out CO-49224</t>
         </is>
       </c>
       <c r="C7" s="20" t="inlineStr">
@@ -3135,7 +3135,7 @@
       </c>
       <c r="B8" s="20" t="inlineStr">
         <is>
-          <t>Call-out 10, September</t>
+          <t>Call-out CO-49225</t>
         </is>
       </c>
       <c r="C8" s="20" t="inlineStr">
@@ -3144,22 +3144,22 @@
         </is>
       </c>
       <c r="D8" s="21" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="E8" s="21" t="n">
-        <v>46286</v>
+        <v>46280</v>
       </c>
       <c r="F8" s="22" t="n">
-        <v>593</v>
+        <v>658</v>
       </c>
       <c r="G8" s="22" t="n">
         <v>489</v>
       </c>
       <c r="H8" s="22" t="n">
-        <v>104</v>
+        <v>169</v>
       </c>
       <c r="I8" s="22" t="n">
-        <v>80</v>
+        <v>130</v>
       </c>
       <c r="J8" s="22" t="n">
         <v>0</v>
@@ -3188,7 +3188,7 @@
       </c>
       <c r="B9" s="20" t="inlineStr">
         <is>
-          <t>Call-out 11, September</t>
+          <t>Call-out CO-49226</t>
         </is>
       </c>
       <c r="C9" s="20" t="inlineStr">
@@ -3197,22 +3197,22 @@
         </is>
       </c>
       <c r="D9" s="21" t="n">
-        <v>46289</v>
+        <v>46276</v>
       </c>
       <c r="E9" s="21" t="n">
-        <v>46296</v>
+        <v>46276</v>
       </c>
       <c r="F9" s="22" t="n">
-        <v>580</v>
+        <v>619</v>
       </c>
       <c r="G9" s="22" t="n">
         <v>489</v>
       </c>
       <c r="H9" s="22" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I9" s="22" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J9" s="22" t="n">
         <v>0</v>
@@ -3241,7 +3241,7 @@
       </c>
       <c r="B10" s="20" t="inlineStr">
         <is>
-          <t>Call-out 12, September</t>
+          <t>Call-out CO-49227</t>
         </is>
       </c>
       <c r="C10" s="20" t="inlineStr">
@@ -3250,28 +3250,28 @@
         </is>
       </c>
       <c r="D10" s="21" t="n">
-        <v>46282</v>
+        <v>46277</v>
       </c>
       <c r="E10" s="21" t="n">
-        <v>46289</v>
+        <v>46279</v>
       </c>
       <c r="F10" s="22" t="n">
-        <v>440</v>
+        <v>508</v>
       </c>
       <c r="G10" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H10" s="22" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="I10" s="22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J10" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K10" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L10" s="22">
         <f>K10*$B$4</f>
@@ -3294,7 +3294,7 @@
       </c>
       <c r="B11" s="20" t="inlineStr">
         <is>
-          <t>Call-out 13, September</t>
+          <t>Call-out CO-49228</t>
         </is>
       </c>
       <c r="C11" s="20" t="inlineStr">
@@ -3303,28 +3303,28 @@
         </is>
       </c>
       <c r="D11" s="21" t="n">
-        <v>46269</v>
+        <v>46291</v>
       </c>
       <c r="E11" s="21" t="n">
-        <v>46269</v>
+        <v>46293</v>
       </c>
       <c r="F11" s="22" t="n">
-        <v>847</v>
+        <v>508</v>
       </c>
       <c r="G11" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H11" s="22" t="n">
-        <v>195</v>
+        <v>182</v>
       </c>
       <c r="I11" s="22" t="n">
-        <v>150</v>
+        <v>140</v>
       </c>
       <c r="J11" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K11" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L11" s="22">
         <f>K11*$B$4</f>
@@ -3347,7 +3347,7 @@
       </c>
       <c r="B12" s="20" t="inlineStr">
         <is>
-          <t>Call-out 14, September</t>
+          <t>Call-out CO-49229</t>
         </is>
       </c>
       <c r="C12" s="20" t="inlineStr">
@@ -3356,28 +3356,28 @@
         </is>
       </c>
       <c r="D12" s="21" t="n">
-        <v>46269</v>
+        <v>46275</v>
       </c>
       <c r="E12" s="21" t="n">
-        <v>46269</v>
+        <v>46282</v>
       </c>
       <c r="F12" s="22" t="n">
-        <v>375</v>
+        <v>499</v>
       </c>
       <c r="G12" s="22" t="n">
-        <v>245</v>
+        <v>408</v>
       </c>
       <c r="H12" s="22" t="n">
-        <v>130</v>
+        <v>91</v>
       </c>
       <c r="I12" s="22" t="n">
-        <v>100</v>
+        <v>70</v>
       </c>
       <c r="J12" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K12" s="23" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L12" s="22">
         <f>K12*$B$4</f>
@@ -3400,7 +3400,7 @@
       </c>
       <c r="B13" s="20" t="inlineStr">
         <is>
-          <t>Call-out 15, September</t>
+          <t>Call-out CO-49231</t>
         </is>
       </c>
       <c r="C13" s="20" t="inlineStr">
@@ -3412,25 +3412,25 @@
         <v>46280</v>
       </c>
       <c r="E13" s="21" t="n">
-        <v>46310</v>
+        <v>46294</v>
       </c>
       <c r="F13" s="22" t="n">
-        <v>847</v>
+        <v>788</v>
       </c>
       <c r="G13" s="22" t="n">
-        <v>652</v>
+        <v>489</v>
       </c>
       <c r="H13" s="22" t="n">
-        <v>195</v>
+        <v>299</v>
       </c>
       <c r="I13" s="22" t="n">
-        <v>150</v>
+        <v>230</v>
       </c>
       <c r="J13" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K13" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L13" s="22">
         <f>K13*$B$4</f>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="B14" s="20" t="inlineStr">
         <is>
-          <t>Call-out 16, September</t>
+          <t>Call-out CO-49232</t>
         </is>
       </c>
       <c r="C14" s="20" t="inlineStr">
@@ -3462,28 +3462,28 @@
         </is>
       </c>
       <c r="D14" s="21" t="n">
-        <v>46266</v>
+        <v>46267</v>
       </c>
       <c r="E14" s="21" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="F14" s="22" t="n">
-        <v>404</v>
+        <v>462</v>
       </c>
       <c r="G14" s="22" t="n">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="H14" s="22" t="n">
-        <v>78</v>
+        <v>299</v>
       </c>
       <c r="I14" s="22" t="n">
-        <v>60</v>
+        <v>230</v>
       </c>
       <c r="J14" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K14" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L14" s="22">
         <f>K14*$B$4</f>
@@ -3506,7 +3506,7 @@
       </c>
       <c r="B15" s="20" t="inlineStr">
         <is>
-          <t>Call-out 17, September</t>
+          <t>Call-out CO-49233</t>
         </is>
       </c>
       <c r="C15" s="20" t="inlineStr">
@@ -3515,28 +3515,28 @@
         </is>
       </c>
       <c r="D15" s="21" t="n">
-        <v>46273</v>
+        <v>46287</v>
       </c>
       <c r="E15" s="21" t="n">
-        <v>46280</v>
+        <v>46317</v>
       </c>
       <c r="F15" s="22" t="n">
-        <v>580</v>
+        <v>834</v>
       </c>
       <c r="G15" s="22" t="n">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="H15" s="22" t="n">
-        <v>91</v>
+        <v>182</v>
       </c>
       <c r="I15" s="22" t="n">
-        <v>70</v>
+        <v>140</v>
       </c>
       <c r="J15" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L15" s="22">
         <f>K15*$B$4</f>
@@ -3559,7 +3559,7 @@
       </c>
       <c r="B16" s="20" t="inlineStr">
         <is>
-          <t>Call-out 18, September</t>
+          <t>Call-out CO-49234</t>
         </is>
       </c>
       <c r="C16" s="20" t="inlineStr">
@@ -3568,16 +3568,16 @@
         </is>
       </c>
       <c r="D16" s="21" t="n">
-        <v>46271</v>
+        <v>46282</v>
       </c>
       <c r="E16" s="21" t="n">
-        <v>46272</v>
+        <v>46286</v>
       </c>
       <c r="F16" s="22" t="n">
-        <v>512</v>
+        <v>593</v>
       </c>
       <c r="G16" s="22" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="H16" s="22" t="n">
         <v>104</v>
@@ -3589,7 +3589,7 @@
         <v>0</v>
       </c>
       <c r="K16" s="23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L16" s="22">
         <f>K16*$B$4</f>
@@ -3612,7 +3612,7 @@
       </c>
       <c r="B17" s="20" t="inlineStr">
         <is>
-          <t>Call-out 19, September</t>
+          <t>Call-out CO-49235</t>
         </is>
       </c>
       <c r="C17" s="20" t="inlineStr">
@@ -3621,28 +3621,28 @@
         </is>
       </c>
       <c r="D17" s="21" t="n">
-        <v>46288</v>
+        <v>46289</v>
       </c>
       <c r="E17" s="21" t="n">
-        <v>46288</v>
+        <v>46296</v>
       </c>
       <c r="F17" s="22" t="n">
-        <v>625</v>
+        <v>580</v>
       </c>
       <c r="G17" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H17" s="22" t="n">
-        <v>299</v>
+        <v>91</v>
       </c>
       <c r="I17" s="22" t="n">
-        <v>230</v>
+        <v>70</v>
       </c>
       <c r="J17" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K17" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L17" s="22">
         <f>K17*$B$4</f>
@@ -3665,7 +3665,7 @@
       </c>
       <c r="B18" s="20" t="inlineStr">
         <is>
-          <t>Call-out 2, September</t>
+          <t>Call-out CO-49236</t>
         </is>
       </c>
       <c r="C18" s="20" t="inlineStr">
@@ -3674,28 +3674,28 @@
         </is>
       </c>
       <c r="D18" s="21" t="n">
-        <v>46280</v>
+        <v>46282</v>
       </c>
       <c r="E18" s="21" t="n">
-        <v>46280</v>
+        <v>46289</v>
       </c>
       <c r="F18" s="22" t="n">
-        <v>658</v>
+        <v>440</v>
       </c>
       <c r="G18" s="22" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="H18" s="22" t="n">
-        <v>169</v>
+        <v>195</v>
       </c>
       <c r="I18" s="22" t="n">
-        <v>130</v>
+        <v>150</v>
       </c>
       <c r="J18" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K18" s="23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L18" s="22">
         <f>K18*$B$4</f>
@@ -3718,7 +3718,7 @@
       </c>
       <c r="B19" s="20" t="inlineStr">
         <is>
-          <t>Call-out 20, September</t>
+          <t>Call-out CO-49238</t>
         </is>
       </c>
       <c r="C19" s="20" t="inlineStr">
@@ -3727,28 +3727,28 @@
         </is>
       </c>
       <c r="D19" s="21" t="n">
-        <v>46289</v>
+        <v>46269</v>
       </c>
       <c r="E19" s="21" t="n">
-        <v>46296</v>
+        <v>46269</v>
       </c>
       <c r="F19" s="22" t="n">
-        <v>378</v>
+        <v>847</v>
       </c>
       <c r="G19" s="22" t="n">
-        <v>326</v>
+        <v>652</v>
       </c>
       <c r="H19" s="22" t="n">
-        <v>52</v>
+        <v>195</v>
       </c>
       <c r="I19" s="22" t="n">
-        <v>40</v>
+        <v>150</v>
       </c>
       <c r="J19" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K19" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L19" s="22">
         <f>K19*$B$4</f>
@@ -3771,7 +3771,7 @@
       </c>
       <c r="B20" s="20" t="inlineStr">
         <is>
-          <t>Call-out 21, September</t>
+          <t>Call-out CO-49239</t>
         </is>
       </c>
       <c r="C20" s="20" t="inlineStr">
@@ -3780,28 +3780,28 @@
         </is>
       </c>
       <c r="D20" s="21" t="n">
-        <v>46290</v>
+        <v>46269</v>
       </c>
       <c r="E20" s="21" t="n">
-        <v>46297</v>
+        <v>46269</v>
       </c>
       <c r="F20" s="22" t="n">
-        <v>515</v>
+        <v>375</v>
       </c>
       <c r="G20" s="22" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="H20" s="22" t="n">
-        <v>26</v>
+        <v>130</v>
       </c>
       <c r="I20" s="22" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="J20" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K20" s="23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L20" s="22">
         <f>K20*$B$4</f>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="B21" s="20" t="inlineStr">
         <is>
-          <t>Call-out 22, September</t>
+          <t>Call-out CO-49240</t>
         </is>
       </c>
       <c r="C21" s="20" t="inlineStr">
@@ -3833,28 +3833,28 @@
         </is>
       </c>
       <c r="D21" s="21" t="n">
-        <v>46282</v>
+        <v>46280</v>
       </c>
       <c r="E21" s="21" t="n">
-        <v>46314</v>
+        <v>46310</v>
       </c>
       <c r="F21" s="22" t="n">
-        <v>486</v>
+        <v>847</v>
       </c>
       <c r="G21" s="22" t="n">
-        <v>408</v>
+        <v>652</v>
       </c>
       <c r="H21" s="22" t="n">
-        <v>78</v>
+        <v>195</v>
       </c>
       <c r="I21" s="22" t="n">
-        <v>60</v>
+        <v>150</v>
       </c>
       <c r="J21" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K21" s="23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L21" s="22">
         <f>K21*$B$4</f>
@@ -3877,7 +3877,7 @@
       </c>
       <c r="B22" s="20" t="inlineStr">
         <is>
-          <t>Call-out 23, September</t>
+          <t>Call-out CO-49241</t>
         </is>
       </c>
       <c r="C22" s="20" t="inlineStr">
@@ -3886,28 +3886,28 @@
         </is>
       </c>
       <c r="D22" s="21" t="n">
-        <v>46287</v>
+        <v>46266</v>
       </c>
       <c r="E22" s="21" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="F22" s="22" t="n">
-        <v>821</v>
+        <v>404</v>
       </c>
       <c r="G22" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H22" s="22" t="n">
-        <v>169</v>
+        <v>78</v>
       </c>
       <c r="I22" s="22" t="n">
-        <v>130</v>
+        <v>60</v>
       </c>
       <c r="J22" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K22" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L22" s="22">
         <f>K22*$B$4</f>
@@ -3930,7 +3930,7 @@
       </c>
       <c r="B23" s="20" t="inlineStr">
         <is>
-          <t>Call-out 24, September</t>
+          <t>Call-out CO-49242</t>
         </is>
       </c>
       <c r="C23" s="20" t="inlineStr">
@@ -3939,28 +3939,28 @@
         </is>
       </c>
       <c r="D23" s="21" t="n">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="E23" s="21" t="n">
-        <v>46293</v>
+        <v>46280</v>
       </c>
       <c r="F23" s="22" t="n">
-        <v>873</v>
+        <v>580</v>
       </c>
       <c r="G23" s="22" t="n">
-        <v>652</v>
+        <v>489</v>
       </c>
       <c r="H23" s="22" t="n">
-        <v>221</v>
+        <v>91</v>
       </c>
       <c r="I23" s="22" t="n">
-        <v>170</v>
+        <v>70</v>
       </c>
       <c r="J23" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K23" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L23" s="22">
         <f>K23*$B$4</f>
@@ -3983,7 +3983,7 @@
       </c>
       <c r="B24" s="20" t="inlineStr">
         <is>
-          <t>Call-out 25, September</t>
+          <t>Call-out CO-49244</t>
         </is>
       </c>
       <c r="C24" s="20" t="inlineStr">
@@ -3992,16 +3992,16 @@
         </is>
       </c>
       <c r="D24" s="21" t="n">
-        <v>46291</v>
+        <v>46271</v>
       </c>
       <c r="E24" s="21" t="n">
-        <v>46293</v>
+        <v>46272</v>
       </c>
       <c r="F24" s="22" t="n">
-        <v>349</v>
+        <v>512</v>
       </c>
       <c r="G24" s="22" t="n">
-        <v>245</v>
+        <v>408</v>
       </c>
       <c r="H24" s="22" t="n">
         <v>104</v>
@@ -4013,7 +4013,7 @@
         <v>0</v>
       </c>
       <c r="K24" s="23" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L24" s="22">
         <f>K24*$B$4</f>
@@ -4036,7 +4036,7 @@
       </c>
       <c r="B25" s="20" t="inlineStr">
         <is>
-          <t>Call-out 26, September</t>
+          <t>Call-out CO-49245</t>
         </is>
       </c>
       <c r="C25" s="20" t="inlineStr">
@@ -4045,28 +4045,28 @@
         </is>
       </c>
       <c r="D25" s="21" t="n">
-        <v>46291</v>
+        <v>46288</v>
       </c>
       <c r="E25" s="21" t="n">
-        <v>46307</v>
+        <v>46288</v>
       </c>
       <c r="F25" s="22" t="n">
-        <v>401</v>
+        <v>625</v>
       </c>
       <c r="G25" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H25" s="22" t="n">
-        <v>156</v>
+        <v>299</v>
       </c>
       <c r="I25" s="22" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="J25" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K25" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L25" s="22">
         <f>K25*$B$4</f>
@@ -4089,7 +4089,7 @@
       </c>
       <c r="B26" s="20" t="inlineStr">
         <is>
-          <t>Call-out 27, September</t>
+          <t>Call-out CO-49246</t>
         </is>
       </c>
       <c r="C26" s="20" t="inlineStr">
@@ -4098,22 +4098,22 @@
         </is>
       </c>
       <c r="D26" s="21" t="n">
-        <v>46269</v>
+        <v>46289</v>
       </c>
       <c r="E26" s="21" t="n">
-        <v>46276</v>
+        <v>46296</v>
       </c>
       <c r="F26" s="22" t="n">
-        <v>586</v>
+        <v>378</v>
       </c>
       <c r="G26" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H26" s="22" t="n">
-        <v>260</v>
+        <v>52</v>
       </c>
       <c r="I26" s="22" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J26" s="22" t="n">
         <v>0</v>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="B27" s="20" t="inlineStr">
         <is>
-          <t>Call-out 28, September</t>
+          <t>Call-out CO-49247</t>
         </is>
       </c>
       <c r="C27" s="20" t="inlineStr">
@@ -4154,25 +4154,25 @@
         <v>46290</v>
       </c>
       <c r="E27" s="21" t="n">
-        <v>46304</v>
+        <v>46297</v>
       </c>
       <c r="F27" s="22" t="n">
-        <v>599</v>
+        <v>515</v>
       </c>
       <c r="G27" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H27" s="22" t="n">
-        <v>273</v>
+        <v>26</v>
       </c>
       <c r="I27" s="22" t="n">
-        <v>210</v>
+        <v>20</v>
       </c>
       <c r="J27" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K27" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L27" s="22">
         <f>K27*$B$4</f>
@@ -4195,7 +4195,7 @@
       </c>
       <c r="B28" s="20" t="inlineStr">
         <is>
-          <t>Call-out 29, September</t>
+          <t>Call-out CO-49248</t>
         </is>
       </c>
       <c r="C28" s="20" t="inlineStr">
@@ -4204,28 +4204,28 @@
         </is>
       </c>
       <c r="D28" s="21" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="E28" s="21" t="n">
-        <v>46301</v>
+        <v>46314</v>
       </c>
       <c r="F28" s="22" t="n">
-        <v>678</v>
+        <v>486</v>
       </c>
       <c r="G28" s="22" t="n">
-        <v>652</v>
+        <v>408</v>
       </c>
       <c r="H28" s="22" t="n">
-        <v>26</v>
+        <v>78</v>
       </c>
       <c r="I28" s="22" t="n">
-        <v>20</v>
+        <v>60</v>
       </c>
       <c r="J28" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K28" s="23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="L28" s="22">
         <f>K28*$B$4</f>
@@ -4248,7 +4248,7 @@
       </c>
       <c r="B29" s="20" t="inlineStr">
         <is>
-          <t>Call-out 3, September</t>
+          <t>Call-out CO-49249</t>
         </is>
       </c>
       <c r="C29" s="20" t="inlineStr">
@@ -4257,28 +4257,28 @@
         </is>
       </c>
       <c r="D29" s="21" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="E29" s="21" t="n">
-        <v>46276</v>
+        <v>46287</v>
       </c>
       <c r="F29" s="22" t="n">
-        <v>619</v>
+        <v>821</v>
       </c>
       <c r="G29" s="22" t="n">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="H29" s="22" t="n">
+        <v>169</v>
+      </c>
+      <c r="I29" s="22" t="n">
         <v>130</v>
       </c>
-      <c r="I29" s="22" t="n">
-        <v>100</v>
-      </c>
       <c r="J29" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K29" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L29" s="22">
         <f>K29*$B$4</f>
@@ -4301,7 +4301,7 @@
       </c>
       <c r="B30" s="20" t="inlineStr">
         <is>
-          <t>Call-out 30, September</t>
+          <t>Call-out CO-49251</t>
         </is>
       </c>
       <c r="C30" s="20" t="inlineStr">
@@ -4310,28 +4310,28 @@
         </is>
       </c>
       <c r="D30" s="21" t="n">
-        <v>46278</v>
+        <v>46293</v>
       </c>
       <c r="E30" s="21" t="n">
-        <v>46279</v>
+        <v>46293</v>
       </c>
       <c r="F30" s="22" t="n">
-        <v>697</v>
+        <v>873</v>
       </c>
       <c r="G30" s="22" t="n">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="H30" s="22" t="n">
-        <v>208</v>
+        <v>221</v>
       </c>
       <c r="I30" s="22" t="n">
-        <v>160</v>
+        <v>170</v>
       </c>
       <c r="J30" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K30" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L30" s="22">
         <f>K30*$B$4</f>
@@ -4354,7 +4354,7 @@
       </c>
       <c r="B31" s="20" t="inlineStr">
         <is>
-          <t>Call-out 31, September</t>
+          <t>Call-out CO-49252</t>
         </is>
       </c>
       <c r="C31" s="20" t="inlineStr">
@@ -4363,28 +4363,28 @@
         </is>
       </c>
       <c r="D31" s="21" t="n">
-        <v>46278</v>
+        <v>46291</v>
       </c>
       <c r="E31" s="21" t="n">
-        <v>46308</v>
+        <v>46293</v>
       </c>
       <c r="F31" s="22" t="n">
-        <v>378</v>
+        <v>349</v>
       </c>
       <c r="G31" s="22" t="n">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="H31" s="22" t="n">
-        <v>52</v>
+        <v>104</v>
       </c>
       <c r="I31" s="22" t="n">
-        <v>40</v>
+        <v>80</v>
       </c>
       <c r="J31" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K31" s="23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L31" s="22">
         <f>K31*$B$4</f>
@@ -4407,7 +4407,7 @@
       </c>
       <c r="B32" s="20" t="inlineStr">
         <is>
-          <t>Call-out 32, September</t>
+          <t>Call-out CO-49253</t>
         </is>
       </c>
       <c r="C32" s="20" t="inlineStr">
@@ -4416,28 +4416,28 @@
         </is>
       </c>
       <c r="D32" s="21" t="n">
-        <v>46286</v>
+        <v>46291</v>
       </c>
       <c r="E32" s="21" t="n">
-        <v>46316</v>
+        <v>46307</v>
       </c>
       <c r="F32" s="22" t="n">
-        <v>642</v>
+        <v>401</v>
       </c>
       <c r="G32" s="22" t="n">
-        <v>408</v>
+        <v>245</v>
       </c>
       <c r="H32" s="22" t="n">
-        <v>234</v>
+        <v>156</v>
       </c>
       <c r="I32" s="22" t="n">
-        <v>180</v>
+        <v>120</v>
       </c>
       <c r="J32" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K32" s="23" t="n">
-        <v>2.5</v>
+        <v>1.5</v>
       </c>
       <c r="L32" s="22">
         <f>K32*$B$4</f>
@@ -4460,7 +4460,7 @@
       </c>
       <c r="B33" s="20" t="inlineStr">
         <is>
-          <t>Call-out 33, September</t>
+          <t>Call-out CO-49254</t>
         </is>
       </c>
       <c r="C33" s="20" t="inlineStr">
@@ -4469,28 +4469,28 @@
         </is>
       </c>
       <c r="D33" s="21" t="n">
-        <v>46273</v>
+        <v>46269</v>
       </c>
       <c r="E33" s="21" t="n">
-        <v>46273</v>
+        <v>46276</v>
       </c>
       <c r="F33" s="22" t="n">
-        <v>479</v>
+        <v>586</v>
       </c>
       <c r="G33" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H33" s="22" t="n">
-        <v>234</v>
+        <v>260</v>
       </c>
       <c r="I33" s="22" t="n">
-        <v>180</v>
+        <v>200</v>
       </c>
       <c r="J33" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K33" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L33" s="22">
         <f>K33*$B$4</f>
@@ -4513,7 +4513,7 @@
       </c>
       <c r="B34" s="20" t="inlineStr">
         <is>
-          <t>Call-out 34, September</t>
+          <t>Call-out CO-49255</t>
         </is>
       </c>
       <c r="C34" s="20" t="inlineStr">
@@ -4522,28 +4522,28 @@
         </is>
       </c>
       <c r="D34" s="21" t="n">
-        <v>46267</v>
+        <v>46290</v>
       </c>
       <c r="E34" s="21" t="n">
-        <v>46274</v>
+        <v>46304</v>
       </c>
       <c r="F34" s="22" t="n">
-        <v>486</v>
+        <v>599</v>
       </c>
       <c r="G34" s="22" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="H34" s="22" t="n">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="I34" s="22" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="J34" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K34" s="23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L34" s="22">
         <f>K34*$B$4</f>
@@ -4566,7 +4566,7 @@
       </c>
       <c r="B35" s="20" t="inlineStr">
         <is>
-          <t>Call-out 35, September</t>
+          <t>Call-out CO-49256</t>
         </is>
       </c>
       <c r="C35" s="20" t="inlineStr">
@@ -4575,16 +4575,16 @@
         </is>
       </c>
       <c r="D35" s="21" t="n">
-        <v>46270</v>
+        <v>46293</v>
       </c>
       <c r="E35" s="21" t="n">
-        <v>46279</v>
+        <v>46301</v>
       </c>
       <c r="F35" s="22" t="n">
-        <v>352</v>
+        <v>678</v>
       </c>
       <c r="G35" s="22" t="n">
-        <v>326</v>
+        <v>652</v>
       </c>
       <c r="H35" s="22" t="n">
         <v>26</v>
@@ -4596,7 +4596,7 @@
         <v>0</v>
       </c>
       <c r="K35" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L35" s="22">
         <f>K35*$B$4</f>
@@ -4619,7 +4619,7 @@
       </c>
       <c r="B36" s="20" t="inlineStr">
         <is>
-          <t>Call-out 36, September</t>
+          <t>Call-out CO-49258</t>
         </is>
       </c>
       <c r="C36" s="20" t="inlineStr">
@@ -4634,22 +4634,22 @@
         <v>46279</v>
       </c>
       <c r="F36" s="22" t="n">
-        <v>362</v>
+        <v>697</v>
       </c>
       <c r="G36" s="22" t="n">
-        <v>245</v>
+        <v>489</v>
       </c>
       <c r="H36" s="22" t="n">
-        <v>117</v>
+        <v>208</v>
       </c>
       <c r="I36" s="22" t="n">
-        <v>90</v>
+        <v>160</v>
       </c>
       <c r="J36" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K36" s="23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L36" s="22">
         <f>K36*$B$4</f>
@@ -4672,7 +4672,7 @@
       </c>
       <c r="B37" s="20" t="inlineStr">
         <is>
-          <t>Call-out 37, September</t>
+          <t>Call-out CO-49259</t>
         </is>
       </c>
       <c r="C37" s="20" t="inlineStr">
@@ -4681,28 +4681,28 @@
         </is>
       </c>
       <c r="D37" s="21" t="n">
-        <v>46283</v>
+        <v>46278</v>
       </c>
       <c r="E37" s="21" t="n">
-        <v>46286</v>
+        <v>46308</v>
       </c>
       <c r="F37" s="22" t="n">
-        <v>349</v>
+        <v>378</v>
       </c>
       <c r="G37" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H37" s="22" t="n">
-        <v>104</v>
+        <v>52</v>
       </c>
       <c r="I37" s="22" t="n">
-        <v>80</v>
+        <v>40</v>
       </c>
       <c r="J37" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K37" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L37" s="22">
         <f>K37*$B$4</f>
@@ -4725,7 +4725,7 @@
       </c>
       <c r="B38" s="20" t="inlineStr">
         <is>
-          <t>Call-out 38, September</t>
+          <t>Call-out CO-49260</t>
         </is>
       </c>
       <c r="C38" s="20" t="inlineStr">
@@ -4734,28 +4734,28 @@
         </is>
       </c>
       <c r="D38" s="21" t="n">
-        <v>46288</v>
+        <v>46286</v>
       </c>
       <c r="E38" s="21" t="n">
-        <v>46302</v>
+        <v>46316</v>
       </c>
       <c r="F38" s="22" t="n">
-        <v>417</v>
+        <v>642</v>
       </c>
       <c r="G38" s="22" t="n">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="H38" s="22" t="n">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="I38" s="22" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="J38" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K38" s="23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L38" s="22">
         <f>K38*$B$4</f>
@@ -4778,7 +4778,7 @@
       </c>
       <c r="B39" s="20" t="inlineStr">
         <is>
-          <t>Call-out 39, September</t>
+          <t>Call-out CO-49261</t>
         </is>
       </c>
       <c r="C39" s="20" t="inlineStr">
@@ -4787,28 +4787,28 @@
         </is>
       </c>
       <c r="D39" s="21" t="n">
-        <v>46288</v>
+        <v>46273</v>
       </c>
       <c r="E39" s="21" t="n">
-        <v>46288</v>
+        <v>46273</v>
       </c>
       <c r="F39" s="22" t="n">
-        <v>280</v>
+        <v>479</v>
       </c>
       <c r="G39" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H39" s="22" t="n">
-        <v>117</v>
+        <v>234</v>
       </c>
       <c r="I39" s="22" t="n">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="J39" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K39" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L39" s="22">
         <f>K39*$B$4</f>
@@ -4831,7 +4831,7 @@
       </c>
       <c r="B40" s="20" t="inlineStr">
         <is>
-          <t>Call-out 4, September</t>
+          <t>Call-out CO-49262</t>
         </is>
       </c>
       <c r="C40" s="20" t="inlineStr">
@@ -4840,28 +4840,28 @@
         </is>
       </c>
       <c r="D40" s="21" t="n">
-        <v>46277</v>
+        <v>46267</v>
       </c>
       <c r="E40" s="21" t="n">
-        <v>46279</v>
+        <v>46274</v>
       </c>
       <c r="F40" s="22" t="n">
-        <v>508</v>
+        <v>486</v>
       </c>
       <c r="G40" s="22" t="n">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="H40" s="22" t="n">
-        <v>182</v>
+        <v>78</v>
       </c>
       <c r="I40" s="22" t="n">
-        <v>140</v>
+        <v>60</v>
       </c>
       <c r="J40" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K40" s="23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L40" s="22">
         <f>K40*$B$4</f>
@@ -4884,7 +4884,7 @@
       </c>
       <c r="B41" s="20" t="inlineStr">
         <is>
-          <t>Call-out 40, September</t>
+          <t>Call-out CO-49264</t>
         </is>
       </c>
       <c r="C41" s="20" t="inlineStr">
@@ -4893,28 +4893,28 @@
         </is>
       </c>
       <c r="D41" s="21" t="n">
-        <v>46266</v>
+        <v>46270</v>
       </c>
       <c r="E41" s="21" t="n">
-        <v>46296</v>
+        <v>46279</v>
       </c>
       <c r="F41" s="22" t="n">
-        <v>668</v>
+        <v>352</v>
       </c>
       <c r="G41" s="22" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="H41" s="22" t="n">
-        <v>260</v>
+        <v>26</v>
       </c>
       <c r="I41" s="22" t="n">
-        <v>200</v>
+        <v>20</v>
       </c>
       <c r="J41" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K41" s="23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L41" s="22">
         <f>K41*$B$4</f>
@@ -4937,7 +4937,7 @@
       </c>
       <c r="B42" s="20" t="inlineStr">
         <is>
-          <t>Call-out 41, September</t>
+          <t>Call-out CO-49265</t>
         </is>
       </c>
       <c r="C42" s="20" t="inlineStr">
@@ -4946,28 +4946,28 @@
         </is>
       </c>
       <c r="D42" s="21" t="n">
-        <v>46283</v>
+        <v>46278</v>
       </c>
       <c r="E42" s="21" t="n">
-        <v>46290</v>
+        <v>46279</v>
       </c>
       <c r="F42" s="22" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="G42" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H42" s="22" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="I42" s="22" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J42" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K42" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L42" s="22">
         <f>K42*$B$4</f>
@@ -4990,7 +4990,7 @@
       </c>
       <c r="B43" s="20" t="inlineStr">
         <is>
-          <t>Call-out 42, September</t>
+          <t>Call-out CO-49266</t>
         </is>
       </c>
       <c r="C43" s="20" t="inlineStr">
@@ -4999,28 +4999,28 @@
         </is>
       </c>
       <c r="D43" s="21" t="n">
-        <v>46278</v>
+        <v>46283</v>
       </c>
       <c r="E43" s="21" t="n">
-        <v>46293</v>
+        <v>46286</v>
       </c>
       <c r="F43" s="22" t="n">
-        <v>606</v>
+        <v>349</v>
       </c>
       <c r="G43" s="22" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="H43" s="22" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I43" s="22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J43" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K43" s="23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L43" s="22">
         <f>K43*$B$4</f>
@@ -5043,7 +5043,7 @@
       </c>
       <c r="B44" s="20" t="inlineStr">
         <is>
-          <t>Call-out 43, September</t>
+          <t>Call-out CO-49267</t>
         </is>
       </c>
       <c r="C44" s="20" t="inlineStr">
@@ -5052,28 +5052,28 @@
         </is>
       </c>
       <c r="D44" s="21" t="n">
-        <v>46281</v>
+        <v>46288</v>
       </c>
       <c r="E44" s="21" t="n">
-        <v>46311</v>
+        <v>46302</v>
       </c>
       <c r="F44" s="22" t="n">
-        <v>297</v>
+        <v>417</v>
       </c>
       <c r="G44" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H44" s="22" t="n">
-        <v>52</v>
+        <v>91</v>
       </c>
       <c r="I44" s="22" t="n">
-        <v>40</v>
+        <v>70</v>
       </c>
       <c r="J44" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K44" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L44" s="22">
         <f>K44*$B$4</f>
@@ -5096,7 +5096,7 @@
       </c>
       <c r="B45" s="20" t="inlineStr">
         <is>
-          <t>Call-out 44, September</t>
+          <t>Call-out CO-49268</t>
         </is>
       </c>
       <c r="C45" s="20" t="inlineStr">
@@ -5105,28 +5105,28 @@
         </is>
       </c>
       <c r="D45" s="21" t="n">
-        <v>46286</v>
+        <v>46288</v>
       </c>
       <c r="E45" s="21" t="n">
-        <v>46293</v>
+        <v>46288</v>
       </c>
       <c r="F45" s="22" t="n">
-        <v>756</v>
+        <v>280</v>
       </c>
       <c r="G45" s="22" t="n">
-        <v>652</v>
+        <v>163</v>
       </c>
       <c r="H45" s="22" t="n">
-        <v>104</v>
+        <v>117</v>
       </c>
       <c r="I45" s="22" t="n">
-        <v>80</v>
+        <v>90</v>
       </c>
       <c r="J45" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K45" s="23" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="L45" s="22">
         <f>K45*$B$4</f>
@@ -5149,7 +5149,7 @@
       </c>
       <c r="B46" s="20" t="inlineStr">
         <is>
-          <t>Call-out 45, September</t>
+          <t>Call-out CO-49269</t>
         </is>
       </c>
       <c r="C46" s="20" t="inlineStr">
@@ -5158,28 +5158,28 @@
         </is>
       </c>
       <c r="D46" s="21" t="n">
-        <v>46282</v>
+        <v>46266</v>
       </c>
       <c r="E46" s="21" t="n">
-        <v>46282</v>
+        <v>46296</v>
       </c>
       <c r="F46" s="22" t="n">
-        <v>717</v>
+        <v>668</v>
       </c>
       <c r="G46" s="22" t="n">
-        <v>652</v>
+        <v>408</v>
       </c>
       <c r="H46" s="22" t="n">
-        <v>65</v>
+        <v>260</v>
       </c>
       <c r="I46" s="22" t="n">
-        <v>50</v>
+        <v>200</v>
       </c>
       <c r="J46" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="L46" s="22">
         <f>K46*$B$4</f>
@@ -5202,7 +5202,7 @@
       </c>
       <c r="B47" s="20" t="inlineStr">
         <is>
-          <t>Call-out 46, September</t>
+          <t>Call-out CO-49271</t>
         </is>
       </c>
       <c r="C47" s="20" t="inlineStr">
@@ -5211,28 +5211,28 @@
         </is>
       </c>
       <c r="D47" s="21" t="n">
-        <v>46273</v>
+        <v>46283</v>
       </c>
       <c r="E47" s="21" t="n">
-        <v>46273</v>
+        <v>46290</v>
       </c>
       <c r="F47" s="22" t="n">
-        <v>619</v>
+        <v>306</v>
       </c>
       <c r="G47" s="22" t="n">
-        <v>489</v>
+        <v>163</v>
       </c>
       <c r="H47" s="22" t="n">
-        <v>130</v>
+        <v>143</v>
       </c>
       <c r="I47" s="22" t="n">
-        <v>100</v>
+        <v>110</v>
       </c>
       <c r="J47" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K47" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L47" s="22">
         <f>K47*$B$4</f>
@@ -5255,7 +5255,7 @@
       </c>
       <c r="B48" s="20" t="inlineStr">
         <is>
-          <t>Call-out 47, September</t>
+          <t>Call-out CO-49272</t>
         </is>
       </c>
       <c r="C48" s="20" t="inlineStr">
@@ -5264,28 +5264,28 @@
         </is>
       </c>
       <c r="D48" s="21" t="n">
-        <v>46266</v>
+        <v>46278</v>
       </c>
       <c r="E48" s="21" t="n">
-        <v>46273</v>
+        <v>46293</v>
       </c>
       <c r="F48" s="22" t="n">
-        <v>486</v>
+        <v>606</v>
       </c>
       <c r="G48" s="22" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="H48" s="22" t="n">
-        <v>78</v>
+        <v>117</v>
       </c>
       <c r="I48" s="22" t="n">
-        <v>60</v>
+        <v>90</v>
       </c>
       <c r="J48" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K48" s="23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L48" s="22">
         <f>K48*$B$4</f>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="B49" s="20" t="inlineStr">
         <is>
-          <t>Call-out 48, September</t>
+          <t>Call-out CO-49273</t>
         </is>
       </c>
       <c r="C49" s="20" t="inlineStr">
@@ -5320,25 +5320,25 @@
         <v>46281</v>
       </c>
       <c r="E49" s="21" t="n">
-        <v>46283</v>
+        <v>46311</v>
       </c>
       <c r="F49" s="22" t="n">
-        <v>345</v>
+        <v>297</v>
       </c>
       <c r="G49" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H49" s="22" t="n">
-        <v>182</v>
+        <v>52</v>
       </c>
       <c r="I49" s="22" t="n">
-        <v>140</v>
+        <v>40</v>
       </c>
       <c r="J49" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K49" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L49" s="22">
         <f>K49*$B$4</f>
@@ -5361,7 +5361,7 @@
       </c>
       <c r="B50" s="20" t="inlineStr">
         <is>
-          <t>Call-out 49, September</t>
+          <t>Call-out CO-49274</t>
         </is>
       </c>
       <c r="C50" s="20" t="inlineStr">
@@ -5370,28 +5370,28 @@
         </is>
       </c>
       <c r="D50" s="21" t="n">
-        <v>46292</v>
+        <v>46286</v>
       </c>
       <c r="E50" s="21" t="n">
-        <v>46307</v>
+        <v>46293</v>
       </c>
       <c r="F50" s="22" t="n">
-        <v>586</v>
+        <v>756</v>
       </c>
       <c r="G50" s="22" t="n">
-        <v>326</v>
+        <v>652</v>
       </c>
       <c r="H50" s="22" t="n">
-        <v>260</v>
+        <v>104</v>
       </c>
       <c r="I50" s="22" t="n">
-        <v>200</v>
+        <v>80</v>
       </c>
       <c r="J50" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K50" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L50" s="22">
         <f>K50*$B$4</f>
@@ -5414,7 +5414,7 @@
       </c>
       <c r="B51" s="20" t="inlineStr">
         <is>
-          <t>Call-out 5, September</t>
+          <t>Call-out CO-49275</t>
         </is>
       </c>
       <c r="C51" s="20" t="inlineStr">
@@ -5423,28 +5423,28 @@
         </is>
       </c>
       <c r="D51" s="21" t="n">
-        <v>46291</v>
+        <v>46282</v>
       </c>
       <c r="E51" s="21" t="n">
-        <v>46293</v>
+        <v>46282</v>
       </c>
       <c r="F51" s="22" t="n">
-        <v>508</v>
+        <v>717</v>
       </c>
       <c r="G51" s="22" t="n">
-        <v>326</v>
+        <v>652</v>
       </c>
       <c r="H51" s="22" t="n">
-        <v>182</v>
+        <v>65</v>
       </c>
       <c r="I51" s="22" t="n">
-        <v>140</v>
+        <v>50</v>
       </c>
       <c r="J51" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K51" s="23" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="L51" s="22">
         <f>K51*$B$4</f>
@@ -5467,7 +5467,7 @@
       </c>
       <c r="B52" s="20" t="inlineStr">
         <is>
-          <t>Call-out 50, September</t>
+          <t>Call-out CO-49276</t>
         </is>
       </c>
       <c r="C52" s="20" t="inlineStr">
@@ -5476,28 +5476,28 @@
         </is>
       </c>
       <c r="D52" s="21" t="n">
-        <v>46293</v>
+        <v>46273</v>
       </c>
       <c r="E52" s="21" t="n">
-        <v>46323</v>
+        <v>46273</v>
       </c>
       <c r="F52" s="22" t="n">
-        <v>544</v>
+        <v>619</v>
       </c>
       <c r="G52" s="22" t="n">
-        <v>245</v>
+        <v>489</v>
       </c>
       <c r="H52" s="22" t="n">
-        <v>299</v>
+        <v>130</v>
       </c>
       <c r="I52" s="22" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="J52" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K52" s="23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L52" s="22">
         <f>K52*$B$4</f>
@@ -5520,7 +5520,7 @@
       </c>
       <c r="B53" s="20" t="inlineStr">
         <is>
-          <t>Call-out 51, September</t>
+          <t>Call-out CO-49278</t>
         </is>
       </c>
       <c r="C53" s="20" t="inlineStr">
@@ -5529,28 +5529,28 @@
         </is>
       </c>
       <c r="D53" s="21" t="n">
-        <v>46287</v>
+        <v>46266</v>
       </c>
       <c r="E53" s="21" t="n">
-        <v>46287</v>
+        <v>46273</v>
       </c>
       <c r="F53" s="22" t="n">
-        <v>697</v>
+        <v>486</v>
       </c>
       <c r="G53" s="22" t="n">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="H53" s="22" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="I53" s="22" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="J53" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K53" s="23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L53" s="22">
         <f>K53*$B$4</f>
@@ -5573,7 +5573,7 @@
       </c>
       <c r="B54" s="20" t="inlineStr">
         <is>
-          <t>Call-out 52, September</t>
+          <t>Call-out CO-49279</t>
         </is>
       </c>
       <c r="C54" s="20" t="inlineStr">
@@ -5582,28 +5582,28 @@
         </is>
       </c>
       <c r="D54" s="21" t="n">
-        <v>46287</v>
+        <v>46281</v>
       </c>
       <c r="E54" s="21" t="n">
-        <v>46294</v>
+        <v>46283</v>
       </c>
       <c r="F54" s="22" t="n">
-        <v>456</v>
+        <v>345</v>
       </c>
       <c r="G54" s="22" t="n">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="H54" s="22" t="n">
-        <v>130</v>
+        <v>182</v>
       </c>
       <c r="I54" s="22" t="n">
-        <v>100</v>
+        <v>140</v>
       </c>
       <c r="J54" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K54" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L54" s="22">
         <f>K54*$B$4</f>
@@ -5626,7 +5626,7 @@
       </c>
       <c r="B55" s="20" t="inlineStr">
         <is>
-          <t>Call-out 53, September</t>
+          <t>Call-out CO-49280</t>
         </is>
       </c>
       <c r="C55" s="20" t="inlineStr">
@@ -5635,28 +5635,28 @@
         </is>
       </c>
       <c r="D55" s="21" t="n">
-        <v>46267</v>
+        <v>46292</v>
       </c>
       <c r="E55" s="21" t="n">
-        <v>46267</v>
+        <v>46307</v>
       </c>
       <c r="F55" s="22" t="n">
-        <v>336</v>
+        <v>586</v>
       </c>
       <c r="G55" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H55" s="22" t="n">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="I55" s="22" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="J55" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K55" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L55" s="22">
         <f>K55*$B$4</f>
@@ -5679,7 +5679,7 @@
       </c>
       <c r="B56" s="20" t="inlineStr">
         <is>
-          <t>Call-out 54, September</t>
+          <t>Call-out CO-49281</t>
         </is>
       </c>
       <c r="C56" s="20" t="inlineStr">
@@ -5688,28 +5688,28 @@
         </is>
       </c>
       <c r="D56" s="21" t="n">
-        <v>46271</v>
+        <v>46293</v>
       </c>
       <c r="E56" s="21" t="n">
-        <v>46272</v>
+        <v>46323</v>
       </c>
       <c r="F56" s="22" t="n">
-        <v>482</v>
+        <v>544</v>
       </c>
       <c r="G56" s="22" t="n">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="H56" s="22" t="n">
-        <v>156</v>
+        <v>299</v>
       </c>
       <c r="I56" s="22" t="n">
-        <v>120</v>
+        <v>230</v>
       </c>
       <c r="J56" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K56" s="23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L56" s="22">
         <f>K56*$B$4</f>
@@ -5732,7 +5732,7 @@
       </c>
       <c r="B57" s="20" t="inlineStr">
         <is>
-          <t>Call-out 55, September</t>
+          <t>Call-out CO-49282</t>
         </is>
       </c>
       <c r="C57" s="20" t="inlineStr">
@@ -5741,28 +5741,28 @@
         </is>
       </c>
       <c r="D57" s="21" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="E57" s="21" t="n">
-        <v>46279</v>
+        <v>46287</v>
       </c>
       <c r="F57" s="22" t="n">
-        <v>189</v>
+        <v>697</v>
       </c>
       <c r="G57" s="22" t="n">
-        <v>163</v>
+        <v>489</v>
       </c>
       <c r="H57" s="22" t="n">
-        <v>26</v>
+        <v>208</v>
       </c>
       <c r="I57" s="22" t="n">
-        <v>20</v>
+        <v>160</v>
       </c>
       <c r="J57" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K57" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L57" s="22">
         <f>K57*$B$4</f>
@@ -5785,7 +5785,7 @@
       </c>
       <c r="B58" s="20" t="inlineStr">
         <is>
-          <t>Call-out 56, September</t>
+          <t>Call-out CO-49284</t>
         </is>
       </c>
       <c r="C58" s="20" t="inlineStr">
@@ -5794,28 +5794,28 @@
         </is>
       </c>
       <c r="D58" s="21" t="n">
-        <v>46275</v>
+        <v>46287</v>
       </c>
       <c r="E58" s="21" t="n">
-        <v>46275</v>
+        <v>46294</v>
       </c>
       <c r="F58" s="22" t="n">
-        <v>808</v>
+        <v>456</v>
       </c>
       <c r="G58" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H58" s="22" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="I58" s="22" t="n">
-        <v>120</v>
+        <v>100</v>
       </c>
       <c r="J58" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K58" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L58" s="22">
         <f>K58*$B$4</f>
@@ -5838,7 +5838,7 @@
       </c>
       <c r="B59" s="20" t="inlineStr">
         <is>
-          <t>Call-out 57, September</t>
+          <t>Call-out CO-49285</t>
         </is>
       </c>
       <c r="C59" s="20" t="inlineStr">
@@ -5847,28 +5847,28 @@
         </is>
       </c>
       <c r="D59" s="21" t="n">
-        <v>46292</v>
+        <v>46267</v>
       </c>
       <c r="E59" s="21" t="n">
-        <v>46293</v>
+        <v>46267</v>
       </c>
       <c r="F59" s="22" t="n">
-        <v>586</v>
+        <v>336</v>
       </c>
       <c r="G59" s="22" t="n">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="H59" s="22" t="n">
-        <v>260</v>
+        <v>91</v>
       </c>
       <c r="I59" s="22" t="n">
-        <v>200</v>
+        <v>70</v>
       </c>
       <c r="J59" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K59" s="23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L59" s="22">
         <f>K59*$B$4</f>
@@ -5891,7 +5891,7 @@
       </c>
       <c r="B60" s="20" t="inlineStr">
         <is>
-          <t>Call-out 58, September</t>
+          <t>Call-out CO-49286</t>
         </is>
       </c>
       <c r="C60" s="20" t="inlineStr">
@@ -5900,28 +5900,28 @@
         </is>
       </c>
       <c r="D60" s="21" t="n">
-        <v>46282</v>
+        <v>46271</v>
       </c>
       <c r="E60" s="21" t="n">
-        <v>46289</v>
+        <v>46272</v>
       </c>
       <c r="F60" s="22" t="n">
-        <v>349</v>
+        <v>482</v>
       </c>
       <c r="G60" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H60" s="22" t="n">
-        <v>104</v>
+        <v>156</v>
       </c>
       <c r="I60" s="22" t="n">
-        <v>80</v>
+        <v>120</v>
       </c>
       <c r="J60" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K60" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L60" s="22">
         <f>K60*$B$4</f>
@@ -5944,7 +5944,7 @@
       </c>
       <c r="B61" s="20" t="inlineStr">
         <is>
-          <t>Call-out 59, September</t>
+          <t>Call-out CO-49287</t>
         </is>
       </c>
       <c r="C61" s="20" t="inlineStr">
@@ -5953,28 +5953,28 @@
         </is>
       </c>
       <c r="D61" s="21" t="n">
-        <v>46292</v>
+        <v>46279</v>
       </c>
       <c r="E61" s="21" t="n">
-        <v>46294</v>
+        <v>46279</v>
       </c>
       <c r="F61" s="22" t="n">
-        <v>375</v>
+        <v>189</v>
       </c>
       <c r="G61" s="22" t="n">
-        <v>245</v>
+        <v>163</v>
       </c>
       <c r="H61" s="22" t="n">
-        <v>130</v>
+        <v>26</v>
       </c>
       <c r="I61" s="22" t="n">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="J61" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K61" s="23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L61" s="22">
         <f>K61*$B$4</f>
@@ -5997,7 +5997,7 @@
       </c>
       <c r="B62" s="20" t="inlineStr">
         <is>
-          <t>Call-out 6, September</t>
+          <t>Call-out CO-49288</t>
         </is>
       </c>
       <c r="C62" s="20" t="inlineStr">
@@ -6009,25 +6009,25 @@
         <v>46275</v>
       </c>
       <c r="E62" s="21" t="n">
-        <v>46282</v>
+        <v>46275</v>
       </c>
       <c r="F62" s="22" t="n">
-        <v>499</v>
+        <v>808</v>
       </c>
       <c r="G62" s="22" t="n">
-        <v>408</v>
+        <v>652</v>
       </c>
       <c r="H62" s="22" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
       <c r="I62" s="22" t="n">
-        <v>70</v>
+        <v>120</v>
       </c>
       <c r="J62" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K62" s="23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L62" s="22">
         <f>K62*$B$4</f>
@@ -6050,7 +6050,7 @@
       </c>
       <c r="B63" s="20" t="inlineStr">
         <is>
-          <t>Call-out 60, September</t>
+          <t>Call-out CO-49289</t>
         </is>
       </c>
       <c r="C63" s="20" t="inlineStr">
@@ -6059,22 +6059,22 @@
         </is>
       </c>
       <c r="D63" s="21" t="n">
-        <v>46284</v>
+        <v>46292</v>
       </c>
       <c r="E63" s="21" t="n">
-        <v>46286</v>
+        <v>46293</v>
       </c>
       <c r="F63" s="22" t="n">
-        <v>417</v>
+        <v>586</v>
       </c>
       <c r="G63" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H63" s="22" t="n">
-        <v>91</v>
+        <v>260</v>
       </c>
       <c r="I63" s="22" t="n">
-        <v>70</v>
+        <v>200</v>
       </c>
       <c r="J63" s="22" t="n">
         <v>0</v>
@@ -6103,7 +6103,7 @@
       </c>
       <c r="B64" s="20" t="inlineStr">
         <is>
-          <t>Call-out 61, September</t>
+          <t>Call-out CO-49291</t>
         </is>
       </c>
       <c r="C64" s="20" t="inlineStr">
@@ -6112,28 +6112,28 @@
         </is>
       </c>
       <c r="D64" s="21" t="n">
-        <v>46284</v>
+        <v>46282</v>
       </c>
       <c r="E64" s="21" t="n">
-        <v>46301</v>
+        <v>46289</v>
       </c>
       <c r="F64" s="22" t="n">
-        <v>319</v>
+        <v>349</v>
       </c>
       <c r="G64" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H64" s="22" t="n">
-        <v>156</v>
+        <v>104</v>
       </c>
       <c r="I64" s="22" t="n">
-        <v>120</v>
+        <v>80</v>
       </c>
       <c r="J64" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K64" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L64" s="22">
         <f>K64*$B$4</f>
@@ -6156,7 +6156,7 @@
       </c>
       <c r="B65" s="20" t="inlineStr">
         <is>
-          <t>Call-out 62, September</t>
+          <t>Call-out CO-49292</t>
         </is>
       </c>
       <c r="C65" s="20" t="inlineStr">
@@ -6165,22 +6165,22 @@
         </is>
       </c>
       <c r="D65" s="21" t="n">
-        <v>46281</v>
+        <v>46292</v>
       </c>
       <c r="E65" s="21" t="n">
-        <v>46281</v>
+        <v>46294</v>
       </c>
       <c r="F65" s="22" t="n">
-        <v>362</v>
+        <v>375</v>
       </c>
       <c r="G65" s="22" t="n">
         <v>245</v>
       </c>
       <c r="H65" s="22" t="n">
-        <v>117</v>
+        <v>130</v>
       </c>
       <c r="I65" s="22" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
       <c r="J65" s="22" t="n">
         <v>0</v>
@@ -6209,7 +6209,7 @@
       </c>
       <c r="B66" s="20" t="inlineStr">
         <is>
-          <t>Call-out 63, September</t>
+          <t>Call-out CO-49293</t>
         </is>
       </c>
       <c r="C66" s="20" t="inlineStr">
@@ -6218,28 +6218,28 @@
         </is>
       </c>
       <c r="D66" s="21" t="n">
-        <v>46280</v>
+        <v>46284</v>
       </c>
       <c r="E66" s="21" t="n">
-        <v>46310</v>
+        <v>46286</v>
       </c>
       <c r="F66" s="22" t="n">
-        <v>577</v>
+        <v>417</v>
       </c>
       <c r="G66" s="22" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="H66" s="22" t="n">
-        <v>169</v>
+        <v>91</v>
       </c>
       <c r="I66" s="22" t="n">
-        <v>130</v>
+        <v>70</v>
       </c>
       <c r="J66" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K66" s="23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L66" s="22">
         <f>K66*$B$4</f>
@@ -6262,7 +6262,7 @@
       </c>
       <c r="B67" s="20" t="inlineStr">
         <is>
-          <t>Call-out 64, September</t>
+          <t>Call-out CO-49294</t>
         </is>
       </c>
       <c r="C67" s="20" t="inlineStr">
@@ -6271,28 +6271,28 @@
         </is>
       </c>
       <c r="D67" s="21" t="n">
-        <v>46270</v>
+        <v>46284</v>
       </c>
       <c r="E67" s="21" t="n">
-        <v>46279</v>
+        <v>46301</v>
       </c>
       <c r="F67" s="22" t="n">
-        <v>495</v>
+        <v>319</v>
       </c>
       <c r="G67" s="22" t="n">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="H67" s="22" t="n">
-        <v>169</v>
+        <v>156</v>
       </c>
       <c r="I67" s="22" t="n">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="J67" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K67" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L67" s="22">
         <f>K67*$B$4</f>
@@ -6315,7 +6315,7 @@
       </c>
       <c r="B68" s="20" t="inlineStr">
         <is>
-          <t>Call-out 7, September</t>
+          <t>Call-out CO-49295</t>
         </is>
       </c>
       <c r="C68" s="20" t="inlineStr">
@@ -6324,28 +6324,28 @@
         </is>
       </c>
       <c r="D68" s="21" t="n">
-        <v>46280</v>
+        <v>46281</v>
       </c>
       <c r="E68" s="21" t="n">
-        <v>46294</v>
+        <v>46281</v>
       </c>
       <c r="F68" s="22" t="n">
-        <v>788</v>
+        <v>362</v>
       </c>
       <c r="G68" s="22" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="H68" s="22" t="n">
-        <v>299</v>
+        <v>117</v>
       </c>
       <c r="I68" s="22" t="n">
-        <v>230</v>
+        <v>90</v>
       </c>
       <c r="J68" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K68" s="23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L68" s="22">
         <f>K68*$B$4</f>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="B69" s="20" t="inlineStr">
         <is>
-          <t>Call-out 8, September</t>
+          <t>Call-out CO-49296</t>
         </is>
       </c>
       <c r="C69" s="20" t="inlineStr">
@@ -6377,28 +6377,28 @@
         </is>
       </c>
       <c r="D69" s="21" t="n">
-        <v>46267</v>
+        <v>46280</v>
       </c>
       <c r="E69" s="21" t="n">
-        <v>46269</v>
+        <v>46310</v>
       </c>
       <c r="F69" s="22" t="n">
-        <v>462</v>
+        <v>577</v>
       </c>
       <c r="G69" s="22" t="n">
-        <v>163</v>
+        <v>408</v>
       </c>
       <c r="H69" s="22" t="n">
-        <v>299</v>
+        <v>169</v>
       </c>
       <c r="I69" s="22" t="n">
-        <v>230</v>
+        <v>130</v>
       </c>
       <c r="J69" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K69" s="23" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L69" s="22">
         <f>K69*$B$4</f>
@@ -6421,7 +6421,7 @@
       </c>
       <c r="B70" s="20" t="inlineStr">
         <is>
-          <t>Call-out 9, September</t>
+          <t>Call-out CO-49298</t>
         </is>
       </c>
       <c r="C70" s="20" t="inlineStr">
@@ -6430,28 +6430,28 @@
         </is>
       </c>
       <c r="D70" s="21" t="n">
-        <v>46287</v>
+        <v>46270</v>
       </c>
       <c r="E70" s="21" t="n">
-        <v>46317</v>
+        <v>46279</v>
       </c>
       <c r="F70" s="22" t="n">
-        <v>834</v>
+        <v>495</v>
       </c>
       <c r="G70" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H70" s="22" t="n">
-        <v>182</v>
+        <v>169</v>
       </c>
       <c r="I70" s="22" t="n">
-        <v>140</v>
+        <v>130</v>
       </c>
       <c r="J70" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K70" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L70" s="22">
         <f>K70*$B$4</f>
@@ -7454,7 +7454,7 @@
       </c>
       <c r="B91" s="20" t="inlineStr">
         <is>
-          <t>Call-out 1, August</t>
+          <t>Call-out CO-49132</t>
         </is>
       </c>
       <c r="C91" s="20" t="inlineStr">
@@ -7507,7 +7507,7 @@
       </c>
       <c r="B92" s="20" t="inlineStr">
         <is>
-          <t>Call-out 10, August</t>
+          <t>Call-out CO-49133</t>
         </is>
       </c>
       <c r="C92" s="20" t="inlineStr">
@@ -7516,22 +7516,22 @@
         </is>
       </c>
       <c r="D92" s="21" t="n">
-        <v>46242</v>
+        <v>46253</v>
       </c>
       <c r="E92" s="21" t="n">
-        <v>46272</v>
+        <v>46253</v>
       </c>
       <c r="F92" s="22" t="n">
-        <v>378</v>
+        <v>404</v>
       </c>
       <c r="G92" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H92" s="22" t="n">
-        <v>52</v>
+        <v>78</v>
       </c>
       <c r="I92" s="22" t="n">
-        <v>40</v>
+        <v>60</v>
       </c>
       <c r="J92" s="22" t="n">
         <v>0</v>
@@ -7560,7 +7560,7 @@
       </c>
       <c r="B93" s="20" t="inlineStr">
         <is>
-          <t>Call-out 11, August</t>
+          <t>Call-out CO-49134</t>
         </is>
       </c>
       <c r="C93" s="20" t="inlineStr">
@@ -7569,28 +7569,28 @@
         </is>
       </c>
       <c r="D93" s="21" t="n">
-        <v>46237</v>
+        <v>46235</v>
       </c>
       <c r="E93" s="21" t="n">
         <v>46244</v>
       </c>
       <c r="F93" s="22" t="n">
-        <v>528</v>
+        <v>349</v>
       </c>
       <c r="G93" s="22" t="n">
-        <v>489</v>
+        <v>245</v>
       </c>
       <c r="H93" s="22" t="n">
-        <v>39</v>
+        <v>104</v>
       </c>
       <c r="I93" s="22" t="n">
-        <v>30</v>
+        <v>80</v>
       </c>
       <c r="J93" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K93" s="23" t="n">
-        <v>3</v>
+        <v>1.5</v>
       </c>
       <c r="L93" s="22">
         <f>K93*$B$4</f>
@@ -7613,7 +7613,7 @@
       </c>
       <c r="B94" s="20" t="inlineStr">
         <is>
-          <t>Call-out 12, August</t>
+          <t>Call-out CO-49135</t>
         </is>
       </c>
       <c r="C94" s="20" t="inlineStr">
@@ -7622,28 +7622,28 @@
         </is>
       </c>
       <c r="D94" s="21" t="n">
-        <v>46261</v>
+        <v>46240</v>
       </c>
       <c r="E94" s="21" t="n">
-        <v>46265</v>
+        <v>46240</v>
       </c>
       <c r="F94" s="22" t="n">
-        <v>762</v>
+        <v>345</v>
       </c>
       <c r="G94" s="22" t="n">
-        <v>489</v>
+        <v>163</v>
       </c>
       <c r="H94" s="22" t="n">
-        <v>273</v>
+        <v>182</v>
       </c>
       <c r="I94" s="22" t="n">
-        <v>210</v>
+        <v>140</v>
       </c>
       <c r="J94" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K94" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L94" s="22">
         <f>K94*$B$4</f>
@@ -7666,7 +7666,7 @@
       </c>
       <c r="B95" s="20" t="inlineStr">
         <is>
-          <t>Call-out 13, August</t>
+          <t>Call-out CO-49136</t>
         </is>
       </c>
       <c r="C95" s="20" t="inlineStr">
@@ -7675,28 +7675,28 @@
         </is>
       </c>
       <c r="D95" s="21" t="n">
-        <v>46246</v>
+        <v>46260</v>
       </c>
       <c r="E95" s="21" t="n">
-        <v>46247</v>
+        <v>46267</v>
       </c>
       <c r="F95" s="22" t="n">
-        <v>417</v>
+        <v>538</v>
       </c>
       <c r="G95" s="22" t="n">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="H95" s="22" t="n">
-        <v>91</v>
+        <v>130</v>
       </c>
       <c r="I95" s="22" t="n">
-        <v>70</v>
+        <v>100</v>
       </c>
       <c r="J95" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K95" s="23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L95" s="22">
         <f>K95*$B$4</f>
@@ -7719,7 +7719,7 @@
       </c>
       <c r="B96" s="20" t="inlineStr">
         <is>
-          <t>Call-out 14, August</t>
+          <t>Call-out CO-49137</t>
         </is>
       </c>
       <c r="C96" s="20" t="inlineStr">
@@ -7728,22 +7728,22 @@
         </is>
       </c>
       <c r="D96" s="21" t="n">
-        <v>46239</v>
+        <v>46245</v>
       </c>
       <c r="E96" s="21" t="n">
-        <v>46269</v>
+        <v>46245</v>
       </c>
       <c r="F96" s="22" t="n">
-        <v>749</v>
+        <v>606</v>
       </c>
       <c r="G96" s="22" t="n">
         <v>489</v>
       </c>
       <c r="H96" s="22" t="n">
-        <v>260</v>
+        <v>117</v>
       </c>
       <c r="I96" s="22" t="n">
-        <v>200</v>
+        <v>90</v>
       </c>
       <c r="J96" s="22" t="n">
         <v>0</v>
@@ -7772,7 +7772,7 @@
       </c>
       <c r="B97" s="20" t="inlineStr">
         <is>
-          <t>Call-out 15, August</t>
+          <t>Call-out CO-49139</t>
         </is>
       </c>
       <c r="C97" s="20" t="inlineStr">
@@ -7781,28 +7781,28 @@
         </is>
       </c>
       <c r="D97" s="21" t="n">
-        <v>46243</v>
+        <v>46247</v>
       </c>
       <c r="E97" s="21" t="n">
-        <v>46258</v>
+        <v>46254</v>
       </c>
       <c r="F97" s="22" t="n">
-        <v>593</v>
+        <v>189</v>
       </c>
       <c r="G97" s="22" t="n">
-        <v>489</v>
+        <v>163</v>
       </c>
       <c r="H97" s="22" t="n">
-        <v>104</v>
+        <v>26</v>
       </c>
       <c r="I97" s="22" t="n">
-        <v>80</v>
+        <v>20</v>
       </c>
       <c r="J97" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K97" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L97" s="22">
         <f>K97*$B$4</f>
@@ -7825,7 +7825,7 @@
       </c>
       <c r="B98" s="20" t="inlineStr">
         <is>
-          <t>Call-out 16, August</t>
+          <t>Call-out CO-49140</t>
         </is>
       </c>
       <c r="C98" s="20" t="inlineStr">
@@ -7834,16 +7834,16 @@
         </is>
       </c>
       <c r="D98" s="21" t="n">
-        <v>46256</v>
+        <v>46237</v>
       </c>
       <c r="E98" s="21" t="n">
-        <v>46286</v>
+        <v>46251</v>
       </c>
       <c r="F98" s="22" t="n">
-        <v>912</v>
+        <v>749</v>
       </c>
       <c r="G98" s="22" t="n">
-        <v>652</v>
+        <v>489</v>
       </c>
       <c r="H98" s="22" t="n">
         <v>260</v>
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="K98" s="23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="L98" s="22">
         <f>K98*$B$4</f>
@@ -7878,7 +7878,7 @@
       </c>
       <c r="B99" s="20" t="inlineStr">
         <is>
-          <t>Call-out 17, August</t>
+          <t>Call-out CO-49141</t>
         </is>
       </c>
       <c r="C99" s="20" t="inlineStr">
@@ -7887,22 +7887,22 @@
         </is>
       </c>
       <c r="D99" s="21" t="n">
-        <v>46251</v>
+        <v>46255</v>
       </c>
       <c r="E99" s="21" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="F99" s="22" t="n">
-        <v>938</v>
+        <v>860</v>
       </c>
       <c r="G99" s="22" t="n">
         <v>652</v>
       </c>
       <c r="H99" s="22" t="n">
-        <v>286</v>
+        <v>208</v>
       </c>
       <c r="I99" s="22" t="n">
-        <v>220</v>
+        <v>160</v>
       </c>
       <c r="J99" s="22" t="n">
         <v>0</v>
@@ -7931,7 +7931,7 @@
       </c>
       <c r="B100" s="20" t="inlineStr">
         <is>
-          <t>Call-out 18, August</t>
+          <t>Call-out CO-49142</t>
         </is>
       </c>
       <c r="C100" s="20" t="inlineStr">
@@ -7940,28 +7940,28 @@
         </is>
       </c>
       <c r="D100" s="21" t="n">
-        <v>46253</v>
+        <v>46242</v>
       </c>
       <c r="E100" s="21" t="n">
-        <v>46260</v>
+        <v>46272</v>
       </c>
       <c r="F100" s="22" t="n">
-        <v>658</v>
+        <v>378</v>
       </c>
       <c r="G100" s="22" t="n">
-        <v>489</v>
+        <v>326</v>
       </c>
       <c r="H100" s="22" t="n">
-        <v>169</v>
+        <v>52</v>
       </c>
       <c r="I100" s="22" t="n">
-        <v>130</v>
+        <v>40</v>
       </c>
       <c r="J100" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K100" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L100" s="22">
         <f>K100*$B$4</f>
@@ -7984,7 +7984,7 @@
       </c>
       <c r="B101" s="20" t="inlineStr">
         <is>
-          <t>Call-out 19, August</t>
+          <t>Call-out CO-49143</t>
         </is>
       </c>
       <c r="C101" s="20" t="inlineStr">
@@ -7993,28 +7993,28 @@
         </is>
       </c>
       <c r="D101" s="21" t="n">
-        <v>46245</v>
+        <v>46237</v>
       </c>
       <c r="E101" s="21" t="n">
-        <v>46259</v>
+        <v>46244</v>
       </c>
       <c r="F101" s="22" t="n">
-        <v>560</v>
+        <v>528</v>
       </c>
       <c r="G101" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H101" s="22" t="n">
-        <v>234</v>
+        <v>39</v>
       </c>
       <c r="I101" s="22" t="n">
-        <v>180</v>
+        <v>30</v>
       </c>
       <c r="J101" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K101" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L101" s="22">
         <f>K101*$B$4</f>
@@ -8037,7 +8037,7 @@
       </c>
       <c r="B102" s="20" t="inlineStr">
         <is>
-          <t>Call-out 2, August</t>
+          <t>Call-out CO-49144</t>
         </is>
       </c>
       <c r="C102" s="20" t="inlineStr">
@@ -8046,28 +8046,28 @@
         </is>
       </c>
       <c r="D102" s="21" t="n">
-        <v>46253</v>
+        <v>46261</v>
       </c>
       <c r="E102" s="21" t="n">
-        <v>46253</v>
+        <v>46265</v>
       </c>
       <c r="F102" s="22" t="n">
-        <v>404</v>
+        <v>762</v>
       </c>
       <c r="G102" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H102" s="22" t="n">
-        <v>78</v>
+        <v>273</v>
       </c>
       <c r="I102" s="22" t="n">
-        <v>60</v>
+        <v>210</v>
       </c>
       <c r="J102" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K102" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L102" s="22">
         <f>K102*$B$4</f>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="B103" s="20" t="inlineStr">
         <is>
-          <t>Call-out 20, August</t>
+          <t>Call-out CO-49146</t>
         </is>
       </c>
       <c r="C103" s="20" t="inlineStr">
@@ -8099,28 +8099,28 @@
         </is>
       </c>
       <c r="D103" s="21" t="n">
-        <v>46260</v>
+        <v>46246</v>
       </c>
       <c r="E103" s="21" t="n">
-        <v>46262</v>
+        <v>46247</v>
       </c>
       <c r="F103" s="22" t="n">
-        <v>730</v>
+        <v>417</v>
       </c>
       <c r="G103" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H103" s="22" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I103" s="22" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J103" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K103" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L103" s="22">
         <f>K103*$B$4</f>
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B104" s="20" t="inlineStr">
         <is>
-          <t>Call-out 21, August</t>
+          <t>Call-out CO-49147</t>
         </is>
       </c>
       <c r="C104" s="20" t="inlineStr">
@@ -8152,28 +8152,28 @@
         </is>
       </c>
       <c r="D104" s="21" t="n">
-        <v>46252</v>
+        <v>46239</v>
       </c>
       <c r="E104" s="21" t="n">
-        <v>46252</v>
+        <v>46269</v>
       </c>
       <c r="F104" s="22" t="n">
-        <v>547</v>
+        <v>749</v>
       </c>
       <c r="G104" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H104" s="22" t="n">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="I104" s="22" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="J104" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K104" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L104" s="22">
         <f>K104*$B$4</f>
@@ -8196,7 +8196,7 @@
       </c>
       <c r="B105" s="20" t="inlineStr">
         <is>
-          <t>Call-out 22, August</t>
+          <t>Call-out CO-49148</t>
         </is>
       </c>
       <c r="C105" s="20" t="inlineStr">
@@ -8205,28 +8205,28 @@
         </is>
       </c>
       <c r="D105" s="21" t="n">
-        <v>46259</v>
+        <v>46243</v>
       </c>
       <c r="E105" s="21" t="n">
-        <v>46266</v>
+        <v>46258</v>
       </c>
       <c r="F105" s="22" t="n">
-        <v>469</v>
+        <v>593</v>
       </c>
       <c r="G105" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H105" s="22" t="n">
-        <v>143</v>
+        <v>104</v>
       </c>
       <c r="I105" s="22" t="n">
-        <v>110</v>
+        <v>80</v>
       </c>
       <c r="J105" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K105" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L105" s="22">
         <f>K105*$B$4</f>
@@ -8249,7 +8249,7 @@
       </c>
       <c r="B106" s="20" t="inlineStr">
         <is>
-          <t>Call-out 23, August</t>
+          <t>Call-out CO-49149</t>
         </is>
       </c>
       <c r="C106" s="20" t="inlineStr">
@@ -8258,28 +8258,28 @@
         </is>
       </c>
       <c r="D106" s="21" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="E106" s="21" t="n">
-        <v>46254</v>
+        <v>46286</v>
       </c>
       <c r="F106" s="22" t="n">
-        <v>466</v>
+        <v>912</v>
       </c>
       <c r="G106" s="22" t="n">
-        <v>245</v>
+        <v>652</v>
       </c>
       <c r="H106" s="22" t="n">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="I106" s="22" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="J106" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K106" s="23" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L106" s="22">
         <f>K106*$B$4</f>
@@ -8302,7 +8302,7 @@
       </c>
       <c r="B107" s="20" t="inlineStr">
         <is>
-          <t>Call-out 24, August</t>
+          <t>Call-out CO-49150</t>
         </is>
       </c>
       <c r="C107" s="20" t="inlineStr">
@@ -8311,28 +8311,28 @@
         </is>
       </c>
       <c r="D107" s="21" t="n">
-        <v>46256</v>
+        <v>46251</v>
       </c>
       <c r="E107" s="21" t="n">
-        <v>46265</v>
+        <v>46251</v>
       </c>
       <c r="F107" s="22" t="n">
-        <v>671</v>
+        <v>938</v>
       </c>
       <c r="G107" s="22" t="n">
-        <v>489</v>
+        <v>652</v>
       </c>
       <c r="H107" s="22" t="n">
-        <v>182</v>
+        <v>286</v>
       </c>
       <c r="I107" s="22" t="n">
-        <v>140</v>
+        <v>220</v>
       </c>
       <c r="J107" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K107" s="23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="L107" s="22">
         <f>K107*$B$4</f>
@@ -8355,7 +8355,7 @@
       </c>
       <c r="B108" s="20" t="inlineStr">
         <is>
-          <t>Call-out 25, August</t>
+          <t>Call-out CO-49152</t>
         </is>
       </c>
       <c r="C108" s="20" t="inlineStr">
@@ -8364,28 +8364,28 @@
         </is>
       </c>
       <c r="D108" s="21" t="n">
-        <v>46256</v>
+        <v>46253</v>
       </c>
       <c r="E108" s="21" t="n">
-        <v>46258</v>
+        <v>46260</v>
       </c>
       <c r="F108" s="22" t="n">
-        <v>505</v>
+        <v>658</v>
       </c>
       <c r="G108" s="22" t="n">
-        <v>245</v>
+        <v>489</v>
       </c>
       <c r="H108" s="22" t="n">
-        <v>260</v>
+        <v>169</v>
       </c>
       <c r="I108" s="22" t="n">
-        <v>200</v>
+        <v>130</v>
       </c>
       <c r="J108" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K108" s="23" t="n">
-        <v>1.5</v>
+        <v>3</v>
       </c>
       <c r="L108" s="22">
         <f>K108*$B$4</f>
@@ -8408,7 +8408,7 @@
       </c>
       <c r="B109" s="20" t="inlineStr">
         <is>
-          <t>Call-out 26, August</t>
+          <t>Call-out CO-49153</t>
         </is>
       </c>
       <c r="C109" s="20" t="inlineStr">
@@ -8417,28 +8417,28 @@
         </is>
       </c>
       <c r="D109" s="21" t="n">
-        <v>46248</v>
+        <v>46245</v>
       </c>
       <c r="E109" s="21" t="n">
-        <v>46248</v>
+        <v>46259</v>
       </c>
       <c r="F109" s="22" t="n">
-        <v>736</v>
+        <v>560</v>
       </c>
       <c r="G109" s="22" t="n">
-        <v>489</v>
+        <v>326</v>
       </c>
       <c r="H109" s="22" t="n">
-        <v>247</v>
+        <v>234</v>
       </c>
       <c r="I109" s="22" t="n">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="J109" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K109" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L109" s="22">
         <f>K109*$B$4</f>
@@ -8461,7 +8461,7 @@
       </c>
       <c r="B110" s="20" t="inlineStr">
         <is>
-          <t>Call-out 27, August</t>
+          <t>Call-out CO-49154</t>
         </is>
       </c>
       <c r="C110" s="20" t="inlineStr">
@@ -8470,28 +8470,28 @@
         </is>
       </c>
       <c r="D110" s="21" t="n">
-        <v>46237</v>
+        <v>46260</v>
       </c>
       <c r="E110" s="21" t="n">
-        <v>46267</v>
+        <v>46262</v>
       </c>
       <c r="F110" s="22" t="n">
-        <v>616</v>
+        <v>730</v>
       </c>
       <c r="G110" s="22" t="n">
-        <v>408</v>
+        <v>652</v>
       </c>
       <c r="H110" s="22" t="n">
-        <v>208</v>
+        <v>78</v>
       </c>
       <c r="I110" s="22" t="n">
-        <v>160</v>
+        <v>60</v>
       </c>
       <c r="J110" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K110" s="23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L110" s="22">
         <f>K110*$B$4</f>
@@ -8514,7 +8514,7 @@
       </c>
       <c r="B111" s="20" t="inlineStr">
         <is>
-          <t>Call-out 28, August</t>
+          <t>Call-out CO-49155</t>
         </is>
       </c>
       <c r="C111" s="20" t="inlineStr">
@@ -8523,28 +8523,28 @@
         </is>
       </c>
       <c r="D111" s="21" t="n">
-        <v>46256</v>
+        <v>46252</v>
       </c>
       <c r="E111" s="21" t="n">
-        <v>46258</v>
+        <v>46252</v>
       </c>
       <c r="F111" s="22" t="n">
-        <v>538</v>
+        <v>547</v>
       </c>
       <c r="G111" s="22" t="n">
-        <v>408</v>
+        <v>326</v>
       </c>
       <c r="H111" s="22" t="n">
-        <v>130</v>
+        <v>221</v>
       </c>
       <c r="I111" s="22" t="n">
-        <v>100</v>
+        <v>170</v>
       </c>
       <c r="J111" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K111" s="23" t="n">
-        <v>2.5</v>
+        <v>2</v>
       </c>
       <c r="L111" s="22">
         <f>K111*$B$4</f>
@@ -8567,7 +8567,7 @@
       </c>
       <c r="B112" s="20" t="inlineStr">
         <is>
-          <t>Call-out 29, August</t>
+          <t>Call-out CO-49156</t>
         </is>
       </c>
       <c r="C112" s="20" t="inlineStr">
@@ -8576,28 +8576,28 @@
         </is>
       </c>
       <c r="D112" s="21" t="n">
-        <v>46261</v>
+        <v>46259</v>
       </c>
       <c r="E112" s="21" t="n">
-        <v>46261</v>
+        <v>46266</v>
       </c>
       <c r="F112" s="22" t="n">
-        <v>723</v>
+        <v>469</v>
       </c>
       <c r="G112" s="22" t="n">
-        <v>489</v>
+        <v>326</v>
       </c>
       <c r="H112" s="22" t="n">
-        <v>234</v>
+        <v>143</v>
       </c>
       <c r="I112" s="22" t="n">
-        <v>180</v>
+        <v>110</v>
       </c>
       <c r="J112" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L112" s="22">
         <f>K112*$B$4</f>
@@ -8620,7 +8620,7 @@
       </c>
       <c r="B113" s="20" t="inlineStr">
         <is>
-          <t>Call-out 3, August</t>
+          <t>Call-out CO-49157</t>
         </is>
       </c>
       <c r="C113" s="20" t="inlineStr">
@@ -8629,22 +8629,22 @@
         </is>
       </c>
       <c r="D113" s="21" t="n">
-        <v>46235</v>
+        <v>46247</v>
       </c>
       <c r="E113" s="21" t="n">
-        <v>46244</v>
+        <v>46254</v>
       </c>
       <c r="F113" s="22" t="n">
-        <v>349</v>
+        <v>466</v>
       </c>
       <c r="G113" s="22" t="n">
         <v>245</v>
       </c>
       <c r="H113" s="22" t="n">
-        <v>104</v>
+        <v>221</v>
       </c>
       <c r="I113" s="22" t="n">
-        <v>80</v>
+        <v>170</v>
       </c>
       <c r="J113" s="22" t="n">
         <v>0</v>
@@ -8673,7 +8673,7 @@
       </c>
       <c r="B114" s="20" t="inlineStr">
         <is>
-          <t>Call-out 30, August</t>
+          <t>Call-out CO-49159</t>
         </is>
       </c>
       <c r="C114" s="20" t="inlineStr">
@@ -8682,28 +8682,28 @@
         </is>
       </c>
       <c r="D114" s="21" t="n">
-        <v>46245</v>
+        <v>46256</v>
       </c>
       <c r="E114" s="21" t="n">
-        <v>46245</v>
+        <v>46265</v>
       </c>
       <c r="F114" s="22" t="n">
-        <v>512</v>
+        <v>671</v>
       </c>
       <c r="G114" s="22" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="H114" s="22" t="n">
-        <v>104</v>
+        <v>182</v>
       </c>
       <c r="I114" s="22" t="n">
-        <v>80</v>
+        <v>140</v>
       </c>
       <c r="J114" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K114" s="23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L114" s="22">
         <f>K114*$B$4</f>
@@ -8726,7 +8726,7 @@
       </c>
       <c r="B115" s="20" t="inlineStr">
         <is>
-          <t>Call-out 31, August</t>
+          <t>Call-out CO-49160</t>
         </is>
       </c>
       <c r="C115" s="20" t="inlineStr">
@@ -8735,28 +8735,28 @@
         </is>
       </c>
       <c r="D115" s="21" t="n">
-        <v>46258</v>
+        <v>46256</v>
       </c>
       <c r="E115" s="21" t="n">
         <v>46258</v>
       </c>
       <c r="F115" s="22" t="n">
-        <v>573</v>
+        <v>505</v>
       </c>
       <c r="G115" s="22" t="n">
-        <v>326</v>
+        <v>245</v>
       </c>
       <c r="H115" s="22" t="n">
-        <v>247</v>
+        <v>260</v>
       </c>
       <c r="I115" s="22" t="n">
-        <v>190</v>
+        <v>200</v>
       </c>
       <c r="J115" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K115" s="23" t="n">
-        <v>2</v>
+        <v>1.5</v>
       </c>
       <c r="L115" s="22">
         <f>K115*$B$4</f>
@@ -8779,7 +8779,7 @@
       </c>
       <c r="B116" s="20" t="inlineStr">
         <is>
-          <t>Call-out 32, August</t>
+          <t>Call-out CO-49161</t>
         </is>
       </c>
       <c r="C116" s="20" t="inlineStr">
@@ -8788,28 +8788,28 @@
         </is>
       </c>
       <c r="D116" s="21" t="n">
-        <v>46245</v>
+        <v>46248</v>
       </c>
       <c r="E116" s="21" t="n">
-        <v>46252</v>
+        <v>46248</v>
       </c>
       <c r="F116" s="22" t="n">
-        <v>668</v>
+        <v>736</v>
       </c>
       <c r="G116" s="22" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="H116" s="22" t="n">
-        <v>260</v>
+        <v>247</v>
       </c>
       <c r="I116" s="22" t="n">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="J116" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K116" s="23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L116" s="22">
         <f>K116*$B$4</f>
@@ -8832,7 +8832,7 @@
       </c>
       <c r="B117" s="20" t="inlineStr">
         <is>
-          <t>Call-out 33, August</t>
+          <t>Call-out CO-49162</t>
         </is>
       </c>
       <c r="C117" s="20" t="inlineStr">
@@ -8844,25 +8844,25 @@
         <v>46237</v>
       </c>
       <c r="E117" s="21" t="n">
-        <v>46237</v>
+        <v>46267</v>
       </c>
       <c r="F117" s="22" t="n">
-        <v>508</v>
+        <v>616</v>
       </c>
       <c r="G117" s="22" t="n">
-        <v>326</v>
+        <v>408</v>
       </c>
       <c r="H117" s="22" t="n">
-        <v>182</v>
+        <v>208</v>
       </c>
       <c r="I117" s="22" t="n">
-        <v>140</v>
+        <v>160</v>
       </c>
       <c r="J117" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K117" s="23" t="n">
-        <v>2</v>
+        <v>2.5</v>
       </c>
       <c r="L117" s="22">
         <f>K117*$B$4</f>
@@ -8885,7 +8885,7 @@
       </c>
       <c r="B118" s="20" t="inlineStr">
         <is>
-          <t>Call-out 34, August</t>
+          <t>Call-out CO-49163</t>
         </is>
       </c>
       <c r="C118" s="20" t="inlineStr">
@@ -8894,28 +8894,28 @@
         </is>
       </c>
       <c r="D118" s="21" t="n">
-        <v>46249</v>
+        <v>46256</v>
       </c>
       <c r="E118" s="21" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="F118" s="22" t="n">
-        <v>544</v>
+        <v>538</v>
       </c>
       <c r="G118" s="22" t="n">
-        <v>245</v>
+        <v>408</v>
       </c>
       <c r="H118" s="22" t="n">
-        <v>299</v>
+        <v>130</v>
       </c>
       <c r="I118" s="22" t="n">
-        <v>230</v>
+        <v>100</v>
       </c>
       <c r="J118" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K118" s="23" t="n">
-        <v>1.5</v>
+        <v>2.5</v>
       </c>
       <c r="L118" s="22">
         <f>K118*$B$4</f>
@@ -8938,7 +8938,7 @@
       </c>
       <c r="B119" s="20" t="inlineStr">
         <is>
-          <t>Call-out 35, August</t>
+          <t>Call-out CO-49164</t>
         </is>
       </c>
       <c r="C119" s="20" t="inlineStr">
@@ -8947,22 +8947,22 @@
         </is>
       </c>
       <c r="D119" s="21" t="n">
-        <v>46239</v>
+        <v>46261</v>
       </c>
       <c r="E119" s="21" t="n">
-        <v>46239</v>
+        <v>46261</v>
       </c>
       <c r="F119" s="22" t="n">
-        <v>580</v>
+        <v>723</v>
       </c>
       <c r="G119" s="22" t="n">
         <v>489</v>
       </c>
       <c r="H119" s="22" t="n">
-        <v>91</v>
+        <v>234</v>
       </c>
       <c r="I119" s="22" t="n">
-        <v>70</v>
+        <v>180</v>
       </c>
       <c r="J119" s="22" t="n">
         <v>0</v>
@@ -8991,7 +8991,7 @@
       </c>
       <c r="B120" s="20" t="inlineStr">
         <is>
-          <t>Call-out 36, August</t>
+          <t>Call-out CO-49166</t>
         </is>
       </c>
       <c r="C120" s="20" t="inlineStr">
@@ -9000,28 +9000,28 @@
         </is>
       </c>
       <c r="D120" s="21" t="n">
-        <v>46246</v>
+        <v>46245</v>
       </c>
       <c r="E120" s="21" t="n">
-        <v>46253</v>
+        <v>46245</v>
       </c>
       <c r="F120" s="22" t="n">
-        <v>730</v>
+        <v>512</v>
       </c>
       <c r="G120" s="22" t="n">
-        <v>652</v>
+        <v>408</v>
       </c>
       <c r="H120" s="22" t="n">
-        <v>78</v>
+        <v>104</v>
       </c>
       <c r="I120" s="22" t="n">
-        <v>60</v>
+        <v>80</v>
       </c>
       <c r="J120" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K120" s="23" t="n">
-        <v>4</v>
+        <v>2.5</v>
       </c>
       <c r="L120" s="22">
         <f>K120*$B$4</f>
@@ -9044,7 +9044,7 @@
       </c>
       <c r="B121" s="20" t="inlineStr">
         <is>
-          <t>Call-out 37, August</t>
+          <t>Call-out CO-49167</t>
         </is>
       </c>
       <c r="C121" s="20" t="inlineStr">
@@ -9053,22 +9053,22 @@
         </is>
       </c>
       <c r="D121" s="21" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="E121" s="21" t="n">
-        <v>46245</v>
+        <v>46258</v>
       </c>
       <c r="F121" s="22" t="n">
-        <v>456</v>
+        <v>573</v>
       </c>
       <c r="G121" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H121" s="22" t="n">
-        <v>130</v>
+        <v>247</v>
       </c>
       <c r="I121" s="22" t="n">
-        <v>100</v>
+        <v>190</v>
       </c>
       <c r="J121" s="22" t="n">
         <v>0</v>
@@ -9097,7 +9097,7 @@
       </c>
       <c r="B122" s="20" t="inlineStr">
         <is>
-          <t>Call-out 38, August</t>
+          <t>Call-out CO-49168</t>
         </is>
       </c>
       <c r="C122" s="20" t="inlineStr">
@@ -9106,28 +9106,28 @@
         </is>
       </c>
       <c r="D122" s="21" t="n">
-        <v>46259</v>
+        <v>46245</v>
       </c>
       <c r="E122" s="21" t="n">
-        <v>46289</v>
+        <v>46252</v>
       </c>
       <c r="F122" s="22" t="n">
-        <v>710</v>
+        <v>668</v>
       </c>
       <c r="G122" s="22" t="n">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="H122" s="22" t="n">
-        <v>221</v>
+        <v>260</v>
       </c>
       <c r="I122" s="22" t="n">
-        <v>170</v>
+        <v>200</v>
       </c>
       <c r="J122" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K122" s="23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L122" s="22">
         <f>K122*$B$4</f>
@@ -9150,7 +9150,7 @@
       </c>
       <c r="B123" s="20" t="inlineStr">
         <is>
-          <t>Call-out 39, August</t>
+          <t>Call-out CO-49169</t>
         </is>
       </c>
       <c r="C123" s="20" t="inlineStr">
@@ -9159,22 +9159,22 @@
         </is>
       </c>
       <c r="D123" s="21" t="n">
-        <v>46259</v>
+        <v>46237</v>
       </c>
       <c r="E123" s="21" t="n">
-        <v>46266</v>
+        <v>46237</v>
       </c>
       <c r="F123" s="22" t="n">
-        <v>482</v>
+        <v>508</v>
       </c>
       <c r="G123" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H123" s="22" t="n">
-        <v>156</v>
+        <v>182</v>
       </c>
       <c r="I123" s="22" t="n">
-        <v>120</v>
+        <v>140</v>
       </c>
       <c r="J123" s="22" t="n">
         <v>0</v>
@@ -9203,7 +9203,7 @@
       </c>
       <c r="B124" s="20" t="inlineStr">
         <is>
-          <t>Call-out 4, August</t>
+          <t>Call-out CO-49170</t>
         </is>
       </c>
       <c r="C124" s="20" t="inlineStr">
@@ -9212,28 +9212,28 @@
         </is>
       </c>
       <c r="D124" s="21" t="n">
-        <v>46240</v>
+        <v>46249</v>
       </c>
       <c r="E124" s="21" t="n">
-        <v>46240</v>
+        <v>46251</v>
       </c>
       <c r="F124" s="22" t="n">
-        <v>345</v>
+        <v>544</v>
       </c>
       <c r="G124" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H124" s="22" t="n">
-        <v>182</v>
+        <v>299</v>
       </c>
       <c r="I124" s="22" t="n">
-        <v>140</v>
+        <v>230</v>
       </c>
       <c r="J124" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K124" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L124" s="22">
         <f>K124*$B$4</f>
@@ -9256,7 +9256,7 @@
       </c>
       <c r="B125" s="20" t="inlineStr">
         <is>
-          <t>Call-out 40, August</t>
+          <t>Call-out CO-49172</t>
         </is>
       </c>
       <c r="C125" s="20" t="inlineStr">
@@ -9265,28 +9265,28 @@
         </is>
       </c>
       <c r="D125" s="21" t="n">
-        <v>46262</v>
+        <v>46239</v>
       </c>
       <c r="E125" s="21" t="n">
-        <v>46262</v>
+        <v>46239</v>
       </c>
       <c r="F125" s="22" t="n">
-        <v>486</v>
+        <v>580</v>
       </c>
       <c r="G125" s="22" t="n">
-        <v>408</v>
+        <v>489</v>
       </c>
       <c r="H125" s="22" t="n">
-        <v>78</v>
+        <v>91</v>
       </c>
       <c r="I125" s="22" t="n">
-        <v>60</v>
+        <v>70</v>
       </c>
       <c r="J125" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K125" s="23" t="n">
-        <v>2.5</v>
+        <v>3</v>
       </c>
       <c r="L125" s="22">
         <f>K125*$B$4</f>
@@ -9309,7 +9309,7 @@
       </c>
       <c r="B126" s="20" t="inlineStr">
         <is>
-          <t>Call-out 41, August</t>
+          <t>Call-out CO-49173</t>
         </is>
       </c>
       <c r="C126" s="20" t="inlineStr">
@@ -9318,28 +9318,28 @@
         </is>
       </c>
       <c r="D126" s="21" t="n">
-        <v>46249</v>
+        <v>46246</v>
       </c>
       <c r="E126" s="21" t="n">
-        <v>46251</v>
+        <v>46253</v>
       </c>
       <c r="F126" s="22" t="n">
-        <v>447</v>
+        <v>730</v>
       </c>
       <c r="G126" s="22" t="n">
-        <v>408</v>
+        <v>652</v>
       </c>
       <c r="H126" s="22" t="n">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="I126" s="22" t="n">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="J126" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K126" s="23" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="L126" s="22">
         <f>K126*$B$4</f>
@@ -9362,7 +9362,7 @@
       </c>
       <c r="B127" s="20" t="inlineStr">
         <is>
-          <t>Call-out 42, August</t>
+          <t>Call-out CO-49174</t>
         </is>
       </c>
       <c r="C127" s="20" t="inlineStr">
@@ -9371,16 +9371,16 @@
         </is>
       </c>
       <c r="D127" s="21" t="n">
-        <v>46257</v>
+        <v>46245</v>
       </c>
       <c r="E127" s="21" t="n">
-        <v>46265</v>
+        <v>46245</v>
       </c>
       <c r="F127" s="22" t="n">
-        <v>782</v>
+        <v>456</v>
       </c>
       <c r="G127" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H127" s="22" t="n">
         <v>130</v>
@@ -9392,7 +9392,7 @@
         <v>0</v>
       </c>
       <c r="K127" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L127" s="22">
         <f>K127*$B$4</f>
@@ -9415,7 +9415,7 @@
       </c>
       <c r="B128" s="20" t="inlineStr">
         <is>
-          <t>Call-out 43, August</t>
+          <t>Call-out CO-49175</t>
         </is>
       </c>
       <c r="C128" s="20" t="inlineStr">
@@ -9424,28 +9424,28 @@
         </is>
       </c>
       <c r="D128" s="21" t="n">
-        <v>46242</v>
+        <v>46259</v>
       </c>
       <c r="E128" s="21" t="n">
-        <v>46272</v>
+        <v>46289</v>
       </c>
       <c r="F128" s="22" t="n">
-        <v>391</v>
+        <v>710</v>
       </c>
       <c r="G128" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H128" s="22" t="n">
-        <v>65</v>
+        <v>221</v>
       </c>
       <c r="I128" s="22" t="n">
-        <v>50</v>
+        <v>170</v>
       </c>
       <c r="J128" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K128" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L128" s="22">
         <f>K128*$B$4</f>
@@ -9468,7 +9468,7 @@
       </c>
       <c r="B129" s="20" t="inlineStr">
         <is>
-          <t>Call-out 44, August</t>
+          <t>Call-out CO-49176</t>
         </is>
       </c>
       <c r="C129" s="20" t="inlineStr">
@@ -9477,28 +9477,28 @@
         </is>
       </c>
       <c r="D129" s="21" t="n">
-        <v>46238</v>
+        <v>46259</v>
       </c>
       <c r="E129" s="21" t="n">
-        <v>46268</v>
+        <v>46266</v>
       </c>
       <c r="F129" s="22" t="n">
-        <v>362</v>
+        <v>482</v>
       </c>
       <c r="G129" s="22" t="n">
-        <v>245</v>
+        <v>326</v>
       </c>
       <c r="H129" s="22" t="n">
-        <v>117</v>
+        <v>156</v>
       </c>
       <c r="I129" s="22" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="J129" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K129" s="23" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="L129" s="22">
         <f>K129*$B$4</f>
@@ -9521,7 +9521,7 @@
       </c>
       <c r="B130" s="20" t="inlineStr">
         <is>
-          <t>Call-out 45, August</t>
+          <t>Call-out CO-49177</t>
         </is>
       </c>
       <c r="C130" s="20" t="inlineStr">
@@ -9530,28 +9530,28 @@
         </is>
       </c>
       <c r="D130" s="21" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="E130" s="21" t="n">
-        <v>46248</v>
+        <v>46262</v>
       </c>
       <c r="F130" s="22" t="n">
-        <v>319</v>
+        <v>486</v>
       </c>
       <c r="G130" s="22" t="n">
-        <v>163</v>
+        <v>408</v>
       </c>
       <c r="H130" s="22" t="n">
-        <v>156</v>
+        <v>78</v>
       </c>
       <c r="I130" s="22" t="n">
-        <v>120</v>
+        <v>60</v>
       </c>
       <c r="J130" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K130" s="23" t="n">
-        <v>1</v>
+        <v>2.5</v>
       </c>
       <c r="L130" s="22">
         <f>K130*$B$4</f>
@@ -9574,7 +9574,7 @@
       </c>
       <c r="B131" s="20" t="inlineStr">
         <is>
-          <t>Call-out 46, August</t>
+          <t>Call-out CO-49179</t>
         </is>
       </c>
       <c r="C131" s="20" t="inlineStr">
@@ -9583,28 +9583,28 @@
         </is>
       </c>
       <c r="D131" s="21" t="n">
-        <v>46246</v>
+        <v>46249</v>
       </c>
       <c r="E131" s="21" t="n">
-        <v>46260</v>
+        <v>46251</v>
       </c>
       <c r="F131" s="22" t="n">
-        <v>788</v>
+        <v>447</v>
       </c>
       <c r="G131" s="22" t="n">
-        <v>489</v>
+        <v>408</v>
       </c>
       <c r="H131" s="22" t="n">
-        <v>299</v>
+        <v>39</v>
       </c>
       <c r="I131" s="22" t="n">
-        <v>230</v>
+        <v>30</v>
       </c>
       <c r="J131" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K131" s="23" t="n">
-        <v>3</v>
+        <v>2.5</v>
       </c>
       <c r="L131" s="22">
         <f>K131*$B$4</f>
@@ -9627,7 +9627,7 @@
       </c>
       <c r="B132" s="20" t="inlineStr">
         <is>
-          <t>Call-out 47, August</t>
+          <t>Call-out CO-49180</t>
         </is>
       </c>
       <c r="C132" s="20" t="inlineStr">
@@ -9636,28 +9636,28 @@
         </is>
       </c>
       <c r="D132" s="21" t="n">
-        <v>46242</v>
+        <v>46257</v>
       </c>
       <c r="E132" s="21" t="n">
-        <v>46244</v>
+        <v>46265</v>
       </c>
       <c r="F132" s="22" t="n">
-        <v>297</v>
+        <v>782</v>
       </c>
       <c r="G132" s="22" t="n">
-        <v>245</v>
+        <v>652</v>
       </c>
       <c r="H132" s="22" t="n">
-        <v>52</v>
+        <v>130</v>
       </c>
       <c r="I132" s="22" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="J132" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K132" s="23" t="n">
-        <v>1.5</v>
+        <v>4</v>
       </c>
       <c r="L132" s="22">
         <f>K132*$B$4</f>
@@ -9680,7 +9680,7 @@
       </c>
       <c r="B133" s="20" t="inlineStr">
         <is>
-          <t>Call-out 48, August</t>
+          <t>Call-out CO-49181</t>
         </is>
       </c>
       <c r="C133" s="20" t="inlineStr">
@@ -9689,22 +9689,22 @@
         </is>
       </c>
       <c r="D133" s="21" t="n">
-        <v>46250</v>
+        <v>46242</v>
       </c>
       <c r="E133" s="21" t="n">
-        <v>46252</v>
+        <v>46272</v>
       </c>
       <c r="F133" s="22" t="n">
-        <v>430</v>
+        <v>391</v>
       </c>
       <c r="G133" s="22" t="n">
         <v>326</v>
       </c>
       <c r="H133" s="22" t="n">
-        <v>104</v>
+        <v>65</v>
       </c>
       <c r="I133" s="22" t="n">
-        <v>80</v>
+        <v>50</v>
       </c>
       <c r="J133" s="22" t="n">
         <v>0</v>
@@ -9733,7 +9733,7 @@
       </c>
       <c r="B134" s="20" t="inlineStr">
         <is>
-          <t>Call-out 49, August</t>
+          <t>Call-out CO-49182</t>
         </is>
       </c>
       <c r="C134" s="20" t="inlineStr">
@@ -9742,28 +9742,28 @@
         </is>
       </c>
       <c r="D134" s="21" t="n">
-        <v>46262</v>
+        <v>46238</v>
       </c>
       <c r="E134" s="21" t="n">
-        <v>46262</v>
+        <v>46268</v>
       </c>
       <c r="F134" s="22" t="n">
-        <v>306</v>
+        <v>362</v>
       </c>
       <c r="G134" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H134" s="22" t="n">
-        <v>143</v>
+        <v>117</v>
       </c>
       <c r="I134" s="22" t="n">
-        <v>110</v>
+        <v>90</v>
       </c>
       <c r="J134" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K134" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L134" s="22">
         <f>K134*$B$4</f>
@@ -9786,7 +9786,7 @@
       </c>
       <c r="B135" s="20" t="inlineStr">
         <is>
-          <t>Call-out 5, August</t>
+          <t>Call-out CO-49183</t>
         </is>
       </c>
       <c r="C135" s="20" t="inlineStr">
@@ -9795,28 +9795,28 @@
         </is>
       </c>
       <c r="D135" s="21" t="n">
-        <v>46260</v>
+        <v>46248</v>
       </c>
       <c r="E135" s="21" t="n">
-        <v>46267</v>
+        <v>46248</v>
       </c>
       <c r="F135" s="22" t="n">
-        <v>538</v>
+        <v>319</v>
       </c>
       <c r="G135" s="22" t="n">
-        <v>408</v>
+        <v>163</v>
       </c>
       <c r="H135" s="22" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="I135" s="22" t="n">
-        <v>100</v>
+        <v>120</v>
       </c>
       <c r="J135" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K135" s="23" t="n">
-        <v>2.5</v>
+        <v>1</v>
       </c>
       <c r="L135" s="22">
         <f>K135*$B$4</f>
@@ -9839,7 +9839,7 @@
       </c>
       <c r="B136" s="20" t="inlineStr">
         <is>
-          <t>Call-out 50, August</t>
+          <t>Call-out CO-49184</t>
         </is>
       </c>
       <c r="C136" s="20" t="inlineStr">
@@ -9848,28 +9848,28 @@
         </is>
       </c>
       <c r="D136" s="21" t="n">
-        <v>46235</v>
+        <v>46246</v>
       </c>
       <c r="E136" s="21" t="n">
-        <v>46251</v>
+        <v>46260</v>
       </c>
       <c r="F136" s="22" t="n">
-        <v>332</v>
+        <v>788</v>
       </c>
       <c r="G136" s="22" t="n">
-        <v>163</v>
+        <v>489</v>
       </c>
       <c r="H136" s="22" t="n">
-        <v>169</v>
+        <v>299</v>
       </c>
       <c r="I136" s="22" t="n">
-        <v>130</v>
+        <v>230</v>
       </c>
       <c r="J136" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K136" s="23" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="L136" s="22">
         <f>K136*$B$4</f>
@@ -9892,7 +9892,7 @@
       </c>
       <c r="B137" s="20" t="inlineStr">
         <is>
-          <t>Call-out 51, August</t>
+          <t>Call-out CO-49186</t>
         </is>
       </c>
       <c r="C137" s="20" t="inlineStr">
@@ -9901,28 +9901,28 @@
         </is>
       </c>
       <c r="D137" s="21" t="n">
+        <v>46242</v>
+      </c>
+      <c r="E137" s="21" t="n">
         <v>46244</v>
       </c>
-      <c r="E137" s="21" t="n">
-        <v>46258</v>
-      </c>
       <c r="F137" s="22" t="n">
-        <v>358</v>
+        <v>297</v>
       </c>
       <c r="G137" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H137" s="22" t="n">
-        <v>195</v>
+        <v>52</v>
       </c>
       <c r="I137" s="22" t="n">
-        <v>150</v>
+        <v>40</v>
       </c>
       <c r="J137" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K137" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L137" s="22">
         <f>K137*$B$4</f>
@@ -9945,7 +9945,7 @@
       </c>
       <c r="B138" s="20" t="inlineStr">
         <is>
-          <t>Call-out 52, August</t>
+          <t>Call-out CO-49187</t>
         </is>
       </c>
       <c r="C138" s="20" t="inlineStr">
@@ -9954,28 +9954,28 @@
         </is>
       </c>
       <c r="D138" s="21" t="n">
-        <v>46237</v>
+        <v>46250</v>
       </c>
       <c r="E138" s="21" t="n">
-        <v>46244</v>
+        <v>46252</v>
       </c>
       <c r="F138" s="22" t="n">
-        <v>280</v>
+        <v>430</v>
       </c>
       <c r="G138" s="22" t="n">
-        <v>163</v>
+        <v>326</v>
       </c>
       <c r="H138" s="22" t="n">
-        <v>117</v>
+        <v>104</v>
       </c>
       <c r="I138" s="22" t="n">
-        <v>90</v>
+        <v>80</v>
       </c>
       <c r="J138" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K138" s="23" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L138" s="22">
         <f>K138*$B$4</f>
@@ -9998,7 +9998,7 @@
       </c>
       <c r="B139" s="20" t="inlineStr">
         <is>
-          <t>Call-out 53, August</t>
+          <t>Call-out CO-49188</t>
         </is>
       </c>
       <c r="C139" s="20" t="inlineStr">
@@ -10007,28 +10007,28 @@
         </is>
       </c>
       <c r="D139" s="21" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="E139" s="21" t="n">
-        <v>46258</v>
+        <v>46262</v>
       </c>
       <c r="F139" s="22" t="n">
-        <v>697</v>
+        <v>306</v>
       </c>
       <c r="G139" s="22" t="n">
-        <v>489</v>
+        <v>163</v>
       </c>
       <c r="H139" s="22" t="n">
-        <v>208</v>
+        <v>143</v>
       </c>
       <c r="I139" s="22" t="n">
-        <v>160</v>
+        <v>110</v>
       </c>
       <c r="J139" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K139" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L139" s="22">
         <f>K139*$B$4</f>
@@ -10051,7 +10051,7 @@
       </c>
       <c r="B140" s="20" t="inlineStr">
         <is>
-          <t>Call-out 54, August</t>
+          <t>Call-out CO-49189</t>
         </is>
       </c>
       <c r="C140" s="20" t="inlineStr">
@@ -10060,22 +10060,22 @@
         </is>
       </c>
       <c r="D140" s="21" t="n">
-        <v>46238</v>
+        <v>46235</v>
       </c>
       <c r="E140" s="21" t="n">
-        <v>46238</v>
+        <v>46251</v>
       </c>
       <c r="F140" s="22" t="n">
-        <v>228</v>
+        <v>332</v>
       </c>
       <c r="G140" s="22" t="n">
         <v>163</v>
       </c>
       <c r="H140" s="22" t="n">
-        <v>65</v>
+        <v>169</v>
       </c>
       <c r="I140" s="22" t="n">
-        <v>50</v>
+        <v>130</v>
       </c>
       <c r="J140" s="22" t="n">
         <v>0</v>
@@ -10104,7 +10104,7 @@
       </c>
       <c r="B141" s="20" t="inlineStr">
         <is>
-          <t>Call-out 55, August</t>
+          <t>Call-out CO-49190</t>
         </is>
       </c>
       <c r="C141" s="20" t="inlineStr">
@@ -10113,28 +10113,28 @@
         </is>
       </c>
       <c r="D141" s="21" t="n">
-        <v>46240</v>
+        <v>46244</v>
       </c>
       <c r="E141" s="21" t="n">
-        <v>46244</v>
+        <v>46258</v>
       </c>
       <c r="F141" s="22" t="n">
-        <v>580</v>
+        <v>358</v>
       </c>
       <c r="G141" s="22" t="n">
-        <v>489</v>
+        <v>163</v>
       </c>
       <c r="H141" s="22" t="n">
-        <v>91</v>
+        <v>195</v>
       </c>
       <c r="I141" s="22" t="n">
-        <v>70</v>
+        <v>150</v>
       </c>
       <c r="J141" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K141" s="23" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L141" s="22">
         <f>K141*$B$4</f>
@@ -10157,7 +10157,7 @@
       </c>
       <c r="B142" s="20" t="inlineStr">
         <is>
-          <t>Call-out 56, August</t>
+          <t>Call-out CO-49192</t>
         </is>
       </c>
       <c r="C142" s="20" t="inlineStr">
@@ -10166,28 +10166,28 @@
         </is>
       </c>
       <c r="D142" s="21" t="n">
-        <v>46256</v>
+        <v>46237</v>
       </c>
       <c r="E142" s="21" t="n">
-        <v>46258</v>
+        <v>46244</v>
       </c>
       <c r="F142" s="22" t="n">
-        <v>297</v>
+        <v>280</v>
       </c>
       <c r="G142" s="22" t="n">
-        <v>245</v>
+        <v>163</v>
       </c>
       <c r="H142" s="22" t="n">
-        <v>52</v>
+        <v>117</v>
       </c>
       <c r="I142" s="22" t="n">
-        <v>40</v>
+        <v>90</v>
       </c>
       <c r="J142" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K142" s="23" t="n">
-        <v>1.5</v>
+        <v>1</v>
       </c>
       <c r="L142" s="22">
         <f>K142*$B$4</f>
@@ -10210,7 +10210,7 @@
       </c>
       <c r="B143" s="20" t="inlineStr">
         <is>
-          <t>Call-out 57, August</t>
+          <t>Call-out CO-49193</t>
         </is>
       </c>
       <c r="C143" s="20" t="inlineStr">
@@ -10219,28 +10219,28 @@
         </is>
       </c>
       <c r="D143" s="21" t="n">
-        <v>46257</v>
+        <v>46258</v>
       </c>
       <c r="E143" s="21" t="n">
         <v>46258</v>
       </c>
       <c r="F143" s="22" t="n">
-        <v>378</v>
+        <v>697</v>
       </c>
       <c r="G143" s="22" t="n">
-        <v>326</v>
+        <v>489</v>
       </c>
       <c r="H143" s="22" t="n">
-        <v>52</v>
+        <v>208</v>
       </c>
       <c r="I143" s="22" t="n">
-        <v>40</v>
+        <v>160</v>
       </c>
       <c r="J143" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K143" s="23" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="L143" s="22">
         <f>K143*$B$4</f>
@@ -10263,7 +10263,7 @@
       </c>
       <c r="B144" s="20" t="inlineStr">
         <is>
-          <t>Call-out 58, August</t>
+          <t>Call-out CO-49194</t>
         </is>
       </c>
       <c r="C144" s="20" t="inlineStr">
@@ -10272,16 +10272,16 @@
         </is>
       </c>
       <c r="D144" s="21" t="n">
-        <v>46256</v>
+        <v>46238</v>
       </c>
       <c r="E144" s="21" t="n">
-        <v>46265</v>
+        <v>46238</v>
       </c>
       <c r="F144" s="22" t="n">
-        <v>391</v>
+        <v>228</v>
       </c>
       <c r="G144" s="22" t="n">
-        <v>326</v>
+        <v>163</v>
       </c>
       <c r="H144" s="22" t="n">
         <v>65</v>
@@ -10293,7 +10293,7 @@
         <v>0</v>
       </c>
       <c r="K144" s="23" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L144" s="22">
         <f>K144*$B$4</f>
@@ -10316,7 +10316,7 @@
       </c>
       <c r="B145" s="20" t="inlineStr">
         <is>
-          <t>Call-out 6, August</t>
+          <t>Call-out CO-49195</t>
         </is>
       </c>
       <c r="C145" s="20" t="inlineStr">
@@ -10325,22 +10325,22 @@
         </is>
       </c>
       <c r="D145" s="21" t="n">
-        <v>46245</v>
+        <v>46240</v>
       </c>
       <c r="E145" s="21" t="n">
-        <v>46245</v>
+        <v>46244</v>
       </c>
       <c r="F145" s="22" t="n">
-        <v>606</v>
+        <v>580</v>
       </c>
       <c r="G145" s="22" t="n">
         <v>489</v>
       </c>
       <c r="H145" s="22" t="n">
-        <v>117</v>
+        <v>91</v>
       </c>
       <c r="I145" s="22" t="n">
-        <v>90</v>
+        <v>70</v>
       </c>
       <c r="J145" s="22" t="n">
         <v>0</v>
@@ -10369,7 +10369,7 @@
       </c>
       <c r="B146" s="20" t="inlineStr">
         <is>
-          <t>Call-out 7, August</t>
+          <t>Call-out CO-49196</t>
         </is>
       </c>
       <c r="C146" s="20" t="inlineStr">
@@ -10378,28 +10378,28 @@
         </is>
       </c>
       <c r="D146" s="21" t="n">
-        <v>46247</v>
+        <v>46256</v>
       </c>
       <c r="E146" s="21" t="n">
-        <v>46254</v>
+        <v>46258</v>
       </c>
       <c r="F146" s="22" t="n">
-        <v>189</v>
+        <v>297</v>
       </c>
       <c r="G146" s="22" t="n">
-        <v>163</v>
+        <v>245</v>
       </c>
       <c r="H146" s="22" t="n">
-        <v>26</v>
+        <v>52</v>
       </c>
       <c r="I146" s="22" t="n">
-        <v>20</v>
+        <v>40</v>
       </c>
       <c r="J146" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K146" s="23" t="n">
-        <v>1</v>
+        <v>1.5</v>
       </c>
       <c r="L146" s="22">
         <f>K146*$B$4</f>
@@ -10422,7 +10422,7 @@
       </c>
       <c r="B147" s="20" t="inlineStr">
         <is>
-          <t>Call-out 8, August</t>
+          <t>Call-out CO-49197</t>
         </is>
       </c>
       <c r="C147" s="20" t="inlineStr">
@@ -10431,28 +10431,28 @@
         </is>
       </c>
       <c r="D147" s="21" t="n">
-        <v>46237</v>
+        <v>46257</v>
       </c>
       <c r="E147" s="21" t="n">
-        <v>46251</v>
+        <v>46258</v>
       </c>
       <c r="F147" s="22" t="n">
-        <v>749</v>
+        <v>378</v>
       </c>
       <c r="G147" s="22" t="n">
-        <v>489</v>
+        <v>326</v>
       </c>
       <c r="H147" s="22" t="n">
-        <v>260</v>
+        <v>52</v>
       </c>
       <c r="I147" s="22" t="n">
-        <v>200</v>
+        <v>40</v>
       </c>
       <c r="J147" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K147" s="23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L147" s="22">
         <f>K147*$B$4</f>
@@ -10475,7 +10475,7 @@
       </c>
       <c r="B148" s="20" t="inlineStr">
         <is>
-          <t>Call-out 9, August</t>
+          <t>Call-out CO-49199</t>
         </is>
       </c>
       <c r="C148" s="20" t="inlineStr">
@@ -10484,28 +10484,28 @@
         </is>
       </c>
       <c r="D148" s="21" t="n">
-        <v>46255</v>
+        <v>46256</v>
       </c>
       <c r="E148" s="21" t="n">
-        <v>46258</v>
+        <v>46265</v>
       </c>
       <c r="F148" s="22" t="n">
-        <v>860</v>
+        <v>391</v>
       </c>
       <c r="G148" s="22" t="n">
-        <v>652</v>
+        <v>326</v>
       </c>
       <c r="H148" s="22" t="n">
-        <v>208</v>
+        <v>65</v>
       </c>
       <c r="I148" s="22" t="n">
-        <v>160</v>
+        <v>50</v>
       </c>
       <c r="J148" s="22" t="n">
         <v>0</v>
       </c>
       <c r="K148" s="23" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="L148" s="22">
         <f>K148*$B$4</f>
@@ -11496,7 +11496,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -11547,7 +11547,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -12507,7 +12507,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
@@ -12552,7 +12552,7 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 8:39am</t>
+          <t>Data status: Sep 2026 locked · Aug 2026 locked · Oct 2026 incomplete (data retrieved 2pm, Tue 6 Oct 2026) · Generated 9 Oct 2026, 1:19pm</t>
         </is>
       </c>
     </row>
@@ -12973,7 +12973,7 @@
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <headerFooter>
     <oddHeader>&amp;L&amp;"Roboto,Regular"&amp;8 Sample Electrical &amp;&amp; Air Pty Ltd&amp;R&amp;"Roboto,Regular"&amp;8 &amp;A</oddHeader>
-    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 8:39am&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
+    <oddFooter>&amp;L&amp;"Roboto,Regular"&amp;8 trades-sample-statements.xlsx&amp;C&amp;"Roboto,Regular"&amp;8 Data retrieved 2pm, Tue 6 Oct 2026 · Generated 9 Oct 2026, 1:19pm&amp;R&amp;"Roboto,Regular"&amp;8 Page &amp;P of &amp;N</oddFooter>
     <evenHeader/>
     <evenFooter/>
     <firstHeader/>
